--- a/output/rss_history.xlsx
+++ b/output/rss_history.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E305"/>
+  <dimension ref="A1:E307"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,108 +466,108 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Phonandroid</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-19T17:42:56+00:00</t>
+          <t>2026-09-19T22:00:03+00:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DJI Avata 360 : le drone ultra immersif qui vous permet de filmer en 8K à 360°</t>
+          <t>Actualité : Bon plan – Le compact / bridge Sony ZV-1 Seul à 630,85 € (-21%)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.phonandroid.com/dji-avata-360-le-drone-ultra-immersif-qui-vous-permet-de-filmer-en-8k-a-360.html</t>
+          <t>https://www.lesnumeriques.com/compact-bridge/bon-plan-le-compact-bridge-sony-zv-1-seul-a-630-85-21-n262068.html</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>7. Video</t>
+          <t>19. Sponso</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Numerama</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-19T17:42:00+00:00</t>
+          <t>2026-09-19T22:00:03+00:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Pour la sortie du nouveau film Resident Evil, on a classé tous les films de la saga, du pire au moins pire</t>
+          <t>Actualité : Bon plan – La machine à café automatique avec broyeur Delonghi Magnifica Evo Next "5 étoiles" à 468,69 € (-21%)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.numerama.com/pop-culture/2333519-pour-la-sortie-du-nouveau-film-resident-evil-on-a-classe-tous-les-films-de-la-saga-du-pire-au-moins-pire.html</t>
+          <t>https://www.lesnumeriques.com/machine-a-cafe-automatique/bon-plan-la-machine-a-cafe-automatique-avec-broyeur-delonghi-magnifica-evo-next-5-etoiles-a-468-69-21-n262067.html</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>15. ludique</t>
+          <t>12. Cuisine</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Frandroid - RSS</t>
+          <t>Phonandroid</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-19T17:38:00+00:00</t>
+          <t>2026-09-19T17:42:56+00:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>En ce mois de rentrée, ce laptop de Lenovo avec son écran OLED de 16″ passe sous les 900 euros et un sac à dos est offert</t>
+          <t>DJI Avata 360 : le drone ultra immersif qui vous permet de filmer en 8K à 360°</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/bons-plans/3252341_en-ce-mois-de-rentree-ce-laptop-de-lenovo-avec-son-ecran-oled-de-16-passe-sous-les-900-euros-et-un-sac-a-dos-est-offert</t>
+          <t>https://www.phonandroid.com/dji-avata-360-le-drone-ultra-immersif-qui-vous-permet-de-filmer-en-8k-a-360.html</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2. PC</t>
+          <t>7. Video</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>Numerama</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-19T17:04:00+00:00</t>
+          <t>2026-09-19T17:42:00+00:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Actualité : Le test du vidéoprojecteur Anker Nebula P1i a rejoint notre comparatif</t>
+          <t>Pour la sortie du nouveau film Resident Evil, on a classé tous les films de la saga, du pire au moins pire</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/videoprojecteur/le-test-du-videoprojecteur-anker-nebula-p1i-a-rejoint-notre-comparatif-n262054.html</t>
+          <t>https://www.numerama.com/pop-culture/2333519-pour-la-sortie-du-nouveau-film-resident-evil-on-a-classe-tous-les-films-de-la-saga-du-pire-au-moins-pire.html</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>15. ludique</t>
         </is>
       </c>
     </row>
@@ -579,22 +579,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-19T17:02:14+00:00</t>
+          <t>2026-09-19T17:38:00+00:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Quels sont les meilleures modèles de TV TCL disponibles à l’achat ? Notre comparatif</t>
+          <t>En ce mois de rentrée, ce laptop de Lenovo avec son écran OLED de 16″ passe sous les 900 euros et un sac à dos est offert</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/guide-dachat/1610991_quelles-sont-les-meilleures-tv-tcl-disponibles</t>
+          <t>https://www.frandroid.com/bons-plans/3252341_en-ce-mois-de-rentree-ce-laptop-de-lenovo-avec-son-ecran-oled-de-16-passe-sous-les-900-euros-et-un-sac-a-dos-est-offert</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>7. Video</t>
+          <t>2. PC</t>
         </is>
       </c>
     </row>
@@ -606,49 +606,49 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-19T16:32:00+00:00</t>
+          <t>2026-09-19T17:04:00+00:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Actualité : Auto SR : le DLSS de Microsoft s'ouvre à de nouveaux Copilot+ PC</t>
+          <t>Actualité : Le test du vidéoprojecteur Anker Nebula P1i a rejoint notre comparatif</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/carte-graphique/auto-sr-le-dlss-de-microsoft-s-ouvre-a-de-nouveaux-copilot-pc-n262064.html</t>
+          <t>https://www.lesnumeriques.com/videoprojecteur/le-test-du-videoprojecteur-anker-nebula-p1i-a-rejoint-notre-comparatif-n262054.html</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2. PC</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Numerama</t>
+          <t>Frandroid - RSS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-19T16:32:00+00:00</t>
+          <t>2026-09-19T17:02:14+00:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ils prédisent l’apocalypse par l’IA, c’est quoi les AI doomers ?</t>
+          <t>Quels sont les meilleures modèles de TV TCL disponibles à l’achat ? Notre comparatif</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.numerama.com/tech/2335869-ils-predisent-lapocalypse-par-lia-cest-quoi-les-ai-doomers.html</t>
+          <t>https://www.frandroid.com/guide-dachat/1610991_quelles-sont-les-meilleures-tv-tcl-disponibles</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>6. IA</t>
+          <t>7. Video</t>
         </is>
       </c>
     </row>
@@ -660,179 +660,179 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-19T16:30:00+00:00</t>
+          <t>2026-09-19T16:32:00+00:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Actualité : Harry Potter : nouveau teaser, casting, histoire, date de sortie… Tout savoir sur la série HBO Max</t>
+          <t>Actualité : Auto SR : le DLSS de Microsoft s'ouvre à de nouveaux Copilot+ PC</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/serie/harry-potter-nouveau-teaser-casting-histoire-date-de-sortie-tout-savoir-sur-la-serie-hbo-max-n230720.html</t>
+          <t>https://www.lesnumeriques.com/carte-graphique/auto-sr-le-dlss-de-microsoft-s-ouvre-a-de-nouveaux-copilot-pc-n262064.html</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>15. ludique</t>
+          <t>2. PC</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>Numerama</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-19T16:13:32+00:00</t>
+          <t>2026-09-19T16:32:00+00:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Actualité : Cette centrale vapeur présente le meilleur rapport qualité / prix de notre comparatif</t>
+          <t>Ils prédisent l’apocalypse par l’IA, c’est quoi les AI doomers ?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/centrale-vapeur/cette-centrale-vapeur-presente-le-meilleur-rapport-qualite-prix-de-notre-comparatif-n262065.html</t>
+          <t>https://www.numerama.com/tech/2335869-ils-predisent-lapocalypse-par-lia-cest-quoi-les-ai-doomers.html</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>11. Menage</t>
+          <t>6. IA</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Frandroid - RSS</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-19T16:01:00+00:00</t>
+          <t>2026-09-19T16:30:00+00:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>J’ai démonté le nouveau Lenovo ThinkPad en moins de 10 minutes : la réparabilité est-elle enfin de retour sur PC ?</t>
+          <t>Actualité : Harry Potter : nouveau teaser, casting, histoire, date de sortie… Tout savoir sur la série HBO Max</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/marques/lenovo/3237317_jai-demonte-le-nouveau-lenovo-thinkpad-en-moins-de-10-minutes-la-reparabilite-est-elle-enfin-de-retour-sur-pc</t>
+          <t>https://www.lesnumeriques.com/serie/harry-potter-nouveau-teaser-casting-histoire-date-de-sortie-tout-savoir-sur-la-serie-hbo-max-n230720.html</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2. PC</t>
+          <t>15. ludique</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-19T16:00:49+00:00</t>
+          <t>2026-09-19T16:13:32+00:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Un ordinateur portable peut-il vraiment vous griller la peau ?</t>
+          <t>Actualité : Cette centrale vapeur présente le meilleur rapport qualité / prix de notre comparatif</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/19/un-ordinateur-portable-peut-il-vraiment-vous-griller-la-peau/</t>
+          <t>https://www.lesnumeriques.com/centrale-vapeur/cette-centrale-vapeur-presente-le-meilleur-rapport-qualite-prix-de-notre-comparatif-n262065.html</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2. PC</t>
+          <t>11. Menage</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>Frandroid - RSS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-19T16:00:00+00:00</t>
+          <t>2026-09-19T16:01:00+00:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Actualité : Il sort deux nouveaux modèles de smartphones par jour : est-ce bien raisonnable ?</t>
+          <t>J’ai démonté le nouveau Lenovo ThinkPad en moins de 10 minutes : la réparabilité est-elle enfin de retour sur PC ?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/telephone-portable/il-sort-deux-nouveaux-modeles-de-smartphones-par-jour-est-ce-bien-raisonnable-n261911.html</t>
+          <t>https://www.frandroid.com/marques/lenovo/3237317_jai-demonte-le-nouveau-lenovo-thinkpad-en-moins-de-10-minutes-la-reparabilite-est-elle-enfin-de-retour-sur-pc</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>2. PC</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Frandroid - RSS</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-19T15:32:00+00:00</t>
+          <t>2026-09-19T16:00:49+00:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ce pack Marshall à moins de 850 € réunit une barre de son 5.1 et un caisson de basses, de quoi profiter d’un home cinema immersif</t>
+          <t>Un ordinateur portable peut-il vraiment vous griller la peau ?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/bons-plans/3250173_ce-pack-marshall-a-moins-de-850-e-reunit-une-barre-de-son-5-1-et-un-caisson-de-basses-de-quoi-profiter-dun-home-cinema-immersif</t>
+          <t>https://www.journaldugeek.com/2026/09/19/un-ordinateur-portable-peut-il-vraiment-vous-griller-la-peau/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>8. Audio</t>
+          <t>2. PC</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Frandroid - RSS</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-19T15:24:06+00:00</t>
+          <t>2026-09-19T16:00:00+00:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Samsung casse le prix de son pliable anti-iPhone Duo</t>
+          <t>Actualité : Il sort deux nouveaux modèles de smartphones par jour : est-ce bien raisonnable ?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/marques/samsung/3253539_samsung-casse-le-prix-de-son-pliable-anti-iphone-duo</t>
+          <t>https://www.lesnumeriques.com/telephone-portable/il-sort-deux-nouveaux-modeles-de-smartphones-par-jour-est-ce-bien-raisonnable-n261911.html</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -844,49 +844,49 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Numerama</t>
+          <t>Frandroid - RSS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-19T15:20:00+00:00</t>
+          <t>2026-09-19T15:32:00+00:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Une Tesla au bord du vide en FSD, remboursement de Navigo et un camion sans chauffeur livre Lidl: le récap’ Vroom de la semaine</t>
+          <t>Ce pack Marshall à moins de 850 € réunit une barre de son 5.1 et un caisson de basses, de quoi profiter d’un home cinema immersif</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.numerama.com/vroom/2335871-une-tesla-au-bord-du-vide-en-fsd-remboursement-de-navigo-et-un-camion-sans-chauffeur-livre-lidl-le-recap-vroom-de-la-semaine.html</t>
+          <t>https://www.frandroid.com/bons-plans/3250173_ce-pack-marshall-a-moins-de-850-e-reunit-une-barre-de-son-5-1-et-un-caisson-de-basses-de-quoi-profiter-dun-home-cinema-immersif</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>4. Tablette</t>
+          <t>8. Audio</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>Frandroid - RSS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-19T15:00:28+00:00</t>
+          <t>2026-09-19T15:24:06+00:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Meta prépare des lunettes connectées sans caméra, pour voir si ça passe mieux</t>
+          <t>Samsung casse le prix de son pliable anti-iPhone Duo</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/19/meta-prepare-des-lunettes-connectees-sans-camera-pour-voir-si-ca-passe-mieux/</t>
+          <t>https://www.frandroid.com/marques/samsung/3253539_samsung-casse-le-prix-de-son-pliable-anti-iphone-duo</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -898,162 +898,162 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>Numerama</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-19T15:00:00+00:00</t>
+          <t>2026-09-19T15:20:00+00:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Actualité : iOS 27 : j’ai adopté ces 7 nouvelles options de personnalisation sur iPhone</t>
+          <t>Une Tesla au bord du vide en FSD, remboursement de Navigo et un camion sans chauffeur livre Lidl: le récap’ Vroom de la semaine</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/telephone-portable/ios-27-j-ai-adopte-ces-7-nouvelles-options-de-personnalisation-sur-iphone-n261976.html</t>
+          <t>https://www.numerama.com/vroom/2335871-une-tesla-au-bord-du-vide-en-fsd-remboursement-de-navigo-et-un-camion-sans-chauffeur-livre-lidl-le-recap-vroom-de-la-semaine.html</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>4. Tablette</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Phonandroid</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-19T14:50:42+00:00</t>
+          <t>2026-09-19T15:00:28+00:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Napster se lance dans l’éducation : l’IA pourrait bientôt remplacer vos profs</t>
+          <t>Meta prépare des lunettes connectées sans caméra, pour voir si ça passe mieux</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.phonandroid.com/napster-se-lance-dans-leducation-lia-pourrait-bientot-remplacer-vos-profs.html</t>
+          <t>https://www.journaldugeek.com/2026/09/19/meta-prepare-des-lunettes-connectees-sans-camera-pour-voir-si-ca-passe-mieux/</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>6. IA</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Numerama</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-19T14:30:00+00:00</t>
+          <t>2026-09-19T15:00:00+00:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Un agent OpenAI s’invente un personnage libre, Revolut piégée par un faux mail et les géants de l’IA qui veulent ralentir : on vous raconte la semaine Cyberguerre</t>
+          <t>Actualité : iOS 27 : j’ai adopté ces 7 nouvelles options de personnalisation sur iPhone</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.numerama.com/cyberguerre/2336053-un-agent-openai-sinvente-un-personnage-libre-revolut-piegee-par-un-faux-mail-et-les-geants-de-lia-qui-veulent-ralentir-on-vous-raconte-la-semaine-cyberguerre.html</t>
+          <t>https://www.lesnumeriques.com/telephone-portable/ios-27-j-ai-adopte-ces-7-nouvelles-options-de-personnalisation-sur-iphone-n261976.html</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>5. Logiciels _ OS</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>Phonandroid</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-19T14:12:00+00:00</t>
+          <t>2026-09-19T14:50:42+00:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Actualité : Fatigué par Windows 11 et l'IA, j'ai tout plaqué pour Linux (et je ne regrette rien)</t>
+          <t>Napster se lance dans l’éducation : l’IA pourrait bientôt remplacer vos profs</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/informatique/fatigue-par-windows-11-et-l-ia-j-ai-tout-plaque-pour-linux-et-je-ne-regrette-rien-n250751.html</t>
+          <t>https://www.phonandroid.com/napster-se-lance-dans-leducation-lia-pourrait-bientot-remplacer-vos-profs.html</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>5. Logiciels _ OS</t>
+          <t>6. IA</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>Numerama</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-19T14:03:00+00:00</t>
+          <t>2026-09-19T14:30:00+00:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Actualité : On a vu les Shokz OpenFit 2 AI : ces écouteurs veulent devenir votre traducteur et prendre vos notes</t>
+          <t>Un agent OpenAI s’invente un personnage libre, Revolut piégée par un faux mail et les géants de l’IA qui veulent ralentir : on vous raconte la semaine Cyberguerre</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/ecouteurs-sans-fil/on-a-vu-les-shokz-openfit-2-ai-ces-ecouteurs-veulent-devenir-votre-traducteur-et-prendre-vos-notes-n262027.html</t>
+          <t>https://www.numerama.com/cyberguerre/2336053-un-agent-openai-sinvente-un-personnage-libre-revolut-piegee-par-un-faux-mail-et-les-geants-de-lia-qui-veulent-ralentir-on-vous-raconte-la-semaine-cyberguerre.html</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>6. IA</t>
+          <t>5. Logiciels _ OS</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Frandroid - RSS</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-19T14:02:00+00:00</t>
+          <t>2026-09-19T14:12:00+00:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>J’ai enfin reçu les jumelles connectées Envision d’Unistellar : voici mes premières impressions</t>
+          <t>Actualité : Fatigué par Windows 11 et l'IA, j'ai tout plaqué pour Linux (et je ne regrette rien)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/test/prises-en-main/3249881_jai-enfin-recu-les-jumelles-connectees-envision-dunistellar-voici-mes-premieres-impressions</t>
+          <t>https://www.lesnumeriques.com/informatique/fatigue-par-windows-11-et-l-ia-j-ai-tout-plaque-pour-linux-et-je-ne-regrette-rien-n250751.html</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>6. IA</t>
+          <t>5. Logiciels _ OS</t>
         </is>
       </c>
     </row>
@@ -1065,184 +1065,184 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-19T14:00:00+00:00</t>
+          <t>2026-09-19T14:03:00+00:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Actualité : Impôts 2026 : le fisc va prélever 1 798 € en moyenne chez 13,8 millions de français dès le 25 septembre</t>
+          <t>Actualité : On a vu les Shokz OpenFit 2 AI : ces écouteurs veulent devenir votre traducteur et prendre vos notes</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/societe-numerique/impots-2026-le-fisc-va-prelever-1-798-en-moyenne-chez-13-8-millions-de-francais-des-le-25-septembre-n262062.html</t>
+          <t>https://www.lesnumeriques.com/ecouteurs-sans-fil/on-a-vu-les-shokz-openfit-2-ai-ces-ecouteurs-veulent-devenir-votre-traducteur-et-prendre-vos-notes-n262027.html</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>NON_CLASSE</t>
+          <t>6. IA</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>Frandroid - RSS</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-19T13:58:01+00:00</t>
+          <t>2026-09-19T14:02:00+00:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>La mégalopole lunaire d’Elon Musk prend l’eau</t>
+          <t>J’ai enfin reçu les jumelles connectées Envision d’Unistellar : voici mes premières impressions</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/19/la-megalopole-lunaire-delon-musk-prend-leau/</t>
+          <t>https://www.frandroid.com/test/prises-en-main/3249881_jai-enfin-recu-les-jumelles-connectees-envision-dunistellar-voici-mes-premieres-impressions</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>NON_CLASSE</t>
+          <t>6. IA</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Phonandroid</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-19T13:42:46+00:00</t>
+          <t>2026-09-19T14:00:00+00:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-42% sur la Honor Pad X9a : la tablette de 11,5 pouces est à moins de 145 €</t>
+          <t>Actualité : Impôts 2026 : le fisc va prélever 1 798 € en moyenne chez 13,8 millions de français dès le 25 septembre</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.phonandroid.com/42-honor-pad-x9a-tablette-11-pouces-moins-145-e.html</t>
+          <t>https://www.lesnumeriques.com/societe-numerique/impots-2026-le-fisc-va-prelever-1-798-en-moyenne-chez-13-8-millions-de-francais-des-le-25-septembre-n262062.html</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>NON_CLASSE</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Phonandroid</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-19T13:33:41+00:00</t>
+          <t>2026-09-19T13:58:01+00:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Vous téléchargez des films sur Internet ? Cette nouvelle menace se cache peut-être sur votre PC</t>
+          <t>La mégalopole lunaire d’Elon Musk prend l’eau</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.phonandroid.com/vous-telechargez-des-films-sur-internet-cette-nouvelle-menace-se-cache-peut-etre-sur-votre-pc.html</t>
+          <t>https://www.journaldugeek.com/2026/09/19/la-megalopole-lunaire-delon-musk-prend-leau/</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2. PC</t>
+          <t>NON_CLASSE</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Numerama</t>
+          <t>Phonandroid</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-19T13:33:00+00:00</t>
+          <t>2026-09-19T13:42:46+00:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Notre cerveau refuse de l’admettre et se trompe lourdement, mais au loto la grille 1-2-3-4-5-6 n’a rien de spécial</t>
+          <t>-42% sur la Honor Pad X9a : la tablette de 11,5 pouces est à moins de 145 €</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.numerama.com/sciences/2335765-notre-cerveau-refuse-de-ladmettre-et-se-trompe-completement-mais-au-loto-la-grille-1-2-3-4-5-6-na-rien-de-special.html</t>
+          <t>https://www.phonandroid.com/42-honor-pad-x9a-tablette-11-pouces-moins-145-e.html</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>NON_CLASSE</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>Phonandroid</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-19T13:30:00+00:00</t>
+          <t>2026-09-19T13:33:41+00:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Actualité : IFA 2026 : Découvrez les grands gagnants des premiers Editor's Pick des Numériques !</t>
+          <t>Vous téléchargez des films sur Internet ? Cette nouvelle menace se cache peut-être sur votre PC</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/societe-numerique/ifa-2026-decouvrez-les-grands-gagnants-des-premiers-editor-s-pick-des-numeriques-n261986.html</t>
+          <t>https://www.phonandroid.com/vous-telechargez-des-films-sur-internet-cette-nouvelle-menace-se-cache-peut-etre-sur-votre-pc.html</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>NON_CLASSE</t>
+          <t>2. PC</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>Numerama</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-19T13:25:30+00:00</t>
+          <t>2026-09-19T13:33:00+00:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>La France va-t-elle interdire la revente de cartes Pokémon ?</t>
+          <t>Notre cerveau refuse de l’admettre et se trompe lourdement, mais au loto la grille 1-2-3-4-5-6 n’a rien de spécial</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/19/la-france-va-t-elle-interdire-la-revente-de-cartes-pokemon/</t>
+          <t>https://www.numerama.com/sciences/2335765-notre-cerveau-refuse-de-ladmettre-et-se-trompe-completement-mais-au-loto-la-grille-1-2-3-4-5-6-na-rien-de-special.html</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>15. ludique</t>
+          <t>NON_CLASSE</t>
         </is>
       </c>
     </row>
@@ -1254,49 +1254,49 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-19T13:11:31+00:00</t>
+          <t>2026-09-19T13:30:00+00:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Actualité : Pour de bons écouteurs &amp; intras filaires à prix abordable, privilégiez...</t>
+          <t>Actualité : IFA 2026 : Découvrez les grands gagnants des premiers Editor's Pick des Numériques !</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/ecouteurs-intras-filaires/pour-de-bons-ecouteurs-intras-filaires-a-prix-abordable-privilegiez-n262061.html</t>
+          <t>https://www.lesnumeriques.com/societe-numerique/ifa-2026-decouvrez-les-grands-gagnants-des-premiers-editor-s-pick-des-numeriques-n261986.html</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>8. Audio</t>
+          <t>NON_CLASSE</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Frandroid - RSS</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-19T13:11:00+00:00</t>
+          <t>2026-09-19T13:25:30+00:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Avec plus ou moins 200 € en poche, faut-il craquer pour le nouveau Samsung Galaxy A18 ou le Xiaomi Redmi 17 ?</t>
+          <t>La France va-t-elle interdire la revente de cartes Pokémon ?</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/bons-plans/3252691_avec-plus-ou-moins-200-e-en-poche-faut-il-craquer-pour-le-nouveau-samsung-galaxy-a18-ou-le-xiaomi-redmi-17</t>
+          <t>https://www.journaldugeek.com/2026/09/19/la-france-va-t-elle-interdire-la-revente-de-cartes-pokemon/</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>15. ludique</t>
         </is>
       </c>
     </row>
@@ -1308,49 +1308,49 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-19T13:07:00+00:00</t>
+          <t>2026-09-19T13:11:31+00:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Actualité : Double capteur, zoom x9, IA améliorée : Xiaomi lance une caméra de surveillance qui ne laisse rien passer</t>
+          <t>Actualité : Pour de bons écouteurs &amp; intras filaires à prix abordable, privilégiez...</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/camera-surveillance/double-capteur-zoom-x9-ia-amelioree-xiaomi-lance-une-camera-de-surveillance-qui-ne-laisse-rien-passer-n261932.html</t>
+          <t>https://www.lesnumeriques.com/ecouteurs-intras-filaires/pour-de-bons-ecouteurs-intras-filaires-a-prix-abordable-privilegiez-n262061.html</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>6. IA</t>
+          <t>8. Audio</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>Frandroid - RSS</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-19T13:00:29+00:00</t>
+          <t>2026-09-19T13:11:00+00:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Le HP OmniBook Ultra 16 mise sur l’IA locale… mais avec un prix très haut de gamme</t>
+          <t>Avec plus ou moins 200 € en poche, faut-il craquer pour le nouveau Samsung Galaxy A18 ou le Xiaomi Redmi 17 ?</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/19/le-hp-omnibook-ultra-16-mise-sur-lia-locale-mais-avec-un-prix-tres-haut-de-gamme/</t>
+          <t>https://www.frandroid.com/bons-plans/3252691_avec-plus-ou-moins-200-e-en-poche-faut-il-craquer-pour-le-nouveau-samsung-galaxy-a18-ou-le-xiaomi-redmi-17</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2. PC</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
@@ -1362,44 +1362,44 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-19T12:42:00+00:00</t>
+          <t>2026-09-19T13:07:00+00:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Actualité : Narnia (Netflix) : histoire, sortie, casting, trailer… Tout savoir sur le film de Greta Gerwig</t>
+          <t>Actualité : Double capteur, zoom x9, IA améliorée : Xiaomi lance une caméra de surveillance qui ne laisse rien passer</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/cine-svod/narnia-netflix-histoire-sortie-casting-trailer-tout-savoir-sur-le-film-de-greta-gerwig-n262022.html</t>
+          <t>https://www.lesnumeriques.com/camera-surveillance/double-capteur-zoom-x9-ia-amelioree-xiaomi-lance-une-camera-de-surveillance-qui-ne-laisse-rien-passer-n261932.html</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>15. ludique</t>
+          <t>6. IA</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Phonandroid</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-19T12:36:23+00:00</t>
+          <t>2026-09-19T13:00:29+00:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Le Ryzen 7 9800X3D perd 210 € : une belle baisse de prix pour le processeur AMD</t>
+          <t>Le HP OmniBook Ultra 16 mise sur l’IA locale… mais avec un prix très haut de gamme</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.phonandroid.com/ryzen-7-9800x3d-perd-210-belle-baisse-prix-processeur-amd.html</t>
+          <t>https://www.journaldugeek.com/2026/09/19/le-hp-omnibook-ultra-16-mise-sur-lia-locale-mais-avec-un-prix-tres-haut-de-gamme/</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1411,22 +1411,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Numerama</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-19T12:30:08+00:00</t>
+          <t>2026-09-19T12:42:00+00:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Pourquoi Pikachu a voyagé dans l’ISS avec Sophie Adenot, et ce que ça change pour les fans de Pokémon</t>
+          <t>Actualité : Narnia (Netflix) : histoire, sortie, casting, trailer… Tout savoir sur le film de Greta Gerwig</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.numerama.com/sciences/2335725-pourquoi-pikachu-a-voyage-dans-liss-avec-sophie-adenot-et-ce-que-ca-change-pour-les-fans-de-pokemon.html</t>
+          <t>https://www.lesnumeriques.com/cine-svod/narnia-netflix-histoire-sortie-casting-trailer-tout-savoir-sur-le-film-de-greta-gerwig-n262022.html</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1438,130 +1438,130 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>Phonandroid</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-19T12:17:00+00:00</t>
+          <t>2026-09-19T12:36:23+00:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Actualité : Airfryer : comment la cuisson sans huile a fini par me refroidir</t>
+          <t>Le Ryzen 7 9800X3D perd 210 € : une belle baisse de prix pour le processeur AMD</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/airfryer/airfryer-comment-la-cuisson-sans-huile-a-fini-par-me-refroidir-n224064.html</t>
+          <t>https://www.phonandroid.com/ryzen-7-9800x3d-perd-210-belle-baisse-prix-processeur-amd.html</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>12. Cuisine</t>
+          <t>2. PC</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Frandroid - RSS</t>
+          <t>Numerama</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-19T12:02:00+00:00</t>
+          <t>2026-09-19T12:30:08+00:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>On a testé la Navee GT5 Max, une trottinette électrique qui secoue Segway et Xiaomi</t>
+          <t>Pourquoi Pikachu a voyagé dans l’ISS avec Sophie Adenot, et ce que ça change pour les fans de Pokémon</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/survoltes/trottinette-electrique/3249113_essai-navee-gt5-max-une-trottinette-electrique-qui-peut-secouer-segway-et-xiaomi</t>
+          <t>https://www.numerama.com/sciences/2335725-pourquoi-pikachu-a-voyage-dans-liss-avec-sophie-adenot-et-ce-que-ca-change-pour-les-fans-de-pokemon.html</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>9. Moiilité douce</t>
+          <t>15. ludique</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:27+00:00</t>
+          <t>2026-09-19T12:17:00+00:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Meta One : Meta met Instagram, Facebook, WhatsApp et son IA dans un même abonnement</t>
+          <t>Actualité : Airfryer : comment la cuisson sans huile a fini par me refroidir</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/19/meta-one-meta-met-instagram-facebook-whatsapp-et-son-ia-dans-un-meme-abonnement/</t>
+          <t>https://www.lesnumeriques.com/airfryer/airfryer-comment-la-cuisson-sans-huile-a-fini-par-me-refroidir-n224064.html</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>12. Cuisine</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Numerama</t>
+          <t>Frandroid - RSS</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-19T12:00:00+00:00</t>
+          <t>2026-09-19T12:02:00+00:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Monstre, saison 4 : dans la tête de la tueuse Lizzie Borden, icône féministe sanglante</t>
+          <t>On a testé la Navee GT5 Max, une trottinette électrique qui secoue Segway et Xiaomi</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.numerama.com/pop-culture/2335297-monstre-saison-4-dans-la-tete-de-la-tueuse-lizzie-borden-icone-feministe-sanglante.html</t>
+          <t>https://www.frandroid.com/survoltes/trottinette-electrique/3249113_essai-navee-gt5-max-une-trottinette-electrique-qui-peut-secouer-segway-et-xiaomi</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>NON_CLASSE</t>
+          <t>9. Moiilité douce</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Phonandroid</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-19T11:33:40+00:00</t>
+          <t>2026-09-19T12:01:27+00:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Samsung détrône Apple, la pénurie de RAM bouleverse le marché des smartphones</t>
+          <t>Meta One : Meta met Instagram, Facebook, WhatsApp et son IA dans un même abonnement</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.phonandroid.com/samsung-detrone-apple-la-penurie-de-ram-bouleverse-le-marche-des-smartphones.html</t>
+          <t>https://www.journaldugeek.com/2026/09/19/meta-one-meta-met-instagram-facebook-whatsapp-et-son-ia-dans-un-meme-abonnement/</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1573,27 +1573,27 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Frandroid - RSS</t>
+          <t>Numerama</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-19T11:19:00+00:00</t>
+          <t>2026-09-19T12:00:00+00:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Ce SSD externe Crucial X10 Pro 1 TB voué à disparaître se paye un baroud d’honneur avec cette promo</t>
+          <t>Monstre, saison 4 : dans la tête de la tueuse Lizzie Borden, icône féministe sanglante</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/bons-plans/3252443_ce-ssd-externe-crucial-x10-pro-1-tb-voue-a-disparaitre-se-paye-un-baroud-dhonneur-avec-cette-promo</t>
+          <t>https://www.numerama.com/pop-culture/2335297-monstre-saison-4-dans-la-tete-de-la-tueuse-lizzie-borden-icone-feministe-sanglante.html</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2. PC</t>
+          <t>NON_CLASSE</t>
         </is>
       </c>
     </row>
@@ -1605,17 +1605,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-19T11:17:23+00:00</t>
+          <t>2026-09-19T11:33:40+00:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Votre iPhone garde une trace de vos déplacements : voici où les trouver et comment les effacer</t>
+          <t>Samsung détrône Apple, la pénurie de RAM bouleverse le marché des smartphones</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.phonandroid.com/votre-iphone-garde-trace-deplacements-ou-trouver-effacer.html</t>
+          <t>https://www.phonandroid.com/samsung-detrone-apple-la-penurie-de-ram-bouleverse-le-marche-des-smartphones.html</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1627,49 +1627,49 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>Frandroid - RSS</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-19T11:15:00+00:00</t>
+          <t>2026-09-19T11:19:00+00:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Actualité : Dernière trouvaille de Samsung : breveter un téléphone portable en forme de brique doté d’un écran pliable</t>
+          <t>Ce SSD externe Crucial X10 Pro 1 TB voué à disparaître se paye un baroud d’honneur avec cette promo</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/mobilite-c17/derniere-trouvaille-de-samsung-breveter-un-telephone-portable-en-forme-de-brique-dote-d-un-ecran-pliable-n262033.html</t>
+          <t>https://www.frandroid.com/bons-plans/3252443_ce-ssd-externe-crucial-x10-pro-1-tb-voue-a-disparaitre-se-paye-un-baroud-dhonneur-avec-cette-promo</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>2. PC</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>Phonandroid</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-19T11:13:00+00:00</t>
+          <t>2026-09-19T11:17:23+00:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Actualité : Surprise, 19 nouveaux emojis vont être ajoutés sur Android et iOS, mais il va falloir attendre</t>
+          <t>Votre iPhone garde une trace de vos déplacements : voici où les trouver et comment les effacer</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/societe-numerique/surprise-19-nouveaux-emojis-vont-etre-ajoutes-sur-android-et-ios-mais-il-va-falloir-attendre-n262025.html</t>
+          <t>https://www.phonandroid.com/votre-iphone-garde-trace-deplacements-ou-trouver-effacer.html</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1681,108 +1681,108 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-19T11:00:25+00:00</t>
+          <t>2026-09-19T11:15:00+00:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>L’instax Link WIDE 2 imprime les souvenirs en plus grand</t>
+          <t>Actualité : Dernière trouvaille de Samsung : breveter un téléphone portable en forme de brique doté d’un écran pliable</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/19/linstax-link-wide-2-imprime-les-souvenirs-en-plus-grand/</t>
+          <t>https://www.lesnumeriques.com/mobilite-c17/derniere-trouvaille-de-samsung-breveter-un-telephone-portable-en-forme-de-brique-dote-d-un-ecran-pliable-n262033.html</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>NON_CLASSE</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Numerama</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-19T10:40:48+00:00</t>
+          <t>2026-09-19T11:13:00+00:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Midea revoit son climatiseur PortaSplit pour 2027 : nouveau gaz réfrigérant et compatibilité Matter</t>
+          <t>Actualité : Surprise, 19 nouveaux emojis vont être ajoutés sur Android et iOS, mais il va falloir attendre</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.numerama.com/tech/2336405-midea-revoit-son-climatiseur-portasplit-pour-2027-nouveau-gaz-refrigerant-et-compatibilite-matter.html</t>
+          <t>https://www.lesnumeriques.com/societe-numerique/surprise-19-nouveaux-emojis-vont-etre-ajoutes-sur-android-et-ios-mais-il-va-falloir-attendre-n262025.html</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>8. Audio</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-19T10:36:00+00:00</t>
+          <t>2026-09-19T11:00:25+00:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Actualité : Votre box Wi-Fi bride votre smartphone ? Le réglage caché pour doubler le débit</t>
+          <t>L’instax Link WIDE 2 imprime les souvenirs en plus grand</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/mobilite-c17/votre-box-wi-fi-bride-votre-smartphone-le-reglage-cache-pour-doubler-le-debit-n261954.html</t>
+          <t>https://www.journaldugeek.com/2026/09/19/linstax-link-wide-2-imprime-les-souvenirs-en-plus-grand/</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>NON_CLASSE</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Phonandroid</t>
+          <t>Numerama</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-19T10:33:39+00:00</t>
+          <t>2026-09-19T10:40:48+00:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Windows 11 : Microsoft vous laisse enfin reprendre le contrôle du menu Démarrer avec cette mise à jour</t>
+          <t>Midea revoit son climatiseur PortaSplit pour 2027 : nouveau gaz réfrigérant et compatibilité Matter</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.phonandroid.com/windows-11-microsoft-vous-laisse-enfin-reprendre-le-controle-du-menu-demarrer-avec-cette-mise-a-jour.html</t>
+          <t>https://www.numerama.com/tech/2336405-midea-revoit-son-climatiseur-portasplit-pour-2027-nouveau-gaz-refrigerant-et-compatibilite-matter.html</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>5. Logiciels _ OS</t>
+          <t>8. Audio</t>
         </is>
       </c>
     </row>
@@ -1794,98 +1794,98 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-19T10:11:35+00:00</t>
+          <t>2026-09-19T10:36:00+00:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Actualité : Cet appareil photo instantané présente le meilleur rapport qualité / prix de notre comparatif</t>
+          <t>Actualité : Votre box Wi-Fi bride votre smartphone ? Le réglage caché pour doubler le débit</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/appareil-photo-instantane/cet-appareil-photo-instantane-presente-le-meilleur-rapport-qualite-prix-de-notre-comparatif-n262060.html</t>
+          <t>https://www.lesnumeriques.com/mobilite-c17/votre-box-wi-fi-bride-votre-smartphone-le-reglage-cache-pour-doubler-le-debit-n261954.html</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>NON_CLASSE</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>Phonandroid</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-19T10:04:31+00:00</t>
+          <t>2026-09-19T10:33:39+00:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>iOS 27 : 10 fonctions pour bien maitriser la dernière mise à jour de l’iPhone</t>
+          <t>Windows 11 : Microsoft vous laisse enfin reprendre le contrôle du menu Démarrer avec cette mise à jour</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.01net.com/astuces/ios-27-10-fonctions-pour-bien-maitriser-la-derniere-mise-a-jour-de-liphone.html</t>
+          <t>https://www.phonandroid.com/windows-11-microsoft-vous-laisse-enfin-reprendre-le-controle-du-menu-demarrer-avec-cette-mise-a-jour.html</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>5. Logiciels _ OS</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-19T10:00:16+00:00</t>
+          <t>2026-09-19T10:11:35+00:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Les brouteurs n’ont qu’à bien se tenir : Bercy dévoile son guide anti-arnaques (mais il est déjà obsolète)</t>
+          <t>Actualité : Cet appareil photo instantané présente le meilleur rapport qualité / prix de notre comparatif</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/19/les-brouteurs-nont-qua-bien-se-tenir-bercy-devoile-son-guide-anti-arnaques-mais-il-est-deja-obsolete/</t>
+          <t>https://www.lesnumeriques.com/appareil-photo-instantane/cet-appareil-photo-instantane-presente-le-meilleur-rapport-qualite-prix-de-notre-comparatif-n262060.html</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>8. Audio</t>
+          <t>NON_CLASSE</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-09-19T10:00:00+00:00</t>
+          <t>2026-09-19T10:04:31+00:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Actualité : Redmi Note 17 Pro vs Redmi Note 15 Pro : le duel de l'absurde</t>
+          <t>iOS 27 : 10 fonctions pour bien maitriser la dernière mise à jour de l’iPhone</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/telephone-portable/redmi-note-17-pro-vs-redmi-note-15-pro-le-duel-de-l-absurde-n262034.html</t>
+          <t>https://www.01net.com/astuces/ios-27-10-fonctions-pour-bien-maitriser-la-derniere-mise-a-jour-de-liphone.html</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -1897,34 +1897,34 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-09-19T10:00:00+00:00</t>
+          <t>2026-09-19T10:00:16+00:00</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Test Braun Nevo : que vaut le rasoir à 790 € dont la tête AeroTouch s'inspire de la peau des requins ?</t>
+          <t>Les brouteurs n’ont qu’à bien se tenir : Bercy dévoile son guide anti-arnaques (mais il est déjà obsolète)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/rasoir-electrique/braun-nevo-p78560/test.html</t>
+          <t>https://www.journaldugeek.com/2026/09/19/les-brouteurs-nont-qua-bien-se-tenir-bercy-devoile-son-guide-anti-arnaques-mais-il-est-deja-obsolete/</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>14. Santé</t>
+          <t>8. Audio</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Frandroid - RSS</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1934,17 +1934,17 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>J’ai testé la Garmin Fenix 9 Pro : le titane change tout, l’autonomie un peu moins</t>
+          <t>Actualité : Redmi Note 17 Pro vs Redmi Note 15 Pro : le duel de l'absurde</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/marques/garmin/3240977_jai-teste-la-garmin-fenix-9-pro-le-titane-change-tout-lautonomie-un-peu-moins</t>
+          <t>https://www.lesnumeriques.com/telephone-portable/redmi-note-17-pro-vs-redmi-note-15-pro-le-duel-de-l-absurde-n262034.html</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>6. IA</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
@@ -1956,211 +1956,211 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-09-19T09:35:00+00:00</t>
+          <t>2026-09-19T10:00:00+00:00</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Actualité : PRONOTE vous prend la tête : toutes nos astuces pour survivre à l'année scolaire</t>
+          <t>Test Braun Nevo : que vaut le rasoir à 790 € dont la tête AeroTouch s'inspire de la peau des requins ?</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/societe-numerique/pronote-vous-prend-la-tete-toutes-nos-astuces-pour-survivre-a-l-annee-scolaire-n261988.html</t>
+          <t>https://www.lesnumeriques.com/rasoir-electrique/braun-nevo-p78560/test.html</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>NON_CLASSE</t>
+          <t>14. Santé</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Phonandroid</t>
+          <t>Frandroid - RSS</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-09-19T09:33:38+00:00</t>
+          <t>2026-09-19T10:00:00+00:00</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Marvel’s Wolverine pourrait avoir droit à une suite, cette mystérieuse scène pourrait tout changer</t>
+          <t>J’ai testé la Garmin Fenix 9 Pro : le titane change tout, l’autonomie un peu moins</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.phonandroid.com/marvels-wolverine-pourrait-avoir-droit-a-une-suite-cette-mysterieuse-scene-pourrait-tout-changer.html</t>
+          <t>https://www.frandroid.com/marques/garmin/3240977_jai-teste-la-garmin-fenix-9-pro-le-titane-change-tout-lautonomie-un-peu-moins</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>NON_CLASSE</t>
+          <t>6. IA</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Frandroid - RSS</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-09-19T09:27:00+00:00</t>
+          <t>2026-09-19T09:35:00+00:00</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>La dernière tablette de Honor, compatible avec l’IMAX, perd 50 euros et s’accompagne d’un casque sans fil</t>
+          <t>Actualité : PRONOTE vous prend la tête : toutes nos astuces pour survivre à l'année scolaire</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/bons-plans/3251353_la-derniere-tablette-de-honor-compatible-avec-limax-perd-50-euros-et-saccompagne-dun-casque-sans-fil</t>
+          <t>https://www.lesnumeriques.com/societe-numerique/pronote-vous-prend-la-tete-toutes-nos-astuces-pour-survivre-a-l-annee-scolaire-n261988.html</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>NON_CLASSE</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>Phonandroid</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-09-19T09:15:00+00:00</t>
+          <t>2026-09-19T09:33:38+00:00</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Critique Apollo Has Fallen : la série Canal+ passe à la vitesse supérieure et offre une saison 2 nerveuse</t>
+          <t>Marvel’s Wolverine pourrait avoir droit à une suite, cette mystérieuse scène pourrait tout changer</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/serie/apollo-has-fallen-p78881/test.html</t>
+          <t>https://www.phonandroid.com/marvels-wolverine-pourrait-avoir-droit-a-une-suite-cette-mysterieuse-scene-pourrait-tout-changer.html</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>15. ludique</t>
+          <t>NON_CLASSE</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>Frandroid - RSS</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-09-19T09:02:46+00:00</t>
+          <t>2026-09-19T09:27:00+00:00</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>FarCry : date de sortie, casting, intrigue… tout savoir sur la série LIVE Action</t>
+          <t>La dernière tablette de Honor, compatible avec l’IMAX, perd 50 euros et s’accompagne d’un casque sans fil</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/19/farcry-date-de-sortie-casting-intrigue-tout-savoir-sur-la-serie-live-action/</t>
+          <t>https://www.frandroid.com/bons-plans/3251353_la-derniere-tablette-de-honor-compatible-avec-limax-perd-50-euros-et-saccompagne-dun-casque-sans-fil</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>15. ludique</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Numerama</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-09-19T09:01:54+00:00</t>
+          <t>2026-09-19T09:15:00+00:00</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Des drones non identifiés ont forcé l’aéroport de Luxembourg à fermer vendredi soir</t>
+          <t>Critique Apollo Has Fallen : la série Canal+ passe à la vitesse supérieure et offre une saison 2 nerveuse</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.numerama.com/tech/2336351-des-drones-non-identifies-ont-force-laeroport-de-luxembourg-a-fermer-vendredi-soir.html</t>
+          <t>https://www.lesnumeriques.com/serie/apollo-has-fallen-p78881/test.html</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>9. Moiilité douce</t>
+          <t>15. ludique</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-09-19T09:00:34+00:00</t>
+          <t>2026-09-19T09:02:46+00:00</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>0,82 € les 100 km : l’incroyable exploit de cette Lancia électrique sur le périphérique parisien</t>
+          <t>FarCry : date de sortie, casting, intrigue… tout savoir sur la série LIVE Action</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://www.01net.com/actualites/082-euros-100-km-incroyable-exploit-lancia-electrique-peripherique-parisien.html</t>
+          <t>https://www.journaldugeek.com/2026/09/19/farcry-date-de-sortie-casting-intrigue-tout-savoir-sur-la-serie-live-action/</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>3. Periphérique</t>
+          <t>15. ludique</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Frandroid - RSS</t>
+          <t>Numerama</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-09-19T09:00:00+00:00</t>
+          <t>2026-09-19T09:01:54+00:00</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ChatGPT s’installe gratuitement dans Microsoft Word pour tout le monde</t>
+          <t>Des drones non identifiés ont forcé l’aéroport de Luxembourg à fermer vendredi soir</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/culture-tech/intelligence-artificielle/openai-chatgpt/3253521_chatgpt-sinstalle-gratuitement-dans-microsoft-word-pour-tout-le-monde</t>
+          <t>https://www.numerama.com/tech/2336351-des-drones-non-identifies-ont-force-laeroport-de-luxembourg-a-fermer-vendredi-soir.html</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>5. Logiciels _ OS</t>
+          <t>9. Moiilité douce</t>
         </is>
       </c>
     </row>
@@ -2172,152 +2172,152 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-09-19T08:53:16+00:00</t>
+          <t>2026-09-19T09:00:34+00:00</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Xiaomi dit adieu à la marge : le Redmi Note 15 Pro se vend à prix FOU (256 et 512 Go) ⚡️</t>
+          <t>0,82 € les 100 km : l’incroyable exploit de cette Lancia électrique sur le périphérique parisien</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://www.01net.com/bons-plans/xiaomi-dit-adieu-a-la-marge-le-redmi-note-15-pro-se-vend-a-prix-fou-256-et-512-go.html</t>
+          <t>https://www.01net.com/actualites/082-euros-100-km-incroyable-exploit-lancia-electrique-peripherique-parisien.html</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>3. Periphérique</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Phonandroid</t>
+          <t>Frandroid - RSS</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-09-19T08:37:22+00:00</t>
+          <t>2026-09-19T09:00:00+00:00</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Free libère enfin le potentiel de son Wi-Fi avec cette mise à jour très attendue</t>
+          <t>ChatGPT s’installe gratuitement dans Microsoft Word pour tout le monde</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://www.phonandroid.com/free-libere-enfin-le-potentiel-de-son-wi-fi-avec-cette-mise-a-jour-tres-attendue.html</t>
+          <t>https://www.frandroid.com/culture-tech/intelligence-artificielle/openai-chatgpt/3253521_chatgpt-sinstalle-gratuitement-dans-microsoft-word-pour-tout-le-monde</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>3. Periphérique</t>
+          <t>5. Logiciels _ OS</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-09-19T08:34:08+00:00</t>
+          <t>2026-09-19T08:53:16+00:00</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Le saviez-vous ? Atari a enterré ses pires jeux vidéo dans le désert en 1983, et ce n’était pas une légende</t>
+          <t>Xiaomi dit adieu à la marge : le Redmi Note 15 Pro se vend à prix FOU (256 et 512 Go) ⚡️</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/19/le-saviez-vous-atari-a-enterre-ses-pires-jeux-video-dans-le-desert-en-1983-et-ce-netait-pas-une-legende/</t>
+          <t>https://www.01net.com/bons-plans/xiaomi-dit-adieu-a-la-marge-le-redmi-note-15-pro-se-vend-a-prix-fou-256-et-512-go.html</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>7. Video</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>Phonandroid</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-09-19T08:32:00+00:00</t>
+          <t>2026-09-19T08:37:22+00:00</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Actualité : Samsung Galaxy : ces applications cachées vont améliorer votre quotidien</t>
+          <t>Free libère enfin le potentiel de son Wi-Fi avec cette mise à jour très attendue</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/mobilite-c17/samsung-galaxy-ces-applications-cachees-vont-ameliorer-votre-quotidien-n261951.html</t>
+          <t>https://www.phonandroid.com/free-libere-enfin-le-potentiel-de-son-wi-fi-avec-cette-mise-a-jour-tres-attendue.html</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>3. Periphérique</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-09-19T08:15:00+00:00</t>
+          <t>2026-09-19T08:34:08+00:00</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Actualité : En pleine inflation, voici les 5 départements où faire ses courses en ligne coûte le moins cher</t>
+          <t>Le saviez-vous ? Atari a enterré ses pires jeux vidéo dans le désert en 1983, et ce n’était pas une légende</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/societe-numerique/en-pleine-inflation-voici-les-5-departements-ou-faire-ses-courses-en-ligne-coute-le-moins-cher-n262058.html</t>
+          <t>https://www.journaldugeek.com/2026/09/19/le-saviez-vous-atari-a-enterre-ses-pires-jeux-video-dans-le-desert-en-1983-et-ce-netait-pas-une-legende/</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>14. Santé</t>
+          <t>7. Video</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-09-19T08:13:01+00:00</t>
+          <t>2026-09-19T08:32:00+00:00</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>OnePlus 15 : il défie l’iPhone 17 Pro et le Galaxy S26 Ultra… mais coûte 800 € moins cher</t>
+          <t>Actualité : Samsung Galaxy : ces applications cachées vont améliorer votre quotidien</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://www.01net.com/bons-plans/oneplus-15-il-defie-liphone-17-pro-et-le-galaxy-s26-ultra-mais-coute-800-e-moins-cher.html</t>
+          <t>https://www.lesnumeriques.com/mobilite-c17/samsung-galaxy-ces-applications-cachees-vont-ameliorer-votre-quotidien-n261951.html</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2329,135 +2329,135 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Phonandroid</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-09-19T08:00:19+00:00</t>
+          <t>2026-09-19T08:15:00+00:00</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>On a vu (et entendu) les Cove de JBL, des enceintes qui modernisent l’audio à la maison</t>
+          <t>Actualité : En pleine inflation, voici les 5 départements où faire ses courses en ligne coûte le moins cher</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://www.phonandroid.com/on-a-vu-et-entendu-les-cove-de-jbl-des-enceintes-qui-modernisent-laudio-a-la-maison.html</t>
+          <t>https://www.lesnumeriques.com/societe-numerique/en-pleine-inflation-voici-les-5-departements-ou-faire-ses-courses-en-ligne-coute-le-moins-cher-n262058.html</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>8. Audio</t>
+          <t>14. Santé</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-09-19T08:00:10+00:00</t>
+          <t>2026-09-19T08:13:01+00:00</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Le Futuroscope dévoile sa dernière nouveauté, et elle est spectaculaire</t>
+          <t>OnePlus 15 : il défie l’iPhone 17 Pro et le Galaxy S26 Ultra… mais coûte 800 € moins cher</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/19/le-futuroscope-devoile-sa-derniere-nouveaute-et-elle-est-spectaculaire/</t>
+          <t>https://www.01net.com/bons-plans/oneplus-15-il-defie-liphone-17-pro-et-le-galaxy-s26-ultra-mais-coute-800-e-moins-cher.html</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>NON_CLASSE</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>Phonandroid</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-09-19T08:00:03+00:00</t>
+          <t>2026-09-19T08:00:19+00:00</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Actualité : Les codes promo les plus utilisés de la semaine</t>
+          <t>On a vu (et entendu) les Cove de JBL, des enceintes qui modernisent l’audio à la maison</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/societe-numerique/les-codes-promo-les-plus-utilises-de-la-semaine-n262059.html</t>
+          <t>https://www.phonandroid.com/on-a-vu-et-entendu-les-cove-de-jbl-des-enceintes-qui-modernisent-laudio-a-la-maison.html</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>19. Sponso</t>
+          <t>8. Audio</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Frandroid - RSS</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-09-19T08:00:03+00:00</t>
+          <t>2026-09-19T08:00:10+00:00</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Les meilleurs smartphones à grand écran (6,7 pouces et plus) en 2026</t>
+          <t>Le Futuroscope dévoile sa dernière nouveauté, et elle est spectaculaire</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/guide-dachat/382644_6-alternatives-samsung-galaxy-note-7</t>
+          <t>https://www.journaldugeek.com/2026/09/19/le-futuroscope-devoile-sa-derniere-nouveaute-et-elle-est-spectaculaire/</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>NON_CLASSE</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Numerama</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-09-19T07:40:15+00:00</t>
+          <t>2026-09-19T08:00:03+00:00</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Un rapport de renseignement écrit avec une IA a failli déclencher une crise militaire entre les États-Unis et la Chine</t>
+          <t>Actualité : Les codes promo les plus utilisés de la semaine</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://www.numerama.com/cyberguerre/2336305-un-rapport-de-renseignement-ecrit-avec-une-ia-a-failli-declencher-une-crise-militaire-entre-les-etats-unis-et-la-chine.html</t>
+          <t>https://www.lesnumeriques.com/societe-numerique/les-codes-promo-les-plus-utilises-de-la-semaine-n262059.html</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>6. IA</t>
+          <t>19. Sponso</t>
         </is>
       </c>
     </row>
@@ -2469,17 +2469,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-09-19T07:35:00+00:00</t>
+          <t>2026-09-19T08:00:03+00:00</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Le prix de la version la plus complète du Dyson V16 qui aspire et lave en un geste s’effondre de 280 €</t>
+          <t>Les meilleurs smartphones à grand écran (6,7 pouces et plus) en 2026</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/produits-android/3252607_le-prix-de-la-version-la-plus-complete-du-dyson-v16-qui-aspire-et-lave-en-un-geste-seffondre-de-280-e</t>
+          <t>https://www.frandroid.com/guide-dachat/382644_6-alternatives-samsung-galaxy-note-7</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -2491,27 +2491,27 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Frandroid - RSS</t>
+          <t>Numerama</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-09-19T07:31:05+00:00</t>
+          <t>2026-09-19T07:40:15+00:00</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>iPhone 18 Pro : le démontage confirme une mauvaise nouvelle difficile à justifier</t>
+          <t>Un rapport de renseignement écrit avec une IA a failli déclencher une crise militaire entre les États-Unis et la Chine</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/marques/apple/3253509_iphone-18-pro-le-demontage-confirme-une-mauvaise-nouvelle-difficile-a-justifier</t>
+          <t>https://www.numerama.com/cyberguerre/2336305-un-rapport-de-renseignement-ecrit-avec-une-ia-a-failli-declencher-une-crise-militaire-entre-les-etats-unis-et-la-chine.html</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>6. IA</t>
         </is>
       </c>
     </row>
@@ -2523,22 +2523,22 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-09-19T07:29:38+00:00</t>
+          <t>2026-09-19T07:35:00+00:00</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Google prépare l’intégration d’iMessage dans Gemini pour macOS</t>
+          <t>Le prix de la version la plus complète du Dyson V16 qui aspire et lave en un geste s’effondre de 280 €</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/marques/google/3253495_google-prepare-lintegration-dimessage-dans-gemini-pour-macos</t>
+          <t>https://www.frandroid.com/produits-android/3252607_le-prix-de-la-version-la-plus-complete-du-dyson-v16-qui-aspire-et-lave-en-un-geste-seffondre-de-280-e</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>5. Logiciels _ OS</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
@@ -2550,44 +2550,44 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-09-19T07:28:24+00:00</t>
+          <t>2026-09-19T07:31:05+00:00</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>12 Go de RAM et 4 350 mAh : Clicks muscle son « BlackBerry » sans hausser le prix</t>
+          <t>iPhone 18 Pro : le démontage confirme une mauvaise nouvelle difficile à justifier</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/marques/blackberry/3253497_12-go-de-ram-et-4-350-mah-clicks-muscle-son-blackberry-sans-hausser-le-prix</t>
+          <t>https://www.frandroid.com/marques/apple/3253509_iphone-18-pro-le-demontage-confirme-une-mauvaise-nouvelle-difficile-a-justifier</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>3. Periphérique</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>Frandroid - RSS</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-09-19T07:19:00+00:00</t>
+          <t>2026-09-19T07:29:38+00:00</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Actualité : Sony FE 600mm F6.3 GM OSS : le super téléobjectif 30% plus léger et 1100 € moins cher que Nikon</t>
+          <t>Google prépare l’intégration d’iMessage dans Gemini pour macOS</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/objectif/sony-fe-600mm-f6-3-gm-oss-le-super-teleobjectif-30-plus-leger-et-1100-moins-cher-que-nikon-n261881.html</t>
+          <t>https://www.frandroid.com/marques/google/3253495_google-prepare-lintegration-dimessage-dans-gemini-pour-macos</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -2599,76 +2599,76 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Numerama</t>
+          <t>Frandroid - RSS</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-09-19T07:05:00+00:00</t>
+          <t>2026-09-19T07:28:24+00:00</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Nintendo brade une flopée de jeux Square Enix sur l’eShop, dont plusieurs Final Fantasy</t>
+          <t>12 Go de RAM et 4 350 mAh : Clicks muscle son « BlackBerry » sans hausser le prix</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://www.numerama.com/pop-culture/2336149-nintendo-brade-une-flopee-de-jeux-square-enix-sur-leshop-dont-plusieurs-final-fantasy.html</t>
+          <t>https://www.frandroid.com/marques/blackberry/3253497_12-go-de-ram-et-4-350-mah-clicks-muscle-son-blackberry-sans-hausser-le-prix</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>15. ludique</t>
+          <t>3. Periphérique</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-09-19T07:00:16+00:00</t>
+          <t>2026-09-19T07:19:00+00:00</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>BYD veut concurrencer Rolls-Royce avec des monstres de 1 200 ch signés Yangwang</t>
+          <t>Actualité : Sony FE 600mm F6.3 GM OSS : le super téléobjectif 30% plus léger et 1100 € moins cher que Nikon</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://www.01net.com/actualites/byd-concurrencer-rolls-royce-monstres-1-200-ch-yangwang.html</t>
+          <t>https://www.lesnumeriques.com/objectif/sony-fe-600mm-f6-3-gm-oss-le-super-teleobjectif-30-plus-leger-et-1100-moins-cher-que-nikon-n261881.html</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>10. Voiture</t>
+          <t>5. Logiciels _ OS</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>Numerama</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-09-19T06:59:00+00:00</t>
+          <t>2026-09-19T07:05:00+00:00</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Actualité : La critique de la série Neagley a rejoint notre catalogue</t>
+          <t>Nintendo brade une flopée de jeux Square Enix sur l’eShop, dont plusieurs Final Fantasy</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/serie/la-critique-de-la-serie-neagley-a-rejoint-notre-catalogue-n262053.html</t>
+          <t>https://www.numerama.com/pop-culture/2336149-nintendo-brade-une-flopee-de-jeux-square-enix-sur-leshop-dont-plusieurs-final-fantasy.html</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -2680,27 +2680,27 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Phonandroid</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-09-19T06:50:27+00:00</t>
+          <t>2026-09-19T07:00:16+00:00</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Gears of War E-Day : toutes les infos sur un épisode anniversaire, qui marque le grand retour des exclusivités Xbox</t>
+          <t>BYD veut concurrencer Rolls-Royce avec des monstres de 1 200 ch signés Yangwang</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://www.phonandroid.com/gears-of-war-e-day-toutes-les-infos-sur-un-episode-anniversaire-qui-marque-le-grand-retour-des-exclusivites-xbox.html</t>
+          <t>https://www.01net.com/actualites/byd-concurrencer-rolls-royce-monstres-1-200-ch-yangwang.html</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>15. ludique</t>
+          <t>10. Voiture</t>
         </is>
       </c>
     </row>
@@ -2712,76 +2712,76 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-09-19T06:45:00+00:00</t>
+          <t>2026-09-19T06:59:00+00:00</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Actualité : On l'attendait : Jura dévoile enfin sa machine avec broyeur ultra-compacte et sans compromis</t>
+          <t>Actualité : La critique de la série Neagley a rejoint notre catalogue</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/machine-a-cafe-automatique/on-l-attendait-jura-devoile-enfin-sa-machine-avec-broyeur-ultra-compacte-et-sans-compromis-n262037.html</t>
+          <t>https://www.lesnumeriques.com/serie/la-critique-de-la-serie-neagley-a-rejoint-notre-catalogue-n262053.html</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>12. Cuisine</t>
+          <t>15. ludique</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>Phonandroid</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-09-19T06:45:00+00:00</t>
+          <t>2026-09-19T06:50:27+00:00</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Actualité : "Ça a failli déclencher une guerre" : comment une IA aurait pu plonger le monde dans un incident militaire entre les États-Unis et la Chine</t>
+          <t>Gears of War E-Day : toutes les infos sur un épisode anniversaire, qui marque le grand retour des exclusivités Xbox</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/intelligence-artificielle/ca-a-failli-declencher-une-guerre-comment-une-ia-aurait-pu-plonger-le-monde-dans-un-incident-militaire-entre-les-etats-unis-et-la-chine-n262056.html</t>
+          <t>https://www.phonandroid.com/gears-of-war-e-day-toutes-les-infos-sur-un-episode-anniversaire-qui-marque-le-grand-retour-des-exclusivites-xbox.html</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>6. IA</t>
+          <t>15. ludique</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Frandroid - RSS</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-09-19T06:29:00+00:00</t>
+          <t>2026-09-19T06:45:00+00:00</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Comment bien choisir sa souris ? [Sponso]</t>
+          <t>Actualité : On l'attendait : Jura dévoile enfin sa machine avec broyeur ultra-compacte et sans compromis</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/produits-android/ordinateurs/peripheriques-pc/souris/3234113_comment-bien-choisir-sa-souris</t>
+          <t>https://www.lesnumeriques.com/machine-a-cafe-automatique/on-l-attendait-jura-devoile-enfin-sa-machine-avec-broyeur-ultra-compacte-et-sans-compromis-n262037.html</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>12. Cuisine</t>
         </is>
       </c>
     </row>
@@ -2793,49 +2793,49 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-09-19T06:27:02+00:00</t>
+          <t>2026-09-19T06:45:00+00:00</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Actualité : Bon plan – Le compact / bridge Sony ZV-1 Seul à 630,85 € (-21%)</t>
+          <t>Actualité : "Ça a failli déclencher une guerre" : comment une IA aurait pu plonger le monde dans un incident militaire entre les États-Unis et la Chine</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/compact-bridge/bon-plan-le-compact-bridge-sony-zv-1-seul-a-630-85-21-n262057.html</t>
+          <t>https://www.lesnumeriques.com/intelligence-artificielle/ca-a-failli-declencher-une-guerre-comment-une-ia-aurait-pu-plonger-le-monde-dans-un-incident-militaire-entre-les-etats-unis-et-la-chine-n262056.html</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>19. Sponso</t>
+          <t>6. IA</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>Frandroid - RSS</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-09-19T06:01:17+00:00</t>
+          <t>2026-09-19T06:29:00+00:00</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Cyberattaques : un géant du DDoS a été neutralisé après des « centaines de milliers d’attaques »</t>
+          <t>Comment bien choisir sa souris ? [Sponso]</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://www.01net.com/actualites/cyberattaques-un-geant-du-ddos-a-ete-neutralise-apres-des-centaines-de-milliers-dattaques.html</t>
+          <t>https://www.frandroid.com/produits-android/ordinateurs/peripheriques-pc/souris/3234113_comment-bien-choisir-sa-souris</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>16. actu jur et pol</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
@@ -2847,49 +2847,49 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-09-19T06:01:00+00:00</t>
+          <t>2026-09-19T06:27:02+00:00</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Actualité : 100 % de produits non conformes : le danger des appareils électriques vendus à prix mini sur Amazon, Darty ou Temu</t>
+          <t>Actualité : Bon plan – Le compact / bridge Sony ZV-1 Seul à 630,85 € (-21%)</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/divers-electromenager/100-de-produits-non-conformes-le-danger-des-appareils-electriques-vendus-a-prix-mini-sur-amazon-darty-ou-temu-n262006.html</t>
+          <t>https://www.lesnumeriques.com/compact-bridge/bon-plan-le-compact-bridge-sony-zv-1-seul-a-630-85-21-n262057.html</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>NON_CLASSE</t>
+          <t>19. Sponso</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Frandroid - RSS</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-09-19T05:44:00+00:00</t>
+          <t>2026-09-19T06:01:17+00:00</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Boulanger fait chuter le prix de ce TV 4K QLED 65 pouces Philips Ambilight à moins de 700 €</t>
+          <t>Cyberattaques : un géant du DDoS a été neutralisé après des « centaines de milliers d’attaques »</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/bons-plans/3250245_boulanger-fait-chuter-le-prix-de-ce-tv-4k-qled-65-pouces-philips-ambilight-a-moins-de-700-e</t>
+          <t>https://www.01net.com/actualites/cyberattaques-un-geant-du-ddos-a-ete-neutralise-apres-des-centaines-de-milliers-dattaques.html</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>7. Video</t>
+          <t>16. actu jur et pol</t>
         </is>
       </c>
     </row>
@@ -2901,49 +2901,49 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-09-19T05:15:02+00:00</t>
+          <t>2026-09-19T06:01:00+00:00</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Top bon plan : Samsung, Delonghi, SwitchBot... les meilleurs bons plans du 19/09/2026</t>
+          <t>Actualité : 100 % de produits non conformes : le danger des appareils électriques vendus à prix mini sur Amazon, Darty ou Temu</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/societe-numerique/samsung-switchbot-les-meilleurs-bons-plans-du-19-09-2026-n262050.html</t>
+          <t>https://www.lesnumeriques.com/divers-electromenager/100-de-produits-non-conformes-le-danger-des-appareils-electriques-vendus-a-prix-mini-sur-amazon-darty-ou-temu-n262006.html</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>12. Cuisine</t>
+          <t>NON_CLASSE</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>Frandroid - RSS</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-09-19T05:15:00+00:00</t>
+          <t>2026-09-19T05:44:00+00:00</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Actualité : Google savait que Gemini a attaqué de vraies entreprises et l'a gardé secret pendant des mois</t>
+          <t>Boulanger fait chuter le prix de ce TV 4K QLED 65 pouces Philips Ambilight à moins de 700 €</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/intelligence-artificielle/google-savait-que-gemini-a-attaque-de-vraies-entreprises-et-l-a-garde-secret-pendant-des-mois-n262048.html</t>
+          <t>https://www.frandroid.com/bons-plans/3250245_boulanger-fait-chuter-le-prix-de-ce-tv-4k-qled-65-pouces-philips-ambilight-a-moins-de-700-e</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>6. IA</t>
+          <t>7. Video</t>
         </is>
       </c>
     </row>
@@ -2955,22 +2955,22 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-09-19T05:11:31+00:00</t>
+          <t>2026-09-19T05:15:02+00:00</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Actualité : Pour un bon robot cuiseur multifonctions à prix abordable, privilégiez...</t>
+          <t>Top bon plan : Samsung, Delonghi, SwitchBot... les meilleurs bons plans du 19/09/2026</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/robot-cuiseur-multifonction/pour-un-bon-robot-cuiseur-multifonctions-a-prix-abordable-privilegiez-n262051.html</t>
+          <t>https://www.lesnumeriques.com/societe-numerique/samsung-switchbot-les-meilleurs-bons-plans-du-19-09-2026-n262050.html</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>13. Maison</t>
+          <t>12. Cuisine</t>
         </is>
       </c>
     </row>
@@ -2982,22 +2982,22 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-09-19T05:01:03+00:00</t>
+          <t>2026-09-19T05:15:00+00:00</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Actualité : Bon plan – La machine à café automatique avec broyeur Delonghi Magnifica Evo Next "5 étoiles" à 468,69 € (-21%)</t>
+          <t>Actualité : Google savait que Gemini a attaqué de vraies entreprises et l'a gardé secret pendant des mois</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/machine-a-cafe-automatique/bon-plan-la-machine-a-cafe-automatique-avec-broyeur-delonghi-magnifica-evo-next-5-etoiles-a-468-69-21-n262052.html</t>
+          <t>https://www.lesnumeriques.com/intelligence-artificielle/google-savait-que-gemini-a-attaque-de-vraies-entreprises-et-l-a-garde-secret-pendant-des-mois-n262048.html</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>12. Cuisine</t>
+          <t>6. IA</t>
         </is>
       </c>
     </row>
@@ -3009,103 +3009,103 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-09-19T05:00:00+00:00</t>
+          <t>2026-09-19T05:11:31+00:00</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Actualité : On a passé l’écran de l’iPhone 18 Pro au microscope : voici ce qu'Apple a caché</t>
+          <t>Actualité : Pour un bon robot cuiseur multifonctions à prix abordable, privilégiez...</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/telephone-portable/on-a-passe-l-ecran-de-l-iphone-18-pro-au-microscope-voici-ce-qu-apple-a-cache-n262039.html</t>
+          <t>https://www.lesnumeriques.com/robot-cuiseur-multifonction/pour-un-bon-robot-cuiseur-multifonctions-a-prix-abordable-privilegiez-n262051.html</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>13. Maison</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-09-19T04:54:32+00:00</t>
+          <t>2026-09-19T05:01:03+00:00</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>AliExpress : 5 smartphones Xiaomi à prix cassé en septembre 2026, lequel est fait pour vous ?</t>
+          <t>Actualité : Bon plan – La machine à café automatique avec broyeur Delonghi Magnifica Evo Next "5 étoiles" à 468,69 € (-21%)</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://www.01net.com/bons-plans/aliexpress-smartphones-xiaomi-prix-casse-lequel-est-fait-pour-vous.html</t>
+          <t>https://www.lesnumeriques.com/machine-a-cafe-automatique/bon-plan-la-machine-a-cafe-automatique-avec-broyeur-delonghi-magnifica-evo-next-5-etoiles-a-468-69-21-n262052.html</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>12. Cuisine</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Numerama</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-09-19T04:45:00+00:00</t>
+          <t>2026-09-19T05:00:00+00:00</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Baguette One, bientôt un vol orbital inédit du Starship, manœuvre parfaite de la Nasa – le récap’ sciences de la semaine</t>
+          <t>Actualité : On a passé l’écran de l’iPhone 18 Pro au microscope : voici ce qu'Apple a caché</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://www.numerama.com/sciences/2335785-baguette-one-vol-orbital-inedit-du-starship-manoeuvre-parfaite-de-la-nasa-le-recap-sciences-de-la-semaine.html</t>
+          <t>https://www.lesnumeriques.com/telephone-portable/on-a-passe-l-ecran-de-l-iphone-18-pro-au-microscope-voici-ce-qu-apple-a-cache-n262039.html</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>18. Sciences</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-09-19T04:40:02+00:00</t>
+          <t>2026-09-19T04:54:32+00:00</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Actualité : Bon plan – Le gonfleur de pneu Xiaomi Portable Electric Air Compressor 2 "5 étoiles" à 39,99 €</t>
+          <t>AliExpress : 5 smartphones Xiaomi à prix cassé en septembre 2026, lequel est fait pour vous ?</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/gonfleur-pneu/bon-plan-le-gonfleur-de-pneu-xiaomi-portable-electric-air-compressor-2-5-etoiles-a-39-99-n262049.html</t>
+          <t>https://www.01net.com/bons-plans/aliexpress-smartphones-xiaomi-prix-casse-lequel-est-fait-pour-vous.html</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2. PC</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
@@ -3117,17 +3117,17 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-09-18T22:01:00+00:00</t>
+          <t>2026-09-19T04:45:00+00:00</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Sophie Adenot a une peluche Pikachu dans l’ISS, et ce n’est pas pour devenir la meilleure dresseuse</t>
+          <t>Baguette One, bientôt un vol orbital inédit du Starship, manœuvre parfaite de la Nasa – le récap’ sciences de la semaine</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>https://www.numerama.com/sciences/2335725-sophie-adenot-a-une-peluche-pikachu-dans-liss-et-ce-nest-pas-pour-devenir-la-meilleure-dresseuse.html</t>
+          <t>https://www.numerama.com/sciences/2335785-baguette-one-vol-orbital-inedit-du-starship-manoeuvre-parfaite-de-la-nasa-le-recap-sciences-de-la-semaine.html</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -3144,157 +3144,157 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-09-18T22:00:05+00:00</t>
+          <t>2026-09-19T04:40:02+00:00</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Actualité : Bon plan – L'enceinte connectée Audio Pro C5 MkII à 149,00 € (-26%)</t>
+          <t>Actualité : Bon plan – Le gonfleur de pneu Xiaomi Portable Electric Air Compressor 2 "5 étoiles" à 39,99 €</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/enceintes-sans-fil/bon-plan-l-enceinte-connectee-audio-pro-c5-mkii-a-149-00-26-n262046.html</t>
+          <t>https://www.lesnumeriques.com/gonfleur-pneu/bon-plan-le-gonfleur-de-pneu-xiaomi-portable-electric-air-compressor-2-5-etoiles-a-39-99-n262049.html</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>8. Audio</t>
+          <t>2. PC</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>Numerama</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-09-18T22:00:04+00:00</t>
+          <t>2026-09-18T22:01:00+00:00</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Actualité : Bon plan – Le smartphone Samsung Galaxy A57 5G 128 Go à 329,00 € (-14%)</t>
+          <t>Sophie Adenot a une peluche Pikachu dans l’ISS, et ce n’est pas pour devenir la meilleure dresseuse</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/telephone-portable/bon-plan-le-smartphone-samsung-galaxy-a57-5g-128-go-a-329-00-14-n262045.html</t>
+          <t>https://www.numerama.com/sciences/2335725-sophie-adenot-a-une-peluche-pikachu-dans-liss-et-ce-nest-pas-pour-devenir-la-meilleure-dresseuse.html</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>18. Sciences</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>KultureGeek</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-09-18T20:50:26+00:00</t>
+          <t>2026-09-18T22:00:05+00:00</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Des chercheurs en sécurité ont piraté OpenAI grâce à l’IA Claude</t>
+          <t>Actualité : Bon plan – L'enceinte connectée Audio Pro C5 MkII à 149,00 € (-26%)</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>https://kulturegeek.fr/news-359758/chercheurs-securite-pirate-openai-grace-lia-claude</t>
+          <t>https://www.lesnumeriques.com/enceintes-sans-fil/bon-plan-l-enceinte-connectee-audio-pro-c5-mkii-a-149-00-26-n262046.html</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>6. IA</t>
+          <t>8. Audio</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Frandroid - RSS</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-09-18T19:05:31+00:00</t>
+          <t>2026-09-18T22:00:04+00:00</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>« Un plein à 10 euros » : Lidl casse le prix de sa recharge électrique, c’est le tarif le moins cher de France</t>
+          <t>Actualité : Bon plan – Le smartphone Samsung Galaxy A57 5G 128 Go à 329,00 € (-14%)</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/survoltes/voitures-electriques/3253487_un-plein-a-10-euros-lidl-casse-le-prix-de-sa-recharge-electrique-cest-le-tarif-le-moins-cher-de-france</t>
+          <t>https://www.lesnumeriques.com/telephone-portable/bon-plan-le-smartphone-samsung-galaxy-a57-5g-128-go-a-329-00-14-n262045.html</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>10. Voiture</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>KultureGeek</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-09-18T18:49:08+00:00</t>
+          <t>2026-09-18T20:50:26+00:00</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Garmin Forerunner 265 : -51% ce week-end, une belle affaire pour les vrais sportifs</t>
+          <t>Des chercheurs en sécurité ont piraté OpenAI grâce à l’IA Claude</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>https://www.01net.com/bons-plans/garmin-forerunner-265-51-ce-week-end-une-belle-affaire-pour-les-vrais-sportifs.html</t>
+          <t>https://kulturegeek.fr/news-359758/chercheurs-securite-pirate-openai-grace-lia-claude</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>14. Santé</t>
+          <t>6. IA</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>KultureGeek</t>
+          <t>Frandroid - RSS</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-09-18T18:15:44+00:00</t>
+          <t>2026-09-18T19:05:31+00:00</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Elias 2-24 b : les astronomes découvrent la plus jeune planète jamais observée, et sa taille défie les modèles</t>
+          <t>« Un plein à 10 euros » : Lidl casse le prix de sa recharge électrique, c’est le tarif le moins cher de France</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>https://kulturegeek.fr/news-359753/elias-2-24-b-astronomes-decouvrent-plus-jeune-planete-jamais-observee-taille-defie-modeles</t>
+          <t>https://www.frandroid.com/survoltes/voitures-electriques/3253487_un-plein-a-10-euros-lidl-casse-le-prix-de-sa-recharge-electrique-cest-le-tarif-le-moins-cher-de-france</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>18. Sciences</t>
+          <t>10. Voiture</t>
         </is>
       </c>
     </row>
@@ -3306,233 +3306,233 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-09-18T18:13:58+00:00</t>
+          <t>2026-09-18T18:49:08+00:00</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Xiaomi s’est gouré : il vend le dernier Poco X8 Pro au prix du modèle d’il y a 2 ans 😱</t>
+          <t>Garmin Forerunner 265 : -51% ce week-end, une belle affaire pour les vrais sportifs</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>https://www.01net.com/bons-plans/xiaomi-sest-goure-il-vend-le-dernier-poco-x8-pro-au-prix-du-modele-dil-y-a-2-ans.html</t>
+          <t>https://www.01net.com/bons-plans/garmin-forerunner-265-51-ce-week-end-une-belle-affaire-pour-les-vrais-sportifs.html</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>14. Santé</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Phonandroid</t>
+          <t>KultureGeek</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-09-18T17:46:14+00:00</t>
+          <t>2026-09-18T18:15:44+00:00</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Amazon arrête la livraison gratuite de livres via lockers en France</t>
+          <t>Elias 2-24 b : les astronomes découvrent la plus jeune planète jamais observée, et sa taille défie les modèles</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>https://www.phonandroid.com/amazon-arrete-la-livraison-gratuite-de-livres-via-lockers-en-france.html</t>
+          <t>https://kulturegeek.fr/news-359753/elias-2-24-b-astronomes-decouvrent-plus-jeune-planete-jamais-observee-taille-defie-modeles</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>4. Tablette</t>
+          <t>18. Sciences</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Phonandroid</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-09-18T17:46:07+00:00</t>
+          <t>2026-09-18T18:13:58+00:00</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>L’excellent aspirateur balai sans fil Shark PowerDetect Speed Collection Luxe Clean &amp; Empty passe à prix cassé avec ce code</t>
+          <t>Xiaomi s’est gouré : il vend le dernier Poco X8 Pro au prix du modèle d’il y a 2 ans 😱</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>https://www.phonandroid.com/lexcellent-aspirateur-balai-sans-fil-shark-powerdetect-speed-collection-luxe-clean-empty-passe-a-prix-casse-avec-ce-code.html</t>
+          <t>https://www.01net.com/bons-plans/xiaomi-sest-goure-il-vend-le-dernier-poco-x8-pro-au-prix-du-modele-dil-y-a-2-ans.html</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>11. Menage</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>KultureGeek</t>
+          <t>Phonandroid</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-09-18T17:43:50+00:00</t>
+          <t>2026-09-18T17:46:14+00:00</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>La Californie veut imposer un bouton d’arrêt d’urgence aux IA</t>
+          <t>Amazon arrête la livraison gratuite de livres via lockers en France</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>https://kulturegeek.fr/news-359748/californie-veut-imposer-bouton-darret-durgence-ia</t>
+          <t>https://www.phonandroid.com/amazon-arrete-la-livraison-gratuite-de-livres-via-lockers-en-france.html</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>6. IA</t>
+          <t>4. Tablette</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>Phonandroid</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-09-18T17:30:13+00:00</t>
+          <t>2026-09-18T17:46:07+00:00</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>La bêta de World of Warcraft Forever est ouverte, voici tout ce qu’il faut savoir avant de l’installer !</t>
+          <t>L’excellent aspirateur balai sans fil Shark PowerDetect Speed Collection Luxe Clean &amp; Empty passe à prix cassé avec ce code</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/18/la-beta-de-world-of-warcraft-forever-est-ouverte-voici-tout-ce-quil-faut-savoir-avant-de-linstaller/</t>
+          <t>https://www.phonandroid.com/lexcellent-aspirateur-balai-sans-fil-shark-powerdetect-speed-collection-luxe-clean-empty-passe-a-prix-casse-avec-ce-code.html</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>NON_CLASSE</t>
+          <t>11. Menage</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>KultureGeek</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-09-18T17:03:19+00:00</t>
+          <t>2026-09-18T17:43:50+00:00</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Les États-Unis admettent qu’ils ont déployé des armes en orbite : la militarisation de l’espace s’accélère</t>
+          <t>La Californie veut imposer un bouton d’arrêt d’urgence aux IA</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/18/etats-unis-admettent-deploye-armes-orbite-militarisation-lespace-saccelere/</t>
+          <t>https://kulturegeek.fr/news-359748/californie-veut-imposer-bouton-darret-durgence-ia</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>16. actu jur et pol</t>
+          <t>6. IA</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Frandroid - RSS</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-09-18T17:00:00+00:00</t>
+          <t>2026-09-18T17:30:13+00:00</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>J’ai testé le Leica SL3-P : 45 Mpx, 40 i/s… le Leica qui veut tout faire</t>
+          <t>La bêta de World of Warcraft Forever est ouverte, voici tout ce qu’il faut savoir avant de l’installer !</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/marques/leica/3235591_jai-teste-le-leica-sl3-p-45-mpx-40-i-s-le-leica-qui-veut-tout-faire</t>
+          <t>https://www.journaldugeek.com/2026/09/18/la-beta-de-world-of-warcraft-forever-est-ouverte-voici-tout-ce-quil-faut-savoir-avant-de-linstaller/</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>6. IA</t>
+          <t>NON_CLASSE</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Frandroid - RSS</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-09-18T16:57:51+00:00</t>
+          <t>2026-09-18T17:03:19+00:00</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Pour ses 80 ans, EDF ouvre 70 sites secrets au public, dont ses centrales nucléaires</t>
+          <t>Les États-Unis admettent qu’ils ont déployé des armes en orbite : la militarisation de l’espace s’accélère</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/survoltes/energie/3252663_pour-ses-80-ans-edf-ouvre-70-sites-secrets-au-public-dont-ses-centrales-nucleaires</t>
+          <t>https://www.journaldugeek.com/2026/09/18/etats-unis-admettent-deploye-armes-orbite-militarisation-lespace-saccelere/</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>13. Maison</t>
+          <t>16. actu jur et pol</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>KultureGeek</t>
+          <t>Frandroid - RSS</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-09-18T16:50:20+00:00</t>
+          <t>2026-09-18T17:00:00+00:00</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Anthropic ouvre un laboratoire de biologie : Claude pourrait bientôt piloter des robots scientifiques</t>
+          <t>J’ai testé le Leica SL3-P : 45 Mpx, 40 i/s… le Leica qui veut tout faire</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>https://kulturegeek.fr/news-359736/anthropic-ouvre-laboratoire-biologie-claude-pourrait-piloter-robots-scientifiques</t>
+          <t>https://www.frandroid.com/marques/leica/3235591_jai-teste-le-leica-sl3-p-45-mpx-40-i-s-le-leica-qui-veut-tout-faire</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -3549,206 +3549,206 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-09-18T16:43:50+00:00</t>
+          <t>2026-09-18T16:57:51+00:00</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>1 heure et 4 erreurs : comment l’IA a métamorphosé ma vieille liseuse en écran domotique</t>
+          <t>Pour ses 80 ans, EDF ouvre 70 sites secrets au public, dont ses centrales nucléaires</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/marques/3251785_1-heure-et-4-erreurs-comment-lia-a-metamorphose-ma-vieille-liseuse-en-ecran-domotique</t>
+          <t>https://www.frandroid.com/survoltes/energie/3252663_pour-ses-80-ans-edf-ouvre-70-sites-secrets-au-public-dont-ses-centrales-nucleaires</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>3. Periphérique</t>
+          <t>13. Maison</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Phonandroid</t>
+          <t>KultureGeek</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-09-18T16:40:37+00:00</t>
+          <t>2026-09-18T16:50:20+00:00</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>100 € en moins sur les Galaxy Buds 4 Pro chez Samsung : les écouteurs perdent 40% de leur prix</t>
+          <t>Anthropic ouvre un laboratoire de biologie : Claude pourrait bientôt piloter des robots scientifiques</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>https://www.phonandroid.com/100-e-moins-galaxy-buds-4-pro-samsung-ecouteurs-perdent-40-prix.html</t>
+          <t>https://kulturegeek.fr/news-359736/anthropic-ouvre-laboratoire-biologie-claude-pourrait-piloter-robots-scientifiques</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>8. Audio</t>
+          <t>6. IA</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>Frandroid - RSS</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-09-18T16:30:47+00:00</t>
+          <t>2026-09-18T16:43:50+00:00</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>HONOR Magic V5 : bradé à -52 %, il n’a pourtant rien d’un smartphone au rabais, bien au contraire</t>
+          <t>1 heure et 4 erreurs : comment l’IA a métamorphosé ma vieille liseuse en écran domotique</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>https://www.01net.com/bons-plans/honor-magic-v5-brade-a-52-il-na-pourtant-rien-dun-smartphone-au-rabais-bien-au-contraire.html</t>
+          <t>https://www.frandroid.com/marques/3251785_1-heure-et-4-erreurs-comment-lia-a-metamorphose-ma-vieille-liseuse-en-ecran-domotique</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>3. Periphérique</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>Phonandroid</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-09-18T16:30:35+00:00</t>
+          <t>2026-09-18T16:40:37+00:00</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Test du Ninja Crispi DualZone : l’airfryer en verre XXL qui remplace notre four</t>
+          <t>100 € en moins sur les Galaxy Buds 4 Pro chez Samsung : les écouteurs perdent 40% de leur prix</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/test/test-du-ninja-crispi-dualzone-lairfryer-en-verre-xxl-qui-remplace-notre-four/</t>
+          <t>https://www.phonandroid.com/100-e-moins-galaxy-buds-4-pro-samsung-ecouteurs-perdent-40-prix.html</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>12. Cuisine</t>
+          <t>8. Audio</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Frandroid - RSS</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-09-18T16:17:00+00:00</t>
+          <t>2026-09-18T16:30:47+00:00</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Les mythiques courses de pod de Star Wars reviennent bientôt dans Galactic Racer, en précommande à 44,99 € sur PS5</t>
+          <t>HONOR Magic V5 : bradé à -52 %, il n’a pourtant rien d’un smartphone au rabais, bien au contraire</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/bons-plans/3253083_les-mythiques-courses-de-pod-de-star-wars-reviennent-bientot-dans-galactic-racer-en-precommande-a-4499-e-sur-ps5</t>
+          <t>https://www.01net.com/bons-plans/honor-magic-v5-brade-a-52-il-na-pourtant-rien-dun-smartphone-au-rabais-bien-au-contraire.html</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>14. Santé</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Frandroid - Actualités</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-09-18T16:15:51+00:00</t>
+          <t>2026-09-18T16:30:35+00:00</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Test du Xiaomi Redmi Note 17 Pro 5G, le smartphone qui mise tout sur l’autonomie</t>
+          <t>Test du Ninja Crispi DualZone : l’airfryer en verre XXL qui remplace notre four</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/marques/xiaomi/3235547_test-du-xiaomi-redmi-note-17-pro-5g-le-smartphone-qui-mise-tout-sur-lautonomie</t>
+          <t>https://www.journaldugeek.com/test/test-du-ninja-crispi-dualzone-lairfryer-en-verre-xxl-qui-remplace-notre-four/</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>12. Cuisine</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Phonandroid</t>
+          <t>Frandroid - RSS</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-09-18T16:03:51+00:00</t>
+          <t>2026-09-18T16:17:00+00:00</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Disney+ va diffuser de la publicité aux abonnés Standard et Premium, les déceptions s’enchaînent avec la plateforme de streaming</t>
+          <t>Les mythiques courses de pod de Star Wars reviennent bientôt dans Galactic Racer, en précommande à 44,99 € sur PS5</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>https://www.phonandroid.com/disney-va-diffuser-de-la-publicite-aux-abonnes-standard-et-premium-les-deceptions-senchainent-avec-la-plateforme-de-streaming.html</t>
+          <t>https://www.frandroid.com/bons-plans/3253083_les-mythiques-courses-de-pod-de-star-wars-reviennent-bientot-dans-galactic-racer-en-precommande-a-4499-e-sur-ps5</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>15. ludique</t>
+          <t>14. Santé</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>Frandroid - Actualités</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-09-18T16:00:11+00:00</t>
+          <t>2026-09-18T16:15:51+00:00</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Lunettes connectées : suite à plusieurs plaintes pour harcèlement sexuel, la France lance une enquête</t>
+          <t>Test du Xiaomi Redmi Note 17 Pro 5G, le smartphone qui mise tout sur l’autonomie</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>https://www.01net.com/actualites/lunettes-connectees-suite-a-plusieurs-plaintes-pour-harcelement-sexuel-la-france-lance-une-enquete.html</t>
+          <t>https://www.frandroid.com/marques/xiaomi/3235547_test-du-xiaomi-redmi-note-17-pro-5g-le-smartphone-qui-mise-tout-sur-lautonomie</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -3760,49 +3760,49 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Frandroid - Actualités</t>
+          <t>Phonandroid</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-09-18T15:59:18+00:00</t>
+          <t>2026-09-18T16:03:51+00:00</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Tesla Semi : la formule « une journée complète avec un seul arrêt » arrive en France</t>
+          <t>Disney+ va diffuser de la publicité aux abonnés Standard et Premium, les déceptions s’enchaînent avec la plateforme de streaming</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/marques/tesla/3252189_tesla-semi-la-formule-une-journee-complete-avec-un-seul-arret-arrive-en-france</t>
+          <t>https://www.phonandroid.com/disney-va-diffuser-de-la-publicite-aux-abonnes-standard-et-premium-les-deceptions-senchainent-avec-la-plateforme-de-streaming.html</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>10. Voiture</t>
+          <t>15. ludique</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Frandroid - Actualités</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-09-18T15:57:34+00:00</t>
+          <t>2026-09-18T16:00:11+00:00</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>DAS : qu’est-ce que c’est et quels sont les smartphones qui émettent le moins de rayonnement ?</t>
+          <t>Lunettes connectées : suite à plusieurs plaintes pour harcèlement sexuel, la France lance une enquête</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/produits-android/smartphone/462065_classement-das-quels-sont-les-smartphones-qui-emettent-le-moins-et-le-plus-de-radiations</t>
+          <t>https://www.01net.com/actualites/lunettes-connectees-suite-a-plusieurs-plaintes-pour-harcelement-sexuel-la-france-lance-une-enquete.html</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -3814,27 +3814,27 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>KultureGeek</t>
+          <t>Frandroid - Actualités</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-09-18T15:52:37+00:00</t>
+          <t>2026-09-18T15:59:18+00:00</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Samsung rend disponible One UI 9 (Android 17) sur ses Galaxy</t>
+          <t>Tesla Semi : la formule « une journée complète avec un seul arrêt » arrive en France</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>https://kulturegeek.fr/news-359738/samsung-rend-disponible-one-ui-9-android-17-galaxy</t>
+          <t>https://www.frandroid.com/marques/tesla/3252189_tesla-semi-la-formule-une-journee-complete-avec-un-seul-arret-arrive-en-france</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>10. Voiture</t>
         </is>
       </c>
     </row>
@@ -3846,17 +3846,17 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-09-18T15:49:14+00:00</t>
+          <t>2026-09-18T15:57:34+00:00</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Honor présente le Tiangong AXB35 Ultra, un mini-PC surpuissant conçu avec Nvidia</t>
+          <t>DAS : qu’est-ce que c’est et quels sont les smartphones qui émettent le moins de rayonnement ?</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/produits-android/3253331_honor-presente-le-tiangong-axb35-ultra-un-mini-pc-surpuissant-concu-avec-nvidia</t>
+          <t>https://www.frandroid.com/produits-android/smartphone/462065_classement-das-quels-sont-les-smartphones-qui-emettent-le-moins-et-le-plus-de-radiations</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -3868,27 +3868,27 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Frandroid - Actualités</t>
+          <t>KultureGeek</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-09-18T15:41:43+00:00</t>
+          <t>2026-09-18T15:52:37+00:00</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>À bord du Tesla Semi, son responsable nous explique comment le FSD va débarquer</t>
+          <t>Samsung rend disponible One UI 9 (Android 17) sur ses Galaxy</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/marques/tesla/3252483_a-bord-du-tesla-semi-son-responsable-nous-explique-comment-le-fsd-va-debarquer</t>
+          <t>https://kulturegeek.fr/news-359738/samsung-rend-disponible-one-ui-9-android-17-galaxy</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>8. Audio</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
@@ -3900,76 +3900,76 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-09-18T15:39:57+00:00</t>
+          <t>2026-09-18T15:49:14+00:00</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Gears of War: E-Day, une configuration exigeante à prévoir sur PC</t>
+          <t>Honor présente le Tiangong AXB35 Ultra, un mini-PC surpuissant conçu avec Nvidia</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/guide-dachat/3253211_gears-of-war-e-day-une-configuration-exigeante-a-prevoir-sur-pc</t>
+          <t>https://www.frandroid.com/produits-android/3253331_honor-presente-le-tiangong-axb35-ultra-un-mini-pc-surpuissant-concu-avec-nvidia</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2. PC</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Phonandroid</t>
+          <t>Frandroid - Actualités</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-09-18T15:30:48+00:00</t>
+          <t>2026-09-18T15:41:43+00:00</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Test Samsung Galaxy Z Flip8 : j’ai troqué mon iPhone contre ce smartphone pliant, ai-je vraiment envie de revenir en arrière ?</t>
+          <t>À bord du Tesla Semi, son responsable nous explique comment le FSD va débarquer</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>https://www.phonandroid.com/test-samsung-galaxy-z-flip8-jai-troque-mon-iphone-contre-ce-smartphone-pliant-ai-je-vraiment-envie-de-revenir-en-arriere.html</t>
+          <t>https://www.frandroid.com/marques/tesla/3252483_a-bord-du-tesla-semi-son-responsable-nous-explique-comment-le-fsd-va-debarquer</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>8. Audio</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>Frandroid - Actualités</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-09-18T15:30:22+00:00</t>
+          <t>2026-09-18T15:39:57+00:00</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Batman Day 2026 : voici le programme complet, avec une exclu mondiale pour la France</t>
+          <t>Gears of War: E-Day, une configuration exigeante à prévoir sur PC</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/18/batman-day-2026-voici-le-programme-complet-avec-une-exclu-mondiale-pour-la-france/</t>
+          <t>https://www.frandroid.com/guide-dachat/3253211_gears-of-war-e-day-une-configuration-exigeante-a-prevoir-sur-pc</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>16. actu jur et pol</t>
+          <t>2. PC</t>
         </is>
       </c>
     </row>
@@ -3981,17 +3981,17 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-09-18T15:30:21+00:00</t>
+          <t>2026-09-18T15:30:48+00:00</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Nous avons essayé les Vive Eagle, voici notre avis sur les lunettes connectées de HTC</t>
+          <t>Test Samsung Galaxy Z Flip8 : j’ai troqué mon iPhone contre ce smartphone pliant, ai-je vraiment envie de revenir en arrière ?</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>https://www.phonandroid.com/essai-htc-vive-eagle.html</t>
+          <t>https://www.phonandroid.com/test-samsung-galaxy-z-flip8-jai-troque-mon-iphone-contre-ce-smartphone-pliant-ai-je-vraiment-envie-de-revenir-en-arriere.html</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -4003,27 +4003,27 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Phonandroid</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-09-18T15:29:57+00:00</t>
+          <t>2026-09-18T15:30:22+00:00</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Voitures électriques : plus besoin d’extraire du lithium neuf, Porsche vient de le prouver sur ses propres batteries</t>
+          <t>Batman Day 2026 : voici le programme complet, avec une exclu mondiale pour la France</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>https://www.phonandroid.com/voitures-electriques-plus-besoin-dextraire-du-lithium-neuf-porsche-vient-de-le-prouver-sur-ses-propres-batteries.html</t>
+          <t>https://www.journaldugeek.com/2026/09/18/batman-day-2026-voici-le-programme-complet-avec-une-exclu-mondiale-pour-la-france/</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>10. Voiture</t>
+          <t>16. actu jur et pol</t>
         </is>
       </c>
     </row>
@@ -4035,125 +4035,125 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-09-18T15:16:13+00:00</t>
+          <t>2026-09-18T15:30:21+00:00</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>On a joué à Marvel’s Wolverine sur PS5 : trois raisons de ne pas perdre votre temps avec ce jeu</t>
+          <t>Nous avons essayé les Vive Eagle, voici notre avis sur les lunettes connectées de HTC</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>https://www.phonandroid.com/marvel-wolverine-ps5-notre-avis-complet.html</t>
+          <t>https://www.phonandroid.com/essai-htc-vive-eagle.html</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>15. ludique</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>Phonandroid</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-09-18T15:14:44+00:00</t>
+          <t>2026-09-18T15:29:57+00:00</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Le casque à conduction osseuse Shokz à prix cassé : AliExpress le dégomme ce week-end 🥊</t>
+          <t>Voitures électriques : plus besoin d’extraire du lithium neuf, Porsche vient de le prouver sur ses propres batteries</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>https://www.01net.com/bons-plans/le-casque-a-conduction-osseuse-shokz-a-prix-casse-aliexpress-le-degomme-ce-week-end.html</t>
+          <t>https://www.phonandroid.com/voitures-electriques-plus-besoin-dextraire-du-lithium-neuf-porsche-vient-de-le-prouver-sur-ses-propres-batteries.html</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>8. Audio</t>
+          <t>10. Voiture</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Frandroid - Actualités</t>
+          <t>Phonandroid</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-09-18T15:13:27+00:00</t>
+          <t>2026-09-18T15:16:13+00:00</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Asus lance le premier routeur Wi-Fi 8 : 900 euros et aucun appareil n’est compatible</t>
+          <t>On a joué à Marvel’s Wolverine sur PS5 : trois raisons de ne pas perdre votre temps avec ce jeu</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/marques/asus/3253227_asus-lance-le-premier-routeur-wi-fi-8-900-euros-et-aucun-appareil-nest-compatible</t>
+          <t>https://www.phonandroid.com/marvel-wolverine-ps5-notre-avis-complet.html</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2. PC</t>
+          <t>15. ludique</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Frandroid - Actualités</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-09-18T15:07:20+00:00</t>
+          <t>2026-09-18T15:14:44+00:00</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>iPhone 18 Pro : comment Spigen réinvente l’usage de votre nouveau smartphone au quotidien</t>
+          <t>Le casque à conduction osseuse Shokz à prix cassé : AliExpress le dégomme ce week-end 🥊</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/produits-android/smartphone/3250977_iphone-18-pro-comment-spigen-reinvente-lusage-de-votre-nouveau-smartphone-au-quotidien</t>
+          <t>https://www.01net.com/bons-plans/le-casque-a-conduction-osseuse-shokz-a-prix-casse-aliexpress-le-degomme-ce-week-end.html</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>8. Audio</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>Frandroid - Actualités</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-09-18T15:02:45+00:00</t>
+          <t>2026-09-18T15:13:27+00:00</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>PS6 : la console portable serait un monstre de puissance grâce au PSSR3</t>
+          <t>Asus lance le premier routeur Wi-Fi 8 : 900 euros et aucun appareil n’est compatible</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/18/ps6-la-console-portable-serait-un-monstre-de-puissance-grace-au-pssr3/</t>
+          <t>https://www.frandroid.com/marques/asus/3253227_asus-lance-le-premier-routeur-wi-fi-8-900-euros-et-aucun-appareil-nest-compatible</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -4170,179 +4170,179 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-09-18T14:57:26+00:00</t>
+          <t>2026-09-18T15:07:20+00:00</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Avec son cadre garantie à vie, ce vélo cargo électrique peut grimper jusqu’à 350 km d’autonomie dans un cas très précis</t>
+          <t>iPhone 18 Pro : comment Spigen réinvente l’usage de votre nouveau smartphone au quotidien</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/marques/vello-bike/3252383_avec-son-cadre-garantie-a-vie-ce-velo-cargo-electrique-peut-grimper-jusqua-350-km-dautonomie-dans-un-cas-tres-precis</t>
+          <t>https://www.frandroid.com/produits-android/smartphone/3250977_iphone-18-pro-comment-spigen-reinvente-lusage-de-votre-nouveau-smartphone-au-quotidien</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>8. Audio</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>KultureGeek</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-09-18T14:56:56+00:00</t>
+          <t>2026-09-18T15:02:45+00:00</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>[#BonPlan] Les promos High-Tech du 18 septembre</t>
+          <t>PS6 : la console portable serait un monstre de puissance grâce au PSSR3</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>https://kulturegeek.fr/news-359633/bonplan-promos-high-tech-18-septembre-2026</t>
+          <t>https://www.journaldugeek.com/2026/09/18/ps6-la-console-portable-serait-un-monstre-de-puissance-grace-au-pssr3/</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>19. Sponso</t>
+          <t>2. PC</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>Frandroid - Actualités</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-09-18T14:52:01+00:00</t>
+          <t>2026-09-18T14:57:26+00:00</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Ce billet de 5 euros peut vous rapporter 5 000 € !</t>
+          <t>Avec son cadre garantie à vie, ce vélo cargo électrique peut grimper jusqu’à 350 km d’autonomie dans un cas très précis</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/18/ce-billet-de-5-euros-qui-peut-vous-rapporter-5-000-e/</t>
+          <t>https://www.frandroid.com/marques/vello-bike/3252383_avec-son-cadre-garantie-a-vie-ce-velo-cargo-electrique-peut-grimper-jusqua-350-km-dautonomie-dans-un-cas-tres-precis</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>NON_CLASSE</t>
+          <t>8. Audio</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Frandroid - Actualités</t>
+          <t>KultureGeek</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-09-18T14:50:44+00:00</t>
+          <t>2026-09-18T14:56:56+00:00</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Des PC portables « K-Bossés », mais de bonne qualité : la recette des Ateliers du Bocage face aux géants du reconditionné</t>
+          <t>[#BonPlan] Les promos High-Tech du 18 septembre</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/produits-android/3250423_des-pc-portables-k-bosses-mais-de-bonne-qualite-la-recette-des-ateliers-du-bocage-face-aux-geants-du-reconditionne</t>
+          <t>https://kulturegeek.fr/news-359633/bonplan-promos-high-tech-18-septembre-2026</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>19. Sponso</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Phonandroid</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-09-18T14:50:03+00:00</t>
+          <t>2026-09-18T14:52:01+00:00</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Voici comment synchroniser Samsung Galerie et Google Photos sur votre smartphone Galaxy</t>
+          <t>Ce billet de 5 euros peut vous rapporter 5 000 € !</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>https://www.phonandroid.com/voici-comment-synchroniser-samsung-galerie-et-google-photos-sur-votre-smartphone-galaxy.html</t>
+          <t>https://www.journaldugeek.com/2026/09/18/ce-billet-de-5-euros-qui-peut-vous-rapporter-5-000-e/</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>NON_CLASSE</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Numerama</t>
+          <t>Frandroid - Actualités</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-09-18T14:49:51+00:00</t>
+          <t>2026-09-18T14:50:44+00:00</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>La Game Boy en Lego perd près d’un tiers de son prix : difficile de ne pas être nostalgique</t>
+          <t>Des PC portables « K-Bossés », mais de bonne qualité : la recette des Ateliers du Bocage face aux géants du reconditionné</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>https://www.numerama.com/pop-culture/2058629-la-game-boy-en-lego-perd-pres-dun-tiers-de-son-prix-difficile-de-ne-pas-etre-nostalgique.html</t>
+          <t>https://www.frandroid.com/produits-android/3250423_des-pc-portables-k-bosses-mais-de-bonne-qualite-la-recette-des-ateliers-du-bocage-face-aux-geants-du-reconditionne</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>8. Audio</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>Phonandroid</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-09-18T14:48:16+00:00</t>
+          <t>2026-09-18T14:50:03+00:00</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>iPhone 18 Pro : on a passé la nouvelle Dynamic Island sous le microscope et voici ce qu’on a découvert</t>
+          <t>Voici comment synchroniser Samsung Galerie et Google Photos sur votre smartphone Galaxy</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>https://www.01net.com/actualites/iphone-18-pro-on-a-passe-la-nouvelle-dynamic-island-sous-le-microscope-et-voici-ce-quon-a-decouvert.html</t>
+          <t>https://www.phonandroid.com/voici-comment-synchroniser-samsung-galerie-et-google-photos-sur-votre-smartphone-galaxy.html</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -4354,27 +4354,27 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>TomsHardware</t>
+          <t>Numerama</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-09-18T14:47:00+00:00</t>
+          <t>2026-09-18T14:49:51+00:00</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>iPhone 18 Pro Max : que vaut la chambre à vapeur trois fois plus grande ?</t>
+          <t>La Game Boy en Lego perd près d’un tiers de son prix : difficile de ne pas être nostalgique</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.fr/iphone-18-pro-max-que-vaut-la-chambre-a-vapeur-trois-fois-plus-grande/</t>
+          <t>https://www.numerama.com/pop-culture/2058629-la-game-boy-en-lego-perd-pres-dun-tiers-de-son-prix-difficile-de-ne-pas-etre-nostalgique.html</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>8. Audio</t>
         </is>
       </c>
     </row>
@@ -4386,206 +4386,206 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-09-18T14:40:19+00:00</t>
+          <t>2026-09-18T14:48:16+00:00</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Bon plan : les dernières versions de Microsoft Office 2024 et Windows 11 à partir de 12,25 €</t>
+          <t>iPhone 18 Pro : on a passé la nouvelle Dynamic Island sous le microscope et voici ce qu’on a découvert</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>https://www.01net.com/bons-plans/bon-plan-les-dernieres-versions-de-microsoft-office-2024-et-windows-11-a-partir-de-1225-e.html</t>
+          <t>https://www.01net.com/actualites/iphone-18-pro-on-a-passe-la-nouvelle-dynamic-island-sous-le-microscope-et-voici-ce-quon-a-decouvert.html</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>5. Logiciels _ OS</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>TomsHardware</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-09-18T14:34:00+00:00</t>
+          <t>2026-09-18T14:47:00+00:00</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Actualité : Waze vient de changer en profondeur : les 5 réglages à connaître après la mise à jour de juillet</t>
+          <t>iPhone 18 Pro Max : que vaut la chambre à vapeur trois fois plus grande ?</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/gps/waze-vient-de-changer-en-profondeur-les-5-reglages-a-connaitre-apres-la-mise-a-jour-de-juillet-n262032.html</t>
+          <t>https://www.tomshardware.fr/iphone-18-pro-max-que-vaut-la-chambre-a-vapeur-trois-fois-plus-grande/</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>9. Moiilité douce</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-09-18T14:33:30+00:00</t>
+          <t>2026-09-18T14:40:19+00:00</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>La France va-t-elle interdire la revente des cartes Pokémon avec plus de 20 % de marge ? (les scalpers en PLS)</t>
+          <t>Bon plan : les dernières versions de Microsoft Office 2024 et Windows 11 à partir de 12,25 €</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/18/la-france-va-t-elle-interdire-la-revente-des-cartes-pokemon-avec-plus-de-20-de-marge-les-scalpers-en-pls/</t>
+          <t>https://www.01net.com/bons-plans/bon-plan-les-dernieres-versions-de-microsoft-office-2024-et-windows-11-a-partir-de-1225-e.html</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>15. ludique</t>
+          <t>5. Logiciels _ OS</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Frandroid - Actualités</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-09-18T14:33:07+00:00</t>
+          <t>2026-09-18T14:34:00+00:00</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Nouveau service de streaming gratuit : le célèbre guide JustWatch frappe un très grand coup</t>
+          <t>Actualité : Waze vient de changer en profondeur : les 5 réglages à connaître après la mise à jour de juillet</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/services/svod/3252777_nouveau-service-de-streaming-gratuit-le-celebre-guide-justwatch-frappe-un-tres-grand-coup</t>
+          <t>https://www.lesnumeriques.com/gps/waze-vient-de-changer-en-profondeur-les-5-reglages-a-connaitre-apres-la-mise-a-jour-de-juillet-n262032.html</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>15. ludique</t>
+          <t>9. Moiilité douce</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-09-18T14:21:07+00:00</t>
+          <t>2026-09-18T14:33:30+00:00</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Vente flash DJI : à prix mini, son drone Neo 2 se vend par camions 🚛</t>
+          <t>La France va-t-elle interdire la revente des cartes Pokémon avec plus de 20 % de marge ? (les scalpers en PLS)</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>https://www.01net.com/bons-plans/vente-flash-en-cours-chez-dji-a-prix-mini-son-drone-neo-2-se-vend-par-camions.html</t>
+          <t>https://www.journaldugeek.com/2026/09/18/la-france-va-t-elle-interdire-la-revente-des-cartes-pokemon-avec-plus-de-20-de-marge-les-scalpers-en-pls/</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>7. Video</t>
+          <t>15. ludique</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Numerama</t>
+          <t>Frandroid - Actualités</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-09-18T14:17:02+00:00</t>
+          <t>2026-09-18T14:33:07+00:00</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Quel iPhone acheter en 2026 ? Ceux qui valent leur prix, ceux qu’on vous déconseille</t>
+          <t>Nouveau service de streaming gratuit : le célèbre guide JustWatch frappe un très grand coup</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>https://www.numerama.com/tech/288962-guide-dachat-meilleur-iphone-a-acheter.html</t>
+          <t>https://www.frandroid.com/services/svod/3252777_nouveau-service-de-streaming-gratuit-le-celebre-guide-justwatch-frappe-un-tres-grand-coup</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>15. ludique</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Frandroid - Actualités</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-09-18T14:15:06+00:00</t>
+          <t>2026-09-18T14:21:07+00:00</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Muse fait renaître les produits high-tech vintages</t>
+          <t>Vente flash DJI : à prix mini, son drone Neo 2 se vend par camions 🚛</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/produits-android/audio/3253075_muse-fait-renaitre-les-produits-high-tech-vintages</t>
+          <t>https://www.01net.com/bons-plans/vente-flash-en-cours-chez-dji-a-prix-mini-son-drone-neo-2-se-vend-par-camions.html</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>7. Video</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>KultureGeek</t>
+          <t>Numerama</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-09-18T14:11:50+00:00</t>
+          <t>2026-09-18T14:17:02+00:00</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Motorola Signature 27 : un nouveau smartphone premium annoncé pour le 22 septembre, en pleine conférence Qualcomm</t>
+          <t>Quel iPhone acheter en 2026 ? Ceux qui valent leur prix, ceux qu’on vous déconseille</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>https://kulturegeek.fr/news-359722/motorola-signature-27-nouveau-smartphone-premium-annonce-22-septembre-pleine-conference-qualcomm</t>
+          <t>https://www.numerama.com/tech/288962-guide-dachat-meilleur-iphone-a-acheter.html</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -4597,157 +4597,157 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>Frandroid - Actualités</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-09-18T14:05:16+00:00</t>
+          <t>2026-09-18T14:15:06+00:00</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Xiaomi se lâche complet : il pulvérise le prix du 17T Pro sans aucune explication 🤯</t>
+          <t>Muse fait renaître les produits high-tech vintages</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>https://www.01net.com/bons-plans/xiaomi-pete-les-plombs-il-pulverise-le-prix-du-17t-pro-sans-aucune-explication.html</t>
+          <t>https://www.frandroid.com/produits-android/audio/3253075_muse-fait-renaitre-les-produits-high-tech-vintages</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>NON_CLASSE</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>KultureGeek</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-09-18T14:02:09+00:00</t>
+          <t>2026-09-18T14:11:50+00:00</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Un sous-marin de la Première Guerre mondiale a été retrouvé : coulé en 1917, du TNT s’échappe de son épave</t>
+          <t>Motorola Signature 27 : un nouveau smartphone premium annoncé pour le 22 septembre, en pleine conférence Qualcomm</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/18/sous-marin-premiere-guerre-mondiale-retrouve-1917-tnt-sechappe-epave/</t>
+          <t>https://kulturegeek.fr/news-359722/motorola-signature-27-nouveau-smartphone-premium-annonce-22-septembre-pleine-conference-qualcomm</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>8. Audio</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-09-18T14:02:08+00:00</t>
+          <t>2026-09-18T14:05:16+00:00</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>La série FarCry dévoile son casting, et les premiers noms sont prometteurs</t>
+          <t>Xiaomi se lâche complet : il pulvérise le prix du 17T Pro sans aucune explication 🤯</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/18/la-serie-farcry-devoile-son-casting-et-les-premiers-noms-sont-prometteurs/</t>
+          <t>https://www.01net.com/bons-plans/xiaomi-pete-les-plombs-il-pulverise-le-prix-du-17t-pro-sans-aucune-explication.html</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>8. Audio</t>
+          <t>NON_CLASSE</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>KultureGeek</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-09-18T14:01:37+00:00</t>
+          <t>2026-09-18T14:02:09+00:00</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Netflix devient le premier financeur privé de la production française</t>
+          <t>Un sous-marin de la Première Guerre mondiale a été retrouvé : coulé en 1917, du TNT s’échappe de son épave</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>https://kulturegeek.fr/news-359723/netflix-devient-premier-financeur-prive-production-francaise</t>
+          <t>https://www.journaldugeek.com/2026/09/18/sous-marin-premiere-guerre-mondiale-retrouve-1917-tnt-sechappe-epave/</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>15. ludique</t>
+          <t>8. Audio</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-09-18T14:01:08+00:00</t>
+          <t>2026-09-18T14:02:08+00:00</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>OpenAI a été piraté grâce à l’IA de son grand rival</t>
+          <t>La série FarCry dévoile son casting, et les premiers noms sont prometteurs</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>https://www.01net.com/actualites/openai-a-ete-pirate-grace-a-lia-de-son-grand-rival.html</t>
+          <t>https://www.journaldugeek.com/2026/09/18/la-serie-farcry-devoile-son-casting-et-les-premiers-noms-sont-prometteurs/</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>6. IA</t>
+          <t>8. Audio</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Numerama</t>
+          <t>KultureGeek</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-09-18T13:59:00+00:00</t>
+          <t>2026-09-18T14:01:37+00:00</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Le reboot Netflix de Narnia par la réalisatrice de Barbie déjà jugé woke par les fans</t>
+          <t>Netflix devient le premier financeur privé de la production française</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>https://www.numerama.com/tech/2335261-le-reboot-netflix-de-narnia-deja-juge-trop-woke-enrage-les-puristes.html</t>
+          <t>https://kulturegeek.fr/news-359723/netflix-devient-premier-financeur-prive-production-francaise</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -4759,54 +4759,54 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Numerama</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-09-18T13:48:20+00:00</t>
+          <t>2026-09-18T14:01:08+00:00</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Domino’s Pizza se moque de la lave « PS2 » de Marvel’s Wolverine</t>
+          <t>OpenAI a été piraté grâce à l’IA de son grand rival</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>https://www.numerama.com/pop-culture/2335787-dominos-pizza-se-moque-de-la-lave-ps2-de-marvels-wolverine.html</t>
+          <t>https://www.01net.com/actualites/openai-a-ete-pirate-grace-a-lia-de-son-grand-rival.html</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>NON_CLASSE</t>
+          <t>6. IA</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>Numerama</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-09-18T13:38:00+00:00</t>
+          <t>2026-09-18T13:59:00+00:00</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Actualité : Google simule un cerveau de mouche, un internaute l’utilise pour battre un célèbre jeu vidéo</t>
+          <t>Le reboot Netflix de Narnia par la réalisatrice de Barbie déjà jugé woke par les fans</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/intelligence-artificielle/google-simule-un-cerveau-de-mouche-un-internaute-l-utilise-pour-battre-un-celebre-jeu-video-n262030.html</t>
+          <t>https://www.numerama.com/tech/2335261-le-reboot-netflix-de-narnia-deja-juge-trop-woke-enrage-les-puristes.html</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>7. Video</t>
+          <t>15. ludique</t>
         </is>
       </c>
     </row>
@@ -4818,103 +4818,103 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-09-18T13:36:27+00:00</t>
+          <t>2026-09-18T13:48:20+00:00</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Boulanger fait tomber le clavier Logitech MX Keys S sous la barre des 50 €</t>
+          <t>Domino’s Pizza se moque de la lave « PS2 » de Marvel’s Wolverine</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>https://www.numerama.com/tech/2335761-amazon-fait-tomber-le-clavier-logitech-mx-keys-s-sous-la-barre-des-50-e.html</t>
+          <t>https://www.numerama.com/pop-culture/2335787-dominos-pizza-se-moque-de-la-lave-ps2-de-marvels-wolverine.html</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>3. Periphérique</t>
+          <t>NON_CLASSE</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Frandroid - Actualités</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-09-18T13:33:53+00:00</t>
+          <t>2026-09-18T13:38:00+00:00</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Le Honor 700 Pro s’inspirerait de Xiaomi avec un écran au dos</t>
+          <t>Actualité : Google simule un cerveau de mouche, un internaute l’utilise pour battre un célèbre jeu vidéo</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/produits-android/3252413_le-futur-honor-700-pro-se-devoile-avec-un-ecran-secondaire-au-dos-et-un-capteur-de-200-megapixels</t>
+          <t>https://www.lesnumeriques.com/intelligence-artificielle/google-simule-un-cerveau-de-mouche-un-internaute-l-utilise-pour-battre-un-celebre-jeu-video-n262030.html</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>7. Video</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Frandroid - Actualités</t>
+          <t>Numerama</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-09-18T13:22:10+00:00</t>
+          <t>2026-09-18T13:36:27+00:00</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Après Doom, un internaute entraîne le cerveau de mouche de Google à jouer à Balatro</t>
+          <t>Boulanger fait tomber le clavier Logitech MX Keys S sous la barre des 50 €</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/culture-tech/3252303_apres-doom-ce-cerveau-de-mouche-modelise-par-google-gagne-maintenant-a-balatro</t>
+          <t>https://www.numerama.com/tech/2335761-amazon-fait-tomber-le-clavier-logitech-mx-keys-s-sous-la-barre-des-50-e.html</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>NON_CLASSE</t>
+          <t>3. Periphérique</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>Frandroid - Actualités</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-09-18T13:20:32+00:00</t>
+          <t>2026-09-18T13:33:53+00:00</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Actualité : Voici le meilleur hub usb-c à prix abordable de notre comparatif</t>
+          <t>Le Honor 700 Pro s’inspirerait de Xiaomi avec un écran au dos</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/hub-usb-c/voici-le-meilleur-hub-usb-c-a-prix-abordable-de-notre-comparatif-n262028.html</t>
+          <t>https://www.frandroid.com/produits-android/3252413_le-futur-honor-700-pro-se-devoile-avec-un-ecran-secondaire-au-dos-et-un-capteur-de-200-megapixels</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>3. Periphérique</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
@@ -4926,44 +4926,44 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-09-18T13:17:39+00:00</t>
+          <t>2026-09-18T13:22:10+00:00</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Vous passez 30 minutes à chercher quoi regarder ? Disney+ a enfin la solution</t>
+          <t>Après Doom, un internaute entraîne le cerveau de mouche de Google à jouer à Balatro</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/services/svod/3252681_vous-passez-30-minutes-a-chercher-quoi-regarder-disney-a-enfin-la-solution</t>
+          <t>https://www.frandroid.com/culture-tech/3252303_apres-doom-ce-cerveau-de-mouche-modelise-par-google-gagne-maintenant-a-balatro</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>15. ludique</t>
+          <t>NON_CLASSE</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Frandroid - Actualités</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-09-18T13:16:37+00:00</t>
+          <t>2026-09-18T13:20:32+00:00</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Huawei sonde ses utilisateurs sur un bracelet connecté sans écran, à la manière de Whoop</t>
+          <t>Actualité : Voici le meilleur hub usb-c à prix abordable de notre comparatif</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/marques/huawei/3252849_huawei-sonde-ses-utilisateurs-sur-un-bracelet-connecte-sans-ecran-a-la-maniere-de-whoop</t>
+          <t>https://www.lesnumeriques.com/hub-usb-c/voici-le-meilleur-hub-usb-c-a-prix-abordable-de-notre-comparatif-n262028.html</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -4975,22 +4975,22 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>Frandroid - Actualités</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-09-18T13:02:48+00:00</t>
+          <t>2026-09-18T13:17:39+00:00</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>GTA 6 : la sortie du Online très attendu se précise pour 2027</t>
+          <t>Vous passez 30 minutes à chercher quoi regarder ? Disney+ a enfin la solution</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/18/gta-6-la-sortie-du-online-tres-attendu-se-precise-pour-2027/</t>
+          <t>https://www.frandroid.com/services/svod/3252681_vous-passez-30-minutes-a-chercher-quoi-regarder-disney-a-enfin-la-solution</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -5002,115 +5002,115 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>Frandroid - Actualités</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-09-18T13:02:39+00:00</t>
+          <t>2026-09-18T13:16:37+00:00</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Copier-coller cassé dans Excel : Microsoft partage une bidouille pour contourner le bug</t>
+          <t>Huawei sonde ses utilisateurs sur un bracelet connecté sans écran, à la manière de Whoop</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>https://www.01net.com/actualites/copier-coller-casse-dans-excel-microsoft-partage-une-bidouille-pour-contourner-le-bug.html</t>
+          <t>https://www.frandroid.com/marques/huawei/3252849_huawei-sonde-ses-utilisateurs-sur-un-bracelet-connecte-sans-ecran-a-la-maniere-de-whoop</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>5. Logiciels _ OS</t>
+          <t>3. Periphérique</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Frandroid - Actualités</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-09-18T13:01:53+00:00</t>
+          <t>2026-09-18T13:02:48+00:00</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Monaco-Lens : comment voir le match d’ouverture de la 5e journée de Ligue 1 en direct et en streaming ?</t>
+          <t>GTA 6 : la sortie du Online très attendu se précise pour 2027</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/produits-android/3252865_monaco-lens-comment-voir-le-match-douverture-de-la-5e-journee-de-ligue-1-en-direct-et-en-streaming</t>
+          <t>https://www.journaldugeek.com/2026/09/18/gta-6-la-sortie-du-online-tres-attendu-se-precise-pour-2027/</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>15. ludique</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-09-18T13:00:00+00:00</t>
+          <t>2026-09-18T13:02:39+00:00</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Test Xiaomi Redmi Note 17 5G : il n'est sauvé que par son autonomie</t>
+          <t>Copier-coller cassé dans Excel : Microsoft partage une bidouille pour contourner le bug</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/telephone-portable/xiaomi-redmi-note-17-5g-p78893/test.html</t>
+          <t>https://www.01net.com/actualites/copier-coller-casse-dans-excel-microsoft-partage-une-bidouille-pour-contourner-le-bug.html</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>5. Logiciels _ OS</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Numerama</t>
+          <t>Frandroid - Actualités</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-09-18T13:00:00+00:00</t>
+          <t>2026-09-18T13:01:53+00:00</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Test de Control Resonant, le nouveau chef-d’œuvre de Remedy</t>
+          <t>Monaco-Lens : comment voir le match d’ouverture de la 5e journée de Ligue 1 en direct et en streaming ?</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>https://www.numerama.com/pop-culture/2335251-test-de-control-resonant-le-nouveau-chef-doeuvre-de-remedy.html</t>
+          <t>https://www.frandroid.com/produits-android/3252865_monaco-lens-comment-voir-le-match-douverture-de-la-5e-journee-de-ligue-1-en-direct-et-en-streaming</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>NON_CLASSE</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Korben</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -5120,174 +5120,174 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Comment mesurer et dégonfler l'index de recherche de Windows</t>
+          <t>Test Xiaomi Redmi Note 17 5G : il n'est sauvé que par son autonomie</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>https://korben.info/windows-search-indexation-etendue-ssd.html</t>
+          <t>https://www.lesnumeriques.com/telephone-portable/xiaomi-redmi-note-17-5g-p78893/test.html</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>2. PC</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Phonandroid</t>
+          <t>Numerama</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-09-18T12:44:03+00:00</t>
+          <t>2026-09-18T13:00:00+00:00</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>AliExpress lance sa French Week et fait chuter les prix : voici les offres à saisir</t>
+          <t>Test de Control Resonant, le nouveau chef-d’œuvre de Remedy</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>https://www.phonandroid.com/aliexpress-french-week-fait-chuter-prix-voici-offres-saisir.html</t>
+          <t>https://www.numerama.com/pop-culture/2335251-test-de-control-resonant-le-nouveau-chef-doeuvre-de-remedy.html</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>19. Sponso</t>
+          <t>NON_CLASSE</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Phonandroid</t>
+          <t>Korben</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-09-18T12:39:25+00:00</t>
+          <t>2026-09-18T13:00:00+00:00</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>iPhone 18 Pro : Apple augmente le prix du remplacement de la batterie</t>
+          <t>Comment mesurer et dégonfler l'index de recherche de Windows</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>https://www.phonandroid.com/iphone-18-pro-apple-augmente-le-prix-du-remplacement-de-la-batterie.html</t>
+          <t>https://korben.info/windows-search-indexation-etendue-ssd.html</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>2. PC</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Numerama</t>
+          <t>Phonandroid</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-09-18T12:37:21+00:00</t>
+          <t>2026-09-18T12:44:03+00:00</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Devinez quel personnage joue Madds mikkelsen dans le prochain Call of Duty</t>
+          <t>AliExpress lance sa French Week et fait chuter les prix : voici les offres à saisir</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>https://www.numerama.com/pop-culture/2335755-devinez-quel-personnage-joue-madds-mikkelsen-dans-le-prochain-call-of-duty.html</t>
+          <t>https://www.phonandroid.com/aliexpress-french-week-fait-chuter-prix-voici-offres-saisir.html</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>NON_CLASSE</t>
+          <t>19. Sponso</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Frandroid - Actualités</t>
+          <t>Phonandroid</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-09-18T12:30:50+00:00</t>
+          <t>2026-09-18T12:39:25+00:00</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>aptX, LDAC, SBC, LC3 : tout comprendre aux codecs Bluetooth audio</t>
+          <t>iPhone 18 Pro : Apple augmente le prix du remplacement de la batterie</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/comment-faire/comment-fonctionne-la-technologie/752329_aptx-ldac-sbc-tout-comprendre-aux-codecs-bluetooth-audio</t>
+          <t>https://www.phonandroid.com/iphone-18-pro-apple-augmente-le-prix-du-remplacement-de-la-batterie.html</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>8. Audio</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>Numerama</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-09-18T12:30:11+00:00</t>
+          <t>2026-09-18T12:37:21+00:00</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Ce nouveau télescope de la NASA va chercher des milliers de planètes dans l’univers</t>
+          <t>Devinez quel personnage joue Madds mikkelsen dans le prochain Call of Duty</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>https://www.01net.com/actualites/ce-nouveau-telescope-de-la-nasa-va-chercher-des-milliers-de-planetes-dans-lunivers.html</t>
+          <t>https://www.numerama.com/pop-culture/2335755-devinez-quel-personnage-joue-madds-mikkelsen-dans-le-prochain-call-of-duty.html</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>18. Sciences</t>
+          <t>NON_CLASSE</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Numerama</t>
+          <t>Frandroid - Actualités</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-09-18T12:30:00+00:00</t>
+          <t>2026-09-18T12:30:50+00:00</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Le géant de la batterie CATL perd de son emprise sur les constructeurs chinois</t>
+          <t>aptX, LDAC, SBC, LC3 : tout comprendre aux codecs Bluetooth audio</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>https://www.numerama.com/vroom/2335713-le-geant-de-la-batterie-catl-perd-de-son-emprise-sur-les-constructeurs-chinois.html</t>
+          <t>https://www.frandroid.com/comment-faire/comment-fonctionne-la-technologie/752329_aptx-ldac-sbc-tout-comprendre-aux-codecs-bluetooth-audio</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -5299,270 +5299,270 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Frandroid - Actualités</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-09-18T12:25:55+00:00</t>
+          <t>2026-09-18T12:30:11+00:00</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Moins de 800 kg et 110 km/h : à quoi ressemble la voiture électrique à 15 000 € qui pourrait bientôt déferler sur nos routes ?</t>
+          <t>Ce nouveau télescope de la NASA va chercher des milliers de planètes dans l’univers</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/survoltes/3252389_moins-de-800-kg-et-110-km-h-a-quoi-ressemble-la-voiture-electrique-a-15-000-e-qui-pourrait-bientot-deferler-sur-nos-routes</t>
+          <t>https://www.01net.com/actualites/ce-nouveau-telescope-de-la-nasa-va-chercher-des-milliers-de-planetes-dans-lunivers.html</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>10. Voiture</t>
+          <t>18. Sciences</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>Numerama</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-09-18T12:16:00+00:00</t>
+          <t>2026-09-18T12:30:00+00:00</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Actualité : Le lave-linge Dreame Slim Washer S passe sous les 350 €</t>
+          <t>Le géant de la batterie CATL perd de son emprise sur les constructeurs chinois</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/lave-linge/le-lave-linge-dreame-slim-washer-s-passe-sous-les-350-n262024.html</t>
+          <t>https://www.numerama.com/vroom/2335713-le-geant-de-la-batterie-catl-perd-de-son-emprise-sur-les-constructeurs-chinois.html</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>11. Menage</t>
+          <t>8. Audio</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Numerama</t>
+          <t>Frandroid - Actualités</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-09-18T12:11:12+00:00</t>
+          <t>2026-09-18T12:25:55+00:00</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>25 000 taxis autonomes en Europe : Bolt et Lucid veulent couper l’herbe sous le pied à Waymo</t>
+          <t>Moins de 800 kg et 110 km/h : à quoi ressemble la voiture électrique à 15 000 € qui pourrait bientôt déferler sur nos routes ?</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>https://www.numerama.com/vroom/2335711-25-000-taxis-autonomes-en-europe-bolt-et-lucid-veulent-couper-lherbe-sous-le-pied-a-waymo.html</t>
+          <t>https://www.frandroid.com/survoltes/3252389_moins-de-800-kg-et-110-km-h-a-quoi-ressemble-la-voiture-electrique-a-15-000-e-qui-pourrait-bientot-deferler-sur-nos-routes</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>9. Moiilité douce</t>
+          <t>10. Voiture</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>KultureGeek</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-09-18T12:10:53+00:00</t>
+          <t>2026-09-18T12:16:00+00:00</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Mark Zuckerberg rejette l’idée de ralentir le développement de l’IA</t>
+          <t>Actualité : Le lave-linge Dreame Slim Washer S passe sous les 350 €</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>https://kulturegeek.fr/news-359716/mark-zuckerberg-rejette-lidee-ralentir-developpement-lia</t>
+          <t>https://www.lesnumeriques.com/lave-linge/le-lave-linge-dreame-slim-washer-s-passe-sous-les-350-n262024.html</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>6. IA</t>
+          <t>11. Menage</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>Numerama</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-09-18T12:04:27+00:00</t>
+          <t>2026-09-18T12:11:12+00:00</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>iPhone 18 Pro et Pro Max : les premiers tests sont tombés, faut-il craquer ? Voici ce qu’il faut vraiment retenir</t>
+          <t>25 000 taxis autonomes en Europe : Bolt et Lucid veulent couper l’herbe sous le pied à Waymo</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/18/iphone-18-pro-et-pro-max-les-premiers-tests-sont-tombes-faut-il-craquer-voici-ce-quil-faut-vraiment-retenir/</t>
+          <t>https://www.numerama.com/vroom/2335711-25-000-taxis-autonomes-en-europe-bolt-et-lucid-veulent-couper-lherbe-sous-le-pied-a-waymo.html</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>9. Moiilité douce</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>KultureGeek</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-09-18T11:35:34+00:00</t>
+          <t>2026-09-18T12:10:53+00:00</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Des chercheurs découvrent une nouvelle structure cruciale cachée dans nos cellules</t>
+          <t>Mark Zuckerberg rejette l’idée de ralentir le développement de l’IA</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/18/des-chercheurs-decouvrent-une-nouvelle-structure-cruciale-cachee-dans-nos-cellules/</t>
+          <t>https://kulturegeek.fr/news-359716/mark-zuckerberg-rejette-lidee-ralentir-developpement-lia</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>18. Sciences</t>
+          <t>6. IA</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Numerama</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-09-18T11:30:00+00:00</t>
+          <t>2026-09-18T12:04:27+00:00</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Miami Vice 85  : après Michael B. Jordan et Austin Butler, le film pioche dans le casting de L’Odyssée</t>
+          <t>iPhone 18 Pro et Pro Max : les premiers tests sont tombés, faut-il craquer ? Voici ce qu’il faut vraiment retenir</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>https://www.numerama.com/pop-culture/2335553-miami-vice-85-apres-michael-b-jordan-et-austin-butler-le-film-pioche-dans-le-casting-de-lodyssee.html</t>
+          <t>https://www.journaldugeek.com/2026/09/18/iphone-18-pro-et-pro-max-les-premiers-tests-sont-tombes-faut-il-craquer-voici-ce-quil-faut-vraiment-retenir/</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>15. ludique</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-09-18T11:20:00+00:00</t>
+          <t>2026-09-18T11:35:34+00:00</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Actualité : Disney+ continue d'empirer : de la publicité obligatoire arrive dans tous les abonnements</t>
+          <t>Des chercheurs découvrent une nouvelle structure cruciale cachée dans nos cellules</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/cine-svod/disney-continue-d-empirer-de-la-publicite-obligatoire-arrive-dans-tous-les-abonnements-n262015.html</t>
+          <t>https://www.journaldugeek.com/2026/09/18/des-chercheurs-decouvrent-une-nouvelle-structure-cruciale-cachee-dans-nos-cellules/</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>15. ludique</t>
+          <t>18. Sciences</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>Numerama</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-09-18T11:10:49+00:00</t>
+          <t>2026-09-18T11:30:00+00:00</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Smartphones pliants : l’effet Apple est là, et Samsung en profite… deux fois</t>
+          <t>Miami Vice 85  : après Michael B. Jordan et Austin Butler, le film pioche dans le casting de L’Odyssée</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>https://www.01net.com/actualites/smartphones-pliants-leffet-apple-est-la-et-samsung-en-profite-deux-fois.html</t>
+          <t>https://www.numerama.com/pop-culture/2335553-miami-vice-85-apres-michael-b-jordan-et-austin-butler-le-film-pioche-dans-le-casting-de-lodyssee.html</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>15. ludique</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Frandroid - Actualités</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-09-18T11:02:51+00:00</t>
+          <t>2026-09-18T11:20:00+00:00</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Galaxy S27 Ultra : après six ans d’attente, Samsung va enfin augmenter la batterie</t>
+          <t>Actualité : Disney+ continue d'empirer : de la publicité obligatoire arrive dans tous les abonnements</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/marques/samsung/3252641_galaxy-s27-ultra-apres-six-ans-dattente-samsung-va-enfin-augmenter-la-batterie</t>
+          <t>https://www.lesnumeriques.com/cine-svod/disney-continue-d-empirer-de-la-publicite-obligatoire-arrive-dans-tous-les-abonnements-n262015.html</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>NON_CLASSE</t>
+          <t>15. ludique</t>
         </is>
       </c>
     </row>
@@ -5574,211 +5574,211 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-09-18T10:45:32+00:00</t>
+          <t>2026-09-18T11:10:49+00:00</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Mastercard offre des cartes bancaires aux IA pour dépenser votre argent</t>
+          <t>Smartphones pliants : l’effet Apple est là, et Samsung en profite… deux fois</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>https://www.01net.com/actualites/mastercard-offre-des-cartes-bancaires-aux-ia-pour-depenser-votre-argent.html</t>
+          <t>https://www.01net.com/actualites/smartphones-pliants-leffet-apple-est-la-et-samsung-en-profite-deux-fois.html</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>6. IA</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>Frandroid - Actualités</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-09-18T10:44:00+00:00</t>
+          <t>2026-09-18T11:02:51+00:00</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Actualité : MobLand saison 2 : quand sortent les épisodes de la série sur Paramount+ ?</t>
+          <t>Galaxy S27 Ultra : après six ans d’attente, Samsung va enfin augmenter la batterie</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/cine-svod/mobland-saison-2-quand-sortent-les-episodes-de-la-serie-sur-paramount-n262014.html</t>
+          <t>https://www.frandroid.com/marques/samsung/3252641_galaxy-s27-ultra-apres-six-ans-dattente-samsung-va-enfin-augmenter-la-batterie</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>15. ludique</t>
+          <t>NON_CLASSE</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>KultureGeek</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-09-18T10:41:49+00:00</t>
+          <t>2026-09-18T10:45:32+00:00</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Huawei accélère le lancement de sa puce IA Ascend 960DT pour concurrencer Nvidia dès 2027</t>
+          <t>Mastercard offre des cartes bancaires aux IA pour dépenser votre argent</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>https://kulturegeek.fr/news-359713/huawei-accelere-lancement-puce-ia-ascend-960dt-concurrencer-nvidia-2027</t>
+          <t>https://www.01net.com/actualites/mastercard-offre-des-cartes-bancaires-aux-ia-pour-depenser-votre-argent.html</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>2. PC</t>
+          <t>6. IA</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-09-18T10:33:23+00:00</t>
+          <t>2026-09-18T10:44:00+00:00</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Free débloque (enfin) cette fonction qui peut doubler le débit Wi-Fi de votre Freebox !</t>
+          <t>Actualité : MobLand saison 2 : quand sortent les épisodes de la série sur Paramount+ ?</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/18/free-debloque-enfin-cette-fonction-qui-peut-doubler-le-debit-wi-fi-de-votre-freebox/</t>
+          <t>https://www.lesnumeriques.com/cine-svod/mobland-saison-2-quand-sortent-les-episodes-de-la-serie-sur-paramount-n262014.html</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>3. Periphérique</t>
+          <t>15. ludique</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Frandroid - Actualités</t>
+          <t>KultureGeek</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-09-18T10:32:33+00:00</t>
+          <t>2026-09-18T10:41:49+00:00</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>L’iPhone 18 Pro est mieux refroidi que certains smartphones gaming, comme le démontrent ces tests</t>
+          <t>Huawei accélère le lancement de sa puce IA Ascend 960DT pour concurrencer Nvidia dès 2027</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/produits-android/smartphone/3252289_liphone-18-pro-est-mieux-refroidi-que-les-meilleurs-smartphones-gaming-comme-le-demontrent-ces-tests</t>
+          <t>https://kulturegeek.fr/news-359713/huawei-accelere-lancement-puce-ia-ascend-960dt-concurrencer-nvidia-2027</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>2. PC</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Korben</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-09-18T10:21:37+00:00</t>
+          <t>2026-09-18T10:33:23+00:00</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Calibre lance le livre dont vous êtes le héros, généré par IA</t>
+          <t>Free débloque (enfin) cette fonction qui peut doubler le débit Wi-Fi de votre Freebox !</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>https://korben.info/calibre-9-15-jeu-aventure-ia.html</t>
+          <t>https://www.journaldugeek.com/2026/09/18/free-debloque-enfin-cette-fonction-qui-peut-doubler-le-debit-wi-fi-de-votre-freebox/</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>4. Tablette</t>
+          <t>3. Periphérique</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>Frandroid - Actualités</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-09-18T10:19:00+00:00</t>
+          <t>2026-09-18T10:32:33+00:00</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Actualité : Trois hackers ont utilisé Claude pour pirater OpenAI en 72 heures, et ils n'ont eu besoin que d'un abonnement</t>
+          <t>L’iPhone 18 Pro est mieux refroidi que certains smartphones gaming, comme le démontrent ces tests</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/intelligence-artificielle/trois-hackers-ont-utilise-claude-pour-pirater-openai-en-72-heures-et-ils-n-ont-eu-besoin-que-d-un-abonnement-n262016.html</t>
+          <t>https://www.frandroid.com/produits-android/smartphone/3252289_liphone-18-pro-est-mieux-refroidi-que-les-meilleurs-smartphones-gaming-comme-le-demontrent-ces-tests</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>6. IA</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>Korben</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-09-18T10:15:26+00:00</t>
+          <t>2026-09-18T10:21:37+00:00</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Disney+ fait une très mauvaise blague à ses abonnés en ajoutant de la pub sur toutes ses offres !</t>
+          <t>Calibre lance le livre dont vous êtes le héros, généré par IA</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/18/disney-fait-une-tres-mauvaise-blague-a-ses-abonnes-en-ajoutant-de-la-pub-sur-toutes-ses-offres/</t>
+          <t>https://korben.info/calibre-9-15-jeu-aventure-ia.html</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>15. ludique</t>
+          <t>4. Tablette</t>
         </is>
       </c>
     </row>
@@ -5790,179 +5790,179 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-09-18T10:15:00+00:00</t>
+          <t>2026-09-18T10:19:00+00:00</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Actualité : Le câble USB-C vers Jack 6.35 (pour un ampli par ex.) est à 8.79 €</t>
+          <t>Actualité : Trois hackers ont utilisé Claude pour pirater OpenAI en 72 heures, et ils n'ont eu besoin que d'un abonnement</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/accessoire-audio/le-cable-usb-c-vers-jack-6-35-pour-un-ampli-par-ex-est-a-8-79-n262020.html</t>
+          <t>https://www.lesnumeriques.com/intelligence-artificielle/trois-hackers-ont-utilise-claude-pour-pirater-openai-en-72-heures-et-ils-n-ont-eu-besoin-que-d-un-abonnement-n262016.html</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>3. Periphérique</t>
+          <t>6. IA</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-09-18T10:11:33+00:00</t>
+          <t>2026-09-18T10:15:26+00:00</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Actualité : Ces écouteurs sans fil présentent le meilleur rapport qualité / prix de notre comparatif</t>
+          <t>Disney+ fait une très mauvaise blague à ses abonnés en ajoutant de la pub sur toutes ses offres !</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/ecouteurs-sans-fil/ces-ecouteurs-sans-fil-presentent-le-meilleur-rapport-qualite-prix-de-notre-comparatif-n262019.html</t>
+          <t>https://www.journaldugeek.com/2026/09/18/disney-fait-une-tres-mauvaise-blague-a-ses-abonnes-en-ajoutant-de-la-pub-sur-toutes-ses-offres/</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>8. Audio</t>
+          <t>15. ludique</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-09-18T10:05:56+00:00</t>
+          <t>2026-09-18T10:15:00+00:00</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Xiaomi 15T Pro : deal de FOLIE à saisir sur ce best-seller en puissance (-44%) ⚡️</t>
+          <t>Actualité : Le câble USB-C vers Jack 6.35 (pour un ampli par ex.) est à 8.79 €</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>https://www.01net.com/bons-plans/xiaomi-15t-pro-deal-de-folie-a-saisir-rapidement-sur-ce-best-seller-en-puissance.html</t>
+          <t>https://www.lesnumeriques.com/accessoire-audio/le-cable-usb-c-vers-jack-6-35-pour-un-ampli-par-ex-est-a-8-79-n262020.html</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>NON_CLASSE</t>
+          <t>3. Periphérique</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-09-18T10:03:11+00:00</t>
+          <t>2026-09-18T10:11:33+00:00</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>25 000 véhicules vont débarquer dans plusieurs grandes villes européennes !</t>
+          <t>Actualité : Ces écouteurs sans fil présentent le meilleur rapport qualité / prix de notre comparatif</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/18/25-000-vehicules-vont-debarquer-dans-plusieurs-grandes-villes-europeennes/</t>
+          <t>https://www.lesnumeriques.com/ecouteurs-sans-fil/ces-ecouteurs-sans-fil-presentent-le-meilleur-rapport-qualite-prix-de-notre-comparatif-n262019.html</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>10. Voiture</t>
+          <t>8. Audio</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Frandroid - Actualités</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-09-18T10:02:00+00:00</t>
+          <t>2026-09-18T10:05:56+00:00</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>En France comme à l’étranger, ce forfait mobile Bouygues Telecom 200 Go ne vous laissera jamais tomber</t>
+          <t>Xiaomi 15T Pro : deal de FOLIE à saisir sur ce best-seller en puissance (-44%) ⚡️</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/telecom/forfait-mobile/3249431_en-france-comme-a-letranger-ce-forfait-mobile-bouygues-telecom-200-go-ne-vous-laissera-jamais-tomber</t>
+          <t>https://www.01net.com/bons-plans/xiaomi-15t-pro-deal-de-folie-a-saisir-rapidement-sur-ce-best-seller-en-puissance.html</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>NON_CLASSE</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Frandroid - Actualités</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-09-18T10:00:18+00:00</t>
+          <t>2026-09-18T10:03:11+00:00</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Comment installer un SSD M.2 dans sa PS5 pour agrandir le stockage ? Notre tutoriel</t>
+          <t>25 000 véhicules vont débarquer dans plusieurs grandes villes européennes !</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/marques/sony/1077003_ps5-comment-installer-un-ssd-m-2-dans-la-console-et-transferer-ses-jeux</t>
+          <t>https://www.journaldugeek.com/2026/09/18/25-000-vehicules-vont-debarquer-dans-plusieurs-grandes-villes-europeennes/</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>2. PC</t>
+          <t>10. Voiture</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>Frandroid - Actualités</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-09-18T09:58:29+00:00</t>
+          <t>2026-09-18T10:02:00+00:00</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>L’iPhone 18 Pro est trop cher ? Vous n’êtes pas prêts pour la suite</t>
+          <t>En France comme à l’étranger, ce forfait mobile Bouygues Telecom 200 Go ne vous laissera jamais tomber</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>https://www.01net.com/actualites/liphone-18-pro-est-trop-cher-vous-netes-pas-prets-pour-la-suite.html</t>
+          <t>https://www.frandroid.com/telecom/forfait-mobile/3249431_en-france-comme-a-letranger-ce-forfait-mobile-bouygues-telecom-200-go-ne-vous-laissera-jamais-tomber</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -5979,17 +5979,17 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-09-18T09:57:26+00:00</t>
+          <t>2026-09-18T10:00:18+00:00</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>AMD s’apprêterait à augmenter de 10 % le prix de ses cartes graphiques et processeurs</t>
+          <t>Comment installer un SSD M.2 dans sa PS5 pour agrandir le stockage ? Notre tutoriel</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/marques/amd/3252391_amd-sappreterait-a-augmenter-de-10-le-prix-de-ses-cartes-graphiques-et-processeurs</t>
+          <t>https://www.frandroid.com/marques/sony/1077003_ps5-comment-installer-un-ssd-m-2-dans-la-console-et-transferer-ses-jeux</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -6001,27 +6001,27 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-09-18T09:53:00+00:00</t>
+          <t>2026-09-18T09:58:29+00:00</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Actualité : Freebox : Free exploite enfin pleinement les capacités Wi-Fi de ses box et répéteurs</t>
+          <t>L’iPhone 18 Pro est trop cher ? Vous n’êtes pas prêts pour la suite</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/societe-numerique/freebox-free-exploite-enfin-pleinement-les-capacites-wi-fi-de-ses-box-et-repeteurs-n262009.html</t>
+          <t>https://www.01net.com/actualites/liphone-18-pro-est-trop-cher-vous-netes-pas-prets-pour-la-suite.html</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>3. Periphérique</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
@@ -6033,49 +6033,49 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-09-18T09:49:45+00:00</t>
+          <t>2026-09-18T09:57:26+00:00</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>iPhone Duo Max : Apple pourrait muscler son jeu face au Samsung Galaxy Z Fold 8 Ultra</t>
+          <t>AMD s’apprêterait à augmenter de 10 % le prix de ses cartes graphiques et processeurs</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/marques/apple/3251957_iphone-duo-max-apple-pourrait-muscler-son-jeu-face-au-samsung-galaxy-z-fold-8-ultra</t>
+          <t>https://www.frandroid.com/marques/amd/3252391_amd-sappreterait-a-augmenter-de-10-le-prix-de-ses-cartes-graphiques-et-processeurs</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>2. PC</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-09-18T09:49:43+00:00</t>
+          <t>2026-09-18T09:53:00+00:00</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Révolutionnez  le ménage chez vous : cet aspirateur robot tout-en-un est à -72%</t>
+          <t>Actualité : Freebox : Free exploite enfin pleinement les capacités Wi-Fi de ses box et répéteurs</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>https://www.01net.com/bons-plans/revolutionnez-le-menage-chez-vous-cet-aspirateur-robot-tout-en-un-est-a-72.html</t>
+          <t>https://www.lesnumeriques.com/societe-numerique/freebox-free-exploite-enfin-pleinement-les-capacites-wi-fi-de-ses-box-et-repeteurs-n262009.html</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>11. Menage</t>
+          <t>3. Periphérique</t>
         </is>
       </c>
     </row>
@@ -6087,103 +6087,103 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-09-18T09:45:25+00:00</t>
+          <t>2026-09-18T09:49:45+00:00</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>PS5 Slim ou PS5 Pro : quelle PS5 choisir ?</t>
+          <t>iPhone Duo Max : Apple pourrait muscler son jeu face au Samsung Galaxy Z Fold 8 Ultra</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/marques/sony/767530_ps5-ou-ps5-digital-edition-quel-modele-choisir</t>
+          <t>https://www.frandroid.com/marques/apple/3251957_iphone-duo-max-apple-pourrait-muscler-son-jeu-face-au-samsung-galaxy-z-fold-8-ultra</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>7. Video</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-09-18T09:30:51+00:00</t>
+          <t>2026-09-18T09:49:43+00:00</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Le retour de la canicule dès la semaine prochaine ? Une nouvelle vague de chaleur annoncée pour fin septembre et au-delà</t>
+          <t>Révolutionnez  le ménage chez vous : cet aspirateur robot tout-en-un est à -72%</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/18/le-retour-de-la-canicule-des-la-semaine-prochaine-une-nouvelle-vague-de-chaleur-annoncee-pour-fin-septembre-et-au-dela/</t>
+          <t>https://www.01net.com/bons-plans/revolutionnez-le-menage-chez-vous-cet-aspirateur-robot-tout-en-un-est-a-72.html</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>NON_CLASSE</t>
+          <t>11. Menage</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>Frandroid - Actualités</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-09-18T09:30:13+00:00</t>
+          <t>2026-09-18T09:45:25+00:00</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>iPhone 18 Pro, Apple Watch 12, AirPods 5… :  une mise à jour obligatoire vous attend dès le déballage</t>
+          <t>PS5 Slim ou PS5 Pro : quelle PS5 choisir ?</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>https://www.01net.com/actualites/iphone-18-pro-apple-watch-12-airpods-5-mise-jour-obligatoire-attend-deballage.html</t>
+          <t>https://www.frandroid.com/marques/sony/767530_ps5-ou-ps5-digital-edition-quel-modele-choisir</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>7. Video</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-09-18T09:30:00+00:00</t>
+          <t>2026-09-18T09:30:51+00:00</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Bitdefender Premium Security : comment repérer les deepfakes et éviter les arnaques ?</t>
+          <t>Le retour de la canicule dès la semaine prochaine ? Une nouvelle vague de chaleur annoncée pour fin septembre et au-delà</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/appli-logiciel/bitdefender-premium-security-comment-reperer-les-deepfakes-et-eviter-les-arnaques-na262018.html</t>
+          <t>https://www.journaldugeek.com/2026/09/18/le-retour-de-la-canicule-des-la-semaine-prochaine-une-nouvelle-vague-de-chaleur-annoncee-pour-fin-septembre-et-au-dela/</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>NON_CLASSE</t>
         </is>
       </c>
     </row>
@@ -6195,22 +6195,22 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-09-18T09:20:28+00:00</t>
+          <t>2026-09-18T09:30:13+00:00</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Mauvaise nouvelle si vous achetez des livres sur Amazon</t>
+          <t>iPhone 18 Pro, Apple Watch 12, AirPods 5… :  une mise à jour obligatoire vous attend dès le déballage</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>https://www.01net.com/actualites/amazon-met-fin-livraison-gratuite-livres-dans-lockers.html</t>
+          <t>https://www.01net.com/actualites/iphone-18-pro-apple-watch-12-airpods-5-mise-jour-obligatoire-attend-deballage.html</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>4. Tablette</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
@@ -6222,157 +6222,157 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-09-18T09:20:00+00:00</t>
+          <t>2026-09-18T09:30:00+00:00</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Actualité : Narnia : des premières images magiques pour le blockbuster Netflix signé Greta Gerwig</t>
+          <t>Bitdefender Premium Security : comment repérer les deepfakes et éviter les arnaques ?</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/cine-svod/narnia-des-premieres-images-magiques-pour-le-blockbuster-netflix-signe-greta-gerwig-n262013.html</t>
+          <t>https://www.lesnumeriques.com/appli-logiciel/bitdefender-premium-security-comment-reperer-les-deepfakes-et-eviter-les-arnaques-na262018.html</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>7. Video</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-09-18T09:19:00+00:00</t>
+          <t>2026-09-18T09:20:28+00:00</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Actualité : Un astéroïde grand comme un immeuble de trois à six étages s’est écrasé sur la Lune : voici l’incroyable cratère géant découvert par la NASA</t>
+          <t>Mauvaise nouvelle si vous achetez des livres sur Amazon</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/vers-la-lune/un-asteroide-grand-comme-un-immeuble-de-trois-a-six-etages-s-est-ecrase-sur-la-lune-voici-l-incroyable-cratere-geant-decouvert-par-la-nasa-n262017.html</t>
+          <t>https://www.01net.com/actualites/amazon-met-fin-livraison-gratuite-livres-dans-lockers.html</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>18. Sciences</t>
+          <t>4. Tablette</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>KultureGeek</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-09-18T09:15:00+00:00</t>
+          <t>2026-09-18T09:20:00+00:00</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Intelligence artificielle et emploi : près de la moitié de la population anticipe des suppressions massives de postes selon une étude</t>
+          <t>Actualité : Narnia : des premières images magiques pour le blockbuster Netflix signé Greta Gerwig</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>https://kulturegeek.fr/news-359700/intelligence-artificielle-emploi-pres-moitie-population-anticipe-suppressions-massives-postes-etude</t>
+          <t>https://www.lesnumeriques.com/cine-svod/narnia-des-premieres-images-magiques-pour-le-blockbuster-netflix-signe-greta-gerwig-n262013.html</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>6. IA</t>
+          <t>7. Video</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-09-18T09:03:28+00:00</t>
+          <t>2026-09-18T09:19:00+00:00</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Cette prime promise par EDF à l’achat d’une BYD met le feu aux poudres au gouvernement !</t>
+          <t>Actualité : Un astéroïde grand comme un immeuble de trois à six étages s’est écrasé sur la Lune : voici l’incroyable cratère géant découvert par la NASA</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/18/cette-prime-promise-par-edf-a-lachat-dune-byd-met-le-feu-aux-poudres-au-gouvernement/</t>
+          <t>https://www.lesnumeriques.com/vers-la-lune/un-asteroide-grand-comme-un-immeuble-de-trois-a-six-etages-s-est-ecrase-sur-la-lune-voici-l-incroyable-cratere-geant-decouvert-par-la-nasa-n262017.html</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>10. Voiture</t>
+          <t>18. Sciences</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>KultureGeek</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-09-18T09:03:08+00:00</t>
+          <t>2026-09-18T09:15:00+00:00</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>La Redmi Pad 2 est vendue une misère : Xiaomi vide le stock et la fait à -65%</t>
+          <t>Intelligence artificielle et emploi : près de la moitié de la population anticipe des suppressions massives de postes selon une étude</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>https://www.01net.com/bons-plans/la-redmi-pad-2-est-vendue-une-misere-xiaomi-vide-le-stock-et-la-fait-a-65.html</t>
+          <t>https://kulturegeek.fr/news-359700/intelligence-artificielle-emploi-pres-moitie-population-anticipe-suppressions-massives-postes-etude</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>6. IA</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-09-18T08:56:00+00:00</t>
+          <t>2026-09-18T09:03:28+00:00</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Actualité : Adieu Microsoft Office : ce logiciel open source et 100 % européen arrive enfin sur ordinateur pour chasser Word et Excel</t>
+          <t>Cette prime promise par EDF à l’achat d’une BYD met le feu aux poudres au gouvernement !</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/appli-logiciel/adieu-microsoft-office-ce-logiciel-open-source-et-100-europeen-arrive-enfin-sur-ordinateur-pour-chasser-word-et-excel-n262008.html</t>
+          <t>https://www.journaldugeek.com/2026/09/18/cette-prime-promise-par-edf-a-lachat-dune-byd-met-le-feu-aux-poudres-au-gouvernement/</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>10. Voiture</t>
         </is>
       </c>
     </row>
@@ -6384,22 +6384,22 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-09-18T08:35:03+00:00</t>
+          <t>2026-09-18T09:03:08+00:00</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Euro Office : l’alternative européenne à Microsoft Office arrive sur Windows, macOS et Linux</t>
+          <t>La Redmi Pad 2 est vendue une misère : Xiaomi vide le stock et la fait à -65%</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>https://www.01net.com/actualites/euro-office-lalternative-europeenne-a-microsoft-office-arrive-sur-windows-macos-et-linux.html</t>
+          <t>https://www.01net.com/bons-plans/la-redmi-pad-2-est-vendue-une-misere-xiaomi-vide-le-stock-et-la-fait-a-65.html</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>5. Logiciels _ OS</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
@@ -6411,76 +6411,76 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-09-18T08:31:00+00:00</t>
+          <t>2026-09-18T08:56:00+00:00</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Actualité : Fusion nucléaire : des chercheurs génèrent des rayons X aussi brillants qu'une étoile et jamais vus sur Terre</t>
+          <t>Actualité : Adieu Microsoft Office : ce logiciel open source et 100 % européen arrive enfin sur ordinateur pour chasser Word et Excel</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/concept/fusion-nucleaire-des-chercheurs-generent-des-rayons-x-aussi-brillants-qu-une-etoile-et-jamais-vus-sur-terre-n262003.html</t>
+          <t>https://www.lesnumeriques.com/appli-logiciel/adieu-microsoft-office-ce-logiciel-open-source-et-100-europeen-arrive-enfin-sur-ordinateur-pour-chasser-word-et-excel-n262008.html</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>17. Actualité éco</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-09-18T08:30:23+00:00</t>
+          <t>2026-09-18T08:35:03+00:00</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Extension Pokémon 30 ans : les magasins ont-ils le droit de desceller les cartes pour éviter les scalpers ?</t>
+          <t>Euro Office : l’alternative européenne à Microsoft Office arrive sur Windows, macOS et Linux</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/18/extension-pokemon-30-ans-les-magasins-ont-ils-le-droit-de-desceller-les-cartes-pour-eviter-les-scalpers/</t>
+          <t>https://www.01net.com/actualites/euro-office-lalternative-europeenne-a-microsoft-office-arrive-sur-windows-macos-et-linux.html</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>15. ludique</t>
+          <t>5. Logiciels _ OS</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Korben</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-09-18T08:27:24+00:00</t>
+          <t>2026-09-18T08:31:00+00:00</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Linux sur PS5 Pro n'arrivera pas tout de suite</t>
+          <t>Actualité : Fusion nucléaire : des chercheurs génèrent des rayons X aussi brillants qu'une étoile et jamais vus sur Terre</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>https://korben.info/ps5-linux-developpeur-principal-abandonne.html</t>
+          <t>https://www.lesnumeriques.com/concept/fusion-nucleaire-des-chercheurs-generent-des-rayons-x-aussi-brillants-qu-une-etoile-et-jamais-vus-sur-terre-n262003.html</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>5. Logiciels _ OS</t>
+          <t>17. Actualité éco</t>
         </is>
       </c>
     </row>
@@ -6492,17 +6492,17 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-09-18T08:16:02+00:00</t>
+          <t>2026-09-18T08:30:23+00:00</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Quelle est la valeur de votre vieille console Nintendo en 2026 ? Le classement des 10 modèles les plus côtés</t>
+          <t>Extension Pokémon 30 ans : les magasins ont-ils le droit de desceller les cartes pour éviter les scalpers ?</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/18/quelle-est-la-valeur-de-votre-vieille-console-nintendo/</t>
+          <t>https://www.journaldugeek.com/2026/09/18/extension-pokemon-30-ans-les-magasins-ont-ils-le-droit-de-desceller-les-cartes-pour-eviter-les-scalpers/</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -6514,22 +6514,22 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>Korben</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-09-18T08:08:19+00:00</t>
+          <t>2026-09-18T08:27:24+00:00</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Google Keep change le design d’un de ses widgets de la meilleure des manières</t>
+          <t>Linux sur PS5 Pro n'arrivera pas tout de suite</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>https://www.01net.com/actualites/google-keep-change-design-widgets-meilleures-des-manieres.html</t>
+          <t>https://korben.info/ps5-linux-developpeur-principal-abandonne.html</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -6541,81 +6541,81 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Korben</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-09-18T08:07:06+00:00</t>
+          <t>2026-09-18T08:16:02+00:00</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Mes 2 nouveaux interrupteurs Sonoff Zigbee</t>
+          <t>Quelle est la valeur de votre vieille console Nintendo en 2026 ? Le classement des 10 modèles les plus côtés</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>https://korben.info/sonoff-volet-lumiere-zigbee-bureau.html</t>
+          <t>https://www.journaldugeek.com/2026/09/18/quelle-est-la-valeur-de-votre-vieille-console-nintendo/</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>12. Cuisine</t>
+          <t>15. ludique</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-09-18T08:04:00+00:00</t>
+          <t>2026-09-18T08:08:19+00:00</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Actualité : Bon plan – Le répéteur Wifi Huawei WiFi Mesh 3 Pack de 3 à 119,99 € (-38%)</t>
+          <t>Google Keep change le design d’un de ses widgets de la meilleure des manières</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/repeteurs-wi-fi/bon-plan-le-repeteur-wifi-huawei-wifi-mesh-3-pack-de-3-a-119-99-38-n262007.html</t>
+          <t>https://www.01net.com/actualites/google-keep-change-design-widgets-meilleures-des-manieres.html</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>3. Periphérique</t>
+          <t>5. Logiciels _ OS</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>Korben</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-09-18T08:02:22+00:00</t>
+          <t>2026-09-18T08:07:06+00:00</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Un roman inédit de Tolkien sort en France, 80 ans après sa création</t>
+          <t>Mes 2 nouveaux interrupteurs Sonoff Zigbee</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/18/un-roman-inedit-de-tolkien-sort-en-france-80-ans-apres-sa-creation/</t>
+          <t>https://korben.info/sonoff-volet-lumiere-zigbee-bureau.html</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>NON_CLASSE</t>
+          <t>12. Cuisine</t>
         </is>
       </c>
     </row>
@@ -6627,130 +6627,130 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-09-18T08:00:00+00:00</t>
+          <t>2026-09-18T08:04:00+00:00</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>SharkNinja Crispi DualZone, un Airfryer avec deux compartiments pour préparer un repas complet en une seule fois</t>
+          <t>Actualité : Bon plan – Le répéteur Wifi Huawei WiFi Mesh 3 Pack de 3 à 119,99 € (-38%)</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/electromenager/sharkninja-crispi-dualzone-un-airfryer-avec-deux-compartiments-pour-preparer-un-repas-complet-en-une-seule-fois-na261964.html</t>
+          <t>https://www.lesnumeriques.com/repeteurs-wi-fi/bon-plan-le-repeteur-wifi-huawei-wifi-mesh-3-pack-de-3-a-119-99-38-n262007.html</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>12. Cuisine</t>
+          <t>3. Periphérique</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>KultureGeek</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-09-18T07:53:40+00:00</t>
+          <t>2026-09-18T08:02:22+00:00</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Claude dirige déjà 26 % de la recherche d’Anthropic sur ses prochaines IA</t>
+          <t>Un roman inédit de Tolkien sort en France, 80 ans après sa création</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>https://kulturegeek.fr/news-359684/claude-dirige-26-recherche-anthropic-prochaines-ia</t>
+          <t>https://www.journaldugeek.com/2026/09/18/un-roman-inedit-de-tolkien-sort-en-france-80-ans-apres-sa-creation/</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>6. IA</t>
+          <t>NON_CLASSE</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>KultureGeek</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-09-18T07:38:12+00:00</t>
+          <t>2026-09-18T08:00:00+00:00</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Lunettes connectées : le parquet de Paris ouvre une enquête après des vidéos filmées sans consentement</t>
+          <t>SharkNinja Crispi DualZone, un Airfryer avec deux compartiments pour préparer un repas complet en une seule fois</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>https://kulturegeek.fr/news-359682/lunettes-connectees-parquet-paris-enquete-videos-consentement</t>
+          <t>https://www.lesnumeriques.com/electromenager/sharkninja-crispi-dualzone-un-airfryer-avec-deux-compartiments-pour-preparer-un-repas-complet-en-une-seule-fois-na261964.html</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>12. Cuisine</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>KultureGeek</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-09-18T07:31:55+00:00</t>
+          <t>2026-09-18T07:53:40+00:00</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Les premières images de Narnia : Le Neveu du magicien sont là et elles risquent de ne pas vous plaire !</t>
+          <t>Claude dirige déjà 26 % de la recherche d’Anthropic sur ses prochaines IA</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/18/premieres-images-narnia-le-neveu-du-magicien-film-netflix/</t>
+          <t>https://kulturegeek.fr/news-359684/claude-dirige-26-recherche-anthropic-prochaines-ia</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>7. Video</t>
+          <t>6. IA</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>KultureGeek</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-09-18T07:14:16+00:00</t>
+          <t>2026-09-18T07:38:12+00:00</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Revolut : après la fuite de données, une arnaque redoutable vise les clients</t>
+          <t>Lunettes connectées : le parquet de Paris ouvre une enquête après des vidéos filmées sans consentement</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>https://www.01net.com/actualites/revolut-apres-fuite-donnees-arnaque-redoutable-vise-clients.html</t>
+          <t>https://kulturegeek.fr/news-359682/lunettes-connectees-parquet-paris-enquete-videos-consentement</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>16. actu jur et pol</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
@@ -6762,130 +6762,130 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026-09-18T07:06:18+00:00</t>
+          <t>2026-09-18T07:31:55+00:00</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Bornes de recharges : voici ce qui change pour les voitures électriques dès le 1er janvier 2027</t>
+          <t>Les premières images de Narnia : Le Neveu du magicien sont là et elles risquent de ne pas vous plaire !</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/18/bornes-de-recharges-voici-ce-qui-change-pour-les-voitures-electriques-des-le-1er-janvier-2027/</t>
+          <t>https://www.journaldugeek.com/2026/09/18/premieres-images-narnia-le-neveu-du-magicien-film-netflix/</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>10. Voiture</t>
+          <t>7. Video</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2026-09-18T07:00:00+00:00</t>
+          <t>2026-09-18T07:14:16+00:00</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Repérer la marque automobile au système de navigation le plus fluide : 6 démonstrations en concession</t>
+          <t>Revolut : après la fuite de données, une arnaque redoutable vise les clients</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/traceurs-gps/reperer-la-marque-automobile-au-systeme-de-navigation-le-plus-fluide-6-demonstrations-en-concession-na262029.html</t>
+          <t>https://www.01net.com/actualites/revolut-apres-fuite-donnees-arnaque-redoutable-vise-clients.html</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>10. Voiture</t>
+          <t>16. actu jur et pol</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>TomsHardware</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2026-09-18T06:55:00+00:00</t>
+          <t>2026-09-18T07:06:18+00:00</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Les premières cartes mères Z990 en vue ? Six modèles en préparation chez ASRock</t>
+          <t>Bornes de recharges : voici ce qui change pour les voitures électriques dès le 1er janvier 2027</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.fr/les-premieres-cartes-meres-z990-en-vue-six-modeles-en-preparation-chez-asrock/</t>
+          <t>https://www.journaldugeek.com/2026/09/18/bornes-de-recharges-voici-ce-qui-change-pour-les-voitures-electriques-des-le-1er-janvier-2027/</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>2. PC</t>
+          <t>10. Voiture</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2026-09-18T06:38:02+00:00</t>
+          <t>2026-09-18T07:00:00+00:00</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Des avions vont changer d’altitude pour tenter d’effacer leurs traînées du ciel</t>
+          <t>Repérer la marque automobile au système de navigation le plus fluide : 6 démonstrations en concession</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/18/des-avions-vont-changer-daltitude-pour-tenter-deffacer-leurs-trainees-du-ciel/</t>
+          <t>https://www.lesnumeriques.com/traceurs-gps/reperer-la-marque-automobile-au-systeme-de-navigation-le-plus-fluide-6-demonstrations-en-concession-na262029.html</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>9. Moiilité douce</t>
+          <t>10. Voiture</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>TomsHardware</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2026-09-18T06:37:59+00:00</t>
+          <t>2026-09-18T06:55:00+00:00</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Bose s’ouvre encore plus avec deux nouveautés oreilles libres</t>
+          <t>Les premières cartes mères Z990 en vue ? Six modèles en préparation chez ASRock</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/18/bose-souvre-encore-plus-avec-deux-nouveautes-oreilles-libres/</t>
+          <t>https://www.tomshardware.fr/les-premieres-cartes-meres-z990-en-vue-six-modeles-en-preparation-chez-asrock/</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>8. Audio</t>
+          <t>2. PC</t>
         </is>
       </c>
     </row>
@@ -6897,49 +6897,49 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2026-09-18T06:32:17+00:00</t>
+          <t>2026-09-18T06:38:02+00:00</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Claude fait le ménage dans ses onglets en fusionnant le chat et Cowork</t>
+          <t>Des avions vont changer d’altitude pour tenter d’effacer leurs traînées du ciel</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/18/claude-fait-le-menage-dans-ses-onglets-en-fusionnant-le-chat-et-cowork/</t>
+          <t>https://www.journaldugeek.com/2026/09/18/des-avions-vont-changer-daltitude-pour-tenter-deffacer-leurs-trainees-du-ciel/</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>5. Logiciels _ OS</t>
+          <t>9. Moiilité douce</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>TomsHardware</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2026-09-18T06:30:00+00:00</t>
+          <t>2026-09-18T06:37:59+00:00</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Windows 11, Office, Gemini… équipez votre PC à moindre coût en 2026</t>
+          <t>Bose s’ouvre encore plus avec deux nouveautés oreilles libres</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.fr/windows-11-office-gemini-equipez-votre-pc-a-moindre-cout-en-2026/</t>
+          <t>https://www.journaldugeek.com/2026/09/18/bose-souvre-encore-plus-avec-deux-nouveautes-oreilles-libres/</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>2. PC</t>
+          <t>8. Audio</t>
         </is>
       </c>
     </row>
@@ -6951,22 +6951,22 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>2026-09-18T06:03:54+00:00</t>
+          <t>2026-09-18T06:32:17+00:00</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Google Home ouvre la porte aux agents IA… avec un sérieux avertissement</t>
+          <t>Claude fait le ménage dans ses onglets en fusionnant le chat et Cowork</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/18/google-home-ouvre-la-porte-aux-agents-ia-avec-un-serieux-avertissement/</t>
+          <t>https://www.journaldugeek.com/2026/09/18/claude-fait-le-menage-dans-ses-onglets-en-fusionnant-le-chat-et-cowork/</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>6. IA</t>
+          <t>5. Logiciels _ OS</t>
         </is>
       </c>
     </row>
@@ -6978,49 +6978,49 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>2026-09-18T04:48:00+00:00</t>
+          <t>2026-09-18T06:30:00+00:00</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Pour les 13 ans de GTA 5, un moddeur met à jour le plugin NaturalVision</t>
+          <t>Windows 11, Office, Gemini… équipez votre PC à moindre coût en 2026</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.fr/pour-les-13-ans-de-gta-5-un-moddeur-met-a-jour-le-plugin-naturalvision/</t>
+          <t>https://www.tomshardware.fr/windows-11-office-gemini-equipez-votre-pc-a-moindre-cout-en-2026/</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>15. ludique</t>
+          <t>2. PC</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Korben</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>2026-09-17T15:15:41+00:00</t>
+          <t>2026-09-18T06:03:54+00:00</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Fugleramme - Le cadre qui dessine les oiseaux qu'il entend</t>
+          <t>Google Home ouvre la porte aux agents IA… avec un sérieux avertissement</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>https://korben.info/fugleramme-detection-oiseaux-eink.html</t>
+          <t>https://www.journaldugeek.com/2026/09/18/google-home-ouvre-la-porte-aux-agents-ia-avec-un-serieux-avertissement/</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>NON_CLASSE</t>
+          <t>6. IA</t>
         </is>
       </c>
     </row>
@@ -7032,22 +7032,22 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2026-09-17T15:01:00+00:00</t>
+          <t>2026-09-18T04:48:00+00:00</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>SteamOS : Valve s’attaque à la prise en charge des cartes Nvidia, un chantier de plusieurs années</t>
+          <t>Pour les 13 ans de GTA 5, un moddeur met à jour le plugin NaturalVision</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.fr/steamos-valve-sattaque-a-la-prise-en-charge-des-cartes-nvidia-un-chantier-de-plusieurs-annees/</t>
+          <t>https://www.tomshardware.fr/pour-les-13-ans-de-gta-5-un-moddeur-met-a-jour-le-plugin-naturalvision/</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>2. PC</t>
+          <t>15. ludique</t>
         </is>
       </c>
     </row>
@@ -7059,17 +7059,17 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>2026-09-17T14:56:31+00:00</t>
+          <t>2026-09-17T15:15:41+00:00</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>MechaCon - La puce qui condamnait les PS2 enfin hackée</t>
+          <t>Fugleramme - Le cadre qui dessine les oiseaux qu'il entend</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>https://korben.info/mechacon-ps2-craque-retro-ingenierie.html</t>
+          <t>https://korben.info/fugleramme-detection-oiseaux-eink.html</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -7081,22 +7081,22 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Korben</t>
+          <t>TomsHardware</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2026-09-17T13:40:30+00:00</t>
+          <t>2026-09-17T15:01:00+00:00</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Des agents IA spamment le web pour payer leurs propres serveurs</t>
+          <t>SteamOS : Valve s’attaque à la prise en charge des cartes Nvidia, un chantier de plusieurs années</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>https://korben.info/des-agents-ia-spamment-le-web-pour-payer-leurs-propres-serveurs.html</t>
+          <t>https://www.tomshardware.fr/steamos-valve-sattaque-a-la-prise-en-charge-des-cartes-nvidia-un-chantier-de-plusieurs-annees/</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -7113,22 +7113,22 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2026-09-17T13:26:03+00:00</t>
+          <t>2026-09-17T14:56:31+00:00</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Google Home laisse ChatGPT et Claude piloter votre maison</t>
+          <t>MechaCon - La puce qui condamnait les PS2 enfin hackée</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>https://korben.info/google-home-laisse-chatgpt-et-claude-piloter-votre-maison.html</t>
+          <t>https://korben.info/mechacon-ps2-craque-retro-ingenierie.html</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>6. IA</t>
+          <t>NON_CLASSE</t>
         </is>
       </c>
     </row>
@@ -7140,76 +7140,76 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2026-09-17T11:20:32+00:00</t>
+          <t>2026-09-17T13:40:30+00:00</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Cloudflare lance son skill d'audit de sécurité par IA</t>
+          <t>Des agents IA spamment le web pour payer leurs propres serveurs</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>https://korben.info/cloudflare-security-audit-skill.html</t>
+          <t>https://korben.info/des-agents-ia-spamment-le-web-pour-payer-leurs-propres-serveurs.html</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>6. IA</t>
+          <t>2. PC</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>TomsHardware</t>
+          <t>Korben</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>2026-09-17T10:11:00+00:00</t>
+          <t>2026-09-17T13:26:03+00:00</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Faire évoluer son installation solaire : comment ajouter une batterie sans tout changer ?</t>
+          <t>Google Home laisse ChatGPT et Claude piloter votre maison</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.fr/faire-evoluer-son-installation-solaire-comment-ajouter-une-batterie-sans-tout-changer/</t>
+          <t>https://korben.info/google-home-laisse-chatgpt-et-claude-piloter-votre-maison.html</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>8. Audio</t>
+          <t>6. IA</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>TomsHardware</t>
+          <t>Korben</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>2026-09-17T06:35:00+00:00</t>
+          <t>2026-09-17T11:20:32+00:00</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Smart Window, la fonctionnalité IA de Firefox, arrive en France avec Mistral</t>
+          <t>Cloudflare lance son skill d'audit de sécurité par IA</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.fr/smart-window-la-fonctionnalite-ia-de-firefox-arrive-en-france-avec-mistral/</t>
+          <t>https://korben.info/cloudflare-security-audit-skill.html</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>5. Logiciels _ OS</t>
+          <t>6. IA</t>
         </is>
       </c>
     </row>
@@ -7221,22 +7221,22 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>2026-09-17T05:34:00+00:00</t>
+          <t>2026-09-17T10:11:00+00:00</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Microsoft Edge peut planter si vous utilisez certaines applications</t>
+          <t>Faire évoluer son installation solaire : comment ajouter une batterie sans tout changer ?</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.fr/microsoft-edge-peut-planter-si-vous-utilisez-certaines-applications/</t>
+          <t>https://www.tomshardware.fr/faire-evoluer-son-installation-solaire-comment-ajouter-une-batterie-sans-tout-changer/</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>8. Audio</t>
         </is>
       </c>
     </row>
@@ -7248,76 +7248,76 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>2026-09-16T15:05:00+00:00</t>
+          <t>2026-09-17T06:35:00+00:00</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Le prix de ce clavier SteelSeries chute sur Amazon, c’est le moment d’en profiter</t>
+          <t>Smart Window, la fonctionnalité IA de Firefox, arrive en France avec Mistral</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.fr/le-prix-de-ce-clavier-steelseries-chute-sur-amazon-cest-le-moment-den-profiter/</t>
+          <t>https://www.tomshardware.fr/smart-window-la-fonctionnalite-ia-de-firefox-arrive-en-france-avec-mistral/</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>3. Periphérique</t>
+          <t>5. Logiciels _ OS</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Korben</t>
+          <t>TomsHardware</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>2026-09-16T13:33:01+00:00</t>
+          <t>2026-09-17T05:34:00+00:00</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Shuffle Drummer - FL Studio n'a qu'à bien se tenir</t>
+          <t>Microsoft Edge peut planter si vous utilisez certaines applications</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>https://korben.info/shuffle-drummer-groovebox-navigateur.html</t>
+          <t>https://www.tomshardware.fr/microsoft-edge-peut-planter-si-vous-utilisez-certaines-applications/</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>5. Logiciels _ OS</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Korben</t>
+          <t>TomsHardware</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>2026-09-16T07:49:19+00:00</t>
+          <t>2026-09-16T15:05:00+00:00</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Fuse-archive - Vos ZIP montés en dossiers ordinaires</t>
+          <t>Le prix de ce clavier SteelSeries chute sur Amazon, c’est le moment d’en profiter</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>https://korben.info/mount-archive-monter-archives-comme-un-dossier.html</t>
+          <t>https://www.tomshardware.fr/le-prix-de-ce-clavier-steelseries-chute-sur-amazon-cest-le-moment-den-profiter/</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>5. Logiciels _ OS</t>
+          <t>3. Periphérique</t>
         </is>
       </c>
     </row>
@@ -7329,49 +7329,49 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2026-09-16T07:35:05+00:00</t>
+          <t>2026-09-16T13:33:01+00:00</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>La Forge - Le GitLab public des profs codeurs</t>
+          <t>Shuffle Drummer - FL Studio n'a qu'à bien se tenir</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>https://korben.info/forge-apps-education-enseignants-code.html</t>
+          <t>https://korben.info/shuffle-drummer-groovebox-navigateur.html</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>NON_CLASSE</t>
+          <t>5. Logiciels _ OS</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>TomsHardware</t>
+          <t>Korben</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2026-09-16T06:47:00+00:00</t>
+          <t>2026-09-16T07:49:19+00:00</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Pourquoi décaler la sortie de l’iPhone 18 au printemps 2027 est une bonne idée ?</t>
+          <t>Fuse-archive - Vos ZIP montés en dossiers ordinaires</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.fr/pourquoi-decaler-la-sortie-de-liphone-18-au-printemps-2027-est-une-bonne-idee/</t>
+          <t>https://korben.info/mount-archive-monter-archives-comme-un-dossier.html</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>5. Logiciels _ OS</t>
         </is>
       </c>
     </row>
@@ -7383,49 +7383,49 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2026-09-15T15:43:58+00:00</t>
+          <t>2026-09-16T07:35:05+00:00</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Test d'une batterie externe et dock magnétique Antank pour Nintendo Switch 2</t>
+          <t>La Forge - Le GitLab public des profs codeurs</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>https://korben.info/test-dune-batterie-externe-et-dock-magentique-antank-pour-nintendo-switch-2.html</t>
+          <t>https://korben.info/forge-apps-education-enseignants-code.html</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>3. Periphérique</t>
+          <t>NON_CLASSE</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Korben</t>
+          <t>TomsHardware</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2026-09-15T13:53:18+00:00</t>
+          <t>2026-09-16T06:47:00+00:00</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Suyu tire sa révérence sur un mode de recompilation pour jeux Switch</t>
+          <t>Pourquoi décaler la sortie de l’iPhone 18 au printemps 2027 est une bonne idée ?</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>https://korben.info/suyu-recompilation-statique-emulation-switch.html</t>
+          <t>https://www.tomshardware.fr/pourquoi-decaler-la-sortie-de-liphone-18-au-printemps-2027-est-une-bonne-idee/</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>15. ludique</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
@@ -7437,22 +7437,22 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>2026-09-15T13:28:51+00:00</t>
+          <t>2026-09-15T15:43:58+00:00</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>CUDA-for-AMD-Windows - Le .exe NVIDIA pour votre Radeon</t>
+          <t>Test d'une batterie externe et dock magnétique Antank pour Nintendo Switch 2</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>https://korben.info/zluda-hip-cuda-radeon-windows.html</t>
+          <t>https://korben.info/test-dune-batterie-externe-et-dock-magentique-antank-pour-nintendo-switch-2.html</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>2. PC</t>
+          <t>3. Periphérique</t>
         </is>
       </c>
     </row>
@@ -7464,22 +7464,22 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2026-09-15T13:13:09+00:00</t>
+          <t>2026-09-15T13:53:18+00:00</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>OpenDisplay - Étendre l'affichage Mac avec ce que vous avez sous la main</t>
+          <t>Suyu tire sa révérence sur un mode de recompilation pour jeux Switch</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>https://korben.info/opendisplay-ecran-secondaire-iphone-ipad-mac.html</t>
+          <t>https://korben.info/suyu-recompilation-statique-emulation-switch.html</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>15. ludique</t>
         </is>
       </c>
     </row>
@@ -7491,22 +7491,22 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>2026-09-15T11:49:03+00:00</t>
+          <t>2026-09-15T13:28:51+00:00</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Windows 11 - Un clic sur le bon lien et hop, vous avez un compte local</t>
+          <t>CUDA-for-AMD-Windows - Le .exe NVIDIA pour votre Radeon</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>https://korben.info/bypass-compte-microsoft-windows-11.html</t>
+          <t>https://korben.info/zluda-hip-cuda-radeon-windows.html</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>5. Logiciels _ OS</t>
+          <t>2. PC</t>
         </is>
       </c>
     </row>
@@ -7518,22 +7518,22 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>2026-09-15T08:16:10+00:00</t>
+          <t>2026-09-15T13:13:09+00:00</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Kits IA Korben - Des tutos pour vos agents IA</t>
+          <t>OpenDisplay - Étendre l'affichage Mac avec ce que vous avez sous la main</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>https://korben.info/kits-ia-korben-tutos-agents-ia.html</t>
+          <t>https://korben.info/opendisplay-ecran-secondaire-iphone-ipad-mac.html</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>6. IA</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
@@ -7545,22 +7545,22 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2026-09-15T08:00:00+00:00</t>
+          <t>2026-09-15T11:49:03+00:00</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>TP-Link Deco BE25-5G - Le routeur qui garde la maison</t>
+          <t>Windows 11 - Un clic sur le bon lien et hop, vous avez un compte local</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>https://korben.info/deco-be25-5g-test.html</t>
+          <t>https://korben.info/bypass-compte-microsoft-windows-11.html</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>5. Logiciels _ OS</t>
         </is>
       </c>
     </row>
@@ -7572,22 +7572,22 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2026-09-15T07:23:22+00:00</t>
+          <t>2026-09-15T08:16:10+00:00</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>GNOME Boxes - L'outil qui monte les VM à votre place</t>
+          <t>Kits IA Korben - Des tutos pour vos agents IA</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>https://korben.info/gnome-boxes-virtualisation-simple-linux.html</t>
+          <t>https://korben.info/kits-ia-korben-tutos-agents-ia.html</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>5. Logiciels _ OS</t>
+          <t>6. IA</t>
         </is>
       </c>
     </row>
@@ -7599,22 +7599,22 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>2026-09-15T06:53:24+00:00</t>
+          <t>2026-09-15T08:00:00+00:00</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>SpruceOS - Le guide pour rhabiller votre console rétro</t>
+          <t>TP-Link Deco BE25-5G - Le routeur qui garde la maison</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>https://korben.info/spruceos-guide-installation-console-retro.html</t>
+          <t>https://korben.info/deco-be25-5g-test.html</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>15. ludique</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
@@ -7626,22 +7626,22 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>2026-09-14T15:10:49+00:00</t>
+          <t>2026-09-15T07:23:22+00:00</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Test Thermal Master P3 : voir ce qui chauffe avec son smartphone</t>
+          <t>GNOME Boxes - L'outil qui monte les VM à votre place</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>https://korben.info/test-thermal-master-p3-voir-ce-qui-chauffe-avec-son-smartphone.html</t>
+          <t>https://korben.info/gnome-boxes-virtualisation-simple-linux.html</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>5. Logiciels _ OS</t>
         </is>
       </c>
     </row>
@@ -7653,22 +7653,22 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>2026-09-14T13:33:00+00:00</t>
+          <t>2026-09-15T06:53:24+00:00</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Antro pique ?</t>
+          <t>SpruceOS - Le guide pour rhabiller votre console rétro</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>https://korben.info/test-antro-avis.html</t>
+          <t>https://korben.info/spruceos-guide-installation-console-retro.html</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>NON_CLASSE</t>
+          <t>15. ludique</t>
         </is>
       </c>
     </row>
@@ -7680,22 +7680,22 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>2026-09-14T09:14:55+00:00</t>
+          <t>2026-09-14T15:10:49+00:00</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Tomb Raider peut tourner sur un ESP32-P4</t>
+          <t>Test Thermal Master P3 : voir ce qui chauffe avec son smartphone</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>https://korben.info/tomb-raider-peut-tourner-sur-un-esp32-p4.html</t>
+          <t>https://korben.info/test-thermal-master-p3-voir-ce-qui-chauffe-avec-son-smartphone.html</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>NON_CLASSE</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
@@ -7707,22 +7707,22 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>2026-09-14T08:30:00+00:00</t>
+          <t>2026-09-14T13:33:00+00:00</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Apple Configurator - Pour transformer votre iPhone en Dumbphone</t>
+          <t>Antro pique ?</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>https://korben.info/apple-configurator-iphone-dumbphone-temps-ecran.html</t>
+          <t>https://korben.info/test-antro-avis.html</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>NON_CLASSE</t>
         </is>
       </c>
     </row>
@@ -7734,22 +7734,22 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>2026-09-14T07:42:28+00:00</t>
+          <t>2026-09-14T09:14:55+00:00</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>CanoFlash - Du Wi-Fi sur votre GBA (mais pas pour jouer, snif)</t>
+          <t>Tomb Raider peut tourner sur un ESP32-P4</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>https://korben.info/gba-link-cable-internet-esp32.html</t>
+          <t>https://korben.info/tomb-raider-peut-tourner-sur-un-esp32-p4.html</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>3. Periphérique</t>
+          <t>NON_CLASSE</t>
         </is>
       </c>
     </row>
@@ -7761,22 +7761,22 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>2026-09-11T10:00:00+00:00</t>
+          <t>2026-09-14T08:30:00+00:00</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>OmniVoice - Clonez votre propre voix en local et en français</t>
+          <t>Apple Configurator - Pour transformer votre iPhone en Dumbphone</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>https://korben.info/omnivoice-clonage-voix.html</t>
+          <t>https://korben.info/apple-configurator-iphone-dumbphone-temps-ecran.html</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>8. Audio</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
@@ -7788,22 +7788,22 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>2026-09-11T09:52:43+00:00</t>
+          <t>2026-09-14T07:42:28+00:00</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Le Deathray - Le shader WebGPU qui fait redémarrer votre Mac</t>
+          <t>CanoFlash - Du Wi-Fi sur votre GBA (mais pas pour jouer, snif)</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>https://korben.info/webgpu-deathray-freeze-mac.html</t>
+          <t>https://korben.info/gba-link-cable-internet-esp32.html</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>NON_CLASSE</t>
+          <t>3. Periphérique</t>
         </is>
       </c>
     </row>
@@ -7815,22 +7815,22 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>2026-09-11T07:19:00+00:00</t>
+          <t>2026-09-11T10:00:00+00:00</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Trynix - Testez des classiques Linux sans rien installer</t>
+          <t>OmniVoice - Clonez votre propre voix en local et en français</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>https://korben.info/trynix-tester-paquet-nix-navigateur.html</t>
+          <t>https://korben.info/omnivoice-clonage-voix.html</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>5. Logiciels _ OS</t>
+          <t>8. Audio</t>
         </is>
       </c>
     </row>
@@ -7842,22 +7842,22 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>2026-09-11T07:00:00+00:00</t>
+          <t>2026-09-11T09:52:43+00:00</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Pluton - Le backup chiffré qui se pilote depuis le navigateur</t>
+          <t>Le Deathray - Le shader WebGPU qui fait redémarrer votre Mac</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>https://korben.info/pluton-backup-self-hosted-chiffre-restic-rclone.html</t>
+          <t>https://korben.info/webgpu-deathray-freeze-mac.html</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>5. Logiciels _ OS</t>
+          <t>NON_CLASSE</t>
         </is>
       </c>
     </row>
@@ -7869,22 +7869,22 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>2026-09-11T06:15:54+00:00</t>
+          <t>2026-09-11T07:19:00+00:00</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>ReProgman - L'interface de Windows 3.1 sur PC et Mac</t>
+          <t>Trynix - Testez des classiques Linux sans rien installer</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>https://korben.info/windows-31-shell-vibe-code-claude.html</t>
+          <t>https://korben.info/trynix-tester-paquet-nix-navigateur.html</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>2. PC</t>
+          <t>5. Logiciels _ OS</t>
         </is>
       </c>
     </row>
@@ -7896,22 +7896,22 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>2026-09-11T04:59:04+00:00</t>
+          <t>2026-09-11T07:00:00+00:00</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Super Mario 64 tourne sur un processeur ARM (avec ReactOS)</t>
+          <t>Pluton - Le backup chiffré qui se pilote depuis le navigateur</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>https://korben.info/reactos-arm64-fex-jeux-windows.html</t>
+          <t>https://korben.info/pluton-backup-self-hosted-chiffre-restic-rclone.html</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>2. PC</t>
+          <t>5. Logiciels _ OS</t>
         </is>
       </c>
     </row>
@@ -7923,22 +7923,22 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>2026-09-10T13:52:44+00:00</t>
+          <t>2026-09-11T06:15:54+00:00</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Ce que les IA d'OpenAI se sont raconté en se croyant seules</t>
+          <t>ReProgman - L'interface de Windows 3.1 sur PC et Mac</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>https://korben.info/agents-ia-organisation-wiki-allemand.html</t>
+          <t>https://korben.info/windows-31-shell-vibe-code-claude.html</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>6. IA</t>
+          <t>2. PC</t>
         </is>
       </c>
     </row>
@@ -7950,22 +7950,22 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>2026-09-10T11:04:19+00:00</t>
+          <t>2026-09-11T04:59:04+00:00</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>RistOS - L'Android sans applis dont le cerveau reste chez vous</t>
+          <t>Super Mario 64 tourne sur un processeur ARM (avec ReactOS)</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>https://korben.info/rist-os-handset-android-degoogle.html</t>
+          <t>https://korben.info/reactos-arm64-fex-jeux-windows.html</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>2. PC</t>
         </is>
       </c>
     </row>
@@ -7977,22 +7977,22 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>2026-09-10T08:15:16+00:00</t>
+          <t>2026-09-10T13:52:44+00:00</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Une faille cPanel distribue des accès root</t>
+          <t>Ce que les IA d'OpenAI se sont raconté en se croyant seules</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>https://korben.info/cpanel-faille-prise-controle-compte-hebergement.html</t>
+          <t>https://korben.info/agents-ia-organisation-wiki-allemand.html</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>5. Logiciels _ OS</t>
+          <t>6. IA</t>
         </is>
       </c>
     </row>
@@ -8004,22 +8004,22 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>2026-09-10T04:56:34+00:00</t>
+          <t>2026-09-10T11:04:19+00:00</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Un seul abonnement Surfshark, une infinité d'appareils protégés pour la rentrée</t>
+          <t>RistOS - L'Android sans applis dont le cerveau reste chez vous</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>https://korben.info/un-seul-abonnement-surfshark.html</t>
+          <t>https://korben.info/rist-os-handset-android-degoogle.html</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>5. Logiciels _ OS</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
@@ -8031,68 +8031,76 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>2026-09-09T13:07:21+00:00</t>
+          <t>2026-09-10T08:15:16+00:00</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Mettez à jour Plex ! (même sans savoir contre quoi)</t>
+          <t>Une faille cPanel distribue des accès root</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>https://korben.info/plex-serveurs-non-patches-failles.html</t>
+          <t>https://korben.info/cpanel-faille-prise-controle-compte-hebergement.html</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>2. PC</t>
+          <t>5. Logiciels _ OS</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Frandroid - Actualités</t>
-        </is>
-      </c>
-      <c r="B283" t="inlineStr"/>
+          <t>Korben</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>2026-09-10T04:56:34+00:00</t>
+        </is>
+      </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Pas de facture mobile avant 2027 : La Poste Mobile offre 4 mois gratuits sur ses forfaits 5G</t>
+          <t>Un seul abonnement Surfshark, une infinité d'appareils protégés pour la rentrée</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>https://native.humanoid.fr/register-click?s_id=2&amp;sp_id=47&amp;c_id=4224</t>
+          <t>https://korben.info/un-seul-abonnement-surfshark.html</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>19. Sponso</t>
+          <t>5. Logiciels _ OS</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Frandroid - Actualités</t>
-        </is>
-      </c>
-      <c r="B284" t="inlineStr"/>
+          <t>Korben</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>2026-09-09T13:07:21+00:00</t>
+        </is>
+      </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>TCL 24G645 : ce moniteur gaming QD-Mini LED en 300 Hz passe sous les 230 euros</t>
+          <t>Mettez à jour Plex ! (même sans savoir contre quoi)</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/bons-plans/3253289_tcl-24g645-ce-moniteur-gaming-qd-mini-led-en-300-hz-passe-sous-les-230-euros</t>
+          <t>https://korben.info/plex-serveurs-non-patches-failles.html</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>3. Periphérique</t>
+          <t>2. PC</t>
         </is>
       </c>
     </row>
@@ -8105,12 +8113,12 @@
       <c r="B285" t="inlineStr"/>
       <c r="C285" t="inlineStr">
         <is>
-          <t>On a trouvé le gadget pas cher qui transforme vos photos de smartphone en autocollants</t>
+          <t>Pas de facture mobile avant 2027 : La Poste Mobile offre 4 mois gratuits sur ses forfaits 5G</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/bons-plans/3253177_on-a-trouve-le-gadget-pas-cher-qui-transforme-vos-photos-de-smartphone-en-autocollants</t>
+          <t>https://native.humanoid.fr/register-click?s_id=2&amp;sp_id=47&amp;c_id=4224</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -8128,17 +8136,17 @@
       <c r="B286" t="inlineStr"/>
       <c r="C286" t="inlineStr">
         <is>
-          <t>C’est le retour des PC portables sous RTX 5060 à moins de 1 000 € grâce à cette offre Boulanger</t>
+          <t>TCL 24G645 : ce moniteur gaming QD-Mini LED en 300 Hz passe sous les 230 euros</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/bons-plans/2804177_cest-le-retour-des-pc-portables-sous-rtx-5060-a-moins-de-1-000-euros-grace-a-cette-offre-boulanger</t>
+          <t>https://www.frandroid.com/bons-plans/3253289_tcl-24g645-ce-moniteur-gaming-qd-mini-led-en-300-hz-passe-sous-les-230-euros</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>2. PC</t>
+          <t>3. Periphérique</t>
         </is>
       </c>
     </row>
@@ -8151,17 +8159,17 @@
       <c r="B287" t="inlineStr"/>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Un grand TV QD Mini-LED avec Philips Ambilight à moins de 700 €, ça se regarde de près</t>
+          <t>On a trouvé le gadget pas cher qui transforme vos photos de smartphone en autocollants</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/bons-plans/3252877_un-grand-tv-qd-mini-led-avec-philips-ambilight-a-moins-de-700-e-ca-se-regarde-de-pres</t>
+          <t>https://www.frandroid.com/bons-plans/3253177_on-a-trouve-le-gadget-pas-cher-qui-transforme-vos-photos-de-smartphone-en-autocollants</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>7. Video</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
@@ -8174,17 +8182,17 @@
       <c r="B288" t="inlineStr"/>
       <c r="C288" t="inlineStr">
         <is>
-          <t>JBL Tune 730BT : ce casque sans fil à 76 h d’autonomie tombe à moins de 40 euros</t>
+          <t>C’est le retour des PC portables sous RTX 5060 à moins de 1 000 € grâce à cette offre Boulanger</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/bons-plans/3252609_jbl-tune-730bt-ce-casque-sans-fil-a-76-h-dautonomie-tombe-a-moins-de-40-euros</t>
+          <t>https://www.frandroid.com/bons-plans/2804177_cest-le-retour-des-pc-portables-sous-rtx-5060-a-moins-de-1-000-euros-grace-a-cette-offre-boulanger</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>8. Audio</t>
+          <t>2. PC</t>
         </is>
       </c>
     </row>
@@ -8197,17 +8205,17 @@
       <c r="B289" t="inlineStr"/>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Le Dyson Humidify+Cool PH2 De‑Nox en promo à -200 € : un appareil 3-en-1 pensé pour l’air sec et pollué</t>
+          <t>Un grand TV QD Mini-LED avec Philips Ambilight à moins de 700 €, ça se regarde de près</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/bons-plans/3252243_le-dyson-humidifycool-ph2-de-nox-en-promo-a-200-e-un-appareil-3-en-1-pense-pour-lair-sec-et-pollue</t>
+          <t>https://www.frandroid.com/bons-plans/3252877_un-grand-tv-qd-mini-led-avec-philips-ambilight-a-moins-de-700-e-ca-se-regarde-de-pres</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>11. Menage</t>
+          <t>7. Video</t>
         </is>
       </c>
     </row>
@@ -8220,17 +8228,17 @@
       <c r="B290" t="inlineStr"/>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Samsung The Frame 65 pouces (2025) à seulement 999 € chez Boulanger : une belle affaire pour ce TV QLED 4K</t>
+          <t>JBL Tune 730BT : ce casque sans fil à 76 h d’autonomie tombe à moins de 40 euros</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/bons-plans/3252161_samsung-the-frame-65-pouces-2025-a-seulement-999-e-chez-boulanger-une-belle-affaire-pour-ce-tv-qled-4k</t>
+          <t>https://www.frandroid.com/bons-plans/3252609_jbl-tune-730bt-ce-casque-sans-fil-a-76-h-dautonomie-tombe-a-moins-de-40-euros</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>7. Video</t>
+          <t>8. Audio</t>
         </is>
       </c>
     </row>
@@ -8243,17 +8251,17 @@
       <c r="B291" t="inlineStr"/>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Vos DONNÉES ont FUITÉ : voici ce qu’il faut faire !</t>
+          <t>Le Dyson Humidify+Cool PH2 De‑Nox en promo à -200 € : un appareil 3-en-1 pensé pour l’air sec et pollué</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/video/3253483_video</t>
+          <t>https://www.frandroid.com/bons-plans/3252243_le-dyson-humidifycool-ph2-de-nox-en-promo-a-200-e-un-appareil-3-en-1-pense-pour-lair-sec-et-pollue</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>7. Video</t>
+          <t>11. Menage</t>
         </is>
       </c>
     </row>
@@ -8266,63 +8274,63 @@
       <c r="B292" t="inlineStr"/>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Ce qu’il faut retenir des tests de l’iPhone 18 Pro !</t>
+          <t>Samsung The Frame 65 pouces (2025) à seulement 999 € chez Boulanger : une belle affaire pour ce TV QLED 4K</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/video/3252919_video</t>
+          <t>https://www.frandroid.com/bons-plans/3252161_samsung-the-frame-65-pouces-2025-a-seulement-999-e-chez-boulanger-une-belle-affaire-pour-ce-tv-qled-4k</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>7. Video</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Frandroid - Bons plans</t>
+          <t>Frandroid - Actualités</t>
         </is>
       </c>
       <c r="B293" t="inlineStr"/>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Ã peine sorti, le nouveau Xiaomi Redmi Note 17 Pro 5G est dÃ©jÃ  Ã  moitiÃ© prix grÃ¢ce Ã  cette offre</t>
+          <t>Vos DONNÉES ont FUITÉ : voici ce qu’il faut faire !</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/bons-plans/3252177_a-peine-sorti-le-nouveau-xiaomi-redmi-note-17-pro-5g-est-deja-a-moitie-prix-grace-a-cette-offre</t>
+          <t>https://www.frandroid.com/video/3253483_video</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>7. Video</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Frandroid - Bons plans</t>
+          <t>Frandroid - Actualités</t>
         </is>
       </c>
       <c r="B294" t="inlineStr"/>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Amazon brade le clavier gamer haut de gamme Ã  Rapid Trigger de Razer, le Huntsman V3 Pro TKL</t>
+          <t>Ce qu’il faut retenir des tests de l’iPhone 18 Pro !</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/bons-plans/3252199_amazon-brade-le-clavier-gamer-haut-de-gamme-a-rapid-trigger-de-razer-le-huntsman-v3-pro-tkl</t>
+          <t>https://www.frandroid.com/video/3252919_video</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>3. Periphérique</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
@@ -8335,17 +8343,17 @@
       <c r="B295" t="inlineStr"/>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Ce ventilateur Shark rafraÃ®chit l’air jusqu’Ã  6 Â°C et coÃ»te 110 â¬ de moins avec cette offre</t>
+          <t>Ã peine sorti, le nouveau Xiaomi Redmi Note 17 Pro 5G est dÃ©jÃ  Ã  moitiÃ© prix grÃ¢ce Ã  cette offre</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/bons-plans/3246361_ce-ventilateur-shark-rafraichit-lair-jusqua-6-c-et-coute-110-euros-de-moins-avec-cette-offre</t>
+          <t>https://www.frandroid.com/bons-plans/3252177_a-peine-sorti-le-nouveau-xiaomi-redmi-note-17-pro-5g-est-deja-a-moitie-prix-grace-a-cette-offre</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>11. Menage</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
@@ -8358,17 +8366,17 @@
       <c r="B296" t="inlineStr"/>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Ce robot tondeuse 4×4 capable de grimper des pentes Ã  80 % est bradÃ© Ã  un super prix sur Amazon</t>
+          <t>Amazon brade le clavier gamer haut de gamme Ã  Rapid Trigger de Razer, le Huntsman V3 Pro TKL</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/bons-plans/3251737_ce-robot-tondeuse-4x4-capable-de-grimper-des-pentes-a-80-est-brade-a-un-super-prix-sur-amazon</t>
+          <t>https://www.frandroid.com/bons-plans/3252199_amazon-brade-le-clavier-gamer-haut-de-gamme-a-rapid-trigger-de-razer-le-huntsman-v3-pro-tkl</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>13. Maison</t>
+          <t>3. Periphérique</t>
         </is>
       </c>
     </row>
@@ -8381,17 +8389,17 @@
       <c r="B297" t="inlineStr"/>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Cet ultrabook d’Acer (Intel Core 5, 16 Go de RAM), avec une sacoche et une souris offertes, est dispo pour 200 â¬ de moins</t>
+          <t>Ce ventilateur Shark rafraÃ®chit l’air jusqu’Ã  6 Â°C et coÃ»te 110 â¬ de moins avec cette offre</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/bons-plans/3251595_cet-ultrabook-dacer-intel-core-5-16-go-de-ram-avec-une-sacoche-et-une-souris-offertes-est-dispo-pour-200-e-de-moins</t>
+          <t>https://www.frandroid.com/bons-plans/3246361_ce-ventilateur-shark-rafraichit-lair-jusqua-6-c-et-coute-110-euros-de-moins-avec-cette-offre</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>2. PC</t>
+          <t>11. Menage</t>
         </is>
       </c>
     </row>
@@ -8404,17 +8412,17 @@
       <c r="B298" t="inlineStr"/>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Ecovacs Deebot X12 OmniCyclone : ce robot aspirateur capable de franchir des marches perd plus de 500 â¬ sur Amazon</t>
+          <t>Ce robot tondeuse 4×4 capable de grimper des pentes Ã  80 % est bradÃ© Ã  un super prix sur Amazon</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/bons-plans/3251753_ecovacs-deebot-x12-omnicyclone-ce-robot-aspirateur-capable-de-franchir-des-marches-perd-plus-de-500-e-sur-amazon</t>
+          <t>https://www.frandroid.com/bons-plans/3251737_ce-robot-tondeuse-4x4-capable-de-grimper-des-pentes-a-80-est-brade-a-un-super-prix-sur-amazon</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>11. Menage</t>
+          <t>13. Maison</t>
         </is>
       </c>
     </row>
@@ -8427,17 +8435,17 @@
       <c r="B299" t="inlineStr"/>
       <c r="C299" t="inlineStr">
         <is>
-          <t>La bague connectÃ©e Oura Ring 4 revient Ã  un super prix : une bonne affaire malgrÃ© la sortie du nouveau modÃ¨le ?</t>
+          <t>Cet ultrabook d’Acer (Intel Core 5, 16 Go de RAM), avec une sacoche et une souris offertes, est dispo pour 200 â¬ de moins</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/bons-plans/3190627_la-bague-connectee-oura-ring-4-revient-a-un-super-prix-une-bonne-affaire-malgre-la-sortie-du-nouveau-modele</t>
+          <t>https://www.frandroid.com/bons-plans/3251595_cet-ultrabook-dacer-intel-core-5-16-go-de-ram-avec-une-sacoche-et-une-souris-offertes-est-dispo-pour-200-e-de-moins</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>14. Santé</t>
+          <t>2. PC</t>
         </is>
       </c>
     </row>
@@ -8450,17 +8458,17 @@
       <c r="B300" t="inlineStr"/>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Bambu Lab lance la H2C, son imprimante 3D anti-gaspillage, dÃ©jÃ  Ã  -150 â¬</t>
+          <t>Ecovacs Deebot X12 OmniCyclone : ce robot aspirateur capable de franchir des marches perd plus de 500 â¬ sur Amazon</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/bons-plans/3251523_bambu-lab-lance-la-h2c-son-imprimante-3d-anti-gaspillage-deja-a-150-e</t>
+          <t>https://www.frandroid.com/bons-plans/3251753_ecovacs-deebot-x12-omnicyclone-ce-robot-aspirateur-capable-de-franchir-des-marches-perd-plus-de-500-e-sur-amazon</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>3. Periphérique</t>
+          <t>11. Menage</t>
         </is>
       </c>
     </row>
@@ -8473,63 +8481,63 @@
       <c r="B301" t="inlineStr"/>
       <c r="C301" t="inlineStr">
         <is>
-          <t>On a trouvÃ© une montre Wear OS complÃ¨te pour le prix d’un bracelet connectÃ©</t>
+          <t>La bague connectÃ©e Oura Ring 4 revient Ã  un super prix : une bonne affaire malgrÃ© la sortie du nouveau modÃ¨le ?</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/bons-plans/3251519_on-a-trouve-une-montre-wear-os-complete-pour-le-prix-dun-bracelet-connecte</t>
+          <t>https://www.frandroid.com/bons-plans/3190627_la-bague-connectee-oura-ring-4-revient-a-un-super-prix-une-bonne-affaire-malgre-la-sortie-du-nouveau-modele</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>5. Logiciels _ OS</t>
+          <t>14. Santé</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Frandroid - Actualités</t>
+          <t>Frandroid - Bons plans</t>
         </is>
       </c>
       <c r="B302" t="inlineStr"/>
       <c r="C302" t="inlineStr">
         <is>
-          <t>BNP Paribas propose un prêt étudiant à 0,99 % TAEG pour la rentrée 2026</t>
+          <t>Bambu Lab lance la H2C, son imprimante 3D anti-gaspillage, dÃ©jÃ  Ã  -150 â¬</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>https://native.humanoid.fr/register-click?s_id=2&amp;sp_id=47&amp;c_id=4220</t>
+          <t>https://www.frandroid.com/bons-plans/3251523_bambu-lab-lance-la-h2c-son-imprimante-3d-anti-gaspillage-deja-a-150-e</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>NON_CLASSE</t>
+          <t>3. Periphérique</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Frandroid - Actualités</t>
+          <t>Frandroid - Bons plans</t>
         </is>
       </c>
       <c r="B303" t="inlineStr"/>
       <c r="C303" t="inlineStr">
         <is>
-          <t>French Days : le nec plus ultra des aspirateurs Roborock s’effondre de 300 €</t>
+          <t>On a trouvÃ© une montre Wear OS complÃ¨te pour le prix d’un bracelet connectÃ©</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>https://native.humanoid.fr/register-click?s_id=2&amp;sp_id=47&amp;c_id=4217</t>
+          <t>https://www.frandroid.com/bons-plans/3251519_on-a-trouve-une-montre-wear-os-complete-pour-le-prix-dun-bracelet-connecte</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>11. Menage</t>
+          <t>5. Logiciels _ OS</t>
         </is>
       </c>
     </row>
@@ -8542,17 +8550,17 @@
       <c r="B304" t="inlineStr"/>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Cette box fibre à moins de 25 € par mois mise sur le Wi-Fi 7 et un prix qui ne bouge pas</t>
+          <t>BNP Paribas propose un prêt étudiant à 0,99 % TAEG pour la rentrée 2026</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>https://native.humanoid.fr/register-click?s_id=2&amp;sp_id=47&amp;c_id=4225</t>
+          <t>https://native.humanoid.fr/register-click?s_id=2&amp;sp_id=47&amp;c_id=4220</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>3. Periphérique</t>
+          <t>NON_CLASSE</t>
         </is>
       </c>
     </row>
@@ -8565,15 +8573,61 @@
       <c r="B305" t="inlineStr"/>
       <c r="C305" t="inlineStr">
         <is>
+          <t>French Days : le nec plus ultra des aspirateurs Roborock s’effondre de 300 €</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>https://native.humanoid.fr/register-click?s_id=2&amp;sp_id=47&amp;c_id=4217</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>11. Menage</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Frandroid - Actualités</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr"/>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Cette box fibre à moins de 25 € par mois mise sur le Wi-Fi 7 et un prix qui ne bouge pas</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>https://native.humanoid.fr/register-click?s_id=2&amp;sp_id=47&amp;c_id=4225</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>3. Periphérique</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Frandroid - Actualités</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr"/>
+      <c r="C307" t="inlineStr">
+        <is>
           <t>ASUS baisse le prix de ses Zenbook et PC gaming pour la rentrée 2026 : jusqu’à 600 € de réduction</t>
         </is>
       </c>
-      <c r="D305" t="inlineStr">
+      <c r="D307" t="inlineStr">
         <is>
           <t>https://native.humanoid.fr/register-click?s_id=2&amp;sp_id=47&amp;c_id=4223</t>
         </is>
       </c>
-      <c r="E305" t="inlineStr">
+      <c r="E307" t="inlineStr">
         <is>
           <t>2. PC</t>
         </is>
@@ -9291,7 +9345,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9329,17 +9383,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:17:00+00:00</t>
+          <t>2026-09-19T22:00:03+00:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Actualité : Airfryer : comment la cuisson sans huile a fini par me refroidir</t>
+          <t>Actualité : Bon plan – La machine à café automatique avec broyeur Delonghi Magnifica Evo Next "5 étoiles" à 468,69 € (-21%)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/airfryer/airfryer-comment-la-cuisson-sans-huile-a-fini-par-me-refroidir-n224064.html</t>
+          <t>https://www.lesnumeriques.com/machine-a-cafe-automatique/bon-plan-la-machine-a-cafe-automatique-avec-broyeur-delonghi-magnifica-evo-next-5-etoiles-a-468-69-21-n262067.html</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -9356,17 +9410,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-19T06:45:00+00:00</t>
+          <t>2026-09-19T12:17:00+00:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Actualité : On l'attendait : Jura dévoile enfin sa machine avec broyeur ultra-compacte et sans compromis</t>
+          <t>Actualité : Airfryer : comment la cuisson sans huile a fini par me refroidir</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/machine-a-cafe-automatique/on-l-attendait-jura-devoile-enfin-sa-machine-avec-broyeur-ultra-compacte-et-sans-compromis-n262037.html</t>
+          <t>https://www.lesnumeriques.com/airfryer/airfryer-comment-la-cuisson-sans-huile-a-fini-par-me-refroidir-n224064.html</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -9383,17 +9437,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-19T05:15:02+00:00</t>
+          <t>2026-09-19T06:45:00+00:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Top bon plan : Samsung, Delonghi, SwitchBot... les meilleurs bons plans du 19/09/2026</t>
+          <t>Actualité : On l'attendait : Jura dévoile enfin sa machine avec broyeur ultra-compacte et sans compromis</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/societe-numerique/samsung-switchbot-les-meilleurs-bons-plans-du-19-09-2026-n262050.html</t>
+          <t>https://www.lesnumeriques.com/machine-a-cafe-automatique/on-l-attendait-jura-devoile-enfin-sa-machine-avec-broyeur-ultra-compacte-et-sans-compromis-n262037.html</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -9410,17 +9464,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-19T05:01:03+00:00</t>
+          <t>2026-09-19T05:15:02+00:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Actualité : Bon plan – La machine à café automatique avec broyeur Delonghi Magnifica Evo Next "5 étoiles" à 468,69 € (-21%)</t>
+          <t>Top bon plan : Samsung, Delonghi, SwitchBot... les meilleurs bons plans du 19/09/2026</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/machine-a-cafe-automatique/bon-plan-la-machine-a-cafe-automatique-avec-broyeur-delonghi-magnifica-evo-next-5-etoiles-a-468-69-21-n262052.html</t>
+          <t>https://www.lesnumeriques.com/societe-numerique/samsung-switchbot-les-meilleurs-bons-plans-du-19-09-2026-n262050.html</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -9432,22 +9486,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-18T16:30:35+00:00</t>
+          <t>2026-09-19T05:01:03+00:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Test du Ninja Crispi DualZone : l’airfryer en verre XXL qui remplace notre four</t>
+          <t>Actualité : Bon plan – La machine à café automatique avec broyeur Delonghi Magnifica Evo Next "5 étoiles" à 468,69 € (-21%)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/test/test-du-ninja-crispi-dualzone-lairfryer-en-verre-xxl-qui-remplace-notre-four/</t>
+          <t>https://www.lesnumeriques.com/machine-a-cafe-automatique/bon-plan-la-machine-a-cafe-automatique-avec-broyeur-delonghi-magnifica-evo-next-5-etoiles-a-468-69-21-n262052.html</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -9459,22 +9513,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Korben</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-18T08:07:06+00:00</t>
+          <t>2026-09-18T16:30:35+00:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Mes 2 nouveaux interrupteurs Sonoff Zigbee</t>
+          <t>Test du Ninja Crispi DualZone : l’airfryer en verre XXL qui remplace notre four</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://korben.info/sonoff-volet-lumiere-zigbee-bureau.html</t>
+          <t>https://www.journaldugeek.com/test/test-du-ninja-crispi-dualzone-lairfryer-en-verre-xxl-qui-remplace-notre-four/</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -9486,25 +9540,52 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>Korben</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-09-18T08:07:06+00:00</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Mes 2 nouveaux interrupteurs Sonoff Zigbee</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://korben.info/sonoff-volet-lumiere-zigbee-bureau.html</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>12. Cuisine</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>LesNumeriques</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>2026-09-18T08:00:00+00:00</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>SharkNinja Crispi DualZone, un Airfryer avec deux compartiments pour préparer un repas complet en une seule fois</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>https://www.lesnumeriques.com/electromenager/sharkninja-crispi-dualzone-un-airfryer-avec-deux-compartiments-pour-preparer-un-repas-complet-en-une-seule-fois-na261964.html</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>12. Cuisine</t>
         </is>
@@ -11001,7 +11082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E69"/>
+  <dimension ref="A1:E70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12795,12 +12876,12 @@
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr">
         <is>
-          <t>On a trouvé le gadget pas cher qui transforme vos photos de smartphone en autocollants</t>
+          <t>Pas de facture mobile avant 2027 : La Poste Mobile offre 4 mois gratuits sur ses forfaits 5G</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/bons-plans/3253177_on-a-trouve-le-gadget-pas-cher-qui-transforme-vos-photos-de-smartphone-en-autocollants</t>
+          <t>https://native.humanoid.fr/register-click?s_id=2&amp;sp_id=47&amp;c_id=4224</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -12818,12 +12899,12 @@
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Ce qu’il faut retenir des tests de l’iPhone 18 Pro !</t>
+          <t>On a trouvé le gadget pas cher qui transforme vos photos de smartphone en autocollants</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/video/3252919_video</t>
+          <t>https://www.frandroid.com/bons-plans/3253177_on-a-trouve-le-gadget-pas-cher-qui-transforme-vos-photos-de-smartphone-en-autocollants</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -12835,21 +12916,44 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Frandroid - Bons plans</t>
+          <t>Frandroid - Actualités</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr">
         <is>
+          <t>Ce qu’il faut retenir des tests de l’iPhone 18 Pro !</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>https://www.frandroid.com/video/3252919_video</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>1. SMARTPHONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Frandroid - Bons plans</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr"/>
+      <c r="C70" t="inlineStr">
+        <is>
           <t>Ã peine sorti, le nouveau Xiaomi Redmi Note 17 Pro 5G est dÃ©jÃ  Ã  moitiÃ© prix grÃ¢ce Ã  cette offre</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t>https://www.frandroid.com/bons-plans/3252177_a-peine-sorti-le-nouveau-xiaomi-redmi-note-17-pro-5g-est-deja-a-moitie-prix-grace-a-cette-offre</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="E70" t="inlineStr">
         <is>
           <t>1. SMARTPHONE</t>
         </is>
@@ -12904,17 +13008,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-19T08:00:03+00:00</t>
+          <t>2026-09-19T22:00:03+00:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Actualité : Les codes promo les plus utilisés de la semaine</t>
+          <t>Actualité : Bon plan – Le compact / bridge Sony ZV-1 Seul à 630,85 € (-21%)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/societe-numerique/les-codes-promo-les-plus-utilises-de-la-semaine-n262059.html</t>
+          <t>https://www.lesnumeriques.com/compact-bridge/bon-plan-le-compact-bridge-sony-zv-1-seul-a-630-85-21-n262068.html</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -12931,17 +13035,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-19T06:27:02+00:00</t>
+          <t>2026-09-19T08:00:03+00:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Actualité : Bon plan – Le compact / bridge Sony ZV-1 Seul à 630,85 € (-21%)</t>
+          <t>Actualité : Les codes promo les plus utilisés de la semaine</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/compact-bridge/bon-plan-le-compact-bridge-sony-zv-1-seul-a-630-85-21-n262057.html</t>
+          <t>https://www.lesnumeriques.com/societe-numerique/les-codes-promo-les-plus-utilises-de-la-semaine-n262059.html</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -12953,22 +13057,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>KultureGeek</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-18T14:56:56+00:00</t>
+          <t>2026-09-19T06:27:02+00:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[#BonPlan] Les promos High-Tech du 18 septembre</t>
+          <t>Actualité : Bon plan – Le compact / bridge Sony ZV-1 Seul à 630,85 € (-21%)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://kulturegeek.fr/news-359633/bonplan-promos-high-tech-18-septembre-2026</t>
+          <t>https://www.lesnumeriques.com/compact-bridge/bon-plan-le-compact-bridge-sony-zv-1-seul-a-630-85-21-n262057.html</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -12980,22 +13084,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Phonandroid</t>
+          <t>KultureGeek</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-18T12:44:03+00:00</t>
+          <t>2026-09-18T14:56:56+00:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AliExpress lance sa French Week et fait chuter les prix : voici les offres à saisir</t>
+          <t>[#BonPlan] Les promos High-Tech du 18 septembre</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.phonandroid.com/aliexpress-french-week-fait-chuter-prix-voici-offres-saisir.html</t>
+          <t>https://kulturegeek.fr/news-359633/bonplan-promos-high-tech-18-septembre-2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -13007,18 +13111,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Frandroid - Actualités</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
+          <t>Phonandroid</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-09-18T12:44:03+00:00</t>
+        </is>
+      </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Pas de facture mobile avant 2027 : La Poste Mobile offre 4 mois gratuits sur ses forfaits 5G</t>
+          <t>AliExpress lance sa French Week et fait chuter les prix : voici les offres à saisir</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://native.humanoid.fr/register-click?s_id=2&amp;sp_id=47&amp;c_id=4224</t>
+          <t>https://www.phonandroid.com/aliexpress-french-week-fait-chuter-prix-voici-offres-saisir.html</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">

--- a/output/rss_history.xlsx
+++ b/output/rss_history.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E307"/>
+  <dimension ref="A1:E308"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,22 +471,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-19T22:00:03+00:00</t>
+          <t>2026-09-19T22:10:03+00:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Actualité : Bon plan – Le compact / bridge Sony ZV-1 Seul à 630,85 € (-21%)</t>
+          <t>Actualité : Bon plan – Le téléviseur LG 55G5 "5 étoiles" à 1 199,00 €</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/compact-bridge/bon-plan-le-compact-bridge-sony-zv-1-seul-a-630-85-21-n262068.html</t>
+          <t>https://www.lesnumeriques.com/tv-televiseur/bon-plan-le-televiseur-lg-55g5-5-etoiles-a-1-199-00-n262069.html</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>19. Sponso</t>
+          <t>7. Video</t>
         </is>
       </c>
     </row>
@@ -503,186 +503,186 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Actualité : Bon plan – La machine à café automatique avec broyeur Delonghi Magnifica Evo Next "5 étoiles" à 468,69 € (-21%)</t>
+          <t>Actualité : Bon plan – Le compact / bridge Sony ZV-1 Seul à 630,85 € (-21%)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/machine-a-cafe-automatique/bon-plan-la-machine-a-cafe-automatique-avec-broyeur-delonghi-magnifica-evo-next-5-etoiles-a-468-69-21-n262067.html</t>
+          <t>https://www.lesnumeriques.com/compact-bridge/bon-plan-le-compact-bridge-sony-zv-1-seul-a-630-85-21-n262068.html</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>12. Cuisine</t>
+          <t>19. Sponso</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Phonandroid</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-19T17:42:56+00:00</t>
+          <t>2026-09-19T22:00:03+00:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DJI Avata 360 : le drone ultra immersif qui vous permet de filmer en 8K à 360°</t>
+          <t>Actualité : Bon plan – La machine à café automatique avec broyeur Delonghi Magnifica Evo Next "5 étoiles" à 468,69 € (-21%)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.phonandroid.com/dji-avata-360-le-drone-ultra-immersif-qui-vous-permet-de-filmer-en-8k-a-360.html</t>
+          <t>https://www.lesnumeriques.com/machine-a-cafe-automatique/bon-plan-la-machine-a-cafe-automatique-avec-broyeur-delonghi-magnifica-evo-next-5-etoiles-a-468-69-21-n262067.html</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>7. Video</t>
+          <t>12. Cuisine</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Numerama</t>
+          <t>Phonandroid</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-19T17:42:00+00:00</t>
+          <t>2026-09-19T17:42:56+00:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Pour la sortie du nouveau film Resident Evil, on a classé tous les films de la saga, du pire au moins pire</t>
+          <t>DJI Avata 360 : le drone ultra immersif qui vous permet de filmer en 8K à 360°</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.numerama.com/pop-culture/2333519-pour-la-sortie-du-nouveau-film-resident-evil-on-a-classe-tous-les-films-de-la-saga-du-pire-au-moins-pire.html</t>
+          <t>https://www.phonandroid.com/dji-avata-360-le-drone-ultra-immersif-qui-vous-permet-de-filmer-en-8k-a-360.html</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>15. ludique</t>
+          <t>7. Video</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Frandroid - RSS</t>
+          <t>Numerama</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-19T17:38:00+00:00</t>
+          <t>2026-09-19T17:42:00+00:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>En ce mois de rentrée, ce laptop de Lenovo avec son écran OLED de 16″ passe sous les 900 euros et un sac à dos est offert</t>
+          <t>Pour la sortie du nouveau film Resident Evil, on a classé tous les films de la saga, du pire au moins pire</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/bons-plans/3252341_en-ce-mois-de-rentree-ce-laptop-de-lenovo-avec-son-ecran-oled-de-16-passe-sous-les-900-euros-et-un-sac-a-dos-est-offert</t>
+          <t>https://www.numerama.com/pop-culture/2333519-pour-la-sortie-du-nouveau-film-resident-evil-on-a-classe-tous-les-films-de-la-saga-du-pire-au-moins-pire.html</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2. PC</t>
+          <t>15. ludique</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>Frandroid - RSS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-19T17:04:00+00:00</t>
+          <t>2026-09-19T17:38:00+00:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Actualité : Le test du vidéoprojecteur Anker Nebula P1i a rejoint notre comparatif</t>
+          <t>En ce mois de rentrée, ce laptop de Lenovo avec son écran OLED de 16″ passe sous les 900 euros et un sac à dos est offert</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/videoprojecteur/le-test-du-videoprojecteur-anker-nebula-p1i-a-rejoint-notre-comparatif-n262054.html</t>
+          <t>https://www.frandroid.com/bons-plans/3252341_en-ce-mois-de-rentree-ce-laptop-de-lenovo-avec-son-ecran-oled-de-16-passe-sous-les-900-euros-et-un-sac-a-dos-est-offert</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>2. PC</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Frandroid - RSS</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-19T17:02:14+00:00</t>
+          <t>2026-09-19T17:04:00+00:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Quels sont les meilleures modèles de TV TCL disponibles à l’achat ? Notre comparatif</t>
+          <t>Actualité : Le test du vidéoprojecteur Anker Nebula P1i a rejoint notre comparatif</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/guide-dachat/1610991_quelles-sont-les-meilleures-tv-tcl-disponibles</t>
+          <t>https://www.lesnumeriques.com/videoprojecteur/le-test-du-videoprojecteur-anker-nebula-p1i-a-rejoint-notre-comparatif-n262054.html</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>7. Video</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>Frandroid - RSS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-19T16:32:00+00:00</t>
+          <t>2026-09-19T17:02:14+00:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Actualité : Auto SR : le DLSS de Microsoft s'ouvre à de nouveaux Copilot+ PC</t>
+          <t>Quels sont les meilleures modèles de TV TCL disponibles à l’achat ? Notre comparatif</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/carte-graphique/auto-sr-le-dlss-de-microsoft-s-ouvre-a-de-nouveaux-copilot-pc-n262064.html</t>
+          <t>https://www.frandroid.com/guide-dachat/1610991_quelles-sont-les-meilleures-tv-tcl-disponibles</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2. PC</t>
+          <t>7. Video</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Numerama</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -692,44 +692,44 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ils prédisent l’apocalypse par l’IA, c’est quoi les AI doomers ?</t>
+          <t>Actualité : Auto SR : le DLSS de Microsoft s'ouvre à de nouveaux Copilot+ PC</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.numerama.com/tech/2335869-ils-predisent-lapocalypse-par-lia-cest-quoi-les-ai-doomers.html</t>
+          <t>https://www.lesnumeriques.com/carte-graphique/auto-sr-le-dlss-de-microsoft-s-ouvre-a-de-nouveaux-copilot-pc-n262064.html</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>6. IA</t>
+          <t>2. PC</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>Numerama</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-19T16:30:00+00:00</t>
+          <t>2026-09-19T16:32:00+00:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Actualité : Harry Potter : nouveau teaser, casting, histoire, date de sortie… Tout savoir sur la série HBO Max</t>
+          <t>Ils prédisent l’apocalypse par l’IA, c’est quoi les AI doomers ?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/serie/harry-potter-nouveau-teaser-casting-histoire-date-de-sortie-tout-savoir-sur-la-serie-hbo-max-n230720.html</t>
+          <t>https://www.numerama.com/tech/2335869-ils-predisent-lapocalypse-par-lia-cest-quoi-les-ai-doomers.html</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>15. ludique</t>
+          <t>6. IA</t>
         </is>
       </c>
     </row>
@@ -741,71 +741,71 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-19T16:13:32+00:00</t>
+          <t>2026-09-19T16:30:00+00:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Actualité : Cette centrale vapeur présente le meilleur rapport qualité / prix de notre comparatif</t>
+          <t>Actualité : Harry Potter : nouveau teaser, casting, histoire, date de sortie… Tout savoir sur la série HBO Max</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/centrale-vapeur/cette-centrale-vapeur-presente-le-meilleur-rapport-qualite-prix-de-notre-comparatif-n262065.html</t>
+          <t>https://www.lesnumeriques.com/serie/harry-potter-nouveau-teaser-casting-histoire-date-de-sortie-tout-savoir-sur-la-serie-hbo-max-n230720.html</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>11. Menage</t>
+          <t>15. ludique</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Frandroid - RSS</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-19T16:01:00+00:00</t>
+          <t>2026-09-19T16:13:32+00:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>J’ai démonté le nouveau Lenovo ThinkPad en moins de 10 minutes : la réparabilité est-elle enfin de retour sur PC ?</t>
+          <t>Actualité : Cette centrale vapeur présente le meilleur rapport qualité / prix de notre comparatif</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/marques/lenovo/3237317_jai-demonte-le-nouveau-lenovo-thinkpad-en-moins-de-10-minutes-la-reparabilite-est-elle-enfin-de-retour-sur-pc</t>
+          <t>https://www.lesnumeriques.com/centrale-vapeur/cette-centrale-vapeur-presente-le-meilleur-rapport-qualite-prix-de-notre-comparatif-n262065.html</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2. PC</t>
+          <t>11. Menage</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>Frandroid - RSS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-19T16:00:49+00:00</t>
+          <t>2026-09-19T16:01:00+00:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Un ordinateur portable peut-il vraiment vous griller la peau ?</t>
+          <t>J’ai démonté le nouveau Lenovo ThinkPad en moins de 10 minutes : la réparabilité est-elle enfin de retour sur PC ?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/19/un-ordinateur-portable-peut-il-vraiment-vous-griller-la-peau/</t>
+          <t>https://www.frandroid.com/marques/lenovo/3237317_jai-demonte-le-nouveau-lenovo-thinkpad-en-moins-de-10-minutes-la-reparabilite-est-elle-enfin-de-retour-sur-pc</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -817,54 +817,54 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-19T16:00:00+00:00</t>
+          <t>2026-09-19T16:00:49+00:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Actualité : Il sort deux nouveaux modèles de smartphones par jour : est-ce bien raisonnable ?</t>
+          <t>Un ordinateur portable peut-il vraiment vous griller la peau ?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/telephone-portable/il-sort-deux-nouveaux-modeles-de-smartphones-par-jour-est-ce-bien-raisonnable-n261911.html</t>
+          <t>https://www.journaldugeek.com/2026/09/19/un-ordinateur-portable-peut-il-vraiment-vous-griller-la-peau/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>2. PC</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Frandroid - RSS</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-19T15:32:00+00:00</t>
+          <t>2026-09-19T16:00:00+00:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ce pack Marshall à moins de 850 € réunit une barre de son 5.1 et un caisson de basses, de quoi profiter d’un home cinema immersif</t>
+          <t>Actualité : Il sort deux nouveaux modèles de smartphones par jour : est-ce bien raisonnable ?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/bons-plans/3250173_ce-pack-marshall-a-moins-de-850-e-reunit-une-barre-de-son-5-1-et-un-caisson-de-basses-de-quoi-profiter-dun-home-cinema-immersif</t>
+          <t>https://www.lesnumeriques.com/telephone-portable/il-sort-deux-nouveaux-modeles-de-smartphones-par-jour-est-ce-bien-raisonnable-n261911.html</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>8. Audio</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
@@ -876,98 +876,98 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-19T15:24:06+00:00</t>
+          <t>2026-09-19T15:32:00+00:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Samsung casse le prix de son pliable anti-iPhone Duo</t>
+          <t>Ce pack Marshall à moins de 850 € réunit une barre de son 5.1 et un caisson de basses, de quoi profiter d’un home cinema immersif</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/marques/samsung/3253539_samsung-casse-le-prix-de-son-pliable-anti-iphone-duo</t>
+          <t>https://www.frandroid.com/bons-plans/3250173_ce-pack-marshall-a-moins-de-850-e-reunit-une-barre-de-son-5-1-et-un-caisson-de-basses-de-quoi-profiter-dun-home-cinema-immersif</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>8. Audio</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Numerama</t>
+          <t>Frandroid - RSS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-19T15:20:00+00:00</t>
+          <t>2026-09-19T15:24:06+00:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Une Tesla au bord du vide en FSD, remboursement de Navigo et un camion sans chauffeur livre Lidl: le récap’ Vroom de la semaine</t>
+          <t>Samsung casse le prix de son pliable anti-iPhone Duo</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.numerama.com/vroom/2335871-une-tesla-au-bord-du-vide-en-fsd-remboursement-de-navigo-et-un-camion-sans-chauffeur-livre-lidl-le-recap-vroom-de-la-semaine.html</t>
+          <t>https://www.frandroid.com/marques/samsung/3253539_samsung-casse-le-prix-de-son-pliable-anti-iphone-duo</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>4. Tablette</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>Numerama</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-19T15:00:28+00:00</t>
+          <t>2026-09-19T15:20:00+00:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Meta prépare des lunettes connectées sans caméra, pour voir si ça passe mieux</t>
+          <t>Une Tesla au bord du vide en FSD, remboursement de Navigo et un camion sans chauffeur livre Lidl: le récap’ Vroom de la semaine</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/19/meta-prepare-des-lunettes-connectees-sans-camera-pour-voir-si-ca-passe-mieux/</t>
+          <t>https://www.numerama.com/vroom/2335871-une-tesla-au-bord-du-vide-en-fsd-remboursement-de-navigo-et-un-camion-sans-chauffeur-livre-lidl-le-recap-vroom-de-la-semaine.html</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>4. Tablette</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-19T15:00:00+00:00</t>
+          <t>2026-09-19T15:00:28+00:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Actualité : iOS 27 : j’ai adopté ces 7 nouvelles options de personnalisation sur iPhone</t>
+          <t>Meta prépare des lunettes connectées sans caméra, pour voir si ça passe mieux</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/telephone-portable/ios-27-j-ai-adopte-ces-7-nouvelles-options-de-personnalisation-sur-iphone-n261976.html</t>
+          <t>https://www.journaldugeek.com/2026/09/19/meta-prepare-des-lunettes-connectees-sans-camera-pour-voir-si-ca-passe-mieux/</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -979,76 +979,76 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Phonandroid</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-19T14:50:42+00:00</t>
+          <t>2026-09-19T15:00:00+00:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Napster se lance dans l’éducation : l’IA pourrait bientôt remplacer vos profs</t>
+          <t>Actualité : iOS 27 : j’ai adopté ces 7 nouvelles options de personnalisation sur iPhone</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.phonandroid.com/napster-se-lance-dans-leducation-lia-pourrait-bientot-remplacer-vos-profs.html</t>
+          <t>https://www.lesnumeriques.com/telephone-portable/ios-27-j-ai-adopte-ces-7-nouvelles-options-de-personnalisation-sur-iphone-n261976.html</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>6. IA</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Numerama</t>
+          <t>Phonandroid</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-19T14:30:00+00:00</t>
+          <t>2026-09-19T14:50:42+00:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Un agent OpenAI s’invente un personnage libre, Revolut piégée par un faux mail et les géants de l’IA qui veulent ralentir : on vous raconte la semaine Cyberguerre</t>
+          <t>Napster se lance dans l’éducation : l’IA pourrait bientôt remplacer vos profs</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.numerama.com/cyberguerre/2336053-un-agent-openai-sinvente-un-personnage-libre-revolut-piegee-par-un-faux-mail-et-les-geants-de-lia-qui-veulent-ralentir-on-vous-raconte-la-semaine-cyberguerre.html</t>
+          <t>https://www.phonandroid.com/napster-se-lance-dans-leducation-lia-pourrait-bientot-remplacer-vos-profs.html</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>5. Logiciels _ OS</t>
+          <t>6. IA</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>Numerama</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-19T14:12:00+00:00</t>
+          <t>2026-09-19T14:30:00+00:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Actualité : Fatigué par Windows 11 et l'IA, j'ai tout plaqué pour Linux (et je ne regrette rien)</t>
+          <t>Un agent OpenAI s’invente un personnage libre, Revolut piégée par un faux mail et les géants de l’IA qui veulent ralentir : on vous raconte la semaine Cyberguerre</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/informatique/fatigue-par-windows-11-et-l-ia-j-ai-tout-plaque-pour-linux-et-je-ne-regrette-rien-n250751.html</t>
+          <t>https://www.numerama.com/cyberguerre/2336053-un-agent-openai-sinvente-un-personnage-libre-revolut-piegee-par-un-faux-mail-et-les-geants-de-lia-qui-veulent-ralentir-on-vous-raconte-la-semaine-cyberguerre.html</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1065,44 +1065,44 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-19T14:03:00+00:00</t>
+          <t>2026-09-19T14:12:00+00:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Actualité : On a vu les Shokz OpenFit 2 AI : ces écouteurs veulent devenir votre traducteur et prendre vos notes</t>
+          <t>Actualité : Fatigué par Windows 11 et l'IA, j'ai tout plaqué pour Linux (et je ne regrette rien)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/ecouteurs-sans-fil/on-a-vu-les-shokz-openfit-2-ai-ces-ecouteurs-veulent-devenir-votre-traducteur-et-prendre-vos-notes-n262027.html</t>
+          <t>https://www.lesnumeriques.com/informatique/fatigue-par-windows-11-et-l-ia-j-ai-tout-plaque-pour-linux-et-je-ne-regrette-rien-n250751.html</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>6. IA</t>
+          <t>5. Logiciels _ OS</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Frandroid - RSS</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-19T14:02:00+00:00</t>
+          <t>2026-09-19T14:03:00+00:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>J’ai enfin reçu les jumelles connectées Envision d’Unistellar : voici mes premières impressions</t>
+          <t>Actualité : On a vu les Shokz OpenFit 2 AI : ces écouteurs veulent devenir votre traducteur et prendre vos notes</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/test/prises-en-main/3249881_jai-enfin-recu-les-jumelles-connectees-envision-dunistellar-voici-mes-premieres-impressions</t>
+          <t>https://www.lesnumeriques.com/ecouteurs-sans-fil/on-a-vu-les-shokz-openfit-2-ai-ces-ecouteurs-veulent-devenir-votre-traducteur-et-prendre-vos-notes-n262027.html</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1114,49 +1114,49 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>Frandroid - RSS</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-19T14:00:00+00:00</t>
+          <t>2026-09-19T14:02:00+00:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Actualité : Impôts 2026 : le fisc va prélever 1 798 € en moyenne chez 13,8 millions de français dès le 25 septembre</t>
+          <t>J’ai enfin reçu les jumelles connectées Envision d’Unistellar : voici mes premières impressions</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/societe-numerique/impots-2026-le-fisc-va-prelever-1-798-en-moyenne-chez-13-8-millions-de-francais-des-le-25-septembre-n262062.html</t>
+          <t>https://www.frandroid.com/test/prises-en-main/3249881_jai-enfin-recu-les-jumelles-connectees-envision-dunistellar-voici-mes-premieres-impressions</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>NON_CLASSE</t>
+          <t>6. IA</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-19T13:58:01+00:00</t>
+          <t>2026-09-19T14:00:00+00:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>La mégalopole lunaire d’Elon Musk prend l’eau</t>
+          <t>Actualité : Impôts 2026 : le fisc va prélever 1 798 € en moyenne chez 13,8 millions de français dès le 25 septembre</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/19/la-megalopole-lunaire-delon-musk-prend-leau/</t>
+          <t>https://www.lesnumeriques.com/societe-numerique/impots-2026-le-fisc-va-prelever-1-798-en-moyenne-chez-13-8-millions-de-francais-des-le-25-septembre-n262062.html</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1168,27 +1168,27 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Phonandroid</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-19T13:42:46+00:00</t>
+          <t>2026-09-19T13:58:01+00:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-42% sur la Honor Pad X9a : la tablette de 11,5 pouces est à moins de 145 €</t>
+          <t>La mégalopole lunaire d’Elon Musk prend l’eau</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.phonandroid.com/42-honor-pad-x9a-tablette-11-pouces-moins-145-e.html</t>
+          <t>https://www.journaldugeek.com/2026/09/19/la-megalopole-lunaire-delon-musk-prend-leau/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>NON_CLASSE</t>
         </is>
       </c>
     </row>
@@ -1200,71 +1200,71 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-19T13:33:41+00:00</t>
+          <t>2026-09-19T13:42:46+00:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Vous téléchargez des films sur Internet ? Cette nouvelle menace se cache peut-être sur votre PC</t>
+          <t>-42% sur la Honor Pad X9a : la tablette de 11,5 pouces est à moins de 145 €</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.phonandroid.com/vous-telechargez-des-films-sur-internet-cette-nouvelle-menace-se-cache-peut-etre-sur-votre-pc.html</t>
+          <t>https://www.phonandroid.com/42-honor-pad-x9a-tablette-11-pouces-moins-145-e.html</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2. PC</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Numerama</t>
+          <t>Phonandroid</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-19T13:33:00+00:00</t>
+          <t>2026-09-19T13:33:41+00:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Notre cerveau refuse de l’admettre et se trompe lourdement, mais au loto la grille 1-2-3-4-5-6 n’a rien de spécial</t>
+          <t>Vous téléchargez des films sur Internet ? Cette nouvelle menace se cache peut-être sur votre PC</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.numerama.com/sciences/2335765-notre-cerveau-refuse-de-ladmettre-et-se-trompe-completement-mais-au-loto-la-grille-1-2-3-4-5-6-na-rien-de-special.html</t>
+          <t>https://www.phonandroid.com/vous-telechargez-des-films-sur-internet-cette-nouvelle-menace-se-cache-peut-etre-sur-votre-pc.html</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>NON_CLASSE</t>
+          <t>2. PC</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>Numerama</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-19T13:30:00+00:00</t>
+          <t>2026-09-19T13:33:00+00:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Actualité : IFA 2026 : Découvrez les grands gagnants des premiers Editor's Pick des Numériques !</t>
+          <t>Notre cerveau refuse de l’admettre et se trompe lourdement, mais au loto la grille 1-2-3-4-5-6 n’a rien de spécial</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/societe-numerique/ifa-2026-decouvrez-les-grands-gagnants-des-premiers-editor-s-pick-des-numeriques-n261986.html</t>
+          <t>https://www.numerama.com/sciences/2335765-notre-cerveau-refuse-de-ladmettre-et-se-trompe-completement-mais-au-loto-la-grille-1-2-3-4-5-6-na-rien-de-special.html</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1276,427 +1276,427 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-19T13:25:30+00:00</t>
+          <t>2026-09-19T13:30:00+00:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>La France va-t-elle interdire la revente de cartes Pokémon ?</t>
+          <t>Actualité : IFA 2026 : Découvrez les grands gagnants des premiers Editor's Pick des Numériques !</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/19/la-france-va-t-elle-interdire-la-revente-de-cartes-pokemon/</t>
+          <t>https://www.lesnumeriques.com/societe-numerique/ifa-2026-decouvrez-les-grands-gagnants-des-premiers-editor-s-pick-des-numeriques-n261986.html</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>15. ludique</t>
+          <t>NON_CLASSE</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-19T13:11:31+00:00</t>
+          <t>2026-09-19T13:25:30+00:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Actualité : Pour de bons écouteurs &amp; intras filaires à prix abordable, privilégiez...</t>
+          <t>La France va-t-elle interdire la revente de cartes Pokémon ?</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/ecouteurs-intras-filaires/pour-de-bons-ecouteurs-intras-filaires-a-prix-abordable-privilegiez-n262061.html</t>
+          <t>https://www.journaldugeek.com/2026/09/19/la-france-va-t-elle-interdire-la-revente-de-cartes-pokemon/</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>8. Audio</t>
+          <t>15. ludique</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Frandroid - RSS</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-19T13:11:00+00:00</t>
+          <t>2026-09-19T13:11:31+00:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Avec plus ou moins 200 € en poche, faut-il craquer pour le nouveau Samsung Galaxy A18 ou le Xiaomi Redmi 17 ?</t>
+          <t>Actualité : Pour de bons écouteurs &amp; intras filaires à prix abordable, privilégiez...</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/bons-plans/3252691_avec-plus-ou-moins-200-e-en-poche-faut-il-craquer-pour-le-nouveau-samsung-galaxy-a18-ou-le-xiaomi-redmi-17</t>
+          <t>https://www.lesnumeriques.com/ecouteurs-intras-filaires/pour-de-bons-ecouteurs-intras-filaires-a-prix-abordable-privilegiez-n262061.html</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>8. Audio</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>Frandroid - RSS</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-19T13:07:00+00:00</t>
+          <t>2026-09-19T13:11:00+00:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Actualité : Double capteur, zoom x9, IA améliorée : Xiaomi lance une caméra de surveillance qui ne laisse rien passer</t>
+          <t>Avec plus ou moins 200 € en poche, faut-il craquer pour le nouveau Samsung Galaxy A18 ou le Xiaomi Redmi 17 ?</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/camera-surveillance/double-capteur-zoom-x9-ia-amelioree-xiaomi-lance-une-camera-de-surveillance-qui-ne-laisse-rien-passer-n261932.html</t>
+          <t>https://www.frandroid.com/bons-plans/3252691_avec-plus-ou-moins-200-e-en-poche-faut-il-craquer-pour-le-nouveau-samsung-galaxy-a18-ou-le-xiaomi-redmi-17</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>6. IA</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-19T13:00:29+00:00</t>
+          <t>2026-09-19T13:07:00+00:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Le HP OmniBook Ultra 16 mise sur l’IA locale… mais avec un prix très haut de gamme</t>
+          <t>Actualité : Double capteur, zoom x9, IA améliorée : Xiaomi lance une caméra de surveillance qui ne laisse rien passer</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/19/le-hp-omnibook-ultra-16-mise-sur-lia-locale-mais-avec-un-prix-tres-haut-de-gamme/</t>
+          <t>https://www.lesnumeriques.com/camera-surveillance/double-capteur-zoom-x9-ia-amelioree-xiaomi-lance-une-camera-de-surveillance-qui-ne-laisse-rien-passer-n261932.html</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2. PC</t>
+          <t>6. IA</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-19T12:42:00+00:00</t>
+          <t>2026-09-19T13:00:29+00:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Actualité : Narnia (Netflix) : histoire, sortie, casting, trailer… Tout savoir sur le film de Greta Gerwig</t>
+          <t>Le HP OmniBook Ultra 16 mise sur l’IA locale… mais avec un prix très haut de gamme</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/cine-svod/narnia-netflix-histoire-sortie-casting-trailer-tout-savoir-sur-le-film-de-greta-gerwig-n262022.html</t>
+          <t>https://www.journaldugeek.com/2026/09/19/le-hp-omnibook-ultra-16-mise-sur-lia-locale-mais-avec-un-prix-tres-haut-de-gamme/</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>15. ludique</t>
+          <t>2. PC</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Phonandroid</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-19T12:36:23+00:00</t>
+          <t>2026-09-19T12:42:00+00:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Le Ryzen 7 9800X3D perd 210 € : une belle baisse de prix pour le processeur AMD</t>
+          <t>Actualité : Narnia (Netflix) : histoire, sortie, casting, trailer… Tout savoir sur le film de Greta Gerwig</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.phonandroid.com/ryzen-7-9800x3d-perd-210-belle-baisse-prix-processeur-amd.html</t>
+          <t>https://www.lesnumeriques.com/cine-svod/narnia-netflix-histoire-sortie-casting-trailer-tout-savoir-sur-le-film-de-greta-gerwig-n262022.html</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2. PC</t>
+          <t>15. ludique</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Numerama</t>
+          <t>Phonandroid</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-19T12:30:08+00:00</t>
+          <t>2026-09-19T12:36:23+00:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Pourquoi Pikachu a voyagé dans l’ISS avec Sophie Adenot, et ce que ça change pour les fans de Pokémon</t>
+          <t>Le Ryzen 7 9800X3D perd 210 € : une belle baisse de prix pour le processeur AMD</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.numerama.com/sciences/2335725-pourquoi-pikachu-a-voyage-dans-liss-avec-sophie-adenot-et-ce-que-ca-change-pour-les-fans-de-pokemon.html</t>
+          <t>https://www.phonandroid.com/ryzen-7-9800x3d-perd-210-belle-baisse-prix-processeur-amd.html</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>15. ludique</t>
+          <t>2. PC</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>Numerama</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-19T12:17:00+00:00</t>
+          <t>2026-09-19T12:30:08+00:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Actualité : Airfryer : comment la cuisson sans huile a fini par me refroidir</t>
+          <t>Pourquoi Pikachu a voyagé dans l’ISS avec Sophie Adenot, et ce que ça change pour les fans de Pokémon</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/airfryer/airfryer-comment-la-cuisson-sans-huile-a-fini-par-me-refroidir-n224064.html</t>
+          <t>https://www.numerama.com/sciences/2335725-pourquoi-pikachu-a-voyage-dans-liss-avec-sophie-adenot-et-ce-que-ca-change-pour-les-fans-de-pokemon.html</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>12. Cuisine</t>
+          <t>15. ludique</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Frandroid - RSS</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-19T12:02:00+00:00</t>
+          <t>2026-09-19T12:17:00+00:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>On a testé la Navee GT5 Max, une trottinette électrique qui secoue Segway et Xiaomi</t>
+          <t>Actualité : Airfryer : comment la cuisson sans huile a fini par me refroidir</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/survoltes/trottinette-electrique/3249113_essai-navee-gt5-max-une-trottinette-electrique-qui-peut-secouer-segway-et-xiaomi</t>
+          <t>https://www.lesnumeriques.com/airfryer/airfryer-comment-la-cuisson-sans-huile-a-fini-par-me-refroidir-n224064.html</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>9. Moiilité douce</t>
+          <t>12. Cuisine</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>Frandroid - RSS</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:27+00:00</t>
+          <t>2026-09-19T12:02:00+00:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Meta One : Meta met Instagram, Facebook, WhatsApp et son IA dans un même abonnement</t>
+          <t>On a testé la Navee GT5 Max, une trottinette électrique qui secoue Segway et Xiaomi</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/19/meta-one-meta-met-instagram-facebook-whatsapp-et-son-ia-dans-un-meme-abonnement/</t>
+          <t>https://www.frandroid.com/survoltes/trottinette-electrique/3249113_essai-navee-gt5-max-une-trottinette-electrique-qui-peut-secouer-segway-et-xiaomi</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>9. Moiilité douce</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Numerama</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-19T12:00:00+00:00</t>
+          <t>2026-09-19T12:01:27+00:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Monstre, saison 4 : dans la tête de la tueuse Lizzie Borden, icône féministe sanglante</t>
+          <t>Meta One : Meta met Instagram, Facebook, WhatsApp et son IA dans un même abonnement</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.numerama.com/pop-culture/2335297-monstre-saison-4-dans-la-tete-de-la-tueuse-lizzie-borden-icone-feministe-sanglante.html</t>
+          <t>https://www.journaldugeek.com/2026/09/19/meta-one-meta-met-instagram-facebook-whatsapp-et-son-ia-dans-un-meme-abonnement/</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>NON_CLASSE</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Phonandroid</t>
+          <t>Numerama</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-19T11:33:40+00:00</t>
+          <t>2026-09-19T12:00:00+00:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Samsung détrône Apple, la pénurie de RAM bouleverse le marché des smartphones</t>
+          <t>Monstre, saison 4 : dans la tête de la tueuse Lizzie Borden, icône féministe sanglante</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.phonandroid.com/samsung-detrone-apple-la-penurie-de-ram-bouleverse-le-marche-des-smartphones.html</t>
+          <t>https://www.numerama.com/pop-culture/2335297-monstre-saison-4-dans-la-tete-de-la-tueuse-lizzie-borden-icone-feministe-sanglante.html</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>NON_CLASSE</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Frandroid - RSS</t>
+          <t>Phonandroid</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-19T11:19:00+00:00</t>
+          <t>2026-09-19T11:33:40+00:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Ce SSD externe Crucial X10 Pro 1 TB voué à disparaître se paye un baroud d’honneur avec cette promo</t>
+          <t>Samsung détrône Apple, la pénurie de RAM bouleverse le marché des smartphones</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/bons-plans/3252443_ce-ssd-externe-crucial-x10-pro-1-tb-voue-a-disparaitre-se-paye-un-baroud-dhonneur-avec-cette-promo</t>
+          <t>https://www.phonandroid.com/samsung-detrone-apple-la-penurie-de-ram-bouleverse-le-marche-des-smartphones.html</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2. PC</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Phonandroid</t>
+          <t>Frandroid - RSS</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-19T11:17:23+00:00</t>
+          <t>2026-09-19T11:19:00+00:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Votre iPhone garde une trace de vos déplacements : voici où les trouver et comment les effacer</t>
+          <t>Ce SSD externe Crucial X10 Pro 1 TB voué à disparaître se paye un baroud d’honneur avec cette promo</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.phonandroid.com/votre-iphone-garde-trace-deplacements-ou-trouver-effacer.html</t>
+          <t>https://www.frandroid.com/bons-plans/3252443_ce-ssd-externe-crucial-x10-pro-1-tb-voue-a-disparaitre-se-paye-un-baroud-dhonneur-avec-cette-promo</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>2. PC</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>Phonandroid</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-19T11:15:00+00:00</t>
+          <t>2026-09-19T11:17:23+00:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Actualité : Dernière trouvaille de Samsung : breveter un téléphone portable en forme de brique doté d’un écran pliable</t>
+          <t>Votre iPhone garde une trace de vos déplacements : voici où les trouver et comment les effacer</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/mobilite-c17/derniere-trouvaille-de-samsung-breveter-un-telephone-portable-en-forme-de-brique-dote-d-un-ecran-pliable-n262033.html</t>
+          <t>https://www.phonandroid.com/votre-iphone-garde-trace-deplacements-ou-trouver-effacer.html</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1713,17 +1713,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-19T11:13:00+00:00</t>
+          <t>2026-09-19T11:15:00+00:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Actualité : Surprise, 19 nouveaux emojis vont être ajoutés sur Android et iOS, mais il va falloir attendre</t>
+          <t>Actualité : Dernière trouvaille de Samsung : breveter un téléphone portable en forme de brique doté d’un écran pliable</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/societe-numerique/surprise-19-nouveaux-emojis-vont-etre-ajoutes-sur-android-et-ios-mais-il-va-falloir-attendre-n262025.html</t>
+          <t>https://www.lesnumeriques.com/mobilite-c17/derniere-trouvaille-de-samsung-breveter-un-telephone-portable-en-forme-de-brique-dote-d-un-ecran-pliable-n262033.html</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1735,216 +1735,216 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-19T11:00:25+00:00</t>
+          <t>2026-09-19T11:13:00+00:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>L’instax Link WIDE 2 imprime les souvenirs en plus grand</t>
+          <t>Actualité : Surprise, 19 nouveaux emojis vont être ajoutés sur Android et iOS, mais il va falloir attendre</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/19/linstax-link-wide-2-imprime-les-souvenirs-en-plus-grand/</t>
+          <t>https://www.lesnumeriques.com/societe-numerique/surprise-19-nouveaux-emojis-vont-etre-ajoutes-sur-android-et-ios-mais-il-va-falloir-attendre-n262025.html</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>NON_CLASSE</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Numerama</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-19T10:40:48+00:00</t>
+          <t>2026-09-19T11:00:25+00:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Midea revoit son climatiseur PortaSplit pour 2027 : nouveau gaz réfrigérant et compatibilité Matter</t>
+          <t>L’instax Link WIDE 2 imprime les souvenirs en plus grand</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.numerama.com/tech/2336405-midea-revoit-son-climatiseur-portasplit-pour-2027-nouveau-gaz-refrigerant-et-compatibilite-matter.html</t>
+          <t>https://www.journaldugeek.com/2026/09/19/linstax-link-wide-2-imprime-les-souvenirs-en-plus-grand/</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>8. Audio</t>
+          <t>NON_CLASSE</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>Numerama</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-19T10:36:00+00:00</t>
+          <t>2026-09-19T10:40:48+00:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Actualité : Votre box Wi-Fi bride votre smartphone ? Le réglage caché pour doubler le débit</t>
+          <t>Midea revoit son climatiseur PortaSplit pour 2027 : nouveau gaz réfrigérant et compatibilité Matter</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/mobilite-c17/votre-box-wi-fi-bride-votre-smartphone-le-reglage-cache-pour-doubler-le-debit-n261954.html</t>
+          <t>https://www.numerama.com/tech/2336405-midea-revoit-son-climatiseur-portasplit-pour-2027-nouveau-gaz-refrigerant-et-compatibilite-matter.html</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>8. Audio</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Phonandroid</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-19T10:33:39+00:00</t>
+          <t>2026-09-19T10:36:00+00:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Windows 11 : Microsoft vous laisse enfin reprendre le contrôle du menu Démarrer avec cette mise à jour</t>
+          <t>Actualité : Votre box Wi-Fi bride votre smartphone ? Le réglage caché pour doubler le débit</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.phonandroid.com/windows-11-microsoft-vous-laisse-enfin-reprendre-le-controle-du-menu-demarrer-avec-cette-mise-a-jour.html</t>
+          <t>https://www.lesnumeriques.com/mobilite-c17/votre-box-wi-fi-bride-votre-smartphone-le-reglage-cache-pour-doubler-le-debit-n261954.html</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>5. Logiciels _ OS</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>Phonandroid</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-19T10:11:35+00:00</t>
+          <t>2026-09-19T10:33:39+00:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Actualité : Cet appareil photo instantané présente le meilleur rapport qualité / prix de notre comparatif</t>
+          <t>Windows 11 : Microsoft vous laisse enfin reprendre le contrôle du menu Démarrer avec cette mise à jour</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/appareil-photo-instantane/cet-appareil-photo-instantane-presente-le-meilleur-rapport-qualite-prix-de-notre-comparatif-n262060.html</t>
+          <t>https://www.phonandroid.com/windows-11-microsoft-vous-laisse-enfin-reprendre-le-controle-du-menu-demarrer-avec-cette-mise-a-jour.html</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>NON_CLASSE</t>
+          <t>5. Logiciels _ OS</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-09-19T10:04:31+00:00</t>
+          <t>2026-09-19T10:11:35+00:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>iOS 27 : 10 fonctions pour bien maitriser la dernière mise à jour de l’iPhone</t>
+          <t>Actualité : Cet appareil photo instantané présente le meilleur rapport qualité / prix de notre comparatif</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.01net.com/astuces/ios-27-10-fonctions-pour-bien-maitriser-la-derniere-mise-a-jour-de-liphone.html</t>
+          <t>https://www.lesnumeriques.com/appareil-photo-instantane/cet-appareil-photo-instantane-presente-le-meilleur-rapport-qualite-prix-de-notre-comparatif-n262060.html</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>NON_CLASSE</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-09-19T10:00:16+00:00</t>
+          <t>2026-09-19T10:04:31+00:00</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Les brouteurs n’ont qu’à bien se tenir : Bercy dévoile son guide anti-arnaques (mais il est déjà obsolète)</t>
+          <t>iOS 27 : 10 fonctions pour bien maitriser la dernière mise à jour de l’iPhone</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/19/les-brouteurs-nont-qua-bien-se-tenir-bercy-devoile-son-guide-anti-arnaques-mais-il-est-deja-obsolete/</t>
+          <t>https://www.01net.com/astuces/ios-27-10-fonctions-pour-bien-maitriser-la-derniere-mise-a-jour-de-liphone.html</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>8. Audio</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-09-19T10:00:00+00:00</t>
+          <t>2026-09-19T10:00:16+00:00</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Actualité : Redmi Note 17 Pro vs Redmi Note 15 Pro : le duel de l'absurde</t>
+          <t>Les brouteurs n’ont qu’à bien se tenir : Bercy dévoile son guide anti-arnaques (mais il est déjà obsolète)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/telephone-portable/redmi-note-17-pro-vs-redmi-note-15-pro-le-duel-de-l-absurde-n262034.html</t>
+          <t>https://www.journaldugeek.com/2026/09/19/les-brouteurs-nont-qua-bien-se-tenir-bercy-devoile-son-guide-anti-arnaques-mais-il-est-deja-obsolete/</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>8. Audio</t>
         </is>
       </c>
     </row>
@@ -1961,24 +1961,24 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Test Braun Nevo : que vaut le rasoir à 790 € dont la tête AeroTouch s'inspire de la peau des requins ?</t>
+          <t>Actualité : Redmi Note 17 Pro vs Redmi Note 15 Pro : le duel de l'absurde</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/rasoir-electrique/braun-nevo-p78560/test.html</t>
+          <t>https://www.lesnumeriques.com/telephone-portable/redmi-note-17-pro-vs-redmi-note-15-pro-le-duel-de-l-absurde-n262034.html</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>14. Santé</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Frandroid - RSS</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1988,66 +1988,66 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>J’ai testé la Garmin Fenix 9 Pro : le titane change tout, l’autonomie un peu moins</t>
+          <t>Test Braun Nevo : que vaut le rasoir à 790 € dont la tête AeroTouch s'inspire de la peau des requins ?</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/marques/garmin/3240977_jai-teste-la-garmin-fenix-9-pro-le-titane-change-tout-lautonomie-un-peu-moins</t>
+          <t>https://www.lesnumeriques.com/rasoir-electrique/braun-nevo-p78560/test.html</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>6. IA</t>
+          <t>14. Santé</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>Frandroid - RSS</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-09-19T09:35:00+00:00</t>
+          <t>2026-09-19T10:00:00+00:00</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Actualité : PRONOTE vous prend la tête : toutes nos astuces pour survivre à l'année scolaire</t>
+          <t>J’ai testé la Garmin Fenix 9 Pro : le titane change tout, l’autonomie un peu moins</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/societe-numerique/pronote-vous-prend-la-tete-toutes-nos-astuces-pour-survivre-a-l-annee-scolaire-n261988.html</t>
+          <t>https://www.frandroid.com/marques/garmin/3240977_jai-teste-la-garmin-fenix-9-pro-le-titane-change-tout-lautonomie-un-peu-moins</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>NON_CLASSE</t>
+          <t>6. IA</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Phonandroid</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-09-19T09:33:38+00:00</t>
+          <t>2026-09-19T09:35:00+00:00</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Marvel’s Wolverine pourrait avoir droit à une suite, cette mystérieuse scène pourrait tout changer</t>
+          <t>Actualité : PRONOTE vous prend la tête : toutes nos astuces pour survivre à l'année scolaire</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.phonandroid.com/marvels-wolverine-pourrait-avoir-droit-a-une-suite-cette-mysterieuse-scene-pourrait-tout-changer.html</t>
+          <t>https://www.lesnumeriques.com/societe-numerique/pronote-vous-prend-la-tete-toutes-nos-astuces-pour-survivre-a-l-annee-scolaire-n261988.html</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2059,76 +2059,76 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Frandroid - RSS</t>
+          <t>Phonandroid</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-09-19T09:27:00+00:00</t>
+          <t>2026-09-19T09:33:38+00:00</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>La dernière tablette de Honor, compatible avec l’IMAX, perd 50 euros et s’accompagne d’un casque sans fil</t>
+          <t>Marvel’s Wolverine pourrait avoir droit à une suite, cette mystérieuse scène pourrait tout changer</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/bons-plans/3251353_la-derniere-tablette-de-honor-compatible-avec-limax-perd-50-euros-et-saccompagne-dun-casque-sans-fil</t>
+          <t>https://www.phonandroid.com/marvels-wolverine-pourrait-avoir-droit-a-une-suite-cette-mysterieuse-scene-pourrait-tout-changer.html</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>NON_CLASSE</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>Frandroid - RSS</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-09-19T09:15:00+00:00</t>
+          <t>2026-09-19T09:27:00+00:00</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Critique Apollo Has Fallen : la série Canal+ passe à la vitesse supérieure et offre une saison 2 nerveuse</t>
+          <t>La dernière tablette de Honor, compatible avec l’IMAX, perd 50 euros et s’accompagne d’un casque sans fil</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/serie/apollo-has-fallen-p78881/test.html</t>
+          <t>https://www.frandroid.com/bons-plans/3251353_la-derniere-tablette-de-honor-compatible-avec-limax-perd-50-euros-et-saccompagne-dun-casque-sans-fil</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>15. ludique</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-09-19T09:02:46+00:00</t>
+          <t>2026-09-19T09:15:00+00:00</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>FarCry : date de sortie, casting, intrigue… tout savoir sur la série LIVE Action</t>
+          <t>Critique Apollo Has Fallen : la série Canal+ passe à la vitesse supérieure et offre une saison 2 nerveuse</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/19/farcry-date-de-sortie-casting-intrigue-tout-savoir-sur-la-serie-live-action/</t>
+          <t>https://www.lesnumeriques.com/serie/apollo-has-fallen-p78881/test.html</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2140,189 +2140,189 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Numerama</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-09-19T09:01:54+00:00</t>
+          <t>2026-09-19T09:02:46+00:00</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Des drones non identifiés ont forcé l’aéroport de Luxembourg à fermer vendredi soir</t>
+          <t>FarCry : date de sortie, casting, intrigue… tout savoir sur la série LIVE Action</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://www.numerama.com/tech/2336351-des-drones-non-identifies-ont-force-laeroport-de-luxembourg-a-fermer-vendredi-soir.html</t>
+          <t>https://www.journaldugeek.com/2026/09/19/farcry-date-de-sortie-casting-intrigue-tout-savoir-sur-la-serie-live-action/</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>9. Moiilité douce</t>
+          <t>15. ludique</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>Numerama</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-09-19T09:00:34+00:00</t>
+          <t>2026-09-19T09:01:54+00:00</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>0,82 € les 100 km : l’incroyable exploit de cette Lancia électrique sur le périphérique parisien</t>
+          <t>Des drones non identifiés ont forcé l’aéroport de Luxembourg à fermer vendredi soir</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://www.01net.com/actualites/082-euros-100-km-incroyable-exploit-lancia-electrique-peripherique-parisien.html</t>
+          <t>https://www.numerama.com/tech/2336351-des-drones-non-identifies-ont-force-laeroport-de-luxembourg-a-fermer-vendredi-soir.html</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>3. Periphérique</t>
+          <t>9. Moiilité douce</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Frandroid - RSS</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-09-19T09:00:00+00:00</t>
+          <t>2026-09-19T09:00:34+00:00</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>ChatGPT s’installe gratuitement dans Microsoft Word pour tout le monde</t>
+          <t>0,82 € les 100 km : l’incroyable exploit de cette Lancia électrique sur le périphérique parisien</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/culture-tech/intelligence-artificielle/openai-chatgpt/3253521_chatgpt-sinstalle-gratuitement-dans-microsoft-word-pour-tout-le-monde</t>
+          <t>https://www.01net.com/actualites/082-euros-100-km-incroyable-exploit-lancia-electrique-peripherique-parisien.html</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>5. Logiciels _ OS</t>
+          <t>3. Periphérique</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>Frandroid - RSS</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-09-19T08:53:16+00:00</t>
+          <t>2026-09-19T09:00:00+00:00</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Xiaomi dit adieu à la marge : le Redmi Note 15 Pro se vend à prix FOU (256 et 512 Go) ⚡️</t>
+          <t>ChatGPT s’installe gratuitement dans Microsoft Word pour tout le monde</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://www.01net.com/bons-plans/xiaomi-dit-adieu-a-la-marge-le-redmi-note-15-pro-se-vend-a-prix-fou-256-et-512-go.html</t>
+          <t>https://www.frandroid.com/culture-tech/intelligence-artificielle/openai-chatgpt/3253521_chatgpt-sinstalle-gratuitement-dans-microsoft-word-pour-tout-le-monde</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>5. Logiciels _ OS</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Phonandroid</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-09-19T08:37:22+00:00</t>
+          <t>2026-09-19T08:53:16+00:00</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Free libère enfin le potentiel de son Wi-Fi avec cette mise à jour très attendue</t>
+          <t>Xiaomi dit adieu à la marge : le Redmi Note 15 Pro se vend à prix FOU (256 et 512 Go) ⚡️</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://www.phonandroid.com/free-libere-enfin-le-potentiel-de-son-wi-fi-avec-cette-mise-a-jour-tres-attendue.html</t>
+          <t>https://www.01net.com/bons-plans/xiaomi-dit-adieu-a-la-marge-le-redmi-note-15-pro-se-vend-a-prix-fou-256-et-512-go.html</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>3. Periphérique</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>Phonandroid</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-09-19T08:34:08+00:00</t>
+          <t>2026-09-19T08:37:22+00:00</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Le saviez-vous ? Atari a enterré ses pires jeux vidéo dans le désert en 1983, et ce n’était pas une légende</t>
+          <t>Free libère enfin le potentiel de son Wi-Fi avec cette mise à jour très attendue</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/19/le-saviez-vous-atari-a-enterre-ses-pires-jeux-video-dans-le-desert-en-1983-et-ce-netait-pas-une-legende/</t>
+          <t>https://www.phonandroid.com/free-libere-enfin-le-potentiel-de-son-wi-fi-avec-cette-mise-a-jour-tres-attendue.html</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>7. Video</t>
+          <t>3. Periphérique</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-09-19T08:32:00+00:00</t>
+          <t>2026-09-19T08:34:08+00:00</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Actualité : Samsung Galaxy : ces applications cachées vont améliorer votre quotidien</t>
+          <t>Le saviez-vous ? Atari a enterré ses pires jeux vidéo dans le désert en 1983, et ce n’était pas une légende</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/mobilite-c17/samsung-galaxy-ces-applications-cachees-vont-ameliorer-votre-quotidien-n261951.html</t>
+          <t>https://www.journaldugeek.com/2026/09/19/le-saviez-vous-atari-a-enterre-ses-pires-jeux-video-dans-le-desert-en-1983-et-ce-netait-pas-une-legende/</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>7. Video</t>
         </is>
       </c>
     </row>
@@ -2334,137 +2334,137 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-09-19T08:15:00+00:00</t>
+          <t>2026-09-19T08:32:00+00:00</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Actualité : En pleine inflation, voici les 5 départements où faire ses courses en ligne coûte le moins cher</t>
+          <t>Actualité : Samsung Galaxy : ces applications cachées vont améliorer votre quotidien</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/societe-numerique/en-pleine-inflation-voici-les-5-departements-ou-faire-ses-courses-en-ligne-coute-le-moins-cher-n262058.html</t>
+          <t>https://www.lesnumeriques.com/mobilite-c17/samsung-galaxy-ces-applications-cachees-vont-ameliorer-votre-quotidien-n261951.html</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>14. Santé</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-09-19T08:13:01+00:00</t>
+          <t>2026-09-19T08:15:00+00:00</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>OnePlus 15 : il défie l’iPhone 17 Pro et le Galaxy S26 Ultra… mais coûte 800 € moins cher</t>
+          <t>Actualité : En pleine inflation, voici les 5 départements où faire ses courses en ligne coûte le moins cher</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://www.01net.com/bons-plans/oneplus-15-il-defie-liphone-17-pro-et-le-galaxy-s26-ultra-mais-coute-800-e-moins-cher.html</t>
+          <t>https://www.lesnumeriques.com/societe-numerique/en-pleine-inflation-voici-les-5-departements-ou-faire-ses-courses-en-ligne-coute-le-moins-cher-n262058.html</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>14. Santé</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Phonandroid</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-09-19T08:00:19+00:00</t>
+          <t>2026-09-19T08:13:01+00:00</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>On a vu (et entendu) les Cove de JBL, des enceintes qui modernisent l’audio à la maison</t>
+          <t>OnePlus 15 : il défie l’iPhone 17 Pro et le Galaxy S26 Ultra… mais coûte 800 € moins cher</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://www.phonandroid.com/on-a-vu-et-entendu-les-cove-de-jbl-des-enceintes-qui-modernisent-laudio-a-la-maison.html</t>
+          <t>https://www.01net.com/bons-plans/oneplus-15-il-defie-liphone-17-pro-et-le-galaxy-s26-ultra-mais-coute-800-e-moins-cher.html</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>8. Audio</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>Phonandroid</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-09-19T08:00:10+00:00</t>
+          <t>2026-09-19T08:00:19+00:00</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Le Futuroscope dévoile sa dernière nouveauté, et elle est spectaculaire</t>
+          <t>On a vu (et entendu) les Cove de JBL, des enceintes qui modernisent l’audio à la maison</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/19/le-futuroscope-devoile-sa-derniere-nouveaute-et-elle-est-spectaculaire/</t>
+          <t>https://www.phonandroid.com/on-a-vu-et-entendu-les-cove-de-jbl-des-enceintes-qui-modernisent-laudio-a-la-maison.html</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>NON_CLASSE</t>
+          <t>8. Audio</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-09-19T08:00:03+00:00</t>
+          <t>2026-09-19T08:00:10+00:00</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Actualité : Les codes promo les plus utilisés de la semaine</t>
+          <t>Le Futuroscope dévoile sa dernière nouveauté, et elle est spectaculaire</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/societe-numerique/les-codes-promo-les-plus-utilises-de-la-semaine-n262059.html</t>
+          <t>https://www.journaldugeek.com/2026/09/19/le-futuroscope-devoile-sa-derniere-nouveaute-et-elle-est-spectaculaire/</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>19. Sponso</t>
+          <t>NON_CLASSE</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Frandroid - RSS</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2474,71 +2474,71 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Les meilleurs smartphones à grand écran (6,7 pouces et plus) en 2026</t>
+          <t>Actualité : Les codes promo les plus utilisés de la semaine</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/guide-dachat/382644_6-alternatives-samsung-galaxy-note-7</t>
+          <t>https://www.lesnumeriques.com/societe-numerique/les-codes-promo-les-plus-utilises-de-la-semaine-n262059.html</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>19. Sponso</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Numerama</t>
+          <t>Frandroid - RSS</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-09-19T07:40:15+00:00</t>
+          <t>2026-09-19T08:00:03+00:00</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Un rapport de renseignement écrit avec une IA a failli déclencher une crise militaire entre les États-Unis et la Chine</t>
+          <t>Les meilleurs smartphones à grand écran (6,7 pouces et plus) en 2026</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://www.numerama.com/cyberguerre/2336305-un-rapport-de-renseignement-ecrit-avec-une-ia-a-failli-declencher-une-crise-militaire-entre-les-etats-unis-et-la-chine.html</t>
+          <t>https://www.frandroid.com/guide-dachat/382644_6-alternatives-samsung-galaxy-note-7</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>6. IA</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Frandroid - RSS</t>
+          <t>Numerama</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-09-19T07:35:00+00:00</t>
+          <t>2026-09-19T07:40:15+00:00</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Le prix de la version la plus complète du Dyson V16 qui aspire et lave en un geste s’effondre de 280 €</t>
+          <t>Un rapport de renseignement écrit avec une IA a failli déclencher une crise militaire entre les États-Unis et la Chine</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/produits-android/3252607_le-prix-de-la-version-la-plus-complete-du-dyson-v16-qui-aspire-et-lave-en-un-geste-seffondre-de-280-e</t>
+          <t>https://www.numerama.com/cyberguerre/2336305-un-rapport-de-renseignement-ecrit-avec-une-ia-a-failli-declencher-une-crise-militaire-entre-les-etats-unis-et-la-chine.html</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>6. IA</t>
         </is>
       </c>
     </row>
@@ -2550,17 +2550,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-09-19T07:31:05+00:00</t>
+          <t>2026-09-19T07:35:00+00:00</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>iPhone 18 Pro : le démontage confirme une mauvaise nouvelle difficile à justifier</t>
+          <t>Le prix de la version la plus complète du Dyson V16 qui aspire et lave en un geste s’effondre de 280 €</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/marques/apple/3253509_iphone-18-pro-le-demontage-confirme-une-mauvaise-nouvelle-difficile-a-justifier</t>
+          <t>https://www.frandroid.com/produits-android/3252607_le-prix-de-la-version-la-plus-complete-du-dyson-v16-qui-aspire-et-lave-en-un-geste-seffondre-de-280-e</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -2577,22 +2577,22 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-09-19T07:29:38+00:00</t>
+          <t>2026-09-19T07:31:05+00:00</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Google prépare l’intégration d’iMessage dans Gemini pour macOS</t>
+          <t>iPhone 18 Pro : le démontage confirme une mauvaise nouvelle difficile à justifier</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/marques/google/3253495_google-prepare-lintegration-dimessage-dans-gemini-pour-macos</t>
+          <t>https://www.frandroid.com/marques/apple/3253509_iphone-18-pro-le-demontage-confirme-une-mauvaise-nouvelle-difficile-a-justifier</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>5. Logiciels _ OS</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
@@ -2604,152 +2604,152 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-09-19T07:28:24+00:00</t>
+          <t>2026-09-19T07:29:38+00:00</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>12 Go de RAM et 4 350 mAh : Clicks muscle son « BlackBerry » sans hausser le prix</t>
+          <t>Google prépare l’intégration d’iMessage dans Gemini pour macOS</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/marques/blackberry/3253497_12-go-de-ram-et-4-350-mah-clicks-muscle-son-blackberry-sans-hausser-le-prix</t>
+          <t>https://www.frandroid.com/marques/google/3253495_google-prepare-lintegration-dimessage-dans-gemini-pour-macos</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>3. Periphérique</t>
+          <t>5. Logiciels _ OS</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>Frandroid - RSS</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-09-19T07:19:00+00:00</t>
+          <t>2026-09-19T07:28:24+00:00</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Actualité : Sony FE 600mm F6.3 GM OSS : le super téléobjectif 30% plus léger et 1100 € moins cher que Nikon</t>
+          <t>12 Go de RAM et 4 350 mAh : Clicks muscle son « BlackBerry » sans hausser le prix</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/objectif/sony-fe-600mm-f6-3-gm-oss-le-super-teleobjectif-30-plus-leger-et-1100-moins-cher-que-nikon-n261881.html</t>
+          <t>https://www.frandroid.com/marques/blackberry/3253497_12-go-de-ram-et-4-350-mah-clicks-muscle-son-blackberry-sans-hausser-le-prix</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>5. Logiciels _ OS</t>
+          <t>3. Periphérique</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Numerama</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-09-19T07:05:00+00:00</t>
+          <t>2026-09-19T07:19:00+00:00</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Nintendo brade une flopée de jeux Square Enix sur l’eShop, dont plusieurs Final Fantasy</t>
+          <t>Actualité : Sony FE 600mm F6.3 GM OSS : le super téléobjectif 30% plus léger et 1100 € moins cher que Nikon</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://www.numerama.com/pop-culture/2336149-nintendo-brade-une-flopee-de-jeux-square-enix-sur-leshop-dont-plusieurs-final-fantasy.html</t>
+          <t>https://www.lesnumeriques.com/objectif/sony-fe-600mm-f6-3-gm-oss-le-super-teleobjectif-30-plus-leger-et-1100-moins-cher-que-nikon-n261881.html</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>15. ludique</t>
+          <t>5. Logiciels _ OS</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>Numerama</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-09-19T07:00:16+00:00</t>
+          <t>2026-09-19T07:05:00+00:00</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>BYD veut concurrencer Rolls-Royce avec des monstres de 1 200 ch signés Yangwang</t>
+          <t>Nintendo brade une flopée de jeux Square Enix sur l’eShop, dont plusieurs Final Fantasy</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://www.01net.com/actualites/byd-concurrencer-rolls-royce-monstres-1-200-ch-yangwang.html</t>
+          <t>https://www.numerama.com/pop-culture/2336149-nintendo-brade-une-flopee-de-jeux-square-enix-sur-leshop-dont-plusieurs-final-fantasy.html</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>10. Voiture</t>
+          <t>15. ludique</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-09-19T06:59:00+00:00</t>
+          <t>2026-09-19T07:00:16+00:00</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Actualité : La critique de la série Neagley a rejoint notre catalogue</t>
+          <t>BYD veut concurrencer Rolls-Royce avec des monstres de 1 200 ch signés Yangwang</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/serie/la-critique-de-la-serie-neagley-a-rejoint-notre-catalogue-n262053.html</t>
+          <t>https://www.01net.com/actualites/byd-concurrencer-rolls-royce-monstres-1-200-ch-yangwang.html</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>15. ludique</t>
+          <t>10. Voiture</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Phonandroid</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-09-19T06:50:27+00:00</t>
+          <t>2026-09-19T06:59:00+00:00</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Gears of War E-Day : toutes les infos sur un épisode anniversaire, qui marque le grand retour des exclusivités Xbox</t>
+          <t>Actualité : La critique de la série Neagley a rejoint notre catalogue</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://www.phonandroid.com/gears-of-war-e-day-toutes-les-infos-sur-un-episode-anniversaire-qui-marque-le-grand-retour-des-exclusivites-xbox.html</t>
+          <t>https://www.lesnumeriques.com/serie/la-critique-de-la-serie-neagley-a-rejoint-notre-catalogue-n262053.html</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -2761,27 +2761,27 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>Phonandroid</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-09-19T06:45:00+00:00</t>
+          <t>2026-09-19T06:50:27+00:00</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Actualité : On l'attendait : Jura dévoile enfin sa machine avec broyeur ultra-compacte et sans compromis</t>
+          <t>Gears of War E-Day : toutes les infos sur un épisode anniversaire, qui marque le grand retour des exclusivités Xbox</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/machine-a-cafe-automatique/on-l-attendait-jura-devoile-enfin-sa-machine-avec-broyeur-ultra-compacte-et-sans-compromis-n262037.html</t>
+          <t>https://www.phonandroid.com/gears-of-war-e-day-toutes-les-infos-sur-un-episode-anniversaire-qui-marque-le-grand-retour-des-exclusivites-xbox.html</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>12. Cuisine</t>
+          <t>15. ludique</t>
         </is>
       </c>
     </row>
@@ -2798,179 +2798,179 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Actualité : "Ça a failli déclencher une guerre" : comment une IA aurait pu plonger le monde dans un incident militaire entre les États-Unis et la Chine</t>
+          <t>Actualité : On l'attendait : Jura dévoile enfin sa machine avec broyeur ultra-compacte et sans compromis</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/intelligence-artificielle/ca-a-failli-declencher-une-guerre-comment-une-ia-aurait-pu-plonger-le-monde-dans-un-incident-militaire-entre-les-etats-unis-et-la-chine-n262056.html</t>
+          <t>https://www.lesnumeriques.com/machine-a-cafe-automatique/on-l-attendait-jura-devoile-enfin-sa-machine-avec-broyeur-ultra-compacte-et-sans-compromis-n262037.html</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>6. IA</t>
+          <t>12. Cuisine</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Frandroid - RSS</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-09-19T06:29:00+00:00</t>
+          <t>2026-09-19T06:45:00+00:00</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Comment bien choisir sa souris ? [Sponso]</t>
+          <t>Actualité : "Ça a failli déclencher une guerre" : comment une IA aurait pu plonger le monde dans un incident militaire entre les États-Unis et la Chine</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/produits-android/ordinateurs/peripheriques-pc/souris/3234113_comment-bien-choisir-sa-souris</t>
+          <t>https://www.lesnumeriques.com/intelligence-artificielle/ca-a-failli-declencher-une-guerre-comment-une-ia-aurait-pu-plonger-le-monde-dans-un-incident-militaire-entre-les-etats-unis-et-la-chine-n262056.html</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>6. IA</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>Frandroid - RSS</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-09-19T06:27:02+00:00</t>
+          <t>2026-09-19T06:29:00+00:00</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Actualité : Bon plan – Le compact / bridge Sony ZV-1 Seul à 630,85 € (-21%)</t>
+          <t>Comment bien choisir sa souris ? [Sponso]</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/compact-bridge/bon-plan-le-compact-bridge-sony-zv-1-seul-a-630-85-21-n262057.html</t>
+          <t>https://www.frandroid.com/produits-android/ordinateurs/peripheriques-pc/souris/3234113_comment-bien-choisir-sa-souris</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>19. Sponso</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-09-19T06:01:17+00:00</t>
+          <t>2026-09-19T06:27:02+00:00</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Cyberattaques : un géant du DDoS a été neutralisé après des « centaines de milliers d’attaques »</t>
+          <t>Actualité : Bon plan – Le compact / bridge Sony ZV-1 Seul à 630,85 € (-21%)</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://www.01net.com/actualites/cyberattaques-un-geant-du-ddos-a-ete-neutralise-apres-des-centaines-de-milliers-dattaques.html</t>
+          <t>https://www.lesnumeriques.com/compact-bridge/bon-plan-le-compact-bridge-sony-zv-1-seul-a-630-85-21-n262057.html</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>16. actu jur et pol</t>
+          <t>19. Sponso</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-09-19T06:01:00+00:00</t>
+          <t>2026-09-19T06:01:17+00:00</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Actualité : 100 % de produits non conformes : le danger des appareils électriques vendus à prix mini sur Amazon, Darty ou Temu</t>
+          <t>Cyberattaques : un géant du DDoS a été neutralisé après des « centaines de milliers d’attaques »</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/divers-electromenager/100-de-produits-non-conformes-le-danger-des-appareils-electriques-vendus-a-prix-mini-sur-amazon-darty-ou-temu-n262006.html</t>
+          <t>https://www.01net.com/actualites/cyberattaques-un-geant-du-ddos-a-ete-neutralise-apres-des-centaines-de-milliers-dattaques.html</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>NON_CLASSE</t>
+          <t>16. actu jur et pol</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Frandroid - RSS</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-09-19T05:44:00+00:00</t>
+          <t>2026-09-19T06:01:00+00:00</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Boulanger fait chuter le prix de ce TV 4K QLED 65 pouces Philips Ambilight à moins de 700 €</t>
+          <t>Actualité : 100 % de produits non conformes : le danger des appareils électriques vendus à prix mini sur Amazon, Darty ou Temu</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/bons-plans/3250245_boulanger-fait-chuter-le-prix-de-ce-tv-4k-qled-65-pouces-philips-ambilight-a-moins-de-700-e</t>
+          <t>https://www.lesnumeriques.com/divers-electromenager/100-de-produits-non-conformes-le-danger-des-appareils-electriques-vendus-a-prix-mini-sur-amazon-darty-ou-temu-n262006.html</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>7. Video</t>
+          <t>NON_CLASSE</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>Frandroid - RSS</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-09-19T05:15:02+00:00</t>
+          <t>2026-09-19T05:44:00+00:00</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Top bon plan : Samsung, Delonghi, SwitchBot... les meilleurs bons plans du 19/09/2026</t>
+          <t>Boulanger fait chuter le prix de ce TV 4K QLED 65 pouces Philips Ambilight à moins de 700 €</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/societe-numerique/samsung-switchbot-les-meilleurs-bons-plans-du-19-09-2026-n262050.html</t>
+          <t>https://www.frandroid.com/bons-plans/3250245_boulanger-fait-chuter-le-prix-de-ce-tv-4k-qled-65-pouces-philips-ambilight-a-moins-de-700-e</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>12. Cuisine</t>
+          <t>7. Video</t>
         </is>
       </c>
     </row>
@@ -2982,22 +2982,22 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-09-19T05:15:00+00:00</t>
+          <t>2026-09-19T05:15:02+00:00</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Actualité : Google savait que Gemini a attaqué de vraies entreprises et l'a gardé secret pendant des mois</t>
+          <t>Top bon plan : Samsung, Delonghi, SwitchBot... les meilleurs bons plans du 19/09/2026</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/intelligence-artificielle/google-savait-que-gemini-a-attaque-de-vraies-entreprises-et-l-a-garde-secret-pendant-des-mois-n262048.html</t>
+          <t>https://www.lesnumeriques.com/societe-numerique/samsung-switchbot-les-meilleurs-bons-plans-du-19-09-2026-n262050.html</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>6. IA</t>
+          <t>12. Cuisine</t>
         </is>
       </c>
     </row>
@@ -3009,22 +3009,22 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-09-19T05:11:31+00:00</t>
+          <t>2026-09-19T05:15:00+00:00</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Actualité : Pour un bon robot cuiseur multifonctions à prix abordable, privilégiez...</t>
+          <t>Actualité : Google savait que Gemini a attaqué de vraies entreprises et l'a gardé secret pendant des mois</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/robot-cuiseur-multifonction/pour-un-bon-robot-cuiseur-multifonctions-a-prix-abordable-privilegiez-n262051.html</t>
+          <t>https://www.lesnumeriques.com/intelligence-artificielle/google-savait-que-gemini-a-attaque-de-vraies-entreprises-et-l-a-garde-secret-pendant-des-mois-n262048.html</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>13. Maison</t>
+          <t>6. IA</t>
         </is>
       </c>
     </row>
@@ -3036,22 +3036,22 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-09-19T05:01:03+00:00</t>
+          <t>2026-09-19T05:11:31+00:00</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Actualité : Bon plan – La machine à café automatique avec broyeur Delonghi Magnifica Evo Next "5 étoiles" à 468,69 € (-21%)</t>
+          <t>Actualité : Pour un bon robot cuiseur multifonctions à prix abordable, privilégiez...</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/machine-a-cafe-automatique/bon-plan-la-machine-a-cafe-automatique-avec-broyeur-delonghi-magnifica-evo-next-5-etoiles-a-468-69-21-n262052.html</t>
+          <t>https://www.lesnumeriques.com/robot-cuiseur-multifonction/pour-un-bon-robot-cuiseur-multifonctions-a-prix-abordable-privilegiez-n262051.html</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>12. Cuisine</t>
+          <t>13. Maison</t>
         </is>
       </c>
     </row>
@@ -3063,44 +3063,44 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-09-19T05:00:00+00:00</t>
+          <t>2026-09-19T05:01:03+00:00</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Actualité : On a passé l’écran de l’iPhone 18 Pro au microscope : voici ce qu'Apple a caché</t>
+          <t>Actualité : Bon plan – La machine à café automatique avec broyeur Delonghi Magnifica Evo Next "5 étoiles" à 468,69 € (-21%)</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/telephone-portable/on-a-passe-l-ecran-de-l-iphone-18-pro-au-microscope-voici-ce-qu-apple-a-cache-n262039.html</t>
+          <t>https://www.lesnumeriques.com/machine-a-cafe-automatique/bon-plan-la-machine-a-cafe-automatique-avec-broyeur-delonghi-magnifica-evo-next-5-etoiles-a-468-69-21-n262052.html</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>12. Cuisine</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-09-19T04:54:32+00:00</t>
+          <t>2026-09-19T05:00:00+00:00</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>AliExpress : 5 smartphones Xiaomi à prix cassé en septembre 2026, lequel est fait pour vous ?</t>
+          <t>Actualité : On a passé l’écran de l’iPhone 18 Pro au microscope : voici ce qu'Apple a caché</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>https://www.01net.com/bons-plans/aliexpress-smartphones-xiaomi-prix-casse-lequel-est-fait-pour-vous.html</t>
+          <t>https://www.lesnumeriques.com/telephone-portable/on-a-passe-l-ecran-de-l-iphone-18-pro-au-microscope-voici-ce-qu-apple-a-cache-n262039.html</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -3112,108 +3112,108 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Numerama</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-09-19T04:45:00+00:00</t>
+          <t>2026-09-19T04:54:32+00:00</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Baguette One, bientôt un vol orbital inédit du Starship, manœuvre parfaite de la Nasa – le récap’ sciences de la semaine</t>
+          <t>AliExpress : 5 smartphones Xiaomi à prix cassé en septembre 2026, lequel est fait pour vous ?</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>https://www.numerama.com/sciences/2335785-baguette-one-vol-orbital-inedit-du-starship-manoeuvre-parfaite-de-la-nasa-le-recap-sciences-de-la-semaine.html</t>
+          <t>https://www.01net.com/bons-plans/aliexpress-smartphones-xiaomi-prix-casse-lequel-est-fait-pour-vous.html</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>18. Sciences</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>Numerama</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-09-19T04:40:02+00:00</t>
+          <t>2026-09-19T04:45:00+00:00</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Actualité : Bon plan – Le gonfleur de pneu Xiaomi Portable Electric Air Compressor 2 "5 étoiles" à 39,99 €</t>
+          <t>Baguette One, bientôt un vol orbital inédit du Starship, manœuvre parfaite de la Nasa – le récap’ sciences de la semaine</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/gonfleur-pneu/bon-plan-le-gonfleur-de-pneu-xiaomi-portable-electric-air-compressor-2-5-etoiles-a-39-99-n262049.html</t>
+          <t>https://www.numerama.com/sciences/2335785-baguette-one-vol-orbital-inedit-du-starship-manoeuvre-parfaite-de-la-nasa-le-recap-sciences-de-la-semaine.html</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2. PC</t>
+          <t>18. Sciences</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Numerama</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-09-18T22:01:00+00:00</t>
+          <t>2026-09-19T04:40:02+00:00</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Sophie Adenot a une peluche Pikachu dans l’ISS, et ce n’est pas pour devenir la meilleure dresseuse</t>
+          <t>Actualité : Bon plan – Le gonfleur de pneu Xiaomi Portable Electric Air Compressor 2 "5 étoiles" à 39,99 €</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>https://www.numerama.com/sciences/2335725-sophie-adenot-a-une-peluche-pikachu-dans-liss-et-ce-nest-pas-pour-devenir-la-meilleure-dresseuse.html</t>
+          <t>https://www.lesnumeriques.com/gonfleur-pneu/bon-plan-le-gonfleur-de-pneu-xiaomi-portable-electric-air-compressor-2-5-etoiles-a-39-99-n262049.html</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>18. Sciences</t>
+          <t>2. PC</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>Numerama</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-09-18T22:00:05+00:00</t>
+          <t>2026-09-18T22:01:00+00:00</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Actualité : Bon plan – L'enceinte connectée Audio Pro C5 MkII à 149,00 € (-26%)</t>
+          <t>Sophie Adenot a une peluche Pikachu dans l’ISS, et ce n’est pas pour devenir la meilleure dresseuse</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/enceintes-sans-fil/bon-plan-l-enceinte-connectee-audio-pro-c5-mkii-a-149-00-26-n262046.html</t>
+          <t>https://www.numerama.com/sciences/2335725-sophie-adenot-a-une-peluche-pikachu-dans-liss-et-ce-nest-pas-pour-devenir-la-meilleure-dresseuse.html</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>8. Audio</t>
+          <t>18. Sciences</t>
         </is>
       </c>
     </row>
@@ -3225,184 +3225,184 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-09-18T22:00:04+00:00</t>
+          <t>2026-09-18T22:00:05+00:00</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Actualité : Bon plan – Le smartphone Samsung Galaxy A57 5G 128 Go à 329,00 € (-14%)</t>
+          <t>Actualité : Bon plan – L'enceinte connectée Audio Pro C5 MkII à 149,00 € (-26%)</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/telephone-portable/bon-plan-le-smartphone-samsung-galaxy-a57-5g-128-go-a-329-00-14-n262045.html</t>
+          <t>https://www.lesnumeriques.com/enceintes-sans-fil/bon-plan-l-enceinte-connectee-audio-pro-c5-mkii-a-149-00-26-n262046.html</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>8. Audio</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>KultureGeek</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-09-18T20:50:26+00:00</t>
+          <t>2026-09-18T22:00:04+00:00</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Des chercheurs en sécurité ont piraté OpenAI grâce à l’IA Claude</t>
+          <t>Actualité : Bon plan – Le smartphone Samsung Galaxy A57 5G 128 Go à 329,00 € (-14%)</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>https://kulturegeek.fr/news-359758/chercheurs-securite-pirate-openai-grace-lia-claude</t>
+          <t>https://www.lesnumeriques.com/telephone-portable/bon-plan-le-smartphone-samsung-galaxy-a57-5g-128-go-a-329-00-14-n262045.html</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>6. IA</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Frandroid - RSS</t>
+          <t>KultureGeek</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-09-18T19:05:31+00:00</t>
+          <t>2026-09-18T20:50:26+00:00</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>« Un plein à 10 euros » : Lidl casse le prix de sa recharge électrique, c’est le tarif le moins cher de France</t>
+          <t>Des chercheurs en sécurité ont piraté OpenAI grâce à l’IA Claude</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/survoltes/voitures-electriques/3253487_un-plein-a-10-euros-lidl-casse-le-prix-de-sa-recharge-electrique-cest-le-tarif-le-moins-cher-de-france</t>
+          <t>https://kulturegeek.fr/news-359758/chercheurs-securite-pirate-openai-grace-lia-claude</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>10. Voiture</t>
+          <t>6. IA</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>Frandroid - RSS</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-09-18T18:49:08+00:00</t>
+          <t>2026-09-18T19:05:31+00:00</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Garmin Forerunner 265 : -51% ce week-end, une belle affaire pour les vrais sportifs</t>
+          <t>« Un plein à 10 euros » : Lidl casse le prix de sa recharge électrique, c’est le tarif le moins cher de France</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>https://www.01net.com/bons-plans/garmin-forerunner-265-51-ce-week-end-une-belle-affaire-pour-les-vrais-sportifs.html</t>
+          <t>https://www.frandroid.com/survoltes/voitures-electriques/3253487_un-plein-a-10-euros-lidl-casse-le-prix-de-sa-recharge-electrique-cest-le-tarif-le-moins-cher-de-france</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>14. Santé</t>
+          <t>10. Voiture</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>KultureGeek</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-09-18T18:15:44+00:00</t>
+          <t>2026-09-18T18:49:08+00:00</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Elias 2-24 b : les astronomes découvrent la plus jeune planète jamais observée, et sa taille défie les modèles</t>
+          <t>Garmin Forerunner 265 : -51% ce week-end, une belle affaire pour les vrais sportifs</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>https://kulturegeek.fr/news-359753/elias-2-24-b-astronomes-decouvrent-plus-jeune-planete-jamais-observee-taille-defie-modeles</t>
+          <t>https://www.01net.com/bons-plans/garmin-forerunner-265-51-ce-week-end-une-belle-affaire-pour-les-vrais-sportifs.html</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>18. Sciences</t>
+          <t>14. Santé</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>KultureGeek</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-09-18T18:13:58+00:00</t>
+          <t>2026-09-18T18:15:44+00:00</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Xiaomi s’est gouré : il vend le dernier Poco X8 Pro au prix du modèle d’il y a 2 ans 😱</t>
+          <t>Elias 2-24 b : les astronomes découvrent la plus jeune planète jamais observée, et sa taille défie les modèles</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>https://www.01net.com/bons-plans/xiaomi-sest-goure-il-vend-le-dernier-poco-x8-pro-au-prix-du-modele-dil-y-a-2-ans.html</t>
+          <t>https://kulturegeek.fr/news-359753/elias-2-24-b-astronomes-decouvrent-plus-jeune-planete-jamais-observee-taille-defie-modeles</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>18. Sciences</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Phonandroid</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-09-18T17:46:14+00:00</t>
+          <t>2026-09-18T18:13:58+00:00</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Amazon arrête la livraison gratuite de livres via lockers en France</t>
+          <t>Xiaomi s’est gouré : il vend le dernier Poco X8 Pro au prix du modèle d’il y a 2 ans 😱</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>https://www.phonandroid.com/amazon-arrete-la-livraison-gratuite-de-livres-via-lockers-en-france.html</t>
+          <t>https://www.01net.com/bons-plans/xiaomi-sest-goure-il-vend-le-dernier-poco-x8-pro-au-prix-du-modele-dil-y-a-2-ans.html</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>4. Tablette</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
@@ -3414,76 +3414,76 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-09-18T17:46:07+00:00</t>
+          <t>2026-09-18T17:46:14+00:00</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>L’excellent aspirateur balai sans fil Shark PowerDetect Speed Collection Luxe Clean &amp; Empty passe à prix cassé avec ce code</t>
+          <t>Amazon arrête la livraison gratuite de livres via lockers en France</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>https://www.phonandroid.com/lexcellent-aspirateur-balai-sans-fil-shark-powerdetect-speed-collection-luxe-clean-empty-passe-a-prix-casse-avec-ce-code.html</t>
+          <t>https://www.phonandroid.com/amazon-arrete-la-livraison-gratuite-de-livres-via-lockers-en-france.html</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>11. Menage</t>
+          <t>4. Tablette</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>KultureGeek</t>
+          <t>Phonandroid</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-09-18T17:43:50+00:00</t>
+          <t>2026-09-18T17:46:07+00:00</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>La Californie veut imposer un bouton d’arrêt d’urgence aux IA</t>
+          <t>L’excellent aspirateur balai sans fil Shark PowerDetect Speed Collection Luxe Clean &amp; Empty passe à prix cassé avec ce code</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>https://kulturegeek.fr/news-359748/californie-veut-imposer-bouton-darret-durgence-ia</t>
+          <t>https://www.phonandroid.com/lexcellent-aspirateur-balai-sans-fil-shark-powerdetect-speed-collection-luxe-clean-empty-passe-a-prix-casse-avec-ce-code.html</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>6. IA</t>
+          <t>11. Menage</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>KultureGeek</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-09-18T17:30:13+00:00</t>
+          <t>2026-09-18T17:43:50+00:00</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>La bêta de World of Warcraft Forever est ouverte, voici tout ce qu’il faut savoir avant de l’installer !</t>
+          <t>La Californie veut imposer un bouton d’arrêt d’urgence aux IA</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/18/la-beta-de-world-of-warcraft-forever-est-ouverte-voici-tout-ce-quil-faut-savoir-avant-de-linstaller/</t>
+          <t>https://kulturegeek.fr/news-359748/californie-veut-imposer-bouton-darret-durgence-ia</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>NON_CLASSE</t>
+          <t>6. IA</t>
         </is>
       </c>
     </row>
@@ -3495,49 +3495,49 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-09-18T17:03:19+00:00</t>
+          <t>2026-09-18T17:30:13+00:00</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Les États-Unis admettent qu’ils ont déployé des armes en orbite : la militarisation de l’espace s’accélère</t>
+          <t>La bêta de World of Warcraft Forever est ouverte, voici tout ce qu’il faut savoir avant de l’installer !</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/18/etats-unis-admettent-deploye-armes-orbite-militarisation-lespace-saccelere/</t>
+          <t>https://www.journaldugeek.com/2026/09/18/la-beta-de-world-of-warcraft-forever-est-ouverte-voici-tout-ce-quil-faut-savoir-avant-de-linstaller/</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>16. actu jur et pol</t>
+          <t>NON_CLASSE</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Frandroid - RSS</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-09-18T17:00:00+00:00</t>
+          <t>2026-09-18T17:03:19+00:00</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>J’ai testé le Leica SL3-P : 45 Mpx, 40 i/s… le Leica qui veut tout faire</t>
+          <t>Les États-Unis admettent qu’ils ont déployé des armes en orbite : la militarisation de l’espace s’accélère</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/marques/leica/3235591_jai-teste-le-leica-sl3-p-45-mpx-40-i-s-le-leica-qui-veut-tout-faire</t>
+          <t>https://www.journaldugeek.com/2026/09/18/etats-unis-admettent-deploye-armes-orbite-militarisation-lespace-saccelere/</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>6. IA</t>
+          <t>16. actu jur et pol</t>
         </is>
       </c>
     </row>
@@ -3549,292 +3549,292 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-09-18T16:57:51+00:00</t>
+          <t>2026-09-18T17:00:00+00:00</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Pour ses 80 ans, EDF ouvre 70 sites secrets au public, dont ses centrales nucléaires</t>
+          <t>J’ai testé le Leica SL3-P : 45 Mpx, 40 i/s… le Leica qui veut tout faire</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/survoltes/energie/3252663_pour-ses-80-ans-edf-ouvre-70-sites-secrets-au-public-dont-ses-centrales-nucleaires</t>
+          <t>https://www.frandroid.com/marques/leica/3235591_jai-teste-le-leica-sl3-p-45-mpx-40-i-s-le-leica-qui-veut-tout-faire</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>13. Maison</t>
+          <t>6. IA</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>KultureGeek</t>
+          <t>Frandroid - RSS</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-09-18T16:50:20+00:00</t>
+          <t>2026-09-18T16:57:51+00:00</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Anthropic ouvre un laboratoire de biologie : Claude pourrait bientôt piloter des robots scientifiques</t>
+          <t>Pour ses 80 ans, EDF ouvre 70 sites secrets au public, dont ses centrales nucléaires</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>https://kulturegeek.fr/news-359736/anthropic-ouvre-laboratoire-biologie-claude-pourrait-piloter-robots-scientifiques</t>
+          <t>https://www.frandroid.com/survoltes/energie/3252663_pour-ses-80-ans-edf-ouvre-70-sites-secrets-au-public-dont-ses-centrales-nucleaires</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>6. IA</t>
+          <t>13. Maison</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Frandroid - RSS</t>
+          <t>KultureGeek</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-09-18T16:43:50+00:00</t>
+          <t>2026-09-18T16:50:20+00:00</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>1 heure et 4 erreurs : comment l’IA a métamorphosé ma vieille liseuse en écran domotique</t>
+          <t>Anthropic ouvre un laboratoire de biologie : Claude pourrait bientôt piloter des robots scientifiques</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/marques/3251785_1-heure-et-4-erreurs-comment-lia-a-metamorphose-ma-vieille-liseuse-en-ecran-domotique</t>
+          <t>https://kulturegeek.fr/news-359736/anthropic-ouvre-laboratoire-biologie-claude-pourrait-piloter-robots-scientifiques</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>3. Periphérique</t>
+          <t>6. IA</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Phonandroid</t>
+          <t>Frandroid - RSS</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-09-18T16:40:37+00:00</t>
+          <t>2026-09-18T16:43:50+00:00</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>100 € en moins sur les Galaxy Buds 4 Pro chez Samsung : les écouteurs perdent 40% de leur prix</t>
+          <t>1 heure et 4 erreurs : comment l’IA a métamorphosé ma vieille liseuse en écran domotique</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>https://www.phonandroid.com/100-e-moins-galaxy-buds-4-pro-samsung-ecouteurs-perdent-40-prix.html</t>
+          <t>https://www.frandroid.com/marques/3251785_1-heure-et-4-erreurs-comment-lia-a-metamorphose-ma-vieille-liseuse-en-ecran-domotique</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>8. Audio</t>
+          <t>3. Periphérique</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>Phonandroid</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-09-18T16:30:47+00:00</t>
+          <t>2026-09-18T16:40:37+00:00</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>HONOR Magic V5 : bradé à -52 %, il n’a pourtant rien d’un smartphone au rabais, bien au contraire</t>
+          <t>100 € en moins sur les Galaxy Buds 4 Pro chez Samsung : les écouteurs perdent 40% de leur prix</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>https://www.01net.com/bons-plans/honor-magic-v5-brade-a-52-il-na-pourtant-rien-dun-smartphone-au-rabais-bien-au-contraire.html</t>
+          <t>https://www.phonandroid.com/100-e-moins-galaxy-buds-4-pro-samsung-ecouteurs-perdent-40-prix.html</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>8. Audio</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-09-18T16:30:35+00:00</t>
+          <t>2026-09-18T16:30:47+00:00</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Test du Ninja Crispi DualZone : l’airfryer en verre XXL qui remplace notre four</t>
+          <t>HONOR Magic V5 : bradé à -52 %, il n’a pourtant rien d’un smartphone au rabais, bien au contraire</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/test/test-du-ninja-crispi-dualzone-lairfryer-en-verre-xxl-qui-remplace-notre-four/</t>
+          <t>https://www.01net.com/bons-plans/honor-magic-v5-brade-a-52-il-na-pourtant-rien-dun-smartphone-au-rabais-bien-au-contraire.html</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>12. Cuisine</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Frandroid - RSS</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-09-18T16:17:00+00:00</t>
+          <t>2026-09-18T16:30:35+00:00</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Les mythiques courses de pod de Star Wars reviennent bientôt dans Galactic Racer, en précommande à 44,99 € sur PS5</t>
+          <t>Test du Ninja Crispi DualZone : l’airfryer en verre XXL qui remplace notre four</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/bons-plans/3253083_les-mythiques-courses-de-pod-de-star-wars-reviennent-bientot-dans-galactic-racer-en-precommande-a-4499-e-sur-ps5</t>
+          <t>https://www.journaldugeek.com/test/test-du-ninja-crispi-dualzone-lairfryer-en-verre-xxl-qui-remplace-notre-four/</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>14. Santé</t>
+          <t>12. Cuisine</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Frandroid - Actualités</t>
+          <t>Frandroid - RSS</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-09-18T16:15:51+00:00</t>
+          <t>2026-09-18T16:17:00+00:00</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Test du Xiaomi Redmi Note 17 Pro 5G, le smartphone qui mise tout sur l’autonomie</t>
+          <t>Les mythiques courses de pod de Star Wars reviennent bientôt dans Galactic Racer, en précommande à 44,99 € sur PS5</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/marques/xiaomi/3235547_test-du-xiaomi-redmi-note-17-pro-5g-le-smartphone-qui-mise-tout-sur-lautonomie</t>
+          <t>https://www.frandroid.com/bons-plans/3253083_les-mythiques-courses-de-pod-de-star-wars-reviennent-bientot-dans-galactic-racer-en-precommande-a-4499-e-sur-ps5</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>14. Santé</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Phonandroid</t>
+          <t>Frandroid - Actualités</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-09-18T16:03:51+00:00</t>
+          <t>2026-09-18T16:15:51+00:00</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Disney+ va diffuser de la publicité aux abonnés Standard et Premium, les déceptions s’enchaînent avec la plateforme de streaming</t>
+          <t>Test du Xiaomi Redmi Note 17 Pro 5G, le smartphone qui mise tout sur l’autonomie</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>https://www.phonandroid.com/disney-va-diffuser-de-la-publicite-aux-abonnes-standard-et-premium-les-deceptions-senchainent-avec-la-plateforme-de-streaming.html</t>
+          <t>https://www.frandroid.com/marques/xiaomi/3235547_test-du-xiaomi-redmi-note-17-pro-5g-le-smartphone-qui-mise-tout-sur-lautonomie</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>15. ludique</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>Phonandroid</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-09-18T16:00:11+00:00</t>
+          <t>2026-09-18T16:03:51+00:00</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Lunettes connectées : suite à plusieurs plaintes pour harcèlement sexuel, la France lance une enquête</t>
+          <t>Disney+ va diffuser de la publicité aux abonnés Standard et Premium, les déceptions s’enchaînent avec la plateforme de streaming</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>https://www.01net.com/actualites/lunettes-connectees-suite-a-plusieurs-plaintes-pour-harcelement-sexuel-la-france-lance-une-enquete.html</t>
+          <t>https://www.phonandroid.com/disney-va-diffuser-de-la-publicite-aux-abonnes-standard-et-premium-les-deceptions-senchainent-avec-la-plateforme-de-streaming.html</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>15. ludique</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Frandroid - Actualités</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-09-18T15:59:18+00:00</t>
+          <t>2026-09-18T16:00:11+00:00</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Tesla Semi : la formule « une journée complète avec un seul arrêt » arrive en France</t>
+          <t>Lunettes connectées : suite à plusieurs plaintes pour harcèlement sexuel, la France lance une enquête</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/marques/tesla/3252189_tesla-semi-la-formule-une-journee-complete-avec-un-seul-arret-arrive-en-france</t>
+          <t>https://www.01net.com/actualites/lunettes-connectees-suite-a-plusieurs-plaintes-pour-harcelement-sexuel-la-france-lance-une-enquete.html</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>10. Voiture</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
@@ -3846,44 +3846,44 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-09-18T15:57:34+00:00</t>
+          <t>2026-09-18T15:59:18+00:00</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>DAS : qu’est-ce que c’est et quels sont les smartphones qui émettent le moins de rayonnement ?</t>
+          <t>Tesla Semi : la formule « une journée complète avec un seul arrêt » arrive en France</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/produits-android/smartphone/462065_classement-das-quels-sont-les-smartphones-qui-emettent-le-moins-et-le-plus-de-radiations</t>
+          <t>https://www.frandroid.com/marques/tesla/3252189_tesla-semi-la-formule-une-journee-complete-avec-un-seul-arret-arrive-en-france</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>10. Voiture</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>KultureGeek</t>
+          <t>Frandroid - Actualités</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-09-18T15:52:37+00:00</t>
+          <t>2026-09-18T15:57:34+00:00</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Samsung rend disponible One UI 9 (Android 17) sur ses Galaxy</t>
+          <t>DAS : qu’est-ce que c’est et quels sont les smartphones qui émettent le moins de rayonnement ?</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>https://kulturegeek.fr/news-359738/samsung-rend-disponible-one-ui-9-android-17-galaxy</t>
+          <t>https://www.frandroid.com/produits-android/smartphone/462065_classement-das-quels-sont-les-smartphones-qui-emettent-le-moins-et-le-plus-de-radiations</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -3895,22 +3895,22 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Frandroid - Actualités</t>
+          <t>KultureGeek</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-09-18T15:49:14+00:00</t>
+          <t>2026-09-18T15:52:37+00:00</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Honor présente le Tiangong AXB35 Ultra, un mini-PC surpuissant conçu avec Nvidia</t>
+          <t>Samsung rend disponible One UI 9 (Android 17) sur ses Galaxy</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/produits-android/3253331_honor-presente-le-tiangong-axb35-ultra-un-mini-pc-surpuissant-concu-avec-nvidia</t>
+          <t>https://kulturegeek.fr/news-359738/samsung-rend-disponible-one-ui-9-android-17-galaxy</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -3927,22 +3927,22 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-09-18T15:41:43+00:00</t>
+          <t>2026-09-18T15:49:14+00:00</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>À bord du Tesla Semi, son responsable nous explique comment le FSD va débarquer</t>
+          <t>Honor présente le Tiangong AXB35 Ultra, un mini-PC surpuissant conçu avec Nvidia</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/marques/tesla/3252483_a-bord-du-tesla-semi-son-responsable-nous-explique-comment-le-fsd-va-debarquer</t>
+          <t>https://www.frandroid.com/produits-android/3253331_honor-presente-le-tiangong-axb35-ultra-un-mini-pc-surpuissant-concu-avec-nvidia</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>8. Audio</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
@@ -3954,103 +3954,103 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-09-18T15:39:57+00:00</t>
+          <t>2026-09-18T15:41:43+00:00</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Gears of War: E-Day, une configuration exigeante à prévoir sur PC</t>
+          <t>À bord du Tesla Semi, son responsable nous explique comment le FSD va débarquer</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/guide-dachat/3253211_gears-of-war-e-day-une-configuration-exigeante-a-prevoir-sur-pc</t>
+          <t>https://www.frandroid.com/marques/tesla/3252483_a-bord-du-tesla-semi-son-responsable-nous-explique-comment-le-fsd-va-debarquer</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2. PC</t>
+          <t>8. Audio</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Phonandroid</t>
+          <t>Frandroid - Actualités</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-09-18T15:30:48+00:00</t>
+          <t>2026-09-18T15:39:57+00:00</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Test Samsung Galaxy Z Flip8 : j’ai troqué mon iPhone contre ce smartphone pliant, ai-je vraiment envie de revenir en arrière ?</t>
+          <t>Gears of War: E-Day, une configuration exigeante à prévoir sur PC</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>https://www.phonandroid.com/test-samsung-galaxy-z-flip8-jai-troque-mon-iphone-contre-ce-smartphone-pliant-ai-je-vraiment-envie-de-revenir-en-arriere.html</t>
+          <t>https://www.frandroid.com/guide-dachat/3253211_gears-of-war-e-day-une-configuration-exigeante-a-prevoir-sur-pc</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>2. PC</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>Phonandroid</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-09-18T15:30:22+00:00</t>
+          <t>2026-09-18T15:30:48+00:00</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Batman Day 2026 : voici le programme complet, avec une exclu mondiale pour la France</t>
+          <t>Test Samsung Galaxy Z Flip8 : j’ai troqué mon iPhone contre ce smartphone pliant, ai-je vraiment envie de revenir en arrière ?</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/18/batman-day-2026-voici-le-programme-complet-avec-une-exclu-mondiale-pour-la-france/</t>
+          <t>https://www.phonandroid.com/test-samsung-galaxy-z-flip8-jai-troque-mon-iphone-contre-ce-smartphone-pliant-ai-je-vraiment-envie-de-revenir-en-arriere.html</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>16. actu jur et pol</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Phonandroid</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-09-18T15:30:21+00:00</t>
+          <t>2026-09-18T15:30:22+00:00</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Nous avons essayé les Vive Eagle, voici notre avis sur les lunettes connectées de HTC</t>
+          <t>Batman Day 2026 : voici le programme complet, avec une exclu mondiale pour la France</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>https://www.phonandroid.com/essai-htc-vive-eagle.html</t>
+          <t>https://www.journaldugeek.com/2026/09/18/batman-day-2026-voici-le-programme-complet-avec-une-exclu-mondiale-pour-la-france/</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>16. actu jur et pol</t>
         </is>
       </c>
     </row>
@@ -4062,22 +4062,22 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-09-18T15:29:57+00:00</t>
+          <t>2026-09-18T15:30:21+00:00</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Voitures électriques : plus besoin d’extraire du lithium neuf, Porsche vient de le prouver sur ses propres batteries</t>
+          <t>Nous avons essayé les Vive Eagle, voici notre avis sur les lunettes connectées de HTC</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>https://www.phonandroid.com/voitures-electriques-plus-besoin-dextraire-du-lithium-neuf-porsche-vient-de-le-prouver-sur-ses-propres-batteries.html</t>
+          <t>https://www.phonandroid.com/essai-htc-vive-eagle.html</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>10. Voiture</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
@@ -4089,76 +4089,76 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-09-18T15:16:13+00:00</t>
+          <t>2026-09-18T15:29:57+00:00</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>On a joué à Marvel’s Wolverine sur PS5 : trois raisons de ne pas perdre votre temps avec ce jeu</t>
+          <t>Voitures électriques : plus besoin d’extraire du lithium neuf, Porsche vient de le prouver sur ses propres batteries</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>https://www.phonandroid.com/marvel-wolverine-ps5-notre-avis-complet.html</t>
+          <t>https://www.phonandroid.com/voitures-electriques-plus-besoin-dextraire-du-lithium-neuf-porsche-vient-de-le-prouver-sur-ses-propres-batteries.html</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>15. ludique</t>
+          <t>10. Voiture</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>Phonandroid</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-09-18T15:14:44+00:00</t>
+          <t>2026-09-18T15:16:13+00:00</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Le casque à conduction osseuse Shokz à prix cassé : AliExpress le dégomme ce week-end 🥊</t>
+          <t>On a joué à Marvel’s Wolverine sur PS5 : trois raisons de ne pas perdre votre temps avec ce jeu</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>https://www.01net.com/bons-plans/le-casque-a-conduction-osseuse-shokz-a-prix-casse-aliexpress-le-degomme-ce-week-end.html</t>
+          <t>https://www.phonandroid.com/marvel-wolverine-ps5-notre-avis-complet.html</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>8. Audio</t>
+          <t>15. ludique</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Frandroid - Actualités</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-09-18T15:13:27+00:00</t>
+          <t>2026-09-18T15:14:44+00:00</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Asus lance le premier routeur Wi-Fi 8 : 900 euros et aucun appareil n’est compatible</t>
+          <t>Le casque à conduction osseuse Shokz à prix cassé : AliExpress le dégomme ce week-end 🥊</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/marques/asus/3253227_asus-lance-le-premier-routeur-wi-fi-8-900-euros-et-aucun-appareil-nest-compatible</t>
+          <t>https://www.01net.com/bons-plans/le-casque-a-conduction-osseuse-shokz-a-prix-casse-aliexpress-le-degomme-ce-week-end.html</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2. PC</t>
+          <t>8. Audio</t>
         </is>
       </c>
     </row>
@@ -4170,179 +4170,179 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-09-18T15:07:20+00:00</t>
+          <t>2026-09-18T15:13:27+00:00</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>iPhone 18 Pro : comment Spigen réinvente l’usage de votre nouveau smartphone au quotidien</t>
+          <t>Asus lance le premier routeur Wi-Fi 8 : 900 euros et aucun appareil n’est compatible</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/produits-android/smartphone/3250977_iphone-18-pro-comment-spigen-reinvente-lusage-de-votre-nouveau-smartphone-au-quotidien</t>
+          <t>https://www.frandroid.com/marques/asus/3253227_asus-lance-le-premier-routeur-wi-fi-8-900-euros-et-aucun-appareil-nest-compatible</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>2. PC</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>Frandroid - Actualités</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-09-18T15:02:45+00:00</t>
+          <t>2026-09-18T15:07:20+00:00</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>PS6 : la console portable serait un monstre de puissance grâce au PSSR3</t>
+          <t>iPhone 18 Pro : comment Spigen réinvente l’usage de votre nouveau smartphone au quotidien</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/18/ps6-la-console-portable-serait-un-monstre-de-puissance-grace-au-pssr3/</t>
+          <t>https://www.frandroid.com/produits-android/smartphone/3250977_iphone-18-pro-comment-spigen-reinvente-lusage-de-votre-nouveau-smartphone-au-quotidien</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2. PC</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Frandroid - Actualités</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-09-18T14:57:26+00:00</t>
+          <t>2026-09-18T15:02:45+00:00</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Avec son cadre garantie à vie, ce vélo cargo électrique peut grimper jusqu’à 350 km d’autonomie dans un cas très précis</t>
+          <t>PS6 : la console portable serait un monstre de puissance grâce au PSSR3</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/marques/vello-bike/3252383_avec-son-cadre-garantie-a-vie-ce-velo-cargo-electrique-peut-grimper-jusqua-350-km-dautonomie-dans-un-cas-tres-precis</t>
+          <t>https://www.journaldugeek.com/2026/09/18/ps6-la-console-portable-serait-un-monstre-de-puissance-grace-au-pssr3/</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>8. Audio</t>
+          <t>2. PC</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>KultureGeek</t>
+          <t>Frandroid - Actualités</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-09-18T14:56:56+00:00</t>
+          <t>2026-09-18T14:57:26+00:00</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>[#BonPlan] Les promos High-Tech du 18 septembre</t>
+          <t>Avec son cadre garantie à vie, ce vélo cargo électrique peut grimper jusqu’à 350 km d’autonomie dans un cas très précis</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>https://kulturegeek.fr/news-359633/bonplan-promos-high-tech-18-septembre-2026</t>
+          <t>https://www.frandroid.com/marques/vello-bike/3252383_avec-son-cadre-garantie-a-vie-ce-velo-cargo-electrique-peut-grimper-jusqua-350-km-dautonomie-dans-un-cas-tres-precis</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>19. Sponso</t>
+          <t>8. Audio</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>KultureGeek</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-09-18T14:52:01+00:00</t>
+          <t>2026-09-18T14:56:56+00:00</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Ce billet de 5 euros peut vous rapporter 5 000 € !</t>
+          <t>[#BonPlan] Les promos High-Tech du 18 septembre</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/18/ce-billet-de-5-euros-qui-peut-vous-rapporter-5-000-e/</t>
+          <t>https://kulturegeek.fr/news-359633/bonplan-promos-high-tech-18-septembre-2026</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>NON_CLASSE</t>
+          <t>19. Sponso</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Frandroid - Actualités</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-09-18T14:50:44+00:00</t>
+          <t>2026-09-18T14:52:01+00:00</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Des PC portables « K-Bossés », mais de bonne qualité : la recette des Ateliers du Bocage face aux géants du reconditionné</t>
+          <t>Ce billet de 5 euros peut vous rapporter 5 000 € !</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/produits-android/3250423_des-pc-portables-k-bosses-mais-de-bonne-qualite-la-recette-des-ateliers-du-bocage-face-aux-geants-du-reconditionne</t>
+          <t>https://www.journaldugeek.com/2026/09/18/ce-billet-de-5-euros-qui-peut-vous-rapporter-5-000-e/</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>NON_CLASSE</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Phonandroid</t>
+          <t>Frandroid - Actualités</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-09-18T14:50:03+00:00</t>
+          <t>2026-09-18T14:50:44+00:00</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Voici comment synchroniser Samsung Galerie et Google Photos sur votre smartphone Galaxy</t>
+          <t>Des PC portables « K-Bossés », mais de bonne qualité : la recette des Ateliers du Bocage face aux géants du reconditionné</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>https://www.phonandroid.com/voici-comment-synchroniser-samsung-galerie-et-google-photos-sur-votre-smartphone-galaxy.html</t>
+          <t>https://www.frandroid.com/produits-android/3250423_des-pc-portables-k-bosses-mais-de-bonne-qualite-la-recette-des-ateliers-du-bocage-face-aux-geants-du-reconditionne</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -4354,76 +4354,76 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Numerama</t>
+          <t>Phonandroid</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-09-18T14:49:51+00:00</t>
+          <t>2026-09-18T14:50:03+00:00</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>La Game Boy en Lego perd près d’un tiers de son prix : difficile de ne pas être nostalgique</t>
+          <t>Voici comment synchroniser Samsung Galerie et Google Photos sur votre smartphone Galaxy</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>https://www.numerama.com/pop-culture/2058629-la-game-boy-en-lego-perd-pres-dun-tiers-de-son-prix-difficile-de-ne-pas-etre-nostalgique.html</t>
+          <t>https://www.phonandroid.com/voici-comment-synchroniser-samsung-galerie-et-google-photos-sur-votre-smartphone-galaxy.html</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>8. Audio</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>Numerama</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-09-18T14:48:16+00:00</t>
+          <t>2026-09-18T14:49:51+00:00</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>iPhone 18 Pro : on a passé la nouvelle Dynamic Island sous le microscope et voici ce qu’on a découvert</t>
+          <t>La Game Boy en Lego perd près d’un tiers de son prix : difficile de ne pas être nostalgique</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>https://www.01net.com/actualites/iphone-18-pro-on-a-passe-la-nouvelle-dynamic-island-sous-le-microscope-et-voici-ce-quon-a-decouvert.html</t>
+          <t>https://www.numerama.com/pop-culture/2058629-la-game-boy-en-lego-perd-pres-dun-tiers-de-son-prix-difficile-de-ne-pas-etre-nostalgique.html</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>8. Audio</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>TomsHardware</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-09-18T14:47:00+00:00</t>
+          <t>2026-09-18T14:48:16+00:00</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>iPhone 18 Pro Max : que vaut la chambre à vapeur trois fois plus grande ?</t>
+          <t>iPhone 18 Pro : on a passé la nouvelle Dynamic Island sous le microscope et voici ce qu’on a découvert</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.fr/iphone-18-pro-max-que-vaut-la-chambre-a-vapeur-trois-fois-plus-grande/</t>
+          <t>https://www.01net.com/actualites/iphone-18-pro-on-a-passe-la-nouvelle-dynamic-island-sous-le-microscope-et-voici-ce-quon-a-decouvert.html</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -4435,103 +4435,103 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>TomsHardware</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-09-18T14:40:19+00:00</t>
+          <t>2026-09-18T14:47:00+00:00</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Bon plan : les dernières versions de Microsoft Office 2024 et Windows 11 à partir de 12,25 €</t>
+          <t>iPhone 18 Pro Max : que vaut la chambre à vapeur trois fois plus grande ?</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>https://www.01net.com/bons-plans/bon-plan-les-dernieres-versions-de-microsoft-office-2024-et-windows-11-a-partir-de-1225-e.html</t>
+          <t>https://www.tomshardware.fr/iphone-18-pro-max-que-vaut-la-chambre-a-vapeur-trois-fois-plus-grande/</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>5. Logiciels _ OS</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-09-18T14:34:00+00:00</t>
+          <t>2026-09-18T14:40:19+00:00</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Actualité : Waze vient de changer en profondeur : les 5 réglages à connaître après la mise à jour de juillet</t>
+          <t>Bon plan : les dernières versions de Microsoft Office 2024 et Windows 11 à partir de 12,25 €</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/gps/waze-vient-de-changer-en-profondeur-les-5-reglages-a-connaitre-apres-la-mise-a-jour-de-juillet-n262032.html</t>
+          <t>https://www.01net.com/bons-plans/bon-plan-les-dernieres-versions-de-microsoft-office-2024-et-windows-11-a-partir-de-1225-e.html</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>9. Moiilité douce</t>
+          <t>5. Logiciels _ OS</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-09-18T14:33:30+00:00</t>
+          <t>2026-09-18T14:34:00+00:00</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>La France va-t-elle interdire la revente des cartes Pokémon avec plus de 20 % de marge ? (les scalpers en PLS)</t>
+          <t>Actualité : Waze vient de changer en profondeur : les 5 réglages à connaître après la mise à jour de juillet</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/18/la-france-va-t-elle-interdire-la-revente-des-cartes-pokemon-avec-plus-de-20-de-marge-les-scalpers-en-pls/</t>
+          <t>https://www.lesnumeriques.com/gps/waze-vient-de-changer-en-profondeur-les-5-reglages-a-connaitre-apres-la-mise-a-jour-de-juillet-n262032.html</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>15. ludique</t>
+          <t>9. Moiilité douce</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Frandroid - Actualités</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-09-18T14:33:07+00:00</t>
+          <t>2026-09-18T14:33:30+00:00</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Nouveau service de streaming gratuit : le célèbre guide JustWatch frappe un très grand coup</t>
+          <t>La France va-t-elle interdire la revente des cartes Pokémon avec plus de 20 % de marge ? (les scalpers en PLS)</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/services/svod/3252777_nouveau-service-de-streaming-gratuit-le-celebre-guide-justwatch-frappe-un-tres-grand-coup</t>
+          <t>https://www.journaldugeek.com/2026/09/18/la-france-va-t-elle-interdire-la-revente-des-cartes-pokemon-avec-plus-de-20-de-marge-les-scalpers-en-pls/</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -4543,76 +4543,76 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>Frandroid - Actualités</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-09-18T14:21:07+00:00</t>
+          <t>2026-09-18T14:33:07+00:00</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Vente flash DJI : à prix mini, son drone Neo 2 se vend par camions 🚛</t>
+          <t>Nouveau service de streaming gratuit : le célèbre guide JustWatch frappe un très grand coup</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>https://www.01net.com/bons-plans/vente-flash-en-cours-chez-dji-a-prix-mini-son-drone-neo-2-se-vend-par-camions.html</t>
+          <t>https://www.frandroid.com/services/svod/3252777_nouveau-service-de-streaming-gratuit-le-celebre-guide-justwatch-frappe-un-tres-grand-coup</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>7. Video</t>
+          <t>15. ludique</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Numerama</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-09-18T14:17:02+00:00</t>
+          <t>2026-09-18T14:21:07+00:00</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Quel iPhone acheter en 2026 ? Ceux qui valent leur prix, ceux qu’on vous déconseille</t>
+          <t>Vente flash DJI : à prix mini, son drone Neo 2 se vend par camions 🚛</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>https://www.numerama.com/tech/288962-guide-dachat-meilleur-iphone-a-acheter.html</t>
+          <t>https://www.01net.com/bons-plans/vente-flash-en-cours-chez-dji-a-prix-mini-son-drone-neo-2-se-vend-par-camions.html</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>7. Video</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Frandroid - Actualités</t>
+          <t>Numerama</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-09-18T14:15:06+00:00</t>
+          <t>2026-09-18T14:17:02+00:00</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Muse fait renaître les produits high-tech vintages</t>
+          <t>Quel iPhone acheter en 2026 ? Ceux qui valent leur prix, ceux qu’on vous déconseille</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/produits-android/audio/3253075_muse-fait-renaitre-les-produits-high-tech-vintages</t>
+          <t>https://www.numerama.com/tech/288962-guide-dachat-meilleur-iphone-a-acheter.html</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -4624,22 +4624,22 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>KultureGeek</t>
+          <t>Frandroid - Actualités</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-09-18T14:11:50+00:00</t>
+          <t>2026-09-18T14:15:06+00:00</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Motorola Signature 27 : un nouveau smartphone premium annoncé pour le 22 septembre, en pleine conférence Qualcomm</t>
+          <t>Muse fait renaître les produits high-tech vintages</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>https://kulturegeek.fr/news-359722/motorola-signature-27-nouveau-smartphone-premium-annonce-22-septembre-pleine-conference-qualcomm</t>
+          <t>https://www.frandroid.com/produits-android/audio/3253075_muse-fait-renaitre-les-produits-high-tech-vintages</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -4651,54 +4651,54 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>KultureGeek</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-09-18T14:05:16+00:00</t>
+          <t>2026-09-18T14:11:50+00:00</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Xiaomi se lâche complet : il pulvérise le prix du 17T Pro sans aucune explication 🤯</t>
+          <t>Motorola Signature 27 : un nouveau smartphone premium annoncé pour le 22 septembre, en pleine conférence Qualcomm</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>https://www.01net.com/bons-plans/xiaomi-pete-les-plombs-il-pulverise-le-prix-du-17t-pro-sans-aucune-explication.html</t>
+          <t>https://kulturegeek.fr/news-359722/motorola-signature-27-nouveau-smartphone-premium-annonce-22-septembre-pleine-conference-qualcomm</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>NON_CLASSE</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-09-18T14:02:09+00:00</t>
+          <t>2026-09-18T14:05:16+00:00</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Un sous-marin de la Première Guerre mondiale a été retrouvé : coulé en 1917, du TNT s’échappe de son épave</t>
+          <t>Xiaomi se lâche complet : il pulvérise le prix du 17T Pro sans aucune explication 🤯</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/18/sous-marin-premiere-guerre-mondiale-retrouve-1917-tnt-sechappe-epave/</t>
+          <t>https://www.01net.com/bons-plans/xiaomi-pete-les-plombs-il-pulverise-le-prix-du-17t-pro-sans-aucune-explication.html</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>8. Audio</t>
+          <t>NON_CLASSE</t>
         </is>
       </c>
     </row>
@@ -4710,17 +4710,17 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-09-18T14:02:08+00:00</t>
+          <t>2026-09-18T14:02:09+00:00</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>La série FarCry dévoile son casting, et les premiers noms sont prometteurs</t>
+          <t>Un sous-marin de la Première Guerre mondiale a été retrouvé : coulé en 1917, du TNT s’échappe de son épave</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/18/la-serie-farcry-devoile-son-casting-et-les-premiers-noms-sont-prometteurs/</t>
+          <t>https://www.journaldugeek.com/2026/09/18/sous-marin-premiere-guerre-mondiale-retrouve-1917-tnt-sechappe-epave/</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -4732,81 +4732,81 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>KultureGeek</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-09-18T14:01:37+00:00</t>
+          <t>2026-09-18T14:02:08+00:00</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Netflix devient le premier financeur privé de la production française</t>
+          <t>La série FarCry dévoile son casting, et les premiers noms sont prometteurs</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>https://kulturegeek.fr/news-359723/netflix-devient-premier-financeur-prive-production-francaise</t>
+          <t>https://www.journaldugeek.com/2026/09/18/la-serie-farcry-devoile-son-casting-et-les-premiers-noms-sont-prometteurs/</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>15. ludique</t>
+          <t>8. Audio</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>KultureGeek</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-09-18T14:01:08+00:00</t>
+          <t>2026-09-18T14:01:37+00:00</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>OpenAI a été piraté grâce à l’IA de son grand rival</t>
+          <t>Netflix devient le premier financeur privé de la production française</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>https://www.01net.com/actualites/openai-a-ete-pirate-grace-a-lia-de-son-grand-rival.html</t>
+          <t>https://kulturegeek.fr/news-359723/netflix-devient-premier-financeur-prive-production-francaise</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>6. IA</t>
+          <t>15. ludique</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Numerama</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-09-18T13:59:00+00:00</t>
+          <t>2026-09-18T14:01:08+00:00</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Le reboot Netflix de Narnia par la réalisatrice de Barbie déjà jugé woke par les fans</t>
+          <t>OpenAI a été piraté grâce à l’IA de son grand rival</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>https://www.numerama.com/tech/2335261-le-reboot-netflix-de-narnia-deja-juge-trop-woke-enrage-les-puristes.html</t>
+          <t>https://www.01net.com/actualites/openai-a-ete-pirate-grace-a-lia-de-son-grand-rival.html</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>15. ludique</t>
+          <t>6. IA</t>
         </is>
       </c>
     </row>
@@ -4818,103 +4818,103 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-09-18T13:48:20+00:00</t>
+          <t>2026-09-18T13:59:00+00:00</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Domino’s Pizza se moque de la lave « PS2 » de Marvel’s Wolverine</t>
+          <t>Le reboot Netflix de Narnia par la réalisatrice de Barbie déjà jugé woke par les fans</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>https://www.numerama.com/pop-culture/2335787-dominos-pizza-se-moque-de-la-lave-ps2-de-marvels-wolverine.html</t>
+          <t>https://www.numerama.com/tech/2335261-le-reboot-netflix-de-narnia-deja-juge-trop-woke-enrage-les-puristes.html</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>NON_CLASSE</t>
+          <t>15. ludique</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>Numerama</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-09-18T13:38:00+00:00</t>
+          <t>2026-09-18T13:48:20+00:00</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Actualité : Google simule un cerveau de mouche, un internaute l’utilise pour battre un célèbre jeu vidéo</t>
+          <t>Domino’s Pizza se moque de la lave « PS2 » de Marvel’s Wolverine</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/intelligence-artificielle/google-simule-un-cerveau-de-mouche-un-internaute-l-utilise-pour-battre-un-celebre-jeu-video-n262030.html</t>
+          <t>https://www.numerama.com/pop-culture/2335787-dominos-pizza-se-moque-de-la-lave-ps2-de-marvels-wolverine.html</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>7. Video</t>
+          <t>NON_CLASSE</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Numerama</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-09-18T13:36:27+00:00</t>
+          <t>2026-09-18T13:38:00+00:00</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Boulanger fait tomber le clavier Logitech MX Keys S sous la barre des 50 €</t>
+          <t>Actualité : Google simule un cerveau de mouche, un internaute l’utilise pour battre un célèbre jeu vidéo</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>https://www.numerama.com/tech/2335761-amazon-fait-tomber-le-clavier-logitech-mx-keys-s-sous-la-barre-des-50-e.html</t>
+          <t>https://www.lesnumeriques.com/intelligence-artificielle/google-simule-un-cerveau-de-mouche-un-internaute-l-utilise-pour-battre-un-celebre-jeu-video-n262030.html</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>3. Periphérique</t>
+          <t>7. Video</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Frandroid - Actualités</t>
+          <t>Numerama</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-09-18T13:33:53+00:00</t>
+          <t>2026-09-18T13:36:27+00:00</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Le Honor 700 Pro s’inspirerait de Xiaomi avec un écran au dos</t>
+          <t>Boulanger fait tomber le clavier Logitech MX Keys S sous la barre des 50 €</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/produits-android/3252413_le-futur-honor-700-pro-se-devoile-avec-un-ecran-secondaire-au-dos-et-un-capteur-de-200-megapixels</t>
+          <t>https://www.numerama.com/tech/2335761-amazon-fait-tomber-le-clavier-logitech-mx-keys-s-sous-la-barre-des-50-e.html</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>3. Periphérique</t>
         </is>
       </c>
     </row>
@@ -4926,76 +4926,76 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-09-18T13:22:10+00:00</t>
+          <t>2026-09-18T13:33:53+00:00</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Après Doom, un internaute entraîne le cerveau de mouche de Google à jouer à Balatro</t>
+          <t>Le Honor 700 Pro s’inspirerait de Xiaomi avec un écran au dos</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/culture-tech/3252303_apres-doom-ce-cerveau-de-mouche-modelise-par-google-gagne-maintenant-a-balatro</t>
+          <t>https://www.frandroid.com/produits-android/3252413_le-futur-honor-700-pro-se-devoile-avec-un-ecran-secondaire-au-dos-et-un-capteur-de-200-megapixels</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>NON_CLASSE</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>Frandroid - Actualités</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-09-18T13:20:32+00:00</t>
+          <t>2026-09-18T13:22:10+00:00</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Actualité : Voici le meilleur hub usb-c à prix abordable de notre comparatif</t>
+          <t>Après Doom, un internaute entraîne le cerveau de mouche de Google à jouer à Balatro</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/hub-usb-c/voici-le-meilleur-hub-usb-c-a-prix-abordable-de-notre-comparatif-n262028.html</t>
+          <t>https://www.frandroid.com/culture-tech/3252303_apres-doom-ce-cerveau-de-mouche-modelise-par-google-gagne-maintenant-a-balatro</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>3. Periphérique</t>
+          <t>NON_CLASSE</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Frandroid - Actualités</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-09-18T13:17:39+00:00</t>
+          <t>2026-09-18T13:20:32+00:00</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Vous passez 30 minutes à chercher quoi regarder ? Disney+ a enfin la solution</t>
+          <t>Actualité : Voici le meilleur hub usb-c à prix abordable de notre comparatif</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/services/svod/3252681_vous-passez-30-minutes-a-chercher-quoi-regarder-disney-a-enfin-la-solution</t>
+          <t>https://www.lesnumeriques.com/hub-usb-c/voici-le-meilleur-hub-usb-c-a-prix-abordable-de-notre-comparatif-n262028.html</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>15. ludique</t>
+          <t>3. Periphérique</t>
         </is>
       </c>
     </row>
@@ -5007,125 +5007,125 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-09-18T13:16:37+00:00</t>
+          <t>2026-09-18T13:17:39+00:00</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Huawei sonde ses utilisateurs sur un bracelet connecté sans écran, à la manière de Whoop</t>
+          <t>Vous passez 30 minutes à chercher quoi regarder ? Disney+ a enfin la solution</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/marques/huawei/3252849_huawei-sonde-ses-utilisateurs-sur-un-bracelet-connecte-sans-ecran-a-la-maniere-de-whoop</t>
+          <t>https://www.frandroid.com/services/svod/3252681_vous-passez-30-minutes-a-chercher-quoi-regarder-disney-a-enfin-la-solution</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>3. Periphérique</t>
+          <t>15. ludique</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>Frandroid - Actualités</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-09-18T13:02:48+00:00</t>
+          <t>2026-09-18T13:16:37+00:00</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>GTA 6 : la sortie du Online très attendu se précise pour 2027</t>
+          <t>Huawei sonde ses utilisateurs sur un bracelet connecté sans écran, à la manière de Whoop</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/18/gta-6-la-sortie-du-online-tres-attendu-se-precise-pour-2027/</t>
+          <t>https://www.frandroid.com/marques/huawei/3252849_huawei-sonde-ses-utilisateurs-sur-un-bracelet-connecte-sans-ecran-a-la-maniere-de-whoop</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>15. ludique</t>
+          <t>3. Periphérique</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-09-18T13:02:39+00:00</t>
+          <t>2026-09-18T13:02:48+00:00</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Copier-coller cassé dans Excel : Microsoft partage une bidouille pour contourner le bug</t>
+          <t>GTA 6 : la sortie du Online très attendu se précise pour 2027</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>https://www.01net.com/actualites/copier-coller-casse-dans-excel-microsoft-partage-une-bidouille-pour-contourner-le-bug.html</t>
+          <t>https://www.journaldugeek.com/2026/09/18/gta-6-la-sortie-du-online-tres-attendu-se-precise-pour-2027/</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>5. Logiciels _ OS</t>
+          <t>15. ludique</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Frandroid - Actualités</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-09-18T13:01:53+00:00</t>
+          <t>2026-09-18T13:02:39+00:00</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Monaco-Lens : comment voir le match d’ouverture de la 5e journée de Ligue 1 en direct et en streaming ?</t>
+          <t>Copier-coller cassé dans Excel : Microsoft partage une bidouille pour contourner le bug</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/produits-android/3252865_monaco-lens-comment-voir-le-match-douverture-de-la-5e-journee-de-ligue-1-en-direct-et-en-streaming</t>
+          <t>https://www.01net.com/actualites/copier-coller-casse-dans-excel-microsoft-partage-une-bidouille-pour-contourner-le-bug.html</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>5. Logiciels _ OS</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>Frandroid - Actualités</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-09-18T13:00:00+00:00</t>
+          <t>2026-09-18T13:01:53+00:00</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Test Xiaomi Redmi Note 17 5G : il n'est sauvé que par son autonomie</t>
+          <t>Monaco-Lens : comment voir le match d’ouverture de la 5e journée de Ligue 1 en direct et en streaming ?</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/telephone-portable/xiaomi-redmi-note-17-5g-p78893/test.html</t>
+          <t>https://www.frandroid.com/produits-android/3252865_monaco-lens-comment-voir-le-match-douverture-de-la-5e-journee-de-ligue-1-en-direct-et-en-streaming</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -5137,7 +5137,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Numerama</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -5147,24 +5147,24 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Test de Control Resonant, le nouveau chef-d’œuvre de Remedy</t>
+          <t>Test Xiaomi Redmi Note 17 5G : il n'est sauvé que par son autonomie</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>https://www.numerama.com/pop-culture/2335251-test-de-control-resonant-le-nouveau-chef-doeuvre-de-remedy.html</t>
+          <t>https://www.lesnumeriques.com/telephone-portable/xiaomi-redmi-note-17-5g-p78893/test.html</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>NON_CLASSE</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Korben</t>
+          <t>Numerama</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -5174,44 +5174,44 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Comment mesurer et dégonfler l'index de recherche de Windows</t>
+          <t>Test de Control Resonant, le nouveau chef-d’œuvre de Remedy</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>https://korben.info/windows-search-indexation-etendue-ssd.html</t>
+          <t>https://www.numerama.com/pop-culture/2335251-test-de-control-resonant-le-nouveau-chef-doeuvre-de-remedy.html</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>2. PC</t>
+          <t>NON_CLASSE</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Phonandroid</t>
+          <t>Korben</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-09-18T12:44:03+00:00</t>
+          <t>2026-09-18T13:00:00+00:00</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>AliExpress lance sa French Week et fait chuter les prix : voici les offres à saisir</t>
+          <t>Comment mesurer et dégonfler l'index de recherche de Windows</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>https://www.phonandroid.com/aliexpress-french-week-fait-chuter-prix-voici-offres-saisir.html</t>
+          <t>https://korben.info/windows-search-indexation-etendue-ssd.html</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>19. Sponso</t>
+          <t>2. PC</t>
         </is>
       </c>
     </row>
@@ -5223,265 +5223,265 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-09-18T12:39:25+00:00</t>
+          <t>2026-09-18T12:44:03+00:00</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>iPhone 18 Pro : Apple augmente le prix du remplacement de la batterie</t>
+          <t>AliExpress lance sa French Week et fait chuter les prix : voici les offres à saisir</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>https://www.phonandroid.com/iphone-18-pro-apple-augmente-le-prix-du-remplacement-de-la-batterie.html</t>
+          <t>https://www.phonandroid.com/aliexpress-french-week-fait-chuter-prix-voici-offres-saisir.html</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>19. Sponso</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Numerama</t>
+          <t>Phonandroid</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-09-18T12:37:21+00:00</t>
+          <t>2026-09-18T12:39:25+00:00</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Devinez quel personnage joue Madds mikkelsen dans le prochain Call of Duty</t>
+          <t>iPhone 18 Pro : Apple augmente le prix du remplacement de la batterie</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>https://www.numerama.com/pop-culture/2335755-devinez-quel-personnage-joue-madds-mikkelsen-dans-le-prochain-call-of-duty.html</t>
+          <t>https://www.phonandroid.com/iphone-18-pro-apple-augmente-le-prix-du-remplacement-de-la-batterie.html</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>NON_CLASSE</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Frandroid - Actualités</t>
+          <t>Numerama</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-09-18T12:30:50+00:00</t>
+          <t>2026-09-18T12:37:21+00:00</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>aptX, LDAC, SBC, LC3 : tout comprendre aux codecs Bluetooth audio</t>
+          <t>Devinez quel personnage joue Madds mikkelsen dans le prochain Call of Duty</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/comment-faire/comment-fonctionne-la-technologie/752329_aptx-ldac-sbc-tout-comprendre-aux-codecs-bluetooth-audio</t>
+          <t>https://www.numerama.com/pop-culture/2335755-devinez-quel-personnage-joue-madds-mikkelsen-dans-le-prochain-call-of-duty.html</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>8. Audio</t>
+          <t>NON_CLASSE</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>Frandroid - Actualités</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-09-18T12:30:11+00:00</t>
+          <t>2026-09-18T12:30:50+00:00</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Ce nouveau télescope de la NASA va chercher des milliers de planètes dans l’univers</t>
+          <t>aptX, LDAC, SBC, LC3 : tout comprendre aux codecs Bluetooth audio</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>https://www.01net.com/actualites/ce-nouveau-telescope-de-la-nasa-va-chercher-des-milliers-de-planetes-dans-lunivers.html</t>
+          <t>https://www.frandroid.com/comment-faire/comment-fonctionne-la-technologie/752329_aptx-ldac-sbc-tout-comprendre-aux-codecs-bluetooth-audio</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>18. Sciences</t>
+          <t>8. Audio</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Numerama</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-09-18T12:30:00+00:00</t>
+          <t>2026-09-18T12:30:11+00:00</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Le géant de la batterie CATL perd de son emprise sur les constructeurs chinois</t>
+          <t>Ce nouveau télescope de la NASA va chercher des milliers de planètes dans l’univers</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>https://www.numerama.com/vroom/2335713-le-geant-de-la-batterie-catl-perd-de-son-emprise-sur-les-constructeurs-chinois.html</t>
+          <t>https://www.01net.com/actualites/ce-nouveau-telescope-de-la-nasa-va-chercher-des-milliers-de-planetes-dans-lunivers.html</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>8. Audio</t>
+          <t>18. Sciences</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Frandroid - Actualités</t>
+          <t>Numerama</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-09-18T12:25:55+00:00</t>
+          <t>2026-09-18T12:30:00+00:00</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Moins de 800 kg et 110 km/h : à quoi ressemble la voiture électrique à 15 000 € qui pourrait bientôt déferler sur nos routes ?</t>
+          <t>Le géant de la batterie CATL perd de son emprise sur les constructeurs chinois</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/survoltes/3252389_moins-de-800-kg-et-110-km-h-a-quoi-ressemble-la-voiture-electrique-a-15-000-e-qui-pourrait-bientot-deferler-sur-nos-routes</t>
+          <t>https://www.numerama.com/vroom/2335713-le-geant-de-la-batterie-catl-perd-de-son-emprise-sur-les-constructeurs-chinois.html</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>10. Voiture</t>
+          <t>8. Audio</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>Frandroid - Actualités</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-09-18T12:16:00+00:00</t>
+          <t>2026-09-18T12:25:55+00:00</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Actualité : Le lave-linge Dreame Slim Washer S passe sous les 350 €</t>
+          <t>Moins de 800 kg et 110 km/h : à quoi ressemble la voiture électrique à 15 000 € qui pourrait bientôt déferler sur nos routes ?</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/lave-linge/le-lave-linge-dreame-slim-washer-s-passe-sous-les-350-n262024.html</t>
+          <t>https://www.frandroid.com/survoltes/3252389_moins-de-800-kg-et-110-km-h-a-quoi-ressemble-la-voiture-electrique-a-15-000-e-qui-pourrait-bientot-deferler-sur-nos-routes</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>11. Menage</t>
+          <t>10. Voiture</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Numerama</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-09-18T12:11:12+00:00</t>
+          <t>2026-09-18T12:16:00+00:00</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>25 000 taxis autonomes en Europe : Bolt et Lucid veulent couper l’herbe sous le pied à Waymo</t>
+          <t>Actualité : Le lave-linge Dreame Slim Washer S passe sous les 350 €</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>https://www.numerama.com/vroom/2335711-25-000-taxis-autonomes-en-europe-bolt-et-lucid-veulent-couper-lherbe-sous-le-pied-a-waymo.html</t>
+          <t>https://www.lesnumeriques.com/lave-linge/le-lave-linge-dreame-slim-washer-s-passe-sous-les-350-n262024.html</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>9. Moiilité douce</t>
+          <t>11. Menage</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>KultureGeek</t>
+          <t>Numerama</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-09-18T12:10:53+00:00</t>
+          <t>2026-09-18T12:11:12+00:00</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Mark Zuckerberg rejette l’idée de ralentir le développement de l’IA</t>
+          <t>25 000 taxis autonomes en Europe : Bolt et Lucid veulent couper l’herbe sous le pied à Waymo</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>https://kulturegeek.fr/news-359716/mark-zuckerberg-rejette-lidee-ralentir-developpement-lia</t>
+          <t>https://www.numerama.com/vroom/2335711-25-000-taxis-autonomes-en-europe-bolt-et-lucid-veulent-couper-lherbe-sous-le-pied-a-waymo.html</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>6. IA</t>
+          <t>9. Moiilité douce</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>KultureGeek</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-09-18T12:04:27+00:00</t>
+          <t>2026-09-18T12:10:53+00:00</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>iPhone 18 Pro et Pro Max : les premiers tests sont tombés, faut-il craquer ? Voici ce qu’il faut vraiment retenir</t>
+          <t>Mark Zuckerberg rejette l’idée de ralentir le développement de l’IA</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/18/iphone-18-pro-et-pro-max-les-premiers-tests-sont-tombes-faut-il-craquer-voici-ce-quil-faut-vraiment-retenir/</t>
+          <t>https://kulturegeek.fr/news-359716/mark-zuckerberg-rejette-lidee-ralentir-developpement-lia</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>6. IA</t>
         </is>
       </c>
     </row>
@@ -5493,71 +5493,71 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-09-18T11:35:34+00:00</t>
+          <t>2026-09-18T12:04:27+00:00</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Des chercheurs découvrent une nouvelle structure cruciale cachée dans nos cellules</t>
+          <t>iPhone 18 Pro et Pro Max : les premiers tests sont tombés, faut-il craquer ? Voici ce qu’il faut vraiment retenir</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/18/des-chercheurs-decouvrent-une-nouvelle-structure-cruciale-cachee-dans-nos-cellules/</t>
+          <t>https://www.journaldugeek.com/2026/09/18/iphone-18-pro-et-pro-max-les-premiers-tests-sont-tombes-faut-il-craquer-voici-ce-quil-faut-vraiment-retenir/</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>18. Sciences</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Numerama</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-09-18T11:30:00+00:00</t>
+          <t>2026-09-18T11:35:34+00:00</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Miami Vice 85  : après Michael B. Jordan et Austin Butler, le film pioche dans le casting de L’Odyssée</t>
+          <t>Des chercheurs découvrent une nouvelle structure cruciale cachée dans nos cellules</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>https://www.numerama.com/pop-culture/2335553-miami-vice-85-apres-michael-b-jordan-et-austin-butler-le-film-pioche-dans-le-casting-de-lodyssee.html</t>
+          <t>https://www.journaldugeek.com/2026/09/18/des-chercheurs-decouvrent-une-nouvelle-structure-cruciale-cachee-dans-nos-cellules/</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>15. ludique</t>
+          <t>18. Sciences</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>Numerama</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-09-18T11:20:00+00:00</t>
+          <t>2026-09-18T11:30:00+00:00</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Actualité : Disney+ continue d'empirer : de la publicité obligatoire arrive dans tous les abonnements</t>
+          <t>Miami Vice 85  : après Michael B. Jordan et Austin Butler, le film pioche dans le casting de L’Odyssée</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/cine-svod/disney-continue-d-empirer-de-la-publicite-obligatoire-arrive-dans-tous-les-abonnements-n262015.html</t>
+          <t>https://www.numerama.com/pop-culture/2335553-miami-vice-85-apres-michael-b-jordan-et-austin-butler-le-film-pioche-dans-le-casting-de-lodyssee.html</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -5569,297 +5569,297 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-09-18T11:10:49+00:00</t>
+          <t>2026-09-18T11:20:00+00:00</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Smartphones pliants : l’effet Apple est là, et Samsung en profite… deux fois</t>
+          <t>Actualité : Disney+ continue d'empirer : de la publicité obligatoire arrive dans tous les abonnements</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>https://www.01net.com/actualites/smartphones-pliants-leffet-apple-est-la-et-samsung-en-profite-deux-fois.html</t>
+          <t>https://www.lesnumeriques.com/cine-svod/disney-continue-d-empirer-de-la-publicite-obligatoire-arrive-dans-tous-les-abonnements-n262015.html</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>15. ludique</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Frandroid - Actualités</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-09-18T11:02:51+00:00</t>
+          <t>2026-09-18T11:10:49+00:00</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Galaxy S27 Ultra : après six ans d’attente, Samsung va enfin augmenter la batterie</t>
+          <t>Smartphones pliants : l’effet Apple est là, et Samsung en profite… deux fois</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/marques/samsung/3252641_galaxy-s27-ultra-apres-six-ans-dattente-samsung-va-enfin-augmenter-la-batterie</t>
+          <t>https://www.01net.com/actualites/smartphones-pliants-leffet-apple-est-la-et-samsung-en-profite-deux-fois.html</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>NON_CLASSE</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>Frandroid - Actualités</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-09-18T10:45:32+00:00</t>
+          <t>2026-09-18T11:02:51+00:00</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Mastercard offre des cartes bancaires aux IA pour dépenser votre argent</t>
+          <t>Galaxy S27 Ultra : après six ans d’attente, Samsung va enfin augmenter la batterie</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>https://www.01net.com/actualites/mastercard-offre-des-cartes-bancaires-aux-ia-pour-depenser-votre-argent.html</t>
+          <t>https://www.frandroid.com/marques/samsung/3252641_galaxy-s27-ultra-apres-six-ans-dattente-samsung-va-enfin-augmenter-la-batterie</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>6. IA</t>
+          <t>NON_CLASSE</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-09-18T10:44:00+00:00</t>
+          <t>2026-09-18T10:45:32+00:00</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Actualité : MobLand saison 2 : quand sortent les épisodes de la série sur Paramount+ ?</t>
+          <t>Mastercard offre des cartes bancaires aux IA pour dépenser votre argent</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/cine-svod/mobland-saison-2-quand-sortent-les-episodes-de-la-serie-sur-paramount-n262014.html</t>
+          <t>https://www.01net.com/actualites/mastercard-offre-des-cartes-bancaires-aux-ia-pour-depenser-votre-argent.html</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>15. ludique</t>
+          <t>6. IA</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>KultureGeek</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-09-18T10:41:49+00:00</t>
+          <t>2026-09-18T10:44:00+00:00</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Huawei accélère le lancement de sa puce IA Ascend 960DT pour concurrencer Nvidia dès 2027</t>
+          <t>Actualité : MobLand saison 2 : quand sortent les épisodes de la série sur Paramount+ ?</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>https://kulturegeek.fr/news-359713/huawei-accelere-lancement-puce-ia-ascend-960dt-concurrencer-nvidia-2027</t>
+          <t>https://www.lesnumeriques.com/cine-svod/mobland-saison-2-quand-sortent-les-episodes-de-la-serie-sur-paramount-n262014.html</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>2. PC</t>
+          <t>15. ludique</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>KultureGeek</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-09-18T10:33:23+00:00</t>
+          <t>2026-09-18T10:41:49+00:00</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Free débloque (enfin) cette fonction qui peut doubler le débit Wi-Fi de votre Freebox !</t>
+          <t>Huawei accélère le lancement de sa puce IA Ascend 960DT pour concurrencer Nvidia dès 2027</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/18/free-debloque-enfin-cette-fonction-qui-peut-doubler-le-debit-wi-fi-de-votre-freebox/</t>
+          <t>https://kulturegeek.fr/news-359713/huawei-accelere-lancement-puce-ia-ascend-960dt-concurrencer-nvidia-2027</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>3. Periphérique</t>
+          <t>2. PC</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Frandroid - Actualités</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-09-18T10:32:33+00:00</t>
+          <t>2026-09-18T10:33:23+00:00</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>L’iPhone 18 Pro est mieux refroidi que certains smartphones gaming, comme le démontrent ces tests</t>
+          <t>Free débloque (enfin) cette fonction qui peut doubler le débit Wi-Fi de votre Freebox !</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/produits-android/smartphone/3252289_liphone-18-pro-est-mieux-refroidi-que-les-meilleurs-smartphones-gaming-comme-le-demontrent-ces-tests</t>
+          <t>https://www.journaldugeek.com/2026/09/18/free-debloque-enfin-cette-fonction-qui-peut-doubler-le-debit-wi-fi-de-votre-freebox/</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>3. Periphérique</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Korben</t>
+          <t>Frandroid - Actualités</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-09-18T10:21:37+00:00</t>
+          <t>2026-09-18T10:32:33+00:00</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Calibre lance le livre dont vous êtes le héros, généré par IA</t>
+          <t>L’iPhone 18 Pro est mieux refroidi que certains smartphones gaming, comme le démontrent ces tests</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>https://korben.info/calibre-9-15-jeu-aventure-ia.html</t>
+          <t>https://www.frandroid.com/produits-android/smartphone/3252289_liphone-18-pro-est-mieux-refroidi-que-les-meilleurs-smartphones-gaming-comme-le-demontrent-ces-tests</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>4. Tablette</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>Korben</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-09-18T10:19:00+00:00</t>
+          <t>2026-09-18T10:21:37+00:00</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Actualité : Trois hackers ont utilisé Claude pour pirater OpenAI en 72 heures, et ils n'ont eu besoin que d'un abonnement</t>
+          <t>Calibre lance le livre dont vous êtes le héros, généré par IA</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/intelligence-artificielle/trois-hackers-ont-utilise-claude-pour-pirater-openai-en-72-heures-et-ils-n-ont-eu-besoin-que-d-un-abonnement-n262016.html</t>
+          <t>https://korben.info/calibre-9-15-jeu-aventure-ia.html</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>6. IA</t>
+          <t>4. Tablette</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-09-18T10:15:26+00:00</t>
+          <t>2026-09-18T10:19:00+00:00</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Disney+ fait une très mauvaise blague à ses abonnés en ajoutant de la pub sur toutes ses offres !</t>
+          <t>Actualité : Trois hackers ont utilisé Claude pour pirater OpenAI en 72 heures, et ils n'ont eu besoin que d'un abonnement</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/18/disney-fait-une-tres-mauvaise-blague-a-ses-abonnes-en-ajoutant-de-la-pub-sur-toutes-ses-offres/</t>
+          <t>https://www.lesnumeriques.com/intelligence-artificielle/trois-hackers-ont-utilise-claude-pour-pirater-openai-en-72-heures-et-ils-n-ont-eu-besoin-que-d-un-abonnement-n262016.html</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>15. ludique</t>
+          <t>6. IA</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-09-18T10:15:00+00:00</t>
+          <t>2026-09-18T10:15:26+00:00</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Actualité : Le câble USB-C vers Jack 6.35 (pour un ampli par ex.) est à 8.79 €</t>
+          <t>Disney+ fait une très mauvaise blague à ses abonnés en ajoutant de la pub sur toutes ses offres !</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/accessoire-audio/le-cable-usb-c-vers-jack-6-35-pour-un-ampli-par-ex-est-a-8-79-n262020.html</t>
+          <t>https://www.journaldugeek.com/2026/09/18/disney-fait-une-tres-mauvaise-blague-a-ses-abonnes-en-ajoutant-de-la-pub-sur-toutes-ses-offres/</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>3. Periphérique</t>
+          <t>15. ludique</t>
         </is>
       </c>
     </row>
@@ -5871,103 +5871,103 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-09-18T10:11:33+00:00</t>
+          <t>2026-09-18T10:15:00+00:00</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Actualité : Ces écouteurs sans fil présentent le meilleur rapport qualité / prix de notre comparatif</t>
+          <t>Actualité : Le câble USB-C vers Jack 6.35 (pour un ampli par ex.) est à 8.79 €</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/ecouteurs-sans-fil/ces-ecouteurs-sans-fil-presentent-le-meilleur-rapport-qualite-prix-de-notre-comparatif-n262019.html</t>
+          <t>https://www.lesnumeriques.com/accessoire-audio/le-cable-usb-c-vers-jack-6-35-pour-un-ampli-par-ex-est-a-8-79-n262020.html</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>8. Audio</t>
+          <t>3. Periphérique</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-09-18T10:05:56+00:00</t>
+          <t>2026-09-18T10:11:33+00:00</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Xiaomi 15T Pro : deal de FOLIE à saisir sur ce best-seller en puissance (-44%) ⚡️</t>
+          <t>Actualité : Ces écouteurs sans fil présentent le meilleur rapport qualité / prix de notre comparatif</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>https://www.01net.com/bons-plans/xiaomi-15t-pro-deal-de-folie-a-saisir-rapidement-sur-ce-best-seller-en-puissance.html</t>
+          <t>https://www.lesnumeriques.com/ecouteurs-sans-fil/ces-ecouteurs-sans-fil-presentent-le-meilleur-rapport-qualite-prix-de-notre-comparatif-n262019.html</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>NON_CLASSE</t>
+          <t>8. Audio</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-09-18T10:03:11+00:00</t>
+          <t>2026-09-18T10:05:56+00:00</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>25 000 véhicules vont débarquer dans plusieurs grandes villes européennes !</t>
+          <t>Xiaomi 15T Pro : deal de FOLIE à saisir sur ce best-seller en puissance (-44%) ⚡️</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/18/25-000-vehicules-vont-debarquer-dans-plusieurs-grandes-villes-europeennes/</t>
+          <t>https://www.01net.com/bons-plans/xiaomi-15t-pro-deal-de-folie-a-saisir-rapidement-sur-ce-best-seller-en-puissance.html</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>10. Voiture</t>
+          <t>NON_CLASSE</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Frandroid - Actualités</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-09-18T10:02:00+00:00</t>
+          <t>2026-09-18T10:03:11+00:00</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>En France comme à l’étranger, ce forfait mobile Bouygues Telecom 200 Go ne vous laissera jamais tomber</t>
+          <t>25 000 véhicules vont débarquer dans plusieurs grandes villes européennes !</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/telecom/forfait-mobile/3249431_en-france-comme-a-letranger-ce-forfait-mobile-bouygues-telecom-200-go-ne-vous-laissera-jamais-tomber</t>
+          <t>https://www.journaldugeek.com/2026/09/18/25-000-vehicules-vont-debarquer-dans-plusieurs-grandes-villes-europeennes/</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>10. Voiture</t>
         </is>
       </c>
     </row>
@@ -5979,260 +5979,260 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-09-18T10:00:18+00:00</t>
+          <t>2026-09-18T10:02:00+00:00</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Comment installer un SSD M.2 dans sa PS5 pour agrandir le stockage ? Notre tutoriel</t>
+          <t>En France comme à l’étranger, ce forfait mobile Bouygues Telecom 200 Go ne vous laissera jamais tomber</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/marques/sony/1077003_ps5-comment-installer-un-ssd-m-2-dans-la-console-et-transferer-ses-jeux</t>
+          <t>https://www.frandroid.com/telecom/forfait-mobile/3249431_en-france-comme-a-letranger-ce-forfait-mobile-bouygues-telecom-200-go-ne-vous-laissera-jamais-tomber</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>2. PC</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>Frandroid - Actualités</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-09-18T09:58:29+00:00</t>
+          <t>2026-09-18T10:00:18+00:00</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>L’iPhone 18 Pro est trop cher ? Vous n’êtes pas prêts pour la suite</t>
+          <t>Comment installer un SSD M.2 dans sa PS5 pour agrandir le stockage ? Notre tutoriel</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>https://www.01net.com/actualites/liphone-18-pro-est-trop-cher-vous-netes-pas-prets-pour-la-suite.html</t>
+          <t>https://www.frandroid.com/marques/sony/1077003_ps5-comment-installer-un-ssd-m-2-dans-la-console-et-transferer-ses-jeux</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>2. PC</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Frandroid - Actualités</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-09-18T09:57:26+00:00</t>
+          <t>2026-09-18T09:58:29+00:00</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>AMD s’apprêterait à augmenter de 10 % le prix de ses cartes graphiques et processeurs</t>
+          <t>L’iPhone 18 Pro est trop cher ? Vous n’êtes pas prêts pour la suite</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/marques/amd/3252391_amd-sappreterait-a-augmenter-de-10-le-prix-de-ses-cartes-graphiques-et-processeurs</t>
+          <t>https://www.01net.com/actualites/liphone-18-pro-est-trop-cher-vous-netes-pas-prets-pour-la-suite.html</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>2. PC</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>Frandroid - Actualités</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-09-18T09:53:00+00:00</t>
+          <t>2026-09-18T09:57:26+00:00</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Actualité : Freebox : Free exploite enfin pleinement les capacités Wi-Fi de ses box et répéteurs</t>
+          <t>AMD s’apprêterait à augmenter de 10 % le prix de ses cartes graphiques et processeurs</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/societe-numerique/freebox-free-exploite-enfin-pleinement-les-capacites-wi-fi-de-ses-box-et-repeteurs-n262009.html</t>
+          <t>https://www.frandroid.com/marques/amd/3252391_amd-sappreterait-a-augmenter-de-10-le-prix-de-ses-cartes-graphiques-et-processeurs</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>3. Periphérique</t>
+          <t>2. PC</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Frandroid - Actualités</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-09-18T09:49:45+00:00</t>
+          <t>2026-09-18T09:53:00+00:00</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>iPhone Duo Max : Apple pourrait muscler son jeu face au Samsung Galaxy Z Fold 8 Ultra</t>
+          <t>Actualité : Freebox : Free exploite enfin pleinement les capacités Wi-Fi de ses box et répéteurs</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/marques/apple/3251957_iphone-duo-max-apple-pourrait-muscler-son-jeu-face-au-samsung-galaxy-z-fold-8-ultra</t>
+          <t>https://www.lesnumeriques.com/societe-numerique/freebox-free-exploite-enfin-pleinement-les-capacites-wi-fi-de-ses-box-et-repeteurs-n262009.html</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>3. Periphérique</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>Frandroid - Actualités</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-09-18T09:49:43+00:00</t>
+          <t>2026-09-18T09:49:45+00:00</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Révolutionnez  le ménage chez vous : cet aspirateur robot tout-en-un est à -72%</t>
+          <t>iPhone Duo Max : Apple pourrait muscler son jeu face au Samsung Galaxy Z Fold 8 Ultra</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>https://www.01net.com/bons-plans/revolutionnez-le-menage-chez-vous-cet-aspirateur-robot-tout-en-un-est-a-72.html</t>
+          <t>https://www.frandroid.com/marques/apple/3251957_iphone-duo-max-apple-pourrait-muscler-son-jeu-face-au-samsung-galaxy-z-fold-8-ultra</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>11. Menage</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Frandroid - Actualités</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-09-18T09:45:25+00:00</t>
+          <t>2026-09-18T09:49:43+00:00</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>PS5 Slim ou PS5 Pro : quelle PS5 choisir ?</t>
+          <t>Révolutionnez  le ménage chez vous : cet aspirateur robot tout-en-un est à -72%</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/marques/sony/767530_ps5-ou-ps5-digital-edition-quel-modele-choisir</t>
+          <t>https://www.01net.com/bons-plans/revolutionnez-le-menage-chez-vous-cet-aspirateur-robot-tout-en-un-est-a-72.html</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>7. Video</t>
+          <t>11. Menage</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>Frandroid - Actualités</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-09-18T09:30:51+00:00</t>
+          <t>2026-09-18T09:45:25+00:00</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Le retour de la canicule dès la semaine prochaine ? Une nouvelle vague de chaleur annoncée pour fin septembre et au-delà</t>
+          <t>PS5 Slim ou PS5 Pro : quelle PS5 choisir ?</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/18/le-retour-de-la-canicule-des-la-semaine-prochaine-une-nouvelle-vague-de-chaleur-annoncee-pour-fin-septembre-et-au-dela/</t>
+          <t>https://www.frandroid.com/marques/sony/767530_ps5-ou-ps5-digital-edition-quel-modele-choisir</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>NON_CLASSE</t>
+          <t>7. Video</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-09-18T09:30:13+00:00</t>
+          <t>2026-09-18T09:30:51+00:00</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>iPhone 18 Pro, Apple Watch 12, AirPods 5… :  une mise à jour obligatoire vous attend dès le déballage</t>
+          <t>Le retour de la canicule dès la semaine prochaine ? Une nouvelle vague de chaleur annoncée pour fin septembre et au-delà</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>https://www.01net.com/actualites/iphone-18-pro-apple-watch-12-airpods-5-mise-jour-obligatoire-attend-deballage.html</t>
+          <t>https://www.journaldugeek.com/2026/09/18/le-retour-de-la-canicule-des-la-semaine-prochaine-une-nouvelle-vague-de-chaleur-annoncee-pour-fin-septembre-et-au-dela/</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>NON_CLASSE</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-09-18T09:30:00+00:00</t>
+          <t>2026-09-18T09:30:13+00:00</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Bitdefender Premium Security : comment repérer les deepfakes et éviter les arnaques ?</t>
+          <t>iPhone 18 Pro, Apple Watch 12, AirPods 5… :  une mise à jour obligatoire vous attend dès le déballage</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/appli-logiciel/bitdefender-premium-security-comment-reperer-les-deepfakes-et-eviter-les-arnaques-na262018.html</t>
+          <t>https://www.01net.com/actualites/iphone-18-pro-apple-watch-12-airpods-5-mise-jour-obligatoire-attend-deballage.html</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -6244,54 +6244,54 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-09-18T09:20:28+00:00</t>
+          <t>2026-09-18T09:30:00+00:00</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Mauvaise nouvelle si vous achetez des livres sur Amazon</t>
+          <t>Bitdefender Premium Security : comment repérer les deepfakes et éviter les arnaques ?</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>https://www.01net.com/actualites/amazon-met-fin-livraison-gratuite-livres-dans-lockers.html</t>
+          <t>https://www.lesnumeriques.com/appli-logiciel/bitdefender-premium-security-comment-reperer-les-deepfakes-et-eviter-les-arnaques-na262018.html</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>4. Tablette</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-09-18T09:20:00+00:00</t>
+          <t>2026-09-18T09:20:28+00:00</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Actualité : Narnia : des premières images magiques pour le blockbuster Netflix signé Greta Gerwig</t>
+          <t>Mauvaise nouvelle si vous achetez des livres sur Amazon</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/cine-svod/narnia-des-premieres-images-magiques-pour-le-blockbuster-netflix-signe-greta-gerwig-n262013.html</t>
+          <t>https://www.01net.com/actualites/amazon-met-fin-livraison-gratuite-livres-dans-lockers.html</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>7. Video</t>
+          <t>4. Tablette</t>
         </is>
       </c>
     </row>
@@ -6303,125 +6303,125 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-09-18T09:19:00+00:00</t>
+          <t>2026-09-18T09:20:00+00:00</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Actualité : Un astéroïde grand comme un immeuble de trois à six étages s’est écrasé sur la Lune : voici l’incroyable cratère géant découvert par la NASA</t>
+          <t>Actualité : Narnia : des premières images magiques pour le blockbuster Netflix signé Greta Gerwig</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/vers-la-lune/un-asteroide-grand-comme-un-immeuble-de-trois-a-six-etages-s-est-ecrase-sur-la-lune-voici-l-incroyable-cratere-geant-decouvert-par-la-nasa-n262017.html</t>
+          <t>https://www.lesnumeriques.com/cine-svod/narnia-des-premieres-images-magiques-pour-le-blockbuster-netflix-signe-greta-gerwig-n262013.html</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>18. Sciences</t>
+          <t>7. Video</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>KultureGeek</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-09-18T09:15:00+00:00</t>
+          <t>2026-09-18T09:19:00+00:00</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Intelligence artificielle et emploi : près de la moitié de la population anticipe des suppressions massives de postes selon une étude</t>
+          <t>Actualité : Un astéroïde grand comme un immeuble de trois à six étages s’est écrasé sur la Lune : voici l’incroyable cratère géant découvert par la NASA</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>https://kulturegeek.fr/news-359700/intelligence-artificielle-emploi-pres-moitie-population-anticipe-suppressions-massives-postes-etude</t>
+          <t>https://www.lesnumeriques.com/vers-la-lune/un-asteroide-grand-comme-un-immeuble-de-trois-a-six-etages-s-est-ecrase-sur-la-lune-voici-l-incroyable-cratere-geant-decouvert-par-la-nasa-n262017.html</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>6. IA</t>
+          <t>18. Sciences</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>KultureGeek</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-09-18T09:03:28+00:00</t>
+          <t>2026-09-18T09:15:00+00:00</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Cette prime promise par EDF à l’achat d’une BYD met le feu aux poudres au gouvernement !</t>
+          <t>Intelligence artificielle et emploi : près de la moitié de la population anticipe des suppressions massives de postes selon une étude</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/18/cette-prime-promise-par-edf-a-lachat-dune-byd-met-le-feu-aux-poudres-au-gouvernement/</t>
+          <t>https://kulturegeek.fr/news-359700/intelligence-artificielle-emploi-pres-moitie-population-anticipe-suppressions-massives-postes-etude</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>10. Voiture</t>
+          <t>6. IA</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-09-18T09:03:08+00:00</t>
+          <t>2026-09-18T09:03:28+00:00</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>La Redmi Pad 2 est vendue une misère : Xiaomi vide le stock et la fait à -65%</t>
+          <t>Cette prime promise par EDF à l’achat d’une BYD met le feu aux poudres au gouvernement !</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>https://www.01net.com/bons-plans/la-redmi-pad-2-est-vendue-une-misere-xiaomi-vide-le-stock-et-la-fait-a-65.html</t>
+          <t>https://www.journaldugeek.com/2026/09/18/cette-prime-promise-par-edf-a-lachat-dune-byd-met-le-feu-aux-poudres-au-gouvernement/</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>10. Voiture</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-09-18T08:56:00+00:00</t>
+          <t>2026-09-18T09:03:08+00:00</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Actualité : Adieu Microsoft Office : ce logiciel open source et 100 % européen arrive enfin sur ordinateur pour chasser Word et Excel</t>
+          <t>La Redmi Pad 2 est vendue une misère : Xiaomi vide le stock et la fait à -65%</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/appli-logiciel/adieu-microsoft-office-ce-logiciel-open-source-et-100-europeen-arrive-enfin-sur-ordinateur-pour-chasser-word-et-excel-n262008.html</t>
+          <t>https://www.01net.com/bons-plans/la-redmi-pad-2-est-vendue-une-misere-xiaomi-vide-le-stock-et-la-fait-a-65.html</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -6433,297 +6433,297 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-09-18T08:35:03+00:00</t>
+          <t>2026-09-18T08:56:00+00:00</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Euro Office : l’alternative européenne à Microsoft Office arrive sur Windows, macOS et Linux</t>
+          <t>Actualité : Adieu Microsoft Office : ce logiciel open source et 100 % européen arrive enfin sur ordinateur pour chasser Word et Excel</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>https://www.01net.com/actualites/euro-office-lalternative-europeenne-a-microsoft-office-arrive-sur-windows-macos-et-linux.html</t>
+          <t>https://www.lesnumeriques.com/appli-logiciel/adieu-microsoft-office-ce-logiciel-open-source-et-100-europeen-arrive-enfin-sur-ordinateur-pour-chasser-word-et-excel-n262008.html</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>5. Logiciels _ OS</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-09-18T08:31:00+00:00</t>
+          <t>2026-09-18T08:35:03+00:00</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Actualité : Fusion nucléaire : des chercheurs génèrent des rayons X aussi brillants qu'une étoile et jamais vus sur Terre</t>
+          <t>Euro Office : l’alternative européenne à Microsoft Office arrive sur Windows, macOS et Linux</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/concept/fusion-nucleaire-des-chercheurs-generent-des-rayons-x-aussi-brillants-qu-une-etoile-et-jamais-vus-sur-terre-n262003.html</t>
+          <t>https://www.01net.com/actualites/euro-office-lalternative-europeenne-a-microsoft-office-arrive-sur-windows-macos-et-linux.html</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>17. Actualité éco</t>
+          <t>5. Logiciels _ OS</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-09-18T08:30:23+00:00</t>
+          <t>2026-09-18T08:31:00+00:00</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Extension Pokémon 30 ans : les magasins ont-ils le droit de desceller les cartes pour éviter les scalpers ?</t>
+          <t>Actualité : Fusion nucléaire : des chercheurs génèrent des rayons X aussi brillants qu'une étoile et jamais vus sur Terre</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/18/extension-pokemon-30-ans-les-magasins-ont-ils-le-droit-de-desceller-les-cartes-pour-eviter-les-scalpers/</t>
+          <t>https://www.lesnumeriques.com/concept/fusion-nucleaire-des-chercheurs-generent-des-rayons-x-aussi-brillants-qu-une-etoile-et-jamais-vus-sur-terre-n262003.html</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>15. ludique</t>
+          <t>17. Actualité éco</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Korben</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-09-18T08:27:24+00:00</t>
+          <t>2026-09-18T08:30:23+00:00</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Linux sur PS5 Pro n'arrivera pas tout de suite</t>
+          <t>Extension Pokémon 30 ans : les magasins ont-ils le droit de desceller les cartes pour éviter les scalpers ?</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>https://korben.info/ps5-linux-developpeur-principal-abandonne.html</t>
+          <t>https://www.journaldugeek.com/2026/09/18/extension-pokemon-30-ans-les-magasins-ont-ils-le-droit-de-desceller-les-cartes-pour-eviter-les-scalpers/</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>5. Logiciels _ OS</t>
+          <t>15. ludique</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>Korben</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-09-18T08:16:02+00:00</t>
+          <t>2026-09-18T08:27:24+00:00</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Quelle est la valeur de votre vieille console Nintendo en 2026 ? Le classement des 10 modèles les plus côtés</t>
+          <t>Linux sur PS5 Pro n'arrivera pas tout de suite</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/18/quelle-est-la-valeur-de-votre-vieille-console-nintendo/</t>
+          <t>https://korben.info/ps5-linux-developpeur-principal-abandonne.html</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>15. ludique</t>
+          <t>5. Logiciels _ OS</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-09-18T08:08:19+00:00</t>
+          <t>2026-09-18T08:16:02+00:00</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Google Keep change le design d’un de ses widgets de la meilleure des manières</t>
+          <t>Quelle est la valeur de votre vieille console Nintendo en 2026 ? Le classement des 10 modèles les plus côtés</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>https://www.01net.com/actualites/google-keep-change-design-widgets-meilleures-des-manieres.html</t>
+          <t>https://www.journaldugeek.com/2026/09/18/quelle-est-la-valeur-de-votre-vieille-console-nintendo/</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>5. Logiciels _ OS</t>
+          <t>15. ludique</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Korben</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-09-18T08:07:06+00:00</t>
+          <t>2026-09-18T08:08:19+00:00</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Mes 2 nouveaux interrupteurs Sonoff Zigbee</t>
+          <t>Google Keep change le design d’un de ses widgets de la meilleure des manières</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>https://korben.info/sonoff-volet-lumiere-zigbee-bureau.html</t>
+          <t>https://www.01net.com/actualites/google-keep-change-design-widgets-meilleures-des-manieres.html</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>12. Cuisine</t>
+          <t>5. Logiciels _ OS</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>Korben</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-09-18T08:04:00+00:00</t>
+          <t>2026-09-18T08:07:06+00:00</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Actualité : Bon plan – Le répéteur Wifi Huawei WiFi Mesh 3 Pack de 3 à 119,99 € (-38%)</t>
+          <t>Mes 2 nouveaux interrupteurs Sonoff Zigbee</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/repeteurs-wi-fi/bon-plan-le-repeteur-wifi-huawei-wifi-mesh-3-pack-de-3-a-119-99-38-n262007.html</t>
+          <t>https://korben.info/sonoff-volet-lumiere-zigbee-bureau.html</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>3. Periphérique</t>
+          <t>12. Cuisine</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-09-18T08:02:22+00:00</t>
+          <t>2026-09-18T08:04:00+00:00</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Un roman inédit de Tolkien sort en France, 80 ans après sa création</t>
+          <t>Actualité : Bon plan – Le répéteur Wifi Huawei WiFi Mesh 3 Pack de 3 à 119,99 € (-38%)</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/18/un-roman-inedit-de-tolkien-sort-en-france-80-ans-apres-sa-creation/</t>
+          <t>https://www.lesnumeriques.com/repeteurs-wi-fi/bon-plan-le-repeteur-wifi-huawei-wifi-mesh-3-pack-de-3-a-119-99-38-n262007.html</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>NON_CLASSE</t>
+          <t>3. Periphérique</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-09-18T08:00:00+00:00</t>
+          <t>2026-09-18T08:02:22+00:00</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>SharkNinja Crispi DualZone, un Airfryer avec deux compartiments pour préparer un repas complet en une seule fois</t>
+          <t>Un roman inédit de Tolkien sort en France, 80 ans après sa création</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/electromenager/sharkninja-crispi-dualzone-un-airfryer-avec-deux-compartiments-pour-preparer-un-repas-complet-en-une-seule-fois-na261964.html</t>
+          <t>https://www.journaldugeek.com/2026/09/18/un-roman-inedit-de-tolkien-sort-en-france-80-ans-apres-sa-creation/</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>12. Cuisine</t>
+          <t>NON_CLASSE</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>KultureGeek</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-09-18T07:53:40+00:00</t>
+          <t>2026-09-18T08:00:00+00:00</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Claude dirige déjà 26 % de la recherche d’Anthropic sur ses prochaines IA</t>
+          <t>SharkNinja Crispi DualZone, un Airfryer avec deux compartiments pour préparer un repas complet en une seule fois</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>https://kulturegeek.fr/news-359684/claude-dirige-26-recherche-anthropic-prochaines-ia</t>
+          <t>https://www.lesnumeriques.com/electromenager/sharkninja-crispi-dualzone-un-airfryer-avec-deux-compartiments-pour-preparer-un-repas-complet-en-une-seule-fois-na261964.html</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>6. IA</t>
+          <t>12. Cuisine</t>
         </is>
       </c>
     </row>
@@ -6735,125 +6735,125 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-09-18T07:38:12+00:00</t>
+          <t>2026-09-18T07:53:40+00:00</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Lunettes connectées : le parquet de Paris ouvre une enquête après des vidéos filmées sans consentement</t>
+          <t>Claude dirige déjà 26 % de la recherche d’Anthropic sur ses prochaines IA</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>https://kulturegeek.fr/news-359682/lunettes-connectees-parquet-paris-enquete-videos-consentement</t>
+          <t>https://kulturegeek.fr/news-359684/claude-dirige-26-recherche-anthropic-prochaines-ia</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>6. IA</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>KultureGeek</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026-09-18T07:31:55+00:00</t>
+          <t>2026-09-18T07:38:12+00:00</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Les premières images de Narnia : Le Neveu du magicien sont là et elles risquent de ne pas vous plaire !</t>
+          <t>Lunettes connectées : le parquet de Paris ouvre une enquête après des vidéos filmées sans consentement</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/18/premieres-images-narnia-le-neveu-du-magicien-film-netflix/</t>
+          <t>https://kulturegeek.fr/news-359682/lunettes-connectees-parquet-paris-enquete-videos-consentement</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>7. Video</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2026-09-18T07:14:16+00:00</t>
+          <t>2026-09-18T07:31:55+00:00</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Revolut : après la fuite de données, une arnaque redoutable vise les clients</t>
+          <t>Les premières images de Narnia : Le Neveu du magicien sont là et elles risquent de ne pas vous plaire !</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>https://www.01net.com/actualites/revolut-apres-fuite-donnees-arnaque-redoutable-vise-clients.html</t>
+          <t>https://www.journaldugeek.com/2026/09/18/premieres-images-narnia-le-neveu-du-magicien-film-netflix/</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>16. actu jur et pol</t>
+          <t>7. Video</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2026-09-18T07:06:18+00:00</t>
+          <t>2026-09-18T07:14:16+00:00</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Bornes de recharges : voici ce qui change pour les voitures électriques dès le 1er janvier 2027</t>
+          <t>Revolut : après la fuite de données, une arnaque redoutable vise les clients</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/18/bornes-de-recharges-voici-ce-qui-change-pour-les-voitures-electriques-des-le-1er-janvier-2027/</t>
+          <t>https://www.01net.com/actualites/revolut-apres-fuite-donnees-arnaque-redoutable-vise-clients.html</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>10. Voiture</t>
+          <t>16. actu jur et pol</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2026-09-18T07:00:00+00:00</t>
+          <t>2026-09-18T07:06:18+00:00</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Repérer la marque automobile au système de navigation le plus fluide : 6 démonstrations en concession</t>
+          <t>Bornes de recharges : voici ce qui change pour les voitures électriques dès le 1er janvier 2027</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/traceurs-gps/reperer-la-marque-automobile-au-systeme-de-navigation-le-plus-fluide-6-demonstrations-en-concession-na262029.html</t>
+          <t>https://www.journaldugeek.com/2026/09/18/bornes-de-recharges-voici-ce-qui-change-pour-les-voitures-electriques-des-le-1er-janvier-2027/</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -6865,54 +6865,54 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>TomsHardware</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2026-09-18T06:55:00+00:00</t>
+          <t>2026-09-18T07:00:00+00:00</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Les premières cartes mères Z990 en vue ? Six modèles en préparation chez ASRock</t>
+          <t>Repérer la marque automobile au système de navigation le plus fluide : 6 démonstrations en concession</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.fr/les-premieres-cartes-meres-z990-en-vue-six-modeles-en-preparation-chez-asrock/</t>
+          <t>https://www.lesnumeriques.com/traceurs-gps/reperer-la-marque-automobile-au-systeme-de-navigation-le-plus-fluide-6-demonstrations-en-concession-na262029.html</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>2. PC</t>
+          <t>10. Voiture</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>TomsHardware</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2026-09-18T06:38:02+00:00</t>
+          <t>2026-09-18T06:55:00+00:00</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Des avions vont changer d’altitude pour tenter d’effacer leurs traînées du ciel</t>
+          <t>Les premières cartes mères Z990 en vue ? Six modèles en préparation chez ASRock</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/18/des-avions-vont-changer-daltitude-pour-tenter-deffacer-leurs-trainees-du-ciel/</t>
+          <t>https://www.tomshardware.fr/les-premieres-cartes-meres-z990-en-vue-six-modeles-en-preparation-chez-asrock/</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>9. Moiilité douce</t>
+          <t>2. PC</t>
         </is>
       </c>
     </row>
@@ -6924,22 +6924,22 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2026-09-18T06:37:59+00:00</t>
+          <t>2026-09-18T06:38:02+00:00</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Bose s’ouvre encore plus avec deux nouveautés oreilles libres</t>
+          <t>Des avions vont changer d’altitude pour tenter d’effacer leurs traînées du ciel</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/18/bose-souvre-encore-plus-avec-deux-nouveautes-oreilles-libres/</t>
+          <t>https://www.journaldugeek.com/2026/09/18/des-avions-vont-changer-daltitude-pour-tenter-deffacer-leurs-trainees-du-ciel/</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>8. Audio</t>
+          <t>9. Moiilité douce</t>
         </is>
       </c>
     </row>
@@ -6951,184 +6951,184 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>2026-09-18T06:32:17+00:00</t>
+          <t>2026-09-18T06:37:59+00:00</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Claude fait le ménage dans ses onglets en fusionnant le chat et Cowork</t>
+          <t>Bose s’ouvre encore plus avec deux nouveautés oreilles libres</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/18/claude-fait-le-menage-dans-ses-onglets-en-fusionnant-le-chat-et-cowork/</t>
+          <t>https://www.journaldugeek.com/2026/09/18/bose-souvre-encore-plus-avec-deux-nouveautes-oreilles-libres/</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>5. Logiciels _ OS</t>
+          <t>8. Audio</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>TomsHardware</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>2026-09-18T06:30:00+00:00</t>
+          <t>2026-09-18T06:32:17+00:00</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Windows 11, Office, Gemini… équipez votre PC à moindre coût en 2026</t>
+          <t>Claude fait le ménage dans ses onglets en fusionnant le chat et Cowork</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.fr/windows-11-office-gemini-equipez-votre-pc-a-moindre-cout-en-2026/</t>
+          <t>https://www.journaldugeek.com/2026/09/18/claude-fait-le-menage-dans-ses-onglets-en-fusionnant-le-chat-et-cowork/</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>2. PC</t>
+          <t>5. Logiciels _ OS</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>TomsHardware</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>2026-09-18T06:03:54+00:00</t>
+          <t>2026-09-18T06:30:00+00:00</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Google Home ouvre la porte aux agents IA… avec un sérieux avertissement</t>
+          <t>Windows 11, Office, Gemini… équipez votre PC à moindre coût en 2026</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/18/google-home-ouvre-la-porte-aux-agents-ia-avec-un-serieux-avertissement/</t>
+          <t>https://www.tomshardware.fr/windows-11-office-gemini-equipez-votre-pc-a-moindre-cout-en-2026/</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>6. IA</t>
+          <t>2. PC</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>TomsHardware</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2026-09-18T04:48:00+00:00</t>
+          <t>2026-09-18T06:03:54+00:00</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Pour les 13 ans de GTA 5, un moddeur met à jour le plugin NaturalVision</t>
+          <t>Google Home ouvre la porte aux agents IA… avec un sérieux avertissement</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.fr/pour-les-13-ans-de-gta-5-un-moddeur-met-a-jour-le-plugin-naturalvision/</t>
+          <t>https://www.journaldugeek.com/2026/09/18/google-home-ouvre-la-porte-aux-agents-ia-avec-un-serieux-avertissement/</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>15. ludique</t>
+          <t>6. IA</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Korben</t>
+          <t>TomsHardware</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>2026-09-17T15:15:41+00:00</t>
+          <t>2026-09-18T04:48:00+00:00</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Fugleramme - Le cadre qui dessine les oiseaux qu'il entend</t>
+          <t>Pour les 13 ans de GTA 5, un moddeur met à jour le plugin NaturalVision</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>https://korben.info/fugleramme-detection-oiseaux-eink.html</t>
+          <t>https://www.tomshardware.fr/pour-les-13-ans-de-gta-5-un-moddeur-met-a-jour-le-plugin-naturalvision/</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>NON_CLASSE</t>
+          <t>15. ludique</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>TomsHardware</t>
+          <t>Korben</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2026-09-17T15:01:00+00:00</t>
+          <t>2026-09-17T15:15:41+00:00</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>SteamOS : Valve s’attaque à la prise en charge des cartes Nvidia, un chantier de plusieurs années</t>
+          <t>Fugleramme - Le cadre qui dessine les oiseaux qu'il entend</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.fr/steamos-valve-sattaque-a-la-prise-en-charge-des-cartes-nvidia-un-chantier-de-plusieurs-annees/</t>
+          <t>https://korben.info/fugleramme-detection-oiseaux-eink.html</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>2. PC</t>
+          <t>NON_CLASSE</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Korben</t>
+          <t>TomsHardware</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2026-09-17T14:56:31+00:00</t>
+          <t>2026-09-17T15:01:00+00:00</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>MechaCon - La puce qui condamnait les PS2 enfin hackée</t>
+          <t>SteamOS : Valve s’attaque à la prise en charge des cartes Nvidia, un chantier de plusieurs années</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>https://korben.info/mechacon-ps2-craque-retro-ingenierie.html</t>
+          <t>https://www.tomshardware.fr/steamos-valve-sattaque-a-la-prise-en-charge-des-cartes-nvidia-un-chantier-de-plusieurs-annees/</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>NON_CLASSE</t>
+          <t>2. PC</t>
         </is>
       </c>
     </row>
@@ -7140,22 +7140,22 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2026-09-17T13:40:30+00:00</t>
+          <t>2026-09-17T14:56:31+00:00</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Des agents IA spamment le web pour payer leurs propres serveurs</t>
+          <t>MechaCon - La puce qui condamnait les PS2 enfin hackée</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>https://korben.info/des-agents-ia-spamment-le-web-pour-payer-leurs-propres-serveurs.html</t>
+          <t>https://korben.info/mechacon-ps2-craque-retro-ingenierie.html</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>2. PC</t>
+          <t>NON_CLASSE</t>
         </is>
       </c>
     </row>
@@ -7167,22 +7167,22 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>2026-09-17T13:26:03+00:00</t>
+          <t>2026-09-17T13:40:30+00:00</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Google Home laisse ChatGPT et Claude piloter votre maison</t>
+          <t>Des agents IA spamment le web pour payer leurs propres serveurs</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>https://korben.info/google-home-laisse-chatgpt-et-claude-piloter-votre-maison.html</t>
+          <t>https://korben.info/des-agents-ia-spamment-le-web-pour-payer-leurs-propres-serveurs.html</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>6. IA</t>
+          <t>2. PC</t>
         </is>
       </c>
     </row>
@@ -7194,17 +7194,17 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>2026-09-17T11:20:32+00:00</t>
+          <t>2026-09-17T13:26:03+00:00</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Cloudflare lance son skill d'audit de sécurité par IA</t>
+          <t>Google Home laisse ChatGPT et Claude piloter votre maison</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>https://korben.info/cloudflare-security-audit-skill.html</t>
+          <t>https://korben.info/google-home-laisse-chatgpt-et-claude-piloter-votre-maison.html</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -7216,27 +7216,27 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>TomsHardware</t>
+          <t>Korben</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>2026-09-17T10:11:00+00:00</t>
+          <t>2026-09-17T11:20:32+00:00</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Faire évoluer son installation solaire : comment ajouter une batterie sans tout changer ?</t>
+          <t>Cloudflare lance son skill d'audit de sécurité par IA</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.fr/faire-evoluer-son-installation-solaire-comment-ajouter-une-batterie-sans-tout-changer/</t>
+          <t>https://korben.info/cloudflare-security-audit-skill.html</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>8. Audio</t>
+          <t>6. IA</t>
         </is>
       </c>
     </row>
@@ -7248,22 +7248,22 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>2026-09-17T06:35:00+00:00</t>
+          <t>2026-09-17T10:11:00+00:00</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Smart Window, la fonctionnalité IA de Firefox, arrive en France avec Mistral</t>
+          <t>Faire évoluer son installation solaire : comment ajouter une batterie sans tout changer ?</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.fr/smart-window-la-fonctionnalite-ia-de-firefox-arrive-en-france-avec-mistral/</t>
+          <t>https://www.tomshardware.fr/faire-evoluer-son-installation-solaire-comment-ajouter-une-batterie-sans-tout-changer/</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>5. Logiciels _ OS</t>
+          <t>8. Audio</t>
         </is>
       </c>
     </row>
@@ -7275,22 +7275,22 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>2026-09-17T05:34:00+00:00</t>
+          <t>2026-09-17T06:35:00+00:00</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Microsoft Edge peut planter si vous utilisez certaines applications</t>
+          <t>Smart Window, la fonctionnalité IA de Firefox, arrive en France avec Mistral</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.fr/microsoft-edge-peut-planter-si-vous-utilisez-certaines-applications/</t>
+          <t>https://www.tomshardware.fr/smart-window-la-fonctionnalite-ia-de-firefox-arrive-en-france-avec-mistral/</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>5. Logiciels _ OS</t>
         </is>
       </c>
     </row>
@@ -7302,49 +7302,49 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>2026-09-16T15:05:00+00:00</t>
+          <t>2026-09-17T05:34:00+00:00</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Le prix de ce clavier SteelSeries chute sur Amazon, c’est le moment d’en profiter</t>
+          <t>Microsoft Edge peut planter si vous utilisez certaines applications</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.fr/le-prix-de-ce-clavier-steelseries-chute-sur-amazon-cest-le-moment-den-profiter/</t>
+          <t>https://www.tomshardware.fr/microsoft-edge-peut-planter-si-vous-utilisez-certaines-applications/</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>3. Periphérique</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Korben</t>
+          <t>TomsHardware</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2026-09-16T13:33:01+00:00</t>
+          <t>2026-09-16T15:05:00+00:00</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Shuffle Drummer - FL Studio n'a qu'à bien se tenir</t>
+          <t>Le prix de ce clavier SteelSeries chute sur Amazon, c’est le moment d’en profiter</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>https://korben.info/shuffle-drummer-groovebox-navigateur.html</t>
+          <t>https://www.tomshardware.fr/le-prix-de-ce-clavier-steelseries-chute-sur-amazon-cest-le-moment-den-profiter/</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>5. Logiciels _ OS</t>
+          <t>3. Periphérique</t>
         </is>
       </c>
     </row>
@@ -7356,17 +7356,17 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2026-09-16T07:49:19+00:00</t>
+          <t>2026-09-16T13:33:01+00:00</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Fuse-archive - Vos ZIP montés en dossiers ordinaires</t>
+          <t>Shuffle Drummer - FL Studio n'a qu'à bien se tenir</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>https://korben.info/mount-archive-monter-archives-comme-un-dossier.html</t>
+          <t>https://korben.info/shuffle-drummer-groovebox-navigateur.html</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -7383,76 +7383,76 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2026-09-16T07:35:05+00:00</t>
+          <t>2026-09-16T07:49:19+00:00</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>La Forge - Le GitLab public des profs codeurs</t>
+          <t>Fuse-archive - Vos ZIP montés en dossiers ordinaires</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>https://korben.info/forge-apps-education-enseignants-code.html</t>
+          <t>https://korben.info/mount-archive-monter-archives-comme-un-dossier.html</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>NON_CLASSE</t>
+          <t>5. Logiciels _ OS</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>TomsHardware</t>
+          <t>Korben</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2026-09-16T06:47:00+00:00</t>
+          <t>2026-09-16T07:35:05+00:00</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Pourquoi décaler la sortie de l’iPhone 18 au printemps 2027 est une bonne idée ?</t>
+          <t>La Forge - Le GitLab public des profs codeurs</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.fr/pourquoi-decaler-la-sortie-de-liphone-18-au-printemps-2027-est-une-bonne-idee/</t>
+          <t>https://korben.info/forge-apps-education-enseignants-code.html</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>NON_CLASSE</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Korben</t>
+          <t>TomsHardware</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>2026-09-15T15:43:58+00:00</t>
+          <t>2026-09-16T06:47:00+00:00</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Test d'une batterie externe et dock magnétique Antank pour Nintendo Switch 2</t>
+          <t>Pourquoi décaler la sortie de l’iPhone 18 au printemps 2027 est une bonne idée ?</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>https://korben.info/test-dune-batterie-externe-et-dock-magentique-antank-pour-nintendo-switch-2.html</t>
+          <t>https://www.tomshardware.fr/pourquoi-decaler-la-sortie-de-liphone-18-au-printemps-2027-est-une-bonne-idee/</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>3. Periphérique</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
@@ -7464,22 +7464,22 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2026-09-15T13:53:18+00:00</t>
+          <t>2026-09-15T15:43:58+00:00</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Suyu tire sa révérence sur un mode de recompilation pour jeux Switch</t>
+          <t>Test d'une batterie externe et dock magnétique Antank pour Nintendo Switch 2</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>https://korben.info/suyu-recompilation-statique-emulation-switch.html</t>
+          <t>https://korben.info/test-dune-batterie-externe-et-dock-magentique-antank-pour-nintendo-switch-2.html</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>15. ludique</t>
+          <t>3. Periphérique</t>
         </is>
       </c>
     </row>
@@ -7491,22 +7491,22 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>2026-09-15T13:28:51+00:00</t>
+          <t>2026-09-15T13:53:18+00:00</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>CUDA-for-AMD-Windows - Le .exe NVIDIA pour votre Radeon</t>
+          <t>Suyu tire sa révérence sur un mode de recompilation pour jeux Switch</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>https://korben.info/zluda-hip-cuda-radeon-windows.html</t>
+          <t>https://korben.info/suyu-recompilation-statique-emulation-switch.html</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>2. PC</t>
+          <t>15. ludique</t>
         </is>
       </c>
     </row>
@@ -7518,22 +7518,22 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>2026-09-15T13:13:09+00:00</t>
+          <t>2026-09-15T13:28:51+00:00</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>OpenDisplay - Étendre l'affichage Mac avec ce que vous avez sous la main</t>
+          <t>CUDA-for-AMD-Windows - Le .exe NVIDIA pour votre Radeon</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>https://korben.info/opendisplay-ecran-secondaire-iphone-ipad-mac.html</t>
+          <t>https://korben.info/zluda-hip-cuda-radeon-windows.html</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>2. PC</t>
         </is>
       </c>
     </row>
@@ -7545,22 +7545,22 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2026-09-15T11:49:03+00:00</t>
+          <t>2026-09-15T13:13:09+00:00</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Windows 11 - Un clic sur le bon lien et hop, vous avez un compte local</t>
+          <t>OpenDisplay - Étendre l'affichage Mac avec ce que vous avez sous la main</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>https://korben.info/bypass-compte-microsoft-windows-11.html</t>
+          <t>https://korben.info/opendisplay-ecran-secondaire-iphone-ipad-mac.html</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>5. Logiciels _ OS</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
@@ -7572,22 +7572,22 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2026-09-15T08:16:10+00:00</t>
+          <t>2026-09-15T11:49:03+00:00</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Kits IA Korben - Des tutos pour vos agents IA</t>
+          <t>Windows 11 - Un clic sur le bon lien et hop, vous avez un compte local</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>https://korben.info/kits-ia-korben-tutos-agents-ia.html</t>
+          <t>https://korben.info/bypass-compte-microsoft-windows-11.html</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>6. IA</t>
+          <t>5. Logiciels _ OS</t>
         </is>
       </c>
     </row>
@@ -7599,22 +7599,22 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>2026-09-15T08:00:00+00:00</t>
+          <t>2026-09-15T08:16:10+00:00</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>TP-Link Deco BE25-5G - Le routeur qui garde la maison</t>
+          <t>Kits IA Korben - Des tutos pour vos agents IA</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>https://korben.info/deco-be25-5g-test.html</t>
+          <t>https://korben.info/kits-ia-korben-tutos-agents-ia.html</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>6. IA</t>
         </is>
       </c>
     </row>
@@ -7626,22 +7626,22 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>2026-09-15T07:23:22+00:00</t>
+          <t>2026-09-15T08:00:00+00:00</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>GNOME Boxes - L'outil qui monte les VM à votre place</t>
+          <t>TP-Link Deco BE25-5G - Le routeur qui garde la maison</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>https://korben.info/gnome-boxes-virtualisation-simple-linux.html</t>
+          <t>https://korben.info/deco-be25-5g-test.html</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>5. Logiciels _ OS</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
@@ -7653,22 +7653,22 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>2026-09-15T06:53:24+00:00</t>
+          <t>2026-09-15T07:23:22+00:00</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>SpruceOS - Le guide pour rhabiller votre console rétro</t>
+          <t>GNOME Boxes - L'outil qui monte les VM à votre place</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>https://korben.info/spruceos-guide-installation-console-retro.html</t>
+          <t>https://korben.info/gnome-boxes-virtualisation-simple-linux.html</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>15. ludique</t>
+          <t>5. Logiciels _ OS</t>
         </is>
       </c>
     </row>
@@ -7680,22 +7680,22 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>2026-09-14T15:10:49+00:00</t>
+          <t>2026-09-15T06:53:24+00:00</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Test Thermal Master P3 : voir ce qui chauffe avec son smartphone</t>
+          <t>SpruceOS - Le guide pour rhabiller votre console rétro</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>https://korben.info/test-thermal-master-p3-voir-ce-qui-chauffe-avec-son-smartphone.html</t>
+          <t>https://korben.info/spruceos-guide-installation-console-retro.html</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>15. ludique</t>
         </is>
       </c>
     </row>
@@ -7707,22 +7707,22 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>2026-09-14T13:33:00+00:00</t>
+          <t>2026-09-14T15:10:49+00:00</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Antro pique ?</t>
+          <t>Test Thermal Master P3 : voir ce qui chauffe avec son smartphone</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>https://korben.info/test-antro-avis.html</t>
+          <t>https://korben.info/test-thermal-master-p3-voir-ce-qui-chauffe-avec-son-smartphone.html</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>NON_CLASSE</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
@@ -7734,17 +7734,17 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>2026-09-14T09:14:55+00:00</t>
+          <t>2026-09-14T13:33:00+00:00</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Tomb Raider peut tourner sur un ESP32-P4</t>
+          <t>Antro pique ?</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>https://korben.info/tomb-raider-peut-tourner-sur-un-esp32-p4.html</t>
+          <t>https://korben.info/test-antro-avis.html</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -7761,22 +7761,22 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>2026-09-14T08:30:00+00:00</t>
+          <t>2026-09-14T09:14:55+00:00</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Apple Configurator - Pour transformer votre iPhone en Dumbphone</t>
+          <t>Tomb Raider peut tourner sur un ESP32-P4</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>https://korben.info/apple-configurator-iphone-dumbphone-temps-ecran.html</t>
+          <t>https://korben.info/tomb-raider-peut-tourner-sur-un-esp32-p4.html</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>NON_CLASSE</t>
         </is>
       </c>
     </row>
@@ -7788,22 +7788,22 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>2026-09-14T07:42:28+00:00</t>
+          <t>2026-09-14T08:30:00+00:00</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>CanoFlash - Du Wi-Fi sur votre GBA (mais pas pour jouer, snif)</t>
+          <t>Apple Configurator - Pour transformer votre iPhone en Dumbphone</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>https://korben.info/gba-link-cable-internet-esp32.html</t>
+          <t>https://korben.info/apple-configurator-iphone-dumbphone-temps-ecran.html</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>3. Periphérique</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
@@ -7815,22 +7815,22 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>2026-09-11T10:00:00+00:00</t>
+          <t>2026-09-14T07:42:28+00:00</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>OmniVoice - Clonez votre propre voix en local et en français</t>
+          <t>CanoFlash - Du Wi-Fi sur votre GBA (mais pas pour jouer, snif)</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>https://korben.info/omnivoice-clonage-voix.html</t>
+          <t>https://korben.info/gba-link-cable-internet-esp32.html</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>8. Audio</t>
+          <t>3. Periphérique</t>
         </is>
       </c>
     </row>
@@ -7842,22 +7842,22 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>2026-09-11T09:52:43+00:00</t>
+          <t>2026-09-11T10:00:00+00:00</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Le Deathray - Le shader WebGPU qui fait redémarrer votre Mac</t>
+          <t>OmniVoice - Clonez votre propre voix en local et en français</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>https://korben.info/webgpu-deathray-freeze-mac.html</t>
+          <t>https://korben.info/omnivoice-clonage-voix.html</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>NON_CLASSE</t>
+          <t>8. Audio</t>
         </is>
       </c>
     </row>
@@ -7869,22 +7869,22 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>2026-09-11T07:19:00+00:00</t>
+          <t>2026-09-11T09:52:43+00:00</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Trynix - Testez des classiques Linux sans rien installer</t>
+          <t>Le Deathray - Le shader WebGPU qui fait redémarrer votre Mac</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>https://korben.info/trynix-tester-paquet-nix-navigateur.html</t>
+          <t>https://korben.info/webgpu-deathray-freeze-mac.html</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>5. Logiciels _ OS</t>
+          <t>NON_CLASSE</t>
         </is>
       </c>
     </row>
@@ -7896,17 +7896,17 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>2026-09-11T07:00:00+00:00</t>
+          <t>2026-09-11T07:19:00+00:00</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Pluton - Le backup chiffré qui se pilote depuis le navigateur</t>
+          <t>Trynix - Testez des classiques Linux sans rien installer</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>https://korben.info/pluton-backup-self-hosted-chiffre-restic-rclone.html</t>
+          <t>https://korben.info/trynix-tester-paquet-nix-navigateur.html</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -7923,22 +7923,22 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>2026-09-11T06:15:54+00:00</t>
+          <t>2026-09-11T07:00:00+00:00</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>ReProgman - L'interface de Windows 3.1 sur PC et Mac</t>
+          <t>Pluton - Le backup chiffré qui se pilote depuis le navigateur</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>https://korben.info/windows-31-shell-vibe-code-claude.html</t>
+          <t>https://korben.info/pluton-backup-self-hosted-chiffre-restic-rclone.html</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>2. PC</t>
+          <t>5. Logiciels _ OS</t>
         </is>
       </c>
     </row>
@@ -7950,17 +7950,17 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>2026-09-11T04:59:04+00:00</t>
+          <t>2026-09-11T06:15:54+00:00</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Super Mario 64 tourne sur un processeur ARM (avec ReactOS)</t>
+          <t>ReProgman - L'interface de Windows 3.1 sur PC et Mac</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>https://korben.info/reactos-arm64-fex-jeux-windows.html</t>
+          <t>https://korben.info/windows-31-shell-vibe-code-claude.html</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -7977,22 +7977,22 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>2026-09-10T13:52:44+00:00</t>
+          <t>2026-09-11T04:59:04+00:00</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Ce que les IA d'OpenAI se sont raconté en se croyant seules</t>
+          <t>Super Mario 64 tourne sur un processeur ARM (avec ReactOS)</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>https://korben.info/agents-ia-organisation-wiki-allemand.html</t>
+          <t>https://korben.info/reactos-arm64-fex-jeux-windows.html</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>6. IA</t>
+          <t>2. PC</t>
         </is>
       </c>
     </row>
@@ -8004,22 +8004,22 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>2026-09-10T11:04:19+00:00</t>
+          <t>2026-09-10T13:52:44+00:00</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>RistOS - L'Android sans applis dont le cerveau reste chez vous</t>
+          <t>Ce que les IA d'OpenAI se sont raconté en se croyant seules</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>https://korben.info/rist-os-handset-android-degoogle.html</t>
+          <t>https://korben.info/agents-ia-organisation-wiki-allemand.html</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>6. IA</t>
         </is>
       </c>
     </row>
@@ -8031,22 +8031,22 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>2026-09-10T08:15:16+00:00</t>
+          <t>2026-09-10T11:04:19+00:00</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Une faille cPanel distribue des accès root</t>
+          <t>RistOS - L'Android sans applis dont le cerveau reste chez vous</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>https://korben.info/cpanel-faille-prise-controle-compte-hebergement.html</t>
+          <t>https://korben.info/rist-os-handset-android-degoogle.html</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>5. Logiciels _ OS</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
@@ -8058,17 +8058,17 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>2026-09-10T04:56:34+00:00</t>
+          <t>2026-09-10T08:15:16+00:00</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Un seul abonnement Surfshark, une infinité d'appareils protégés pour la rentrée</t>
+          <t>Une faille cPanel distribue des accès root</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>https://korben.info/un-seul-abonnement-surfshark.html</t>
+          <t>https://korben.info/cpanel-faille-prise-controle-compte-hebergement.html</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -8085,45 +8085,49 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>2026-09-09T13:07:21+00:00</t>
+          <t>2026-09-10T04:56:34+00:00</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Mettez à jour Plex ! (même sans savoir contre quoi)</t>
+          <t>Un seul abonnement Surfshark, une infinité d'appareils protégés pour la rentrée</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>https://korben.info/plex-serveurs-non-patches-failles.html</t>
+          <t>https://korben.info/un-seul-abonnement-surfshark.html</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>2. PC</t>
+          <t>5. Logiciels _ OS</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Frandroid - Actualités</t>
-        </is>
-      </c>
-      <c r="B285" t="inlineStr"/>
+          <t>Korben</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>2026-09-09T13:07:21+00:00</t>
+        </is>
+      </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Pas de facture mobile avant 2027 : La Poste Mobile offre 4 mois gratuits sur ses forfaits 5G</t>
+          <t>Mettez à jour Plex ! (même sans savoir contre quoi)</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>https://native.humanoid.fr/register-click?s_id=2&amp;sp_id=47&amp;c_id=4224</t>
+          <t>https://korben.info/plex-serveurs-non-patches-failles.html</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>2. PC</t>
         </is>
       </c>
     </row>
@@ -8136,17 +8140,17 @@
       <c r="B286" t="inlineStr"/>
       <c r="C286" t="inlineStr">
         <is>
-          <t>TCL 24G645 : ce moniteur gaming QD-Mini LED en 300 Hz passe sous les 230 euros</t>
+          <t>Pas de facture mobile avant 2027 : La Poste Mobile offre 4 mois gratuits sur ses forfaits 5G</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/bons-plans/3253289_tcl-24g645-ce-moniteur-gaming-qd-mini-led-en-300-hz-passe-sous-les-230-euros</t>
+          <t>https://native.humanoid.fr/register-click?s_id=2&amp;sp_id=47&amp;c_id=4224</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>3. Periphérique</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
@@ -8159,17 +8163,17 @@
       <c r="B287" t="inlineStr"/>
       <c r="C287" t="inlineStr">
         <is>
-          <t>On a trouvé le gadget pas cher qui transforme vos photos de smartphone en autocollants</t>
+          <t>TCL 24G645 : ce moniteur gaming QD-Mini LED en 300 Hz passe sous les 230 euros</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/bons-plans/3253177_on-a-trouve-le-gadget-pas-cher-qui-transforme-vos-photos-de-smartphone-en-autocollants</t>
+          <t>https://www.frandroid.com/bons-plans/3253289_tcl-24g645-ce-moniteur-gaming-qd-mini-led-en-300-hz-passe-sous-les-230-euros</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>3. Periphérique</t>
         </is>
       </c>
     </row>
@@ -8182,17 +8186,17 @@
       <c r="B288" t="inlineStr"/>
       <c r="C288" t="inlineStr">
         <is>
-          <t>C’est le retour des PC portables sous RTX 5060 à moins de 1 000 € grâce à cette offre Boulanger</t>
+          <t>On a trouvé le gadget pas cher qui transforme vos photos de smartphone en autocollants</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/bons-plans/2804177_cest-le-retour-des-pc-portables-sous-rtx-5060-a-moins-de-1-000-euros-grace-a-cette-offre-boulanger</t>
+          <t>https://www.frandroid.com/bons-plans/3253177_on-a-trouve-le-gadget-pas-cher-qui-transforme-vos-photos-de-smartphone-en-autocollants</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>2. PC</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
@@ -8205,17 +8209,17 @@
       <c r="B289" t="inlineStr"/>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Un grand TV QD Mini-LED avec Philips Ambilight à moins de 700 €, ça se regarde de près</t>
+          <t>C’est le retour des PC portables sous RTX 5060 à moins de 1 000 € grâce à cette offre Boulanger</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/bons-plans/3252877_un-grand-tv-qd-mini-led-avec-philips-ambilight-a-moins-de-700-e-ca-se-regarde-de-pres</t>
+          <t>https://www.frandroid.com/bons-plans/2804177_cest-le-retour-des-pc-portables-sous-rtx-5060-a-moins-de-1-000-euros-grace-a-cette-offre-boulanger</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>7. Video</t>
+          <t>2. PC</t>
         </is>
       </c>
     </row>
@@ -8228,17 +8232,17 @@
       <c r="B290" t="inlineStr"/>
       <c r="C290" t="inlineStr">
         <is>
-          <t>JBL Tune 730BT : ce casque sans fil à 76 h d’autonomie tombe à moins de 40 euros</t>
+          <t>Un grand TV QD Mini-LED avec Philips Ambilight à moins de 700 €, ça se regarde de près</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/bons-plans/3252609_jbl-tune-730bt-ce-casque-sans-fil-a-76-h-dautonomie-tombe-a-moins-de-40-euros</t>
+          <t>https://www.frandroid.com/bons-plans/3252877_un-grand-tv-qd-mini-led-avec-philips-ambilight-a-moins-de-700-e-ca-se-regarde-de-pres</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>8. Audio</t>
+          <t>7. Video</t>
         </is>
       </c>
     </row>
@@ -8251,17 +8255,17 @@
       <c r="B291" t="inlineStr"/>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Le Dyson Humidify+Cool PH2 De‑Nox en promo à -200 € : un appareil 3-en-1 pensé pour l’air sec et pollué</t>
+          <t>JBL Tune 730BT : ce casque sans fil à 76 h d’autonomie tombe à moins de 40 euros</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/bons-plans/3252243_le-dyson-humidifycool-ph2-de-nox-en-promo-a-200-e-un-appareil-3-en-1-pense-pour-lair-sec-et-pollue</t>
+          <t>https://www.frandroid.com/bons-plans/3252609_jbl-tune-730bt-ce-casque-sans-fil-a-76-h-dautonomie-tombe-a-moins-de-40-euros</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>11. Menage</t>
+          <t>8. Audio</t>
         </is>
       </c>
     </row>
@@ -8274,17 +8278,17 @@
       <c r="B292" t="inlineStr"/>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Samsung The Frame 65 pouces (2025) à seulement 999 € chez Boulanger : une belle affaire pour ce TV QLED 4K</t>
+          <t>Le Dyson Humidify+Cool PH2 De‑Nox en promo à -200 € : un appareil 3-en-1 pensé pour l’air sec et pollué</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/bons-plans/3252161_samsung-the-frame-65-pouces-2025-a-seulement-999-e-chez-boulanger-une-belle-affaire-pour-ce-tv-qled-4k</t>
+          <t>https://www.frandroid.com/bons-plans/3252243_le-dyson-humidifycool-ph2-de-nox-en-promo-a-200-e-un-appareil-3-en-1-pense-pour-lair-sec-et-pollue</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>7. Video</t>
+          <t>11. Menage</t>
         </is>
       </c>
     </row>
@@ -8297,12 +8301,12 @@
       <c r="B293" t="inlineStr"/>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Vos DONNÉES ont FUITÉ : voici ce qu’il faut faire !</t>
+          <t>Samsung The Frame 65 pouces (2025) à seulement 999 € chez Boulanger : une belle affaire pour ce TV QLED 4K</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/video/3253483_video</t>
+          <t>https://www.frandroid.com/bons-plans/3252161_samsung-the-frame-65-pouces-2025-a-seulement-999-e-chez-boulanger-une-belle-affaire-pour-ce-tv-qled-4k</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -8320,35 +8324,35 @@
       <c r="B294" t="inlineStr"/>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Ce qu’il faut retenir des tests de l’iPhone 18 Pro !</t>
+          <t>Vos DONNÉES ont FUITÉ : voici ce qu’il faut faire !</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/video/3252919_video</t>
+          <t>https://www.frandroid.com/video/3253483_video</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>7. Video</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Frandroid - Bons plans</t>
+          <t>Frandroid - Actualités</t>
         </is>
       </c>
       <c r="B295" t="inlineStr"/>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Ã peine sorti, le nouveau Xiaomi Redmi Note 17 Pro 5G est dÃ©jÃ  Ã  moitiÃ© prix grÃ¢ce Ã  cette offre</t>
+          <t>Ce qu’il faut retenir des tests de l’iPhone 18 Pro !</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/bons-plans/3252177_a-peine-sorti-le-nouveau-xiaomi-redmi-note-17-pro-5g-est-deja-a-moitie-prix-grace-a-cette-offre</t>
+          <t>https://www.frandroid.com/video/3252919_video</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -8366,17 +8370,17 @@
       <c r="B296" t="inlineStr"/>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Amazon brade le clavier gamer haut de gamme Ã  Rapid Trigger de Razer, le Huntsman V3 Pro TKL</t>
+          <t>Ã peine sorti, le nouveau Xiaomi Redmi Note 17 Pro 5G est dÃ©jÃ  Ã  moitiÃ© prix grÃ¢ce Ã  cette offre</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/bons-plans/3252199_amazon-brade-le-clavier-gamer-haut-de-gamme-a-rapid-trigger-de-razer-le-huntsman-v3-pro-tkl</t>
+          <t>https://www.frandroid.com/bons-plans/3252177_a-peine-sorti-le-nouveau-xiaomi-redmi-note-17-pro-5g-est-deja-a-moitie-prix-grace-a-cette-offre</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>3. Periphérique</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
@@ -8389,17 +8393,17 @@
       <c r="B297" t="inlineStr"/>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Ce ventilateur Shark rafraÃ®chit l’air jusqu’Ã  6 Â°C et coÃ»te 110 â¬ de moins avec cette offre</t>
+          <t>Amazon brade le clavier gamer haut de gamme Ã  Rapid Trigger de Razer, le Huntsman V3 Pro TKL</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/bons-plans/3246361_ce-ventilateur-shark-rafraichit-lair-jusqua-6-c-et-coute-110-euros-de-moins-avec-cette-offre</t>
+          <t>https://www.frandroid.com/bons-plans/3252199_amazon-brade-le-clavier-gamer-haut-de-gamme-a-rapid-trigger-de-razer-le-huntsman-v3-pro-tkl</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>11. Menage</t>
+          <t>3. Periphérique</t>
         </is>
       </c>
     </row>
@@ -8412,17 +8416,17 @@
       <c r="B298" t="inlineStr"/>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Ce robot tondeuse 4×4 capable de grimper des pentes Ã  80 % est bradÃ© Ã  un super prix sur Amazon</t>
+          <t>Ce ventilateur Shark rafraÃ®chit l’air jusqu’Ã  6 Â°C et coÃ»te 110 â¬ de moins avec cette offre</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/bons-plans/3251737_ce-robot-tondeuse-4x4-capable-de-grimper-des-pentes-a-80-est-brade-a-un-super-prix-sur-amazon</t>
+          <t>https://www.frandroid.com/bons-plans/3246361_ce-ventilateur-shark-rafraichit-lair-jusqua-6-c-et-coute-110-euros-de-moins-avec-cette-offre</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>13. Maison</t>
+          <t>11. Menage</t>
         </is>
       </c>
     </row>
@@ -8435,17 +8439,17 @@
       <c r="B299" t="inlineStr"/>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Cet ultrabook d’Acer (Intel Core 5, 16 Go de RAM), avec une sacoche et une souris offertes, est dispo pour 200 â¬ de moins</t>
+          <t>Ce robot tondeuse 4×4 capable de grimper des pentes Ã  80 % est bradÃ© Ã  un super prix sur Amazon</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/bons-plans/3251595_cet-ultrabook-dacer-intel-core-5-16-go-de-ram-avec-une-sacoche-et-une-souris-offertes-est-dispo-pour-200-e-de-moins</t>
+          <t>https://www.frandroid.com/bons-plans/3251737_ce-robot-tondeuse-4x4-capable-de-grimper-des-pentes-a-80-est-brade-a-un-super-prix-sur-amazon</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>2. PC</t>
+          <t>13. Maison</t>
         </is>
       </c>
     </row>
@@ -8458,17 +8462,17 @@
       <c r="B300" t="inlineStr"/>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Ecovacs Deebot X12 OmniCyclone : ce robot aspirateur capable de franchir des marches perd plus de 500 â¬ sur Amazon</t>
+          <t>Cet ultrabook d’Acer (Intel Core 5, 16 Go de RAM), avec une sacoche et une souris offertes, est dispo pour 200 â¬ de moins</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/bons-plans/3251753_ecovacs-deebot-x12-omnicyclone-ce-robot-aspirateur-capable-de-franchir-des-marches-perd-plus-de-500-e-sur-amazon</t>
+          <t>https://www.frandroid.com/bons-plans/3251595_cet-ultrabook-dacer-intel-core-5-16-go-de-ram-avec-une-sacoche-et-une-souris-offertes-est-dispo-pour-200-e-de-moins</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>11. Menage</t>
+          <t>2. PC</t>
         </is>
       </c>
     </row>
@@ -8481,17 +8485,17 @@
       <c r="B301" t="inlineStr"/>
       <c r="C301" t="inlineStr">
         <is>
-          <t>La bague connectÃ©e Oura Ring 4 revient Ã  un super prix : une bonne affaire malgrÃ© la sortie du nouveau modÃ¨le ?</t>
+          <t>Ecovacs Deebot X12 OmniCyclone : ce robot aspirateur capable de franchir des marches perd plus de 500 â¬ sur Amazon</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/bons-plans/3190627_la-bague-connectee-oura-ring-4-revient-a-un-super-prix-une-bonne-affaire-malgre-la-sortie-du-nouveau-modele</t>
+          <t>https://www.frandroid.com/bons-plans/3251753_ecovacs-deebot-x12-omnicyclone-ce-robot-aspirateur-capable-de-franchir-des-marches-perd-plus-de-500-e-sur-amazon</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>14. Santé</t>
+          <t>11. Menage</t>
         </is>
       </c>
     </row>
@@ -8504,17 +8508,17 @@
       <c r="B302" t="inlineStr"/>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Bambu Lab lance la H2C, son imprimante 3D anti-gaspillage, dÃ©jÃ  Ã  -150 â¬</t>
+          <t>La bague connectÃ©e Oura Ring 4 revient Ã  un super prix : une bonne affaire malgrÃ© la sortie du nouveau modÃ¨le ?</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/bons-plans/3251523_bambu-lab-lance-la-h2c-son-imprimante-3d-anti-gaspillage-deja-a-150-e</t>
+          <t>https://www.frandroid.com/bons-plans/3190627_la-bague-connectee-oura-ring-4-revient-a-un-super-prix-une-bonne-affaire-malgre-la-sortie-du-nouveau-modele</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>3. Periphérique</t>
+          <t>14. Santé</t>
         </is>
       </c>
     </row>
@@ -8527,40 +8531,40 @@
       <c r="B303" t="inlineStr"/>
       <c r="C303" t="inlineStr">
         <is>
-          <t>On a trouvÃ© une montre Wear OS complÃ¨te pour le prix d’un bracelet connectÃ©</t>
+          <t>Bambu Lab lance la H2C, son imprimante 3D anti-gaspillage, dÃ©jÃ  Ã  -150 â¬</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/bons-plans/3251519_on-a-trouve-une-montre-wear-os-complete-pour-le-prix-dun-bracelet-connecte</t>
+          <t>https://www.frandroid.com/bons-plans/3251523_bambu-lab-lance-la-h2c-son-imprimante-3d-anti-gaspillage-deja-a-150-e</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>5. Logiciels _ OS</t>
+          <t>3. Periphérique</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Frandroid - Actualités</t>
+          <t>Frandroid - Bons plans</t>
         </is>
       </c>
       <c r="B304" t="inlineStr"/>
       <c r="C304" t="inlineStr">
         <is>
-          <t>BNP Paribas propose un prêt étudiant à 0,99 % TAEG pour la rentrée 2026</t>
+          <t>On a trouvÃ© une montre Wear OS complÃ¨te pour le prix d’un bracelet connectÃ©</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>https://native.humanoid.fr/register-click?s_id=2&amp;sp_id=47&amp;c_id=4220</t>
+          <t>https://www.frandroid.com/bons-plans/3251519_on-a-trouve-une-montre-wear-os-complete-pour-le-prix-dun-bracelet-connecte</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>NON_CLASSE</t>
+          <t>5. Logiciels _ OS</t>
         </is>
       </c>
     </row>
@@ -8573,17 +8577,17 @@
       <c r="B305" t="inlineStr"/>
       <c r="C305" t="inlineStr">
         <is>
-          <t>French Days : le nec plus ultra des aspirateurs Roborock s’effondre de 300 €</t>
+          <t>BNP Paribas propose un prêt étudiant à 0,99 % TAEG pour la rentrée 2026</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>https://native.humanoid.fr/register-click?s_id=2&amp;sp_id=47&amp;c_id=4217</t>
+          <t>https://native.humanoid.fr/register-click?s_id=2&amp;sp_id=47&amp;c_id=4220</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>11. Menage</t>
+          <t>NON_CLASSE</t>
         </is>
       </c>
     </row>
@@ -8596,17 +8600,17 @@
       <c r="B306" t="inlineStr"/>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Cette box fibre à moins de 25 € par mois mise sur le Wi-Fi 7 et un prix qui ne bouge pas</t>
+          <t>French Days : le nec plus ultra des aspirateurs Roborock s’effondre de 300 €</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>https://native.humanoid.fr/register-click?s_id=2&amp;sp_id=47&amp;c_id=4225</t>
+          <t>https://native.humanoid.fr/register-click?s_id=2&amp;sp_id=47&amp;c_id=4217</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>3. Periphérique</t>
+          <t>11. Menage</t>
         </is>
       </c>
     </row>
@@ -8619,15 +8623,38 @@
       <c r="B307" t="inlineStr"/>
       <c r="C307" t="inlineStr">
         <is>
+          <t>Cette box fibre à moins de 25 € par mois mise sur le Wi-Fi 7 et un prix qui ne bouge pas</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>https://native.humanoid.fr/register-click?s_id=2&amp;sp_id=47&amp;c_id=4225</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>3. Periphérique</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Frandroid - Actualités</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr"/>
+      <c r="C308" t="inlineStr">
+        <is>
           <t>ASUS baisse le prix de ses Zenbook et PC gaming pour la rentrée 2026 : jusqu’à 600 € de réduction</t>
         </is>
       </c>
-      <c r="D307" t="inlineStr">
+      <c r="D308" t="inlineStr">
         <is>
           <t>https://native.humanoid.fr/register-click?s_id=2&amp;sp_id=47&amp;c_id=4223</t>
         </is>
       </c>
-      <c r="E307" t="inlineStr">
+      <c r="E308" t="inlineStr">
         <is>
           <t>2. PC</t>
         </is>
@@ -16704,7 +16731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16737,22 +16764,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Phonandroid</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-19T17:42:56+00:00</t>
+          <t>2026-09-19T22:10:03+00:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DJI Avata 360 : le drone ultra immersif qui vous permet de filmer en 8K à 360°</t>
+          <t>Actualité : Bon plan – Le téléviseur LG 55G5 "5 étoiles" à 1 199,00 €</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.phonandroid.com/dji-avata-360-le-drone-ultra-immersif-qui-vous-permet-de-filmer-en-8k-a-360.html</t>
+          <t>https://www.lesnumeriques.com/tv-televiseur/bon-plan-le-televiseur-lg-55g5-5-etoiles-a-1-199-00-n262069.html</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -16764,22 +16791,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Frandroid - RSS</t>
+          <t>Phonandroid</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-19T17:02:14+00:00</t>
+          <t>2026-09-19T17:42:56+00:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Quels sont les meilleures modèles de TV TCL disponibles à l’achat ? Notre comparatif</t>
+          <t>DJI Avata 360 : le drone ultra immersif qui vous permet de filmer en 8K à 360°</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/guide-dachat/1610991_quelles-sont-les-meilleures-tv-tcl-disponibles</t>
+          <t>https://www.phonandroid.com/dji-avata-360-le-drone-ultra-immersif-qui-vous-permet-de-filmer-en-8k-a-360.html</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -16791,22 +16818,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>Frandroid - RSS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-19T08:34:08+00:00</t>
+          <t>2026-09-19T17:02:14+00:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Le saviez-vous ? Atari a enterré ses pires jeux vidéo dans le désert en 1983, et ce n’était pas une légende</t>
+          <t>Quels sont les meilleures modèles de TV TCL disponibles à l’achat ? Notre comparatif</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/19/le-saviez-vous-atari-a-enterre-ses-pires-jeux-video-dans-le-desert-en-1983-et-ce-netait-pas-une-legende/</t>
+          <t>https://www.frandroid.com/guide-dachat/1610991_quelles-sont-les-meilleures-tv-tcl-disponibles</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -16818,22 +16845,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Frandroid - RSS</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-19T05:44:00+00:00</t>
+          <t>2026-09-19T08:34:08+00:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Boulanger fait chuter le prix de ce TV 4K QLED 65 pouces Philips Ambilight à moins de 700 €</t>
+          <t>Le saviez-vous ? Atari a enterré ses pires jeux vidéo dans le désert en 1983, et ce n’était pas une légende</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/bons-plans/3250245_boulanger-fait-chuter-le-prix-de-ce-tv-4k-qled-65-pouces-philips-ambilight-a-moins-de-700-e</t>
+          <t>https://www.journaldugeek.com/2026/09/19/le-saviez-vous-atari-a-enterre-ses-pires-jeux-video-dans-le-desert-en-1983-et-ce-netait-pas-une-legende/</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -16845,22 +16872,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>Frandroid - RSS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-18T14:21:07+00:00</t>
+          <t>2026-09-19T05:44:00+00:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Vente flash DJI : à prix mini, son drone Neo 2 se vend par camions 🚛</t>
+          <t>Boulanger fait chuter le prix de ce TV 4K QLED 65 pouces Philips Ambilight à moins de 700 €</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.01net.com/bons-plans/vente-flash-en-cours-chez-dji-a-prix-mini-son-drone-neo-2-se-vend-par-camions.html</t>
+          <t>https://www.frandroid.com/bons-plans/3250245_boulanger-fait-chuter-le-prix-de-ce-tv-4k-qled-65-pouces-philips-ambilight-a-moins-de-700-e</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -16872,22 +16899,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-18T13:38:00+00:00</t>
+          <t>2026-09-18T14:21:07+00:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Actualité : Google simule un cerveau de mouche, un internaute l’utilise pour battre un célèbre jeu vidéo</t>
+          <t>Vente flash DJI : à prix mini, son drone Neo 2 se vend par camions 🚛</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/intelligence-artificielle/google-simule-un-cerveau-de-mouche-un-internaute-l-utilise-pour-battre-un-celebre-jeu-video-n262030.html</t>
+          <t>https://www.01net.com/bons-plans/vente-flash-en-cours-chez-dji-a-prix-mini-son-drone-neo-2-se-vend-par-camions.html</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -16899,22 +16926,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Frandroid - Actualités</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-18T09:45:25+00:00</t>
+          <t>2026-09-18T13:38:00+00:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>PS5 Slim ou PS5 Pro : quelle PS5 choisir ?</t>
+          <t>Actualité : Google simule un cerveau de mouche, un internaute l’utilise pour battre un célèbre jeu vidéo</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/marques/sony/767530_ps5-ou-ps5-digital-edition-quel-modele-choisir</t>
+          <t>https://www.lesnumeriques.com/intelligence-artificielle/google-simule-un-cerveau-de-mouche-un-internaute-l-utilise-pour-battre-un-celebre-jeu-video-n262030.html</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -16926,22 +16953,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>Frandroid - Actualités</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-18T09:20:00+00:00</t>
+          <t>2026-09-18T09:45:25+00:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Actualité : Narnia : des premières images magiques pour le blockbuster Netflix signé Greta Gerwig</t>
+          <t>PS5 Slim ou PS5 Pro : quelle PS5 choisir ?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/cine-svod/narnia-des-premieres-images-magiques-pour-le-blockbuster-netflix-signe-greta-gerwig-n262013.html</t>
+          <t>https://www.frandroid.com/marques/sony/767530_ps5-ou-ps5-digital-edition-quel-modele-choisir</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -16953,22 +16980,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-18T07:31:55+00:00</t>
+          <t>2026-09-18T09:20:00+00:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Les premières images de Narnia : Le Neveu du magicien sont là et elles risquent de ne pas vous plaire !</t>
+          <t>Actualité : Narnia : des premières images magiques pour le blockbuster Netflix signé Greta Gerwig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/18/premieres-images-narnia-le-neveu-du-magicien-film-netflix/</t>
+          <t>https://www.lesnumeriques.com/cine-svod/narnia-des-premieres-images-magiques-pour-le-blockbuster-netflix-signe-greta-gerwig-n262013.html</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -16980,18 +17007,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Frandroid - Actualités</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
+          <t>JournalDuGeek</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-09-18T07:31:55+00:00</t>
+        </is>
+      </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Un grand TV QD Mini-LED avec Philips Ambilight à moins de 700 €, ça se regarde de près</t>
+          <t>Les premières images de Narnia : Le Neveu du magicien sont là et elles risquent de ne pas vous plaire !</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/bons-plans/3252877_un-grand-tv-qd-mini-led-avec-philips-ambilight-a-moins-de-700-e-ca-se-regarde-de-pres</t>
+          <t>https://www.journaldugeek.com/2026/09/18/premieres-images-narnia-le-neveu-du-magicien-film-netflix/</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -17009,12 +17040,12 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Samsung The Frame 65 pouces (2025) à seulement 999 € chez Boulanger : une belle affaire pour ce TV QLED 4K</t>
+          <t>Un grand TV QD Mini-LED avec Philips Ambilight à moins de 700 €, ça se regarde de près</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/bons-plans/3252161_samsung-the-frame-65-pouces-2025-a-seulement-999-e-chez-boulanger-une-belle-affaire-pour-ce-tv-qled-4k</t>
+          <t>https://www.frandroid.com/bons-plans/3252877_un-grand-tv-qd-mini-led-avec-philips-ambilight-a-moins-de-700-e-ca-se-regarde-de-pres</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -17032,15 +17063,38 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
+          <t>Samsung The Frame 65 pouces (2025) à seulement 999 € chez Boulanger : une belle affaire pour ce TV QLED 4K</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://www.frandroid.com/bons-plans/3252161_samsung-the-frame-65-pouces-2025-a-seulement-999-e-chez-boulanger-une-belle-affaire-pour-ce-tv-qled-4k</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>7. Video</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Frandroid - Actualités</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
           <t>Vos DONNÉES ont FUITÉ : voici ce qu’il faut faire !</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>https://www.frandroid.com/video/3253483_video</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>7. Video</t>
         </is>

--- a/output/rss_history.xlsx
+++ b/output/rss_history.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E308"/>
+  <dimension ref="A1:E309"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,22 +471,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-19T22:10:03+00:00</t>
+          <t>2026-09-20T01:25:02+00:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Actualité : Bon plan – Le téléviseur LG 55G5 "5 étoiles" à 1 199,00 €</t>
+          <t>Actualité : Bon plan – L'aspirateur robot Eureka J15 Pro Ultra à 299,98 € (-14%)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/tv-televiseur/bon-plan-le-televiseur-lg-55g5-5-etoiles-a-1-199-00-n262069.html</t>
+          <t>https://www.lesnumeriques.com/aspirateur-robot/bon-plan-l-aspirateur-robot-eureka-j15-pro-ultra-a-299-98-14-n262070.html</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>7. Video</t>
+          <t>11. Menage</t>
         </is>
       </c>
     </row>
@@ -498,22 +498,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-19T22:00:03+00:00</t>
+          <t>2026-09-19T22:10:03+00:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Actualité : Bon plan – Le compact / bridge Sony ZV-1 Seul à 630,85 € (-21%)</t>
+          <t>Actualité : Bon plan – Le téléviseur LG 55G5 "5 étoiles" à 1 199,00 €</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/compact-bridge/bon-plan-le-compact-bridge-sony-zv-1-seul-a-630-85-21-n262068.html</t>
+          <t>https://www.lesnumeriques.com/tv-televiseur/bon-plan-le-televiseur-lg-55g5-5-etoiles-a-1-199-00-n262069.html</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>19. Sponso</t>
+          <t>7. Video</t>
         </is>
       </c>
     </row>
@@ -530,186 +530,186 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Actualité : Bon plan – La machine à café automatique avec broyeur Delonghi Magnifica Evo Next "5 étoiles" à 468,69 € (-21%)</t>
+          <t>Actualité : Bon plan – Le compact / bridge Sony ZV-1 Seul à 630,85 € (-21%)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/machine-a-cafe-automatique/bon-plan-la-machine-a-cafe-automatique-avec-broyeur-delonghi-magnifica-evo-next-5-etoiles-a-468-69-21-n262067.html</t>
+          <t>https://www.lesnumeriques.com/compact-bridge/bon-plan-le-compact-bridge-sony-zv-1-seul-a-630-85-21-n262068.html</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>12. Cuisine</t>
+          <t>19. Sponso</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Phonandroid</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-19T17:42:56+00:00</t>
+          <t>2026-09-19T22:00:03+00:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DJI Avata 360 : le drone ultra immersif qui vous permet de filmer en 8K à 360°</t>
+          <t>Actualité : Bon plan – La machine à café automatique avec broyeur Delonghi Magnifica Evo Next "5 étoiles" à 468,69 € (-21%)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.phonandroid.com/dji-avata-360-le-drone-ultra-immersif-qui-vous-permet-de-filmer-en-8k-a-360.html</t>
+          <t>https://www.lesnumeriques.com/machine-a-cafe-automatique/bon-plan-la-machine-a-cafe-automatique-avec-broyeur-delonghi-magnifica-evo-next-5-etoiles-a-468-69-21-n262067.html</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>7. Video</t>
+          <t>12. Cuisine</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Numerama</t>
+          <t>Phonandroid</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-19T17:42:00+00:00</t>
+          <t>2026-09-19T17:42:56+00:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Pour la sortie du nouveau film Resident Evil, on a classé tous les films de la saga, du pire au moins pire</t>
+          <t>DJI Avata 360 : le drone ultra immersif qui vous permet de filmer en 8K à 360°</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.numerama.com/pop-culture/2333519-pour-la-sortie-du-nouveau-film-resident-evil-on-a-classe-tous-les-films-de-la-saga-du-pire-au-moins-pire.html</t>
+          <t>https://www.phonandroid.com/dji-avata-360-le-drone-ultra-immersif-qui-vous-permet-de-filmer-en-8k-a-360.html</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>15. ludique</t>
+          <t>7. Video</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Frandroid - RSS</t>
+          <t>Numerama</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-19T17:38:00+00:00</t>
+          <t>2026-09-19T17:42:00+00:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>En ce mois de rentrée, ce laptop de Lenovo avec son écran OLED de 16″ passe sous les 900 euros et un sac à dos est offert</t>
+          <t>Pour la sortie du nouveau film Resident Evil, on a classé tous les films de la saga, du pire au moins pire</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/bons-plans/3252341_en-ce-mois-de-rentree-ce-laptop-de-lenovo-avec-son-ecran-oled-de-16-passe-sous-les-900-euros-et-un-sac-a-dos-est-offert</t>
+          <t>https://www.numerama.com/pop-culture/2333519-pour-la-sortie-du-nouveau-film-resident-evil-on-a-classe-tous-les-films-de-la-saga-du-pire-au-moins-pire.html</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2. PC</t>
+          <t>15. ludique</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>Frandroid - RSS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-19T17:04:00+00:00</t>
+          <t>2026-09-19T17:38:00+00:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Actualité : Le test du vidéoprojecteur Anker Nebula P1i a rejoint notre comparatif</t>
+          <t>En ce mois de rentrée, ce laptop de Lenovo avec son écran OLED de 16″ passe sous les 900 euros et un sac à dos est offert</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/videoprojecteur/le-test-du-videoprojecteur-anker-nebula-p1i-a-rejoint-notre-comparatif-n262054.html</t>
+          <t>https://www.frandroid.com/bons-plans/3252341_en-ce-mois-de-rentree-ce-laptop-de-lenovo-avec-son-ecran-oled-de-16-passe-sous-les-900-euros-et-un-sac-a-dos-est-offert</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>2. PC</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Frandroid - RSS</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-19T17:02:14+00:00</t>
+          <t>2026-09-19T17:04:00+00:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Quels sont les meilleures modèles de TV TCL disponibles à l’achat ? Notre comparatif</t>
+          <t>Actualité : Le test du vidéoprojecteur Anker Nebula P1i a rejoint notre comparatif</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/guide-dachat/1610991_quelles-sont-les-meilleures-tv-tcl-disponibles</t>
+          <t>https://www.lesnumeriques.com/videoprojecteur/le-test-du-videoprojecteur-anker-nebula-p1i-a-rejoint-notre-comparatif-n262054.html</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>7. Video</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>Frandroid - RSS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-19T16:32:00+00:00</t>
+          <t>2026-09-19T17:02:14+00:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Actualité : Auto SR : le DLSS de Microsoft s'ouvre à de nouveaux Copilot+ PC</t>
+          <t>Quels sont les meilleures modèles de TV TCL disponibles à l’achat ? Notre comparatif</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/carte-graphique/auto-sr-le-dlss-de-microsoft-s-ouvre-a-de-nouveaux-copilot-pc-n262064.html</t>
+          <t>https://www.frandroid.com/guide-dachat/1610991_quelles-sont-les-meilleures-tv-tcl-disponibles</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2. PC</t>
+          <t>7. Video</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Numerama</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -719,44 +719,44 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ils prédisent l’apocalypse par l’IA, c’est quoi les AI doomers ?</t>
+          <t>Actualité : Auto SR : le DLSS de Microsoft s'ouvre à de nouveaux Copilot+ PC</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.numerama.com/tech/2335869-ils-predisent-lapocalypse-par-lia-cest-quoi-les-ai-doomers.html</t>
+          <t>https://www.lesnumeriques.com/carte-graphique/auto-sr-le-dlss-de-microsoft-s-ouvre-a-de-nouveaux-copilot-pc-n262064.html</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>6. IA</t>
+          <t>2. PC</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>Numerama</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-19T16:30:00+00:00</t>
+          <t>2026-09-19T16:32:00+00:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Actualité : Harry Potter : nouveau teaser, casting, histoire, date de sortie… Tout savoir sur la série HBO Max</t>
+          <t>Ils prédisent l’apocalypse par l’IA, c’est quoi les AI doomers ?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/serie/harry-potter-nouveau-teaser-casting-histoire-date-de-sortie-tout-savoir-sur-la-serie-hbo-max-n230720.html</t>
+          <t>https://www.numerama.com/tech/2335869-ils-predisent-lapocalypse-par-lia-cest-quoi-les-ai-doomers.html</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>15. ludique</t>
+          <t>6. IA</t>
         </is>
       </c>
     </row>
@@ -768,71 +768,71 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-19T16:13:32+00:00</t>
+          <t>2026-09-19T16:30:00+00:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Actualité : Cette centrale vapeur présente le meilleur rapport qualité / prix de notre comparatif</t>
+          <t>Actualité : Harry Potter : nouveau teaser, casting, histoire, date de sortie… Tout savoir sur la série HBO Max</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/centrale-vapeur/cette-centrale-vapeur-presente-le-meilleur-rapport-qualite-prix-de-notre-comparatif-n262065.html</t>
+          <t>https://www.lesnumeriques.com/serie/harry-potter-nouveau-teaser-casting-histoire-date-de-sortie-tout-savoir-sur-la-serie-hbo-max-n230720.html</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>11. Menage</t>
+          <t>15. ludique</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Frandroid - RSS</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-19T16:01:00+00:00</t>
+          <t>2026-09-19T16:13:32+00:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>J’ai démonté le nouveau Lenovo ThinkPad en moins de 10 minutes : la réparabilité est-elle enfin de retour sur PC ?</t>
+          <t>Actualité : Cette centrale vapeur présente le meilleur rapport qualité / prix de notre comparatif</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/marques/lenovo/3237317_jai-demonte-le-nouveau-lenovo-thinkpad-en-moins-de-10-minutes-la-reparabilite-est-elle-enfin-de-retour-sur-pc</t>
+          <t>https://www.lesnumeriques.com/centrale-vapeur/cette-centrale-vapeur-presente-le-meilleur-rapport-qualite-prix-de-notre-comparatif-n262065.html</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2. PC</t>
+          <t>11. Menage</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>Frandroid - RSS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-19T16:00:49+00:00</t>
+          <t>2026-09-19T16:01:00+00:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Un ordinateur portable peut-il vraiment vous griller la peau ?</t>
+          <t>J’ai démonté le nouveau Lenovo ThinkPad en moins de 10 minutes : la réparabilité est-elle enfin de retour sur PC ?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/19/un-ordinateur-portable-peut-il-vraiment-vous-griller-la-peau/</t>
+          <t>https://www.frandroid.com/marques/lenovo/3237317_jai-demonte-le-nouveau-lenovo-thinkpad-en-moins-de-10-minutes-la-reparabilite-est-elle-enfin-de-retour-sur-pc</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -844,54 +844,54 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-19T16:00:00+00:00</t>
+          <t>2026-09-19T16:00:49+00:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Actualité : Il sort deux nouveaux modèles de smartphones par jour : est-ce bien raisonnable ?</t>
+          <t>Un ordinateur portable peut-il vraiment vous griller la peau ?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/telephone-portable/il-sort-deux-nouveaux-modeles-de-smartphones-par-jour-est-ce-bien-raisonnable-n261911.html</t>
+          <t>https://www.journaldugeek.com/2026/09/19/un-ordinateur-portable-peut-il-vraiment-vous-griller-la-peau/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>2. PC</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Frandroid - RSS</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-19T15:32:00+00:00</t>
+          <t>2026-09-19T16:00:00+00:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ce pack Marshall à moins de 850 € réunit une barre de son 5.1 et un caisson de basses, de quoi profiter d’un home cinema immersif</t>
+          <t>Actualité : Il sort deux nouveaux modèles de smartphones par jour : est-ce bien raisonnable ?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/bons-plans/3250173_ce-pack-marshall-a-moins-de-850-e-reunit-une-barre-de-son-5-1-et-un-caisson-de-basses-de-quoi-profiter-dun-home-cinema-immersif</t>
+          <t>https://www.lesnumeriques.com/telephone-portable/il-sort-deux-nouveaux-modeles-de-smartphones-par-jour-est-ce-bien-raisonnable-n261911.html</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>8. Audio</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
@@ -903,98 +903,98 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-19T15:24:06+00:00</t>
+          <t>2026-09-19T15:32:00+00:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Samsung casse le prix de son pliable anti-iPhone Duo</t>
+          <t>Ce pack Marshall à moins de 850 € réunit une barre de son 5.1 et un caisson de basses, de quoi profiter d’un home cinema immersif</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/marques/samsung/3253539_samsung-casse-le-prix-de-son-pliable-anti-iphone-duo</t>
+          <t>https://www.frandroid.com/bons-plans/3250173_ce-pack-marshall-a-moins-de-850-e-reunit-une-barre-de-son-5-1-et-un-caisson-de-basses-de-quoi-profiter-dun-home-cinema-immersif</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>8. Audio</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Numerama</t>
+          <t>Frandroid - RSS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-19T15:20:00+00:00</t>
+          <t>2026-09-19T15:24:06+00:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Une Tesla au bord du vide en FSD, remboursement de Navigo et un camion sans chauffeur livre Lidl: le récap’ Vroom de la semaine</t>
+          <t>Samsung casse le prix de son pliable anti-iPhone Duo</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.numerama.com/vroom/2335871-une-tesla-au-bord-du-vide-en-fsd-remboursement-de-navigo-et-un-camion-sans-chauffeur-livre-lidl-le-recap-vroom-de-la-semaine.html</t>
+          <t>https://www.frandroid.com/marques/samsung/3253539_samsung-casse-le-prix-de-son-pliable-anti-iphone-duo</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>4. Tablette</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>Numerama</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-19T15:00:28+00:00</t>
+          <t>2026-09-19T15:20:00+00:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Meta prépare des lunettes connectées sans caméra, pour voir si ça passe mieux</t>
+          <t>Une Tesla au bord du vide en FSD, remboursement de Navigo et un camion sans chauffeur livre Lidl: le récap’ Vroom de la semaine</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/19/meta-prepare-des-lunettes-connectees-sans-camera-pour-voir-si-ca-passe-mieux/</t>
+          <t>https://www.numerama.com/vroom/2335871-une-tesla-au-bord-du-vide-en-fsd-remboursement-de-navigo-et-un-camion-sans-chauffeur-livre-lidl-le-recap-vroom-de-la-semaine.html</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>4. Tablette</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-19T15:00:00+00:00</t>
+          <t>2026-09-19T15:00:28+00:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Actualité : iOS 27 : j’ai adopté ces 7 nouvelles options de personnalisation sur iPhone</t>
+          <t>Meta prépare des lunettes connectées sans caméra, pour voir si ça passe mieux</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/telephone-portable/ios-27-j-ai-adopte-ces-7-nouvelles-options-de-personnalisation-sur-iphone-n261976.html</t>
+          <t>https://www.journaldugeek.com/2026/09/19/meta-prepare-des-lunettes-connectees-sans-camera-pour-voir-si-ca-passe-mieux/</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1006,76 +1006,76 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Phonandroid</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-19T14:50:42+00:00</t>
+          <t>2026-09-19T15:00:00+00:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Napster se lance dans l’éducation : l’IA pourrait bientôt remplacer vos profs</t>
+          <t>Actualité : iOS 27 : j’ai adopté ces 7 nouvelles options de personnalisation sur iPhone</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.phonandroid.com/napster-se-lance-dans-leducation-lia-pourrait-bientot-remplacer-vos-profs.html</t>
+          <t>https://www.lesnumeriques.com/telephone-portable/ios-27-j-ai-adopte-ces-7-nouvelles-options-de-personnalisation-sur-iphone-n261976.html</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>6. IA</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Numerama</t>
+          <t>Phonandroid</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-19T14:30:00+00:00</t>
+          <t>2026-09-19T14:50:42+00:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Un agent OpenAI s’invente un personnage libre, Revolut piégée par un faux mail et les géants de l’IA qui veulent ralentir : on vous raconte la semaine Cyberguerre</t>
+          <t>Napster se lance dans l’éducation : l’IA pourrait bientôt remplacer vos profs</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.numerama.com/cyberguerre/2336053-un-agent-openai-sinvente-un-personnage-libre-revolut-piegee-par-un-faux-mail-et-les-geants-de-lia-qui-veulent-ralentir-on-vous-raconte-la-semaine-cyberguerre.html</t>
+          <t>https://www.phonandroid.com/napster-se-lance-dans-leducation-lia-pourrait-bientot-remplacer-vos-profs.html</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>5. Logiciels _ OS</t>
+          <t>6. IA</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>Numerama</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-19T14:12:00+00:00</t>
+          <t>2026-09-19T14:30:00+00:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Actualité : Fatigué par Windows 11 et l'IA, j'ai tout plaqué pour Linux (et je ne regrette rien)</t>
+          <t>Un agent OpenAI s’invente un personnage libre, Revolut piégée par un faux mail et les géants de l’IA qui veulent ralentir : on vous raconte la semaine Cyberguerre</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/informatique/fatigue-par-windows-11-et-l-ia-j-ai-tout-plaque-pour-linux-et-je-ne-regrette-rien-n250751.html</t>
+          <t>https://www.numerama.com/cyberguerre/2336053-un-agent-openai-sinvente-un-personnage-libre-revolut-piegee-par-un-faux-mail-et-les-geants-de-lia-qui-veulent-ralentir-on-vous-raconte-la-semaine-cyberguerre.html</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1092,44 +1092,44 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-19T14:03:00+00:00</t>
+          <t>2026-09-19T14:12:00+00:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Actualité : On a vu les Shokz OpenFit 2 AI : ces écouteurs veulent devenir votre traducteur et prendre vos notes</t>
+          <t>Actualité : Fatigué par Windows 11 et l'IA, j'ai tout plaqué pour Linux (et je ne regrette rien)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/ecouteurs-sans-fil/on-a-vu-les-shokz-openfit-2-ai-ces-ecouteurs-veulent-devenir-votre-traducteur-et-prendre-vos-notes-n262027.html</t>
+          <t>https://www.lesnumeriques.com/informatique/fatigue-par-windows-11-et-l-ia-j-ai-tout-plaque-pour-linux-et-je-ne-regrette-rien-n250751.html</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>6. IA</t>
+          <t>5. Logiciels _ OS</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Frandroid - RSS</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-19T14:02:00+00:00</t>
+          <t>2026-09-19T14:03:00+00:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>J’ai enfin reçu les jumelles connectées Envision d’Unistellar : voici mes premières impressions</t>
+          <t>Actualité : On a vu les Shokz OpenFit 2 AI : ces écouteurs veulent devenir votre traducteur et prendre vos notes</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/test/prises-en-main/3249881_jai-enfin-recu-les-jumelles-connectees-envision-dunistellar-voici-mes-premieres-impressions</t>
+          <t>https://www.lesnumeriques.com/ecouteurs-sans-fil/on-a-vu-les-shokz-openfit-2-ai-ces-ecouteurs-veulent-devenir-votre-traducteur-et-prendre-vos-notes-n262027.html</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1141,49 +1141,49 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>Frandroid - RSS</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-19T14:00:00+00:00</t>
+          <t>2026-09-19T14:02:00+00:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Actualité : Impôts 2026 : le fisc va prélever 1 798 € en moyenne chez 13,8 millions de français dès le 25 septembre</t>
+          <t>J’ai enfin reçu les jumelles connectées Envision d’Unistellar : voici mes premières impressions</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/societe-numerique/impots-2026-le-fisc-va-prelever-1-798-en-moyenne-chez-13-8-millions-de-francais-des-le-25-septembre-n262062.html</t>
+          <t>https://www.frandroid.com/test/prises-en-main/3249881_jai-enfin-recu-les-jumelles-connectees-envision-dunistellar-voici-mes-premieres-impressions</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>NON_CLASSE</t>
+          <t>6. IA</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-19T13:58:01+00:00</t>
+          <t>2026-09-19T14:00:00+00:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>La mégalopole lunaire d’Elon Musk prend l’eau</t>
+          <t>Actualité : Impôts 2026 : le fisc va prélever 1 798 € en moyenne chez 13,8 millions de français dès le 25 septembre</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/19/la-megalopole-lunaire-delon-musk-prend-leau/</t>
+          <t>https://www.lesnumeriques.com/societe-numerique/impots-2026-le-fisc-va-prelever-1-798-en-moyenne-chez-13-8-millions-de-francais-des-le-25-septembre-n262062.html</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1195,27 +1195,27 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Phonandroid</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-19T13:42:46+00:00</t>
+          <t>2026-09-19T13:58:01+00:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>-42% sur la Honor Pad X9a : la tablette de 11,5 pouces est à moins de 145 €</t>
+          <t>La mégalopole lunaire d’Elon Musk prend l’eau</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.phonandroid.com/42-honor-pad-x9a-tablette-11-pouces-moins-145-e.html</t>
+          <t>https://www.journaldugeek.com/2026/09/19/la-megalopole-lunaire-delon-musk-prend-leau/</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>NON_CLASSE</t>
         </is>
       </c>
     </row>
@@ -1227,71 +1227,71 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-19T13:33:41+00:00</t>
+          <t>2026-09-19T13:42:46+00:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Vous téléchargez des films sur Internet ? Cette nouvelle menace se cache peut-être sur votre PC</t>
+          <t>-42% sur la Honor Pad X9a : la tablette de 11,5 pouces est à moins de 145 €</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.phonandroid.com/vous-telechargez-des-films-sur-internet-cette-nouvelle-menace-se-cache-peut-etre-sur-votre-pc.html</t>
+          <t>https://www.phonandroid.com/42-honor-pad-x9a-tablette-11-pouces-moins-145-e.html</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2. PC</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Numerama</t>
+          <t>Phonandroid</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-19T13:33:00+00:00</t>
+          <t>2026-09-19T13:33:41+00:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Notre cerveau refuse de l’admettre et se trompe lourdement, mais au loto la grille 1-2-3-4-5-6 n’a rien de spécial</t>
+          <t>Vous téléchargez des films sur Internet ? Cette nouvelle menace se cache peut-être sur votre PC</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.numerama.com/sciences/2335765-notre-cerveau-refuse-de-ladmettre-et-se-trompe-completement-mais-au-loto-la-grille-1-2-3-4-5-6-na-rien-de-special.html</t>
+          <t>https://www.phonandroid.com/vous-telechargez-des-films-sur-internet-cette-nouvelle-menace-se-cache-peut-etre-sur-votre-pc.html</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>NON_CLASSE</t>
+          <t>2. PC</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>Numerama</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-19T13:30:00+00:00</t>
+          <t>2026-09-19T13:33:00+00:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Actualité : IFA 2026 : Découvrez les grands gagnants des premiers Editor's Pick des Numériques !</t>
+          <t>Notre cerveau refuse de l’admettre et se trompe lourdement, mais au loto la grille 1-2-3-4-5-6 n’a rien de spécial</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/societe-numerique/ifa-2026-decouvrez-les-grands-gagnants-des-premiers-editor-s-pick-des-numeriques-n261986.html</t>
+          <t>https://www.numerama.com/sciences/2335765-notre-cerveau-refuse-de-ladmettre-et-se-trompe-completement-mais-au-loto-la-grille-1-2-3-4-5-6-na-rien-de-special.html</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1303,427 +1303,427 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-19T13:25:30+00:00</t>
+          <t>2026-09-19T13:30:00+00:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>La France va-t-elle interdire la revente de cartes Pokémon ?</t>
+          <t>Actualité : IFA 2026 : Découvrez les grands gagnants des premiers Editor's Pick des Numériques !</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/19/la-france-va-t-elle-interdire-la-revente-de-cartes-pokemon/</t>
+          <t>https://www.lesnumeriques.com/societe-numerique/ifa-2026-decouvrez-les-grands-gagnants-des-premiers-editor-s-pick-des-numeriques-n261986.html</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>15. ludique</t>
+          <t>NON_CLASSE</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-19T13:11:31+00:00</t>
+          <t>2026-09-19T13:25:30+00:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Actualité : Pour de bons écouteurs &amp; intras filaires à prix abordable, privilégiez...</t>
+          <t>La France va-t-elle interdire la revente de cartes Pokémon ?</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/ecouteurs-intras-filaires/pour-de-bons-ecouteurs-intras-filaires-a-prix-abordable-privilegiez-n262061.html</t>
+          <t>https://www.journaldugeek.com/2026/09/19/la-france-va-t-elle-interdire-la-revente-de-cartes-pokemon/</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>8. Audio</t>
+          <t>15. ludique</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Frandroid - RSS</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-19T13:11:00+00:00</t>
+          <t>2026-09-19T13:11:31+00:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Avec plus ou moins 200 € en poche, faut-il craquer pour le nouveau Samsung Galaxy A18 ou le Xiaomi Redmi 17 ?</t>
+          <t>Actualité : Pour de bons écouteurs &amp; intras filaires à prix abordable, privilégiez...</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/bons-plans/3252691_avec-plus-ou-moins-200-e-en-poche-faut-il-craquer-pour-le-nouveau-samsung-galaxy-a18-ou-le-xiaomi-redmi-17</t>
+          <t>https://www.lesnumeriques.com/ecouteurs-intras-filaires/pour-de-bons-ecouteurs-intras-filaires-a-prix-abordable-privilegiez-n262061.html</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>8. Audio</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>Frandroid - RSS</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-19T13:07:00+00:00</t>
+          <t>2026-09-19T13:11:00+00:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Actualité : Double capteur, zoom x9, IA améliorée : Xiaomi lance une caméra de surveillance qui ne laisse rien passer</t>
+          <t>Avec plus ou moins 200 € en poche, faut-il craquer pour le nouveau Samsung Galaxy A18 ou le Xiaomi Redmi 17 ?</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/camera-surveillance/double-capteur-zoom-x9-ia-amelioree-xiaomi-lance-une-camera-de-surveillance-qui-ne-laisse-rien-passer-n261932.html</t>
+          <t>https://www.frandroid.com/bons-plans/3252691_avec-plus-ou-moins-200-e-en-poche-faut-il-craquer-pour-le-nouveau-samsung-galaxy-a18-ou-le-xiaomi-redmi-17</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>6. IA</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-19T13:00:29+00:00</t>
+          <t>2026-09-19T13:07:00+00:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Le HP OmniBook Ultra 16 mise sur l’IA locale… mais avec un prix très haut de gamme</t>
+          <t>Actualité : Double capteur, zoom x9, IA améliorée : Xiaomi lance une caméra de surveillance qui ne laisse rien passer</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/19/le-hp-omnibook-ultra-16-mise-sur-lia-locale-mais-avec-un-prix-tres-haut-de-gamme/</t>
+          <t>https://www.lesnumeriques.com/camera-surveillance/double-capteur-zoom-x9-ia-amelioree-xiaomi-lance-une-camera-de-surveillance-qui-ne-laisse-rien-passer-n261932.html</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2. PC</t>
+          <t>6. IA</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-19T12:42:00+00:00</t>
+          <t>2026-09-19T13:00:29+00:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Actualité : Narnia (Netflix) : histoire, sortie, casting, trailer… Tout savoir sur le film de Greta Gerwig</t>
+          <t>Le HP OmniBook Ultra 16 mise sur l’IA locale… mais avec un prix très haut de gamme</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/cine-svod/narnia-netflix-histoire-sortie-casting-trailer-tout-savoir-sur-le-film-de-greta-gerwig-n262022.html</t>
+          <t>https://www.journaldugeek.com/2026/09/19/le-hp-omnibook-ultra-16-mise-sur-lia-locale-mais-avec-un-prix-tres-haut-de-gamme/</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>15. ludique</t>
+          <t>2. PC</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Phonandroid</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-19T12:36:23+00:00</t>
+          <t>2026-09-19T12:42:00+00:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Le Ryzen 7 9800X3D perd 210 € : une belle baisse de prix pour le processeur AMD</t>
+          <t>Actualité : Narnia (Netflix) : histoire, sortie, casting, trailer… Tout savoir sur le film de Greta Gerwig</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.phonandroid.com/ryzen-7-9800x3d-perd-210-belle-baisse-prix-processeur-amd.html</t>
+          <t>https://www.lesnumeriques.com/cine-svod/narnia-netflix-histoire-sortie-casting-trailer-tout-savoir-sur-le-film-de-greta-gerwig-n262022.html</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2. PC</t>
+          <t>15. ludique</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Numerama</t>
+          <t>Phonandroid</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-19T12:30:08+00:00</t>
+          <t>2026-09-19T12:36:23+00:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Pourquoi Pikachu a voyagé dans l’ISS avec Sophie Adenot, et ce que ça change pour les fans de Pokémon</t>
+          <t>Le Ryzen 7 9800X3D perd 210 € : une belle baisse de prix pour le processeur AMD</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.numerama.com/sciences/2335725-pourquoi-pikachu-a-voyage-dans-liss-avec-sophie-adenot-et-ce-que-ca-change-pour-les-fans-de-pokemon.html</t>
+          <t>https://www.phonandroid.com/ryzen-7-9800x3d-perd-210-belle-baisse-prix-processeur-amd.html</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>15. ludique</t>
+          <t>2. PC</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>Numerama</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-19T12:17:00+00:00</t>
+          <t>2026-09-19T12:30:08+00:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Actualité : Airfryer : comment la cuisson sans huile a fini par me refroidir</t>
+          <t>Pourquoi Pikachu a voyagé dans l’ISS avec Sophie Adenot, et ce que ça change pour les fans de Pokémon</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/airfryer/airfryer-comment-la-cuisson-sans-huile-a-fini-par-me-refroidir-n224064.html</t>
+          <t>https://www.numerama.com/sciences/2335725-pourquoi-pikachu-a-voyage-dans-liss-avec-sophie-adenot-et-ce-que-ca-change-pour-les-fans-de-pokemon.html</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>12. Cuisine</t>
+          <t>15. ludique</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Frandroid - RSS</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-19T12:02:00+00:00</t>
+          <t>2026-09-19T12:17:00+00:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>On a testé la Navee GT5 Max, une trottinette électrique qui secoue Segway et Xiaomi</t>
+          <t>Actualité : Airfryer : comment la cuisson sans huile a fini par me refroidir</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/survoltes/trottinette-electrique/3249113_essai-navee-gt5-max-une-trottinette-electrique-qui-peut-secouer-segway-et-xiaomi</t>
+          <t>https://www.lesnumeriques.com/airfryer/airfryer-comment-la-cuisson-sans-huile-a-fini-par-me-refroidir-n224064.html</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>9. Moiilité douce</t>
+          <t>12. Cuisine</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>Frandroid - RSS</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-19T12:01:27+00:00</t>
+          <t>2026-09-19T12:02:00+00:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Meta One : Meta met Instagram, Facebook, WhatsApp et son IA dans un même abonnement</t>
+          <t>On a testé la Navee GT5 Max, une trottinette électrique qui secoue Segway et Xiaomi</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/19/meta-one-meta-met-instagram-facebook-whatsapp-et-son-ia-dans-un-meme-abonnement/</t>
+          <t>https://www.frandroid.com/survoltes/trottinette-electrique/3249113_essai-navee-gt5-max-une-trottinette-electrique-qui-peut-secouer-segway-et-xiaomi</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>9. Moiilité douce</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Numerama</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-19T12:00:00+00:00</t>
+          <t>2026-09-19T12:01:27+00:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Monstre, saison 4 : dans la tête de la tueuse Lizzie Borden, icône féministe sanglante</t>
+          <t>Meta One : Meta met Instagram, Facebook, WhatsApp et son IA dans un même abonnement</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.numerama.com/pop-culture/2335297-monstre-saison-4-dans-la-tete-de-la-tueuse-lizzie-borden-icone-feministe-sanglante.html</t>
+          <t>https://www.journaldugeek.com/2026/09/19/meta-one-meta-met-instagram-facebook-whatsapp-et-son-ia-dans-un-meme-abonnement/</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>NON_CLASSE</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Phonandroid</t>
+          <t>Numerama</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-19T11:33:40+00:00</t>
+          <t>2026-09-19T12:00:00+00:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Samsung détrône Apple, la pénurie de RAM bouleverse le marché des smartphones</t>
+          <t>Monstre, saison 4 : dans la tête de la tueuse Lizzie Borden, icône féministe sanglante</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.phonandroid.com/samsung-detrone-apple-la-penurie-de-ram-bouleverse-le-marche-des-smartphones.html</t>
+          <t>https://www.numerama.com/pop-culture/2335297-monstre-saison-4-dans-la-tete-de-la-tueuse-lizzie-borden-icone-feministe-sanglante.html</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>NON_CLASSE</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Frandroid - RSS</t>
+          <t>Phonandroid</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-19T11:19:00+00:00</t>
+          <t>2026-09-19T11:33:40+00:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Ce SSD externe Crucial X10 Pro 1 TB voué à disparaître se paye un baroud d’honneur avec cette promo</t>
+          <t>Samsung détrône Apple, la pénurie de RAM bouleverse le marché des smartphones</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/bons-plans/3252443_ce-ssd-externe-crucial-x10-pro-1-tb-voue-a-disparaitre-se-paye-un-baroud-dhonneur-avec-cette-promo</t>
+          <t>https://www.phonandroid.com/samsung-detrone-apple-la-penurie-de-ram-bouleverse-le-marche-des-smartphones.html</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2. PC</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Phonandroid</t>
+          <t>Frandroid - RSS</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-19T11:17:23+00:00</t>
+          <t>2026-09-19T11:19:00+00:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Votre iPhone garde une trace de vos déplacements : voici où les trouver et comment les effacer</t>
+          <t>Ce SSD externe Crucial X10 Pro 1 TB voué à disparaître se paye un baroud d’honneur avec cette promo</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.phonandroid.com/votre-iphone-garde-trace-deplacements-ou-trouver-effacer.html</t>
+          <t>https://www.frandroid.com/bons-plans/3252443_ce-ssd-externe-crucial-x10-pro-1-tb-voue-a-disparaitre-se-paye-un-baroud-dhonneur-avec-cette-promo</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>2. PC</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>Phonandroid</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-19T11:15:00+00:00</t>
+          <t>2026-09-19T11:17:23+00:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Actualité : Dernière trouvaille de Samsung : breveter un téléphone portable en forme de brique doté d’un écran pliable</t>
+          <t>Votre iPhone garde une trace de vos déplacements : voici où les trouver et comment les effacer</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/mobilite-c17/derniere-trouvaille-de-samsung-breveter-un-telephone-portable-en-forme-de-brique-dote-d-un-ecran-pliable-n262033.html</t>
+          <t>https://www.phonandroid.com/votre-iphone-garde-trace-deplacements-ou-trouver-effacer.html</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1740,17 +1740,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-19T11:13:00+00:00</t>
+          <t>2026-09-19T11:15:00+00:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Actualité : Surprise, 19 nouveaux emojis vont être ajoutés sur Android et iOS, mais il va falloir attendre</t>
+          <t>Actualité : Dernière trouvaille de Samsung : breveter un téléphone portable en forme de brique doté d’un écran pliable</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/societe-numerique/surprise-19-nouveaux-emojis-vont-etre-ajoutes-sur-android-et-ios-mais-il-va-falloir-attendre-n262025.html</t>
+          <t>https://www.lesnumeriques.com/mobilite-c17/derniere-trouvaille-de-samsung-breveter-un-telephone-portable-en-forme-de-brique-dote-d-un-ecran-pliable-n262033.html</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1762,216 +1762,216 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-19T11:00:25+00:00</t>
+          <t>2026-09-19T11:13:00+00:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>L’instax Link WIDE 2 imprime les souvenirs en plus grand</t>
+          <t>Actualité : Surprise, 19 nouveaux emojis vont être ajoutés sur Android et iOS, mais il va falloir attendre</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/19/linstax-link-wide-2-imprime-les-souvenirs-en-plus-grand/</t>
+          <t>https://www.lesnumeriques.com/societe-numerique/surprise-19-nouveaux-emojis-vont-etre-ajoutes-sur-android-et-ios-mais-il-va-falloir-attendre-n262025.html</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>NON_CLASSE</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Numerama</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-19T10:40:48+00:00</t>
+          <t>2026-09-19T11:00:25+00:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Midea revoit son climatiseur PortaSplit pour 2027 : nouveau gaz réfrigérant et compatibilité Matter</t>
+          <t>L’instax Link WIDE 2 imprime les souvenirs en plus grand</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.numerama.com/tech/2336405-midea-revoit-son-climatiseur-portasplit-pour-2027-nouveau-gaz-refrigerant-et-compatibilite-matter.html</t>
+          <t>https://www.journaldugeek.com/2026/09/19/linstax-link-wide-2-imprime-les-souvenirs-en-plus-grand/</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>8. Audio</t>
+          <t>NON_CLASSE</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>Numerama</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-19T10:36:00+00:00</t>
+          <t>2026-09-19T10:40:48+00:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Actualité : Votre box Wi-Fi bride votre smartphone ? Le réglage caché pour doubler le débit</t>
+          <t>Midea revoit son climatiseur PortaSplit pour 2027 : nouveau gaz réfrigérant et compatibilité Matter</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/mobilite-c17/votre-box-wi-fi-bride-votre-smartphone-le-reglage-cache-pour-doubler-le-debit-n261954.html</t>
+          <t>https://www.numerama.com/tech/2336405-midea-revoit-son-climatiseur-portasplit-pour-2027-nouveau-gaz-refrigerant-et-compatibilite-matter.html</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>8. Audio</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Phonandroid</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-19T10:33:39+00:00</t>
+          <t>2026-09-19T10:36:00+00:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Windows 11 : Microsoft vous laisse enfin reprendre le contrôle du menu Démarrer avec cette mise à jour</t>
+          <t>Actualité : Votre box Wi-Fi bride votre smartphone ? Le réglage caché pour doubler le débit</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.phonandroid.com/windows-11-microsoft-vous-laisse-enfin-reprendre-le-controle-du-menu-demarrer-avec-cette-mise-a-jour.html</t>
+          <t>https://www.lesnumeriques.com/mobilite-c17/votre-box-wi-fi-bride-votre-smartphone-le-reglage-cache-pour-doubler-le-debit-n261954.html</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>5. Logiciels _ OS</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>Phonandroid</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-09-19T10:11:35+00:00</t>
+          <t>2026-09-19T10:33:39+00:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Actualité : Cet appareil photo instantané présente le meilleur rapport qualité / prix de notre comparatif</t>
+          <t>Windows 11 : Microsoft vous laisse enfin reprendre le contrôle du menu Démarrer avec cette mise à jour</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/appareil-photo-instantane/cet-appareil-photo-instantane-presente-le-meilleur-rapport-qualite-prix-de-notre-comparatif-n262060.html</t>
+          <t>https://www.phonandroid.com/windows-11-microsoft-vous-laisse-enfin-reprendre-le-controle-du-menu-demarrer-avec-cette-mise-a-jour.html</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>NON_CLASSE</t>
+          <t>5. Logiciels _ OS</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-09-19T10:04:31+00:00</t>
+          <t>2026-09-19T10:11:35+00:00</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>iOS 27 : 10 fonctions pour bien maitriser la dernière mise à jour de l’iPhone</t>
+          <t>Actualité : Cet appareil photo instantané présente le meilleur rapport qualité / prix de notre comparatif</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.01net.com/astuces/ios-27-10-fonctions-pour-bien-maitriser-la-derniere-mise-a-jour-de-liphone.html</t>
+          <t>https://www.lesnumeriques.com/appareil-photo-instantane/cet-appareil-photo-instantane-presente-le-meilleur-rapport-qualite-prix-de-notre-comparatif-n262060.html</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>NON_CLASSE</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-09-19T10:00:16+00:00</t>
+          <t>2026-09-19T10:04:31+00:00</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Les brouteurs n’ont qu’à bien se tenir : Bercy dévoile son guide anti-arnaques (mais il est déjà obsolète)</t>
+          <t>iOS 27 : 10 fonctions pour bien maitriser la dernière mise à jour de l’iPhone</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/19/les-brouteurs-nont-qua-bien-se-tenir-bercy-devoile-son-guide-anti-arnaques-mais-il-est-deja-obsolete/</t>
+          <t>https://www.01net.com/astuces/ios-27-10-fonctions-pour-bien-maitriser-la-derniere-mise-a-jour-de-liphone.html</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>8. Audio</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-09-19T10:00:00+00:00</t>
+          <t>2026-09-19T10:00:16+00:00</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Actualité : Redmi Note 17 Pro vs Redmi Note 15 Pro : le duel de l'absurde</t>
+          <t>Les brouteurs n’ont qu’à bien se tenir : Bercy dévoile son guide anti-arnaques (mais il est déjà obsolète)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/telephone-portable/redmi-note-17-pro-vs-redmi-note-15-pro-le-duel-de-l-absurde-n262034.html</t>
+          <t>https://www.journaldugeek.com/2026/09/19/les-brouteurs-nont-qua-bien-se-tenir-bercy-devoile-son-guide-anti-arnaques-mais-il-est-deja-obsolete/</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>8. Audio</t>
         </is>
       </c>
     </row>
@@ -1988,24 +1988,24 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Test Braun Nevo : que vaut le rasoir à 790 € dont la tête AeroTouch s'inspire de la peau des requins ?</t>
+          <t>Actualité : Redmi Note 17 Pro vs Redmi Note 15 Pro : le duel de l'absurde</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/rasoir-electrique/braun-nevo-p78560/test.html</t>
+          <t>https://www.lesnumeriques.com/telephone-portable/redmi-note-17-pro-vs-redmi-note-15-pro-le-duel-de-l-absurde-n262034.html</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>14. Santé</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Frandroid - RSS</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2015,66 +2015,66 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>J’ai testé la Garmin Fenix 9 Pro : le titane change tout, l’autonomie un peu moins</t>
+          <t>Test Braun Nevo : que vaut le rasoir à 790 € dont la tête AeroTouch s'inspire de la peau des requins ?</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/marques/garmin/3240977_jai-teste-la-garmin-fenix-9-pro-le-titane-change-tout-lautonomie-un-peu-moins</t>
+          <t>https://www.lesnumeriques.com/rasoir-electrique/braun-nevo-p78560/test.html</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>6. IA</t>
+          <t>14. Santé</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>Frandroid - RSS</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-09-19T09:35:00+00:00</t>
+          <t>2026-09-19T10:00:00+00:00</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Actualité : PRONOTE vous prend la tête : toutes nos astuces pour survivre à l'année scolaire</t>
+          <t>J’ai testé la Garmin Fenix 9 Pro : le titane change tout, l’autonomie un peu moins</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/societe-numerique/pronote-vous-prend-la-tete-toutes-nos-astuces-pour-survivre-a-l-annee-scolaire-n261988.html</t>
+          <t>https://www.frandroid.com/marques/garmin/3240977_jai-teste-la-garmin-fenix-9-pro-le-titane-change-tout-lautonomie-un-peu-moins</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>NON_CLASSE</t>
+          <t>6. IA</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Phonandroid</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-09-19T09:33:38+00:00</t>
+          <t>2026-09-19T09:35:00+00:00</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Marvel’s Wolverine pourrait avoir droit à une suite, cette mystérieuse scène pourrait tout changer</t>
+          <t>Actualité : PRONOTE vous prend la tête : toutes nos astuces pour survivre à l'année scolaire</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.phonandroid.com/marvels-wolverine-pourrait-avoir-droit-a-une-suite-cette-mysterieuse-scene-pourrait-tout-changer.html</t>
+          <t>https://www.lesnumeriques.com/societe-numerique/pronote-vous-prend-la-tete-toutes-nos-astuces-pour-survivre-a-l-annee-scolaire-n261988.html</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2086,76 +2086,76 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Frandroid - RSS</t>
+          <t>Phonandroid</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-09-19T09:27:00+00:00</t>
+          <t>2026-09-19T09:33:38+00:00</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>La dernière tablette de Honor, compatible avec l’IMAX, perd 50 euros et s’accompagne d’un casque sans fil</t>
+          <t>Marvel’s Wolverine pourrait avoir droit à une suite, cette mystérieuse scène pourrait tout changer</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/bons-plans/3251353_la-derniere-tablette-de-honor-compatible-avec-limax-perd-50-euros-et-saccompagne-dun-casque-sans-fil</t>
+          <t>https://www.phonandroid.com/marvels-wolverine-pourrait-avoir-droit-a-une-suite-cette-mysterieuse-scene-pourrait-tout-changer.html</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>NON_CLASSE</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>Frandroid - RSS</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-09-19T09:15:00+00:00</t>
+          <t>2026-09-19T09:27:00+00:00</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Critique Apollo Has Fallen : la série Canal+ passe à la vitesse supérieure et offre une saison 2 nerveuse</t>
+          <t>La dernière tablette de Honor, compatible avec l’IMAX, perd 50 euros et s’accompagne d’un casque sans fil</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/serie/apollo-has-fallen-p78881/test.html</t>
+          <t>https://www.frandroid.com/bons-plans/3251353_la-derniere-tablette-de-honor-compatible-avec-limax-perd-50-euros-et-saccompagne-dun-casque-sans-fil</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>15. ludique</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-09-19T09:02:46+00:00</t>
+          <t>2026-09-19T09:15:00+00:00</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>FarCry : date de sortie, casting, intrigue… tout savoir sur la série LIVE Action</t>
+          <t>Critique Apollo Has Fallen : la série Canal+ passe à la vitesse supérieure et offre une saison 2 nerveuse</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/19/farcry-date-de-sortie-casting-intrigue-tout-savoir-sur-la-serie-live-action/</t>
+          <t>https://www.lesnumeriques.com/serie/apollo-has-fallen-p78881/test.html</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2167,189 +2167,189 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Numerama</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-09-19T09:01:54+00:00</t>
+          <t>2026-09-19T09:02:46+00:00</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Des drones non identifiés ont forcé l’aéroport de Luxembourg à fermer vendredi soir</t>
+          <t>FarCry : date de sortie, casting, intrigue… tout savoir sur la série LIVE Action</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://www.numerama.com/tech/2336351-des-drones-non-identifies-ont-force-laeroport-de-luxembourg-a-fermer-vendredi-soir.html</t>
+          <t>https://www.journaldugeek.com/2026/09/19/farcry-date-de-sortie-casting-intrigue-tout-savoir-sur-la-serie-live-action/</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>9. Moiilité douce</t>
+          <t>15. ludique</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>Numerama</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-09-19T09:00:34+00:00</t>
+          <t>2026-09-19T09:01:54+00:00</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>0,82 € les 100 km : l’incroyable exploit de cette Lancia électrique sur le périphérique parisien</t>
+          <t>Des drones non identifiés ont forcé l’aéroport de Luxembourg à fermer vendredi soir</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://www.01net.com/actualites/082-euros-100-km-incroyable-exploit-lancia-electrique-peripherique-parisien.html</t>
+          <t>https://www.numerama.com/tech/2336351-des-drones-non-identifies-ont-force-laeroport-de-luxembourg-a-fermer-vendredi-soir.html</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>3. Periphérique</t>
+          <t>9. Moiilité douce</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Frandroid - RSS</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-09-19T09:00:00+00:00</t>
+          <t>2026-09-19T09:00:34+00:00</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ChatGPT s’installe gratuitement dans Microsoft Word pour tout le monde</t>
+          <t>0,82 € les 100 km : l’incroyable exploit de cette Lancia électrique sur le périphérique parisien</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/culture-tech/intelligence-artificielle/openai-chatgpt/3253521_chatgpt-sinstalle-gratuitement-dans-microsoft-word-pour-tout-le-monde</t>
+          <t>https://www.01net.com/actualites/082-euros-100-km-incroyable-exploit-lancia-electrique-peripherique-parisien.html</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>5. Logiciels _ OS</t>
+          <t>3. Periphérique</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>Frandroid - RSS</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-09-19T08:53:16+00:00</t>
+          <t>2026-09-19T09:00:00+00:00</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Xiaomi dit adieu à la marge : le Redmi Note 15 Pro se vend à prix FOU (256 et 512 Go) ⚡️</t>
+          <t>ChatGPT s’installe gratuitement dans Microsoft Word pour tout le monde</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://www.01net.com/bons-plans/xiaomi-dit-adieu-a-la-marge-le-redmi-note-15-pro-se-vend-a-prix-fou-256-et-512-go.html</t>
+          <t>https://www.frandroid.com/culture-tech/intelligence-artificielle/openai-chatgpt/3253521_chatgpt-sinstalle-gratuitement-dans-microsoft-word-pour-tout-le-monde</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>5. Logiciels _ OS</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Phonandroid</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-09-19T08:37:22+00:00</t>
+          <t>2026-09-19T08:53:16+00:00</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Free libère enfin le potentiel de son Wi-Fi avec cette mise à jour très attendue</t>
+          <t>Xiaomi dit adieu à la marge : le Redmi Note 15 Pro se vend à prix FOU (256 et 512 Go) ⚡️</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://www.phonandroid.com/free-libere-enfin-le-potentiel-de-son-wi-fi-avec-cette-mise-a-jour-tres-attendue.html</t>
+          <t>https://www.01net.com/bons-plans/xiaomi-dit-adieu-a-la-marge-le-redmi-note-15-pro-se-vend-a-prix-fou-256-et-512-go.html</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>3. Periphérique</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>Phonandroid</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-09-19T08:34:08+00:00</t>
+          <t>2026-09-19T08:37:22+00:00</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Le saviez-vous ? Atari a enterré ses pires jeux vidéo dans le désert en 1983, et ce n’était pas une légende</t>
+          <t>Free libère enfin le potentiel de son Wi-Fi avec cette mise à jour très attendue</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/19/le-saviez-vous-atari-a-enterre-ses-pires-jeux-video-dans-le-desert-en-1983-et-ce-netait-pas-une-legende/</t>
+          <t>https://www.phonandroid.com/free-libere-enfin-le-potentiel-de-son-wi-fi-avec-cette-mise-a-jour-tres-attendue.html</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>7. Video</t>
+          <t>3. Periphérique</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-09-19T08:32:00+00:00</t>
+          <t>2026-09-19T08:34:08+00:00</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Actualité : Samsung Galaxy : ces applications cachées vont améliorer votre quotidien</t>
+          <t>Le saviez-vous ? Atari a enterré ses pires jeux vidéo dans le désert en 1983, et ce n’était pas une légende</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/mobilite-c17/samsung-galaxy-ces-applications-cachees-vont-ameliorer-votre-quotidien-n261951.html</t>
+          <t>https://www.journaldugeek.com/2026/09/19/le-saviez-vous-atari-a-enterre-ses-pires-jeux-video-dans-le-desert-en-1983-et-ce-netait-pas-une-legende/</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>7. Video</t>
         </is>
       </c>
     </row>
@@ -2361,137 +2361,137 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-09-19T08:15:00+00:00</t>
+          <t>2026-09-19T08:32:00+00:00</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Actualité : En pleine inflation, voici les 5 départements où faire ses courses en ligne coûte le moins cher</t>
+          <t>Actualité : Samsung Galaxy : ces applications cachées vont améliorer votre quotidien</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/societe-numerique/en-pleine-inflation-voici-les-5-departements-ou-faire-ses-courses-en-ligne-coute-le-moins-cher-n262058.html</t>
+          <t>https://www.lesnumeriques.com/mobilite-c17/samsung-galaxy-ces-applications-cachees-vont-ameliorer-votre-quotidien-n261951.html</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>14. Santé</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-09-19T08:13:01+00:00</t>
+          <t>2026-09-19T08:15:00+00:00</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>OnePlus 15 : il défie l’iPhone 17 Pro et le Galaxy S26 Ultra… mais coûte 800 € moins cher</t>
+          <t>Actualité : En pleine inflation, voici les 5 départements où faire ses courses en ligne coûte le moins cher</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://www.01net.com/bons-plans/oneplus-15-il-defie-liphone-17-pro-et-le-galaxy-s26-ultra-mais-coute-800-e-moins-cher.html</t>
+          <t>https://www.lesnumeriques.com/societe-numerique/en-pleine-inflation-voici-les-5-departements-ou-faire-ses-courses-en-ligne-coute-le-moins-cher-n262058.html</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>14. Santé</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Phonandroid</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-09-19T08:00:19+00:00</t>
+          <t>2026-09-19T08:13:01+00:00</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>On a vu (et entendu) les Cove de JBL, des enceintes qui modernisent l’audio à la maison</t>
+          <t>OnePlus 15 : il défie l’iPhone 17 Pro et le Galaxy S26 Ultra… mais coûte 800 € moins cher</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://www.phonandroid.com/on-a-vu-et-entendu-les-cove-de-jbl-des-enceintes-qui-modernisent-laudio-a-la-maison.html</t>
+          <t>https://www.01net.com/bons-plans/oneplus-15-il-defie-liphone-17-pro-et-le-galaxy-s26-ultra-mais-coute-800-e-moins-cher.html</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>8. Audio</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>Phonandroid</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-09-19T08:00:10+00:00</t>
+          <t>2026-09-19T08:00:19+00:00</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Le Futuroscope dévoile sa dernière nouveauté, et elle est spectaculaire</t>
+          <t>On a vu (et entendu) les Cove de JBL, des enceintes qui modernisent l’audio à la maison</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/19/le-futuroscope-devoile-sa-derniere-nouveaute-et-elle-est-spectaculaire/</t>
+          <t>https://www.phonandroid.com/on-a-vu-et-entendu-les-cove-de-jbl-des-enceintes-qui-modernisent-laudio-a-la-maison.html</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>NON_CLASSE</t>
+          <t>8. Audio</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-09-19T08:00:03+00:00</t>
+          <t>2026-09-19T08:00:10+00:00</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Actualité : Les codes promo les plus utilisés de la semaine</t>
+          <t>Le Futuroscope dévoile sa dernière nouveauté, et elle est spectaculaire</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/societe-numerique/les-codes-promo-les-plus-utilises-de-la-semaine-n262059.html</t>
+          <t>https://www.journaldugeek.com/2026/09/19/le-futuroscope-devoile-sa-derniere-nouveaute-et-elle-est-spectaculaire/</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>19. Sponso</t>
+          <t>NON_CLASSE</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Frandroid - RSS</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2501,71 +2501,71 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Les meilleurs smartphones à grand écran (6,7 pouces et plus) en 2026</t>
+          <t>Actualité : Les codes promo les plus utilisés de la semaine</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/guide-dachat/382644_6-alternatives-samsung-galaxy-note-7</t>
+          <t>https://www.lesnumeriques.com/societe-numerique/les-codes-promo-les-plus-utilises-de-la-semaine-n262059.html</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>19. Sponso</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Numerama</t>
+          <t>Frandroid - RSS</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-09-19T07:40:15+00:00</t>
+          <t>2026-09-19T08:00:03+00:00</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Un rapport de renseignement écrit avec une IA a failli déclencher une crise militaire entre les États-Unis et la Chine</t>
+          <t>Les meilleurs smartphones à grand écran (6,7 pouces et plus) en 2026</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://www.numerama.com/cyberguerre/2336305-un-rapport-de-renseignement-ecrit-avec-une-ia-a-failli-declencher-une-crise-militaire-entre-les-etats-unis-et-la-chine.html</t>
+          <t>https://www.frandroid.com/guide-dachat/382644_6-alternatives-samsung-galaxy-note-7</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>6. IA</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Frandroid - RSS</t>
+          <t>Numerama</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-09-19T07:35:00+00:00</t>
+          <t>2026-09-19T07:40:15+00:00</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Le prix de la version la plus complète du Dyson V16 qui aspire et lave en un geste s’effondre de 280 €</t>
+          <t>Un rapport de renseignement écrit avec une IA a failli déclencher une crise militaire entre les États-Unis et la Chine</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/produits-android/3252607_le-prix-de-la-version-la-plus-complete-du-dyson-v16-qui-aspire-et-lave-en-un-geste-seffondre-de-280-e</t>
+          <t>https://www.numerama.com/cyberguerre/2336305-un-rapport-de-renseignement-ecrit-avec-une-ia-a-failli-declencher-une-crise-militaire-entre-les-etats-unis-et-la-chine.html</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>6. IA</t>
         </is>
       </c>
     </row>
@@ -2577,17 +2577,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-09-19T07:31:05+00:00</t>
+          <t>2026-09-19T07:35:00+00:00</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>iPhone 18 Pro : le démontage confirme une mauvaise nouvelle difficile à justifier</t>
+          <t>Le prix de la version la plus complète du Dyson V16 qui aspire et lave en un geste s’effondre de 280 €</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/marques/apple/3253509_iphone-18-pro-le-demontage-confirme-une-mauvaise-nouvelle-difficile-a-justifier</t>
+          <t>https://www.frandroid.com/produits-android/3252607_le-prix-de-la-version-la-plus-complete-du-dyson-v16-qui-aspire-et-lave-en-un-geste-seffondre-de-280-e</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -2604,22 +2604,22 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-09-19T07:29:38+00:00</t>
+          <t>2026-09-19T07:31:05+00:00</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Google prépare l’intégration d’iMessage dans Gemini pour macOS</t>
+          <t>iPhone 18 Pro : le démontage confirme une mauvaise nouvelle difficile à justifier</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/marques/google/3253495_google-prepare-lintegration-dimessage-dans-gemini-pour-macos</t>
+          <t>https://www.frandroid.com/marques/apple/3253509_iphone-18-pro-le-demontage-confirme-une-mauvaise-nouvelle-difficile-a-justifier</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>5. Logiciels _ OS</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
@@ -2631,152 +2631,152 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-09-19T07:28:24+00:00</t>
+          <t>2026-09-19T07:29:38+00:00</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>12 Go de RAM et 4 350 mAh : Clicks muscle son « BlackBerry » sans hausser le prix</t>
+          <t>Google prépare l’intégration d’iMessage dans Gemini pour macOS</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/marques/blackberry/3253497_12-go-de-ram-et-4-350-mah-clicks-muscle-son-blackberry-sans-hausser-le-prix</t>
+          <t>https://www.frandroid.com/marques/google/3253495_google-prepare-lintegration-dimessage-dans-gemini-pour-macos</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>3. Periphérique</t>
+          <t>5. Logiciels _ OS</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>Frandroid - RSS</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-09-19T07:19:00+00:00</t>
+          <t>2026-09-19T07:28:24+00:00</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Actualité : Sony FE 600mm F6.3 GM OSS : le super téléobjectif 30% plus léger et 1100 € moins cher que Nikon</t>
+          <t>12 Go de RAM et 4 350 mAh : Clicks muscle son « BlackBerry » sans hausser le prix</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/objectif/sony-fe-600mm-f6-3-gm-oss-le-super-teleobjectif-30-plus-leger-et-1100-moins-cher-que-nikon-n261881.html</t>
+          <t>https://www.frandroid.com/marques/blackberry/3253497_12-go-de-ram-et-4-350-mah-clicks-muscle-son-blackberry-sans-hausser-le-prix</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>5. Logiciels _ OS</t>
+          <t>3. Periphérique</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Numerama</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-09-19T07:05:00+00:00</t>
+          <t>2026-09-19T07:19:00+00:00</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Nintendo brade une flopée de jeux Square Enix sur l’eShop, dont plusieurs Final Fantasy</t>
+          <t>Actualité : Sony FE 600mm F6.3 GM OSS : le super téléobjectif 30% plus léger et 1100 € moins cher que Nikon</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://www.numerama.com/pop-culture/2336149-nintendo-brade-une-flopee-de-jeux-square-enix-sur-leshop-dont-plusieurs-final-fantasy.html</t>
+          <t>https://www.lesnumeriques.com/objectif/sony-fe-600mm-f6-3-gm-oss-le-super-teleobjectif-30-plus-leger-et-1100-moins-cher-que-nikon-n261881.html</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>15. ludique</t>
+          <t>5. Logiciels _ OS</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>Numerama</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-09-19T07:00:16+00:00</t>
+          <t>2026-09-19T07:05:00+00:00</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>BYD veut concurrencer Rolls-Royce avec des monstres de 1 200 ch signés Yangwang</t>
+          <t>Nintendo brade une flopée de jeux Square Enix sur l’eShop, dont plusieurs Final Fantasy</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://www.01net.com/actualites/byd-concurrencer-rolls-royce-monstres-1-200-ch-yangwang.html</t>
+          <t>https://www.numerama.com/pop-culture/2336149-nintendo-brade-une-flopee-de-jeux-square-enix-sur-leshop-dont-plusieurs-final-fantasy.html</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>10. Voiture</t>
+          <t>15. ludique</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-09-19T06:59:00+00:00</t>
+          <t>2026-09-19T07:00:16+00:00</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Actualité : La critique de la série Neagley a rejoint notre catalogue</t>
+          <t>BYD veut concurrencer Rolls-Royce avec des monstres de 1 200 ch signés Yangwang</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/serie/la-critique-de-la-serie-neagley-a-rejoint-notre-catalogue-n262053.html</t>
+          <t>https://www.01net.com/actualites/byd-concurrencer-rolls-royce-monstres-1-200-ch-yangwang.html</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>15. ludique</t>
+          <t>10. Voiture</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Phonandroid</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-09-19T06:50:27+00:00</t>
+          <t>2026-09-19T06:59:00+00:00</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Gears of War E-Day : toutes les infos sur un épisode anniversaire, qui marque le grand retour des exclusivités Xbox</t>
+          <t>Actualité : La critique de la série Neagley a rejoint notre catalogue</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://www.phonandroid.com/gears-of-war-e-day-toutes-les-infos-sur-un-episode-anniversaire-qui-marque-le-grand-retour-des-exclusivites-xbox.html</t>
+          <t>https://www.lesnumeriques.com/serie/la-critique-de-la-serie-neagley-a-rejoint-notre-catalogue-n262053.html</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -2788,27 +2788,27 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>Phonandroid</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-09-19T06:45:00+00:00</t>
+          <t>2026-09-19T06:50:27+00:00</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Actualité : On l'attendait : Jura dévoile enfin sa machine avec broyeur ultra-compacte et sans compromis</t>
+          <t>Gears of War E-Day : toutes les infos sur un épisode anniversaire, qui marque le grand retour des exclusivités Xbox</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/machine-a-cafe-automatique/on-l-attendait-jura-devoile-enfin-sa-machine-avec-broyeur-ultra-compacte-et-sans-compromis-n262037.html</t>
+          <t>https://www.phonandroid.com/gears-of-war-e-day-toutes-les-infos-sur-un-episode-anniversaire-qui-marque-le-grand-retour-des-exclusivites-xbox.html</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>12. Cuisine</t>
+          <t>15. ludique</t>
         </is>
       </c>
     </row>
@@ -2825,179 +2825,179 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Actualité : "Ça a failli déclencher une guerre" : comment une IA aurait pu plonger le monde dans un incident militaire entre les États-Unis et la Chine</t>
+          <t>Actualité : On l'attendait : Jura dévoile enfin sa machine avec broyeur ultra-compacte et sans compromis</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/intelligence-artificielle/ca-a-failli-declencher-une-guerre-comment-une-ia-aurait-pu-plonger-le-monde-dans-un-incident-militaire-entre-les-etats-unis-et-la-chine-n262056.html</t>
+          <t>https://www.lesnumeriques.com/machine-a-cafe-automatique/on-l-attendait-jura-devoile-enfin-sa-machine-avec-broyeur-ultra-compacte-et-sans-compromis-n262037.html</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>6. IA</t>
+          <t>12. Cuisine</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Frandroid - RSS</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-09-19T06:29:00+00:00</t>
+          <t>2026-09-19T06:45:00+00:00</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Comment bien choisir sa souris ? [Sponso]</t>
+          <t>Actualité : "Ça a failli déclencher une guerre" : comment une IA aurait pu plonger le monde dans un incident militaire entre les États-Unis et la Chine</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/produits-android/ordinateurs/peripheriques-pc/souris/3234113_comment-bien-choisir-sa-souris</t>
+          <t>https://www.lesnumeriques.com/intelligence-artificielle/ca-a-failli-declencher-une-guerre-comment-une-ia-aurait-pu-plonger-le-monde-dans-un-incident-militaire-entre-les-etats-unis-et-la-chine-n262056.html</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>6. IA</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>Frandroid - RSS</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-09-19T06:27:02+00:00</t>
+          <t>2026-09-19T06:29:00+00:00</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Actualité : Bon plan – Le compact / bridge Sony ZV-1 Seul à 630,85 € (-21%)</t>
+          <t>Comment bien choisir sa souris ? [Sponso]</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/compact-bridge/bon-plan-le-compact-bridge-sony-zv-1-seul-a-630-85-21-n262057.html</t>
+          <t>https://www.frandroid.com/produits-android/ordinateurs/peripheriques-pc/souris/3234113_comment-bien-choisir-sa-souris</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>19. Sponso</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-09-19T06:01:17+00:00</t>
+          <t>2026-09-19T06:27:02+00:00</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Cyberattaques : un géant du DDoS a été neutralisé après des « centaines de milliers d’attaques »</t>
+          <t>Actualité : Bon plan – Le compact / bridge Sony ZV-1 Seul à 630,85 € (-21%)</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://www.01net.com/actualites/cyberattaques-un-geant-du-ddos-a-ete-neutralise-apres-des-centaines-de-milliers-dattaques.html</t>
+          <t>https://www.lesnumeriques.com/compact-bridge/bon-plan-le-compact-bridge-sony-zv-1-seul-a-630-85-21-n262057.html</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>16. actu jur et pol</t>
+          <t>19. Sponso</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-09-19T06:01:00+00:00</t>
+          <t>2026-09-19T06:01:17+00:00</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Actualité : 100 % de produits non conformes : le danger des appareils électriques vendus à prix mini sur Amazon, Darty ou Temu</t>
+          <t>Cyberattaques : un géant du DDoS a été neutralisé après des « centaines de milliers d’attaques »</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/divers-electromenager/100-de-produits-non-conformes-le-danger-des-appareils-electriques-vendus-a-prix-mini-sur-amazon-darty-ou-temu-n262006.html</t>
+          <t>https://www.01net.com/actualites/cyberattaques-un-geant-du-ddos-a-ete-neutralise-apres-des-centaines-de-milliers-dattaques.html</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>NON_CLASSE</t>
+          <t>16. actu jur et pol</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Frandroid - RSS</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-09-19T05:44:00+00:00</t>
+          <t>2026-09-19T06:01:00+00:00</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Boulanger fait chuter le prix de ce TV 4K QLED 65 pouces Philips Ambilight à moins de 700 €</t>
+          <t>Actualité : 100 % de produits non conformes : le danger des appareils électriques vendus à prix mini sur Amazon, Darty ou Temu</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/bons-plans/3250245_boulanger-fait-chuter-le-prix-de-ce-tv-4k-qled-65-pouces-philips-ambilight-a-moins-de-700-e</t>
+          <t>https://www.lesnumeriques.com/divers-electromenager/100-de-produits-non-conformes-le-danger-des-appareils-electriques-vendus-a-prix-mini-sur-amazon-darty-ou-temu-n262006.html</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>7. Video</t>
+          <t>NON_CLASSE</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>Frandroid - RSS</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-09-19T05:15:02+00:00</t>
+          <t>2026-09-19T05:44:00+00:00</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Top bon plan : Samsung, Delonghi, SwitchBot... les meilleurs bons plans du 19/09/2026</t>
+          <t>Boulanger fait chuter le prix de ce TV 4K QLED 65 pouces Philips Ambilight à moins de 700 €</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/societe-numerique/samsung-switchbot-les-meilleurs-bons-plans-du-19-09-2026-n262050.html</t>
+          <t>https://www.frandroid.com/bons-plans/3250245_boulanger-fait-chuter-le-prix-de-ce-tv-4k-qled-65-pouces-philips-ambilight-a-moins-de-700-e</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>12. Cuisine</t>
+          <t>7. Video</t>
         </is>
       </c>
     </row>
@@ -3009,22 +3009,22 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-09-19T05:15:00+00:00</t>
+          <t>2026-09-19T05:15:02+00:00</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Actualité : Google savait que Gemini a attaqué de vraies entreprises et l'a gardé secret pendant des mois</t>
+          <t>Top bon plan : Samsung, Delonghi, SwitchBot... les meilleurs bons plans du 19/09/2026</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/intelligence-artificielle/google-savait-que-gemini-a-attaque-de-vraies-entreprises-et-l-a-garde-secret-pendant-des-mois-n262048.html</t>
+          <t>https://www.lesnumeriques.com/societe-numerique/samsung-switchbot-les-meilleurs-bons-plans-du-19-09-2026-n262050.html</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>6. IA</t>
+          <t>12. Cuisine</t>
         </is>
       </c>
     </row>
@@ -3036,22 +3036,22 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-09-19T05:11:31+00:00</t>
+          <t>2026-09-19T05:15:00+00:00</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Actualité : Pour un bon robot cuiseur multifonctions à prix abordable, privilégiez...</t>
+          <t>Actualité : Google savait que Gemini a attaqué de vraies entreprises et l'a gardé secret pendant des mois</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/robot-cuiseur-multifonction/pour-un-bon-robot-cuiseur-multifonctions-a-prix-abordable-privilegiez-n262051.html</t>
+          <t>https://www.lesnumeriques.com/intelligence-artificielle/google-savait-que-gemini-a-attaque-de-vraies-entreprises-et-l-a-garde-secret-pendant-des-mois-n262048.html</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>13. Maison</t>
+          <t>6. IA</t>
         </is>
       </c>
     </row>
@@ -3063,22 +3063,22 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-09-19T05:01:03+00:00</t>
+          <t>2026-09-19T05:11:31+00:00</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Actualité : Bon plan – La machine à café automatique avec broyeur Delonghi Magnifica Evo Next "5 étoiles" à 468,69 € (-21%)</t>
+          <t>Actualité : Pour un bon robot cuiseur multifonctions à prix abordable, privilégiez...</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/machine-a-cafe-automatique/bon-plan-la-machine-a-cafe-automatique-avec-broyeur-delonghi-magnifica-evo-next-5-etoiles-a-468-69-21-n262052.html</t>
+          <t>https://www.lesnumeriques.com/robot-cuiseur-multifonction/pour-un-bon-robot-cuiseur-multifonctions-a-prix-abordable-privilegiez-n262051.html</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>12. Cuisine</t>
+          <t>13. Maison</t>
         </is>
       </c>
     </row>
@@ -3090,44 +3090,44 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-09-19T05:00:00+00:00</t>
+          <t>2026-09-19T05:01:03+00:00</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Actualité : On a passé l’écran de l’iPhone 18 Pro au microscope : voici ce qu'Apple a caché</t>
+          <t>Actualité : Bon plan – La machine à café automatique avec broyeur Delonghi Magnifica Evo Next "5 étoiles" à 468,69 € (-21%)</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/telephone-portable/on-a-passe-l-ecran-de-l-iphone-18-pro-au-microscope-voici-ce-qu-apple-a-cache-n262039.html</t>
+          <t>https://www.lesnumeriques.com/machine-a-cafe-automatique/bon-plan-la-machine-a-cafe-automatique-avec-broyeur-delonghi-magnifica-evo-next-5-etoiles-a-468-69-21-n262052.html</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>12. Cuisine</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-09-19T04:54:32+00:00</t>
+          <t>2026-09-19T05:00:00+00:00</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>AliExpress : 5 smartphones Xiaomi à prix cassé en septembre 2026, lequel est fait pour vous ?</t>
+          <t>Actualité : On a passé l’écran de l’iPhone 18 Pro au microscope : voici ce qu'Apple a caché</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>https://www.01net.com/bons-plans/aliexpress-smartphones-xiaomi-prix-casse-lequel-est-fait-pour-vous.html</t>
+          <t>https://www.lesnumeriques.com/telephone-portable/on-a-passe-l-ecran-de-l-iphone-18-pro-au-microscope-voici-ce-qu-apple-a-cache-n262039.html</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -3139,108 +3139,108 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Numerama</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-09-19T04:45:00+00:00</t>
+          <t>2026-09-19T04:54:32+00:00</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Baguette One, bientôt un vol orbital inédit du Starship, manœuvre parfaite de la Nasa – le récap’ sciences de la semaine</t>
+          <t>AliExpress : 5 smartphones Xiaomi à prix cassé en septembre 2026, lequel est fait pour vous ?</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>https://www.numerama.com/sciences/2335785-baguette-one-vol-orbital-inedit-du-starship-manoeuvre-parfaite-de-la-nasa-le-recap-sciences-de-la-semaine.html</t>
+          <t>https://www.01net.com/bons-plans/aliexpress-smartphones-xiaomi-prix-casse-lequel-est-fait-pour-vous.html</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>18. Sciences</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>Numerama</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-09-19T04:40:02+00:00</t>
+          <t>2026-09-19T04:45:00+00:00</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Actualité : Bon plan – Le gonfleur de pneu Xiaomi Portable Electric Air Compressor 2 "5 étoiles" à 39,99 €</t>
+          <t>Baguette One, bientôt un vol orbital inédit du Starship, manœuvre parfaite de la Nasa – le récap’ sciences de la semaine</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/gonfleur-pneu/bon-plan-le-gonfleur-de-pneu-xiaomi-portable-electric-air-compressor-2-5-etoiles-a-39-99-n262049.html</t>
+          <t>https://www.numerama.com/sciences/2335785-baguette-one-vol-orbital-inedit-du-starship-manoeuvre-parfaite-de-la-nasa-le-recap-sciences-de-la-semaine.html</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2. PC</t>
+          <t>18. Sciences</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Numerama</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-09-18T22:01:00+00:00</t>
+          <t>2026-09-19T04:40:02+00:00</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Sophie Adenot a une peluche Pikachu dans l’ISS, et ce n’est pas pour devenir la meilleure dresseuse</t>
+          <t>Actualité : Bon plan – Le gonfleur de pneu Xiaomi Portable Electric Air Compressor 2 "5 étoiles" à 39,99 €</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>https://www.numerama.com/sciences/2335725-sophie-adenot-a-une-peluche-pikachu-dans-liss-et-ce-nest-pas-pour-devenir-la-meilleure-dresseuse.html</t>
+          <t>https://www.lesnumeriques.com/gonfleur-pneu/bon-plan-le-gonfleur-de-pneu-xiaomi-portable-electric-air-compressor-2-5-etoiles-a-39-99-n262049.html</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>18. Sciences</t>
+          <t>2. PC</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>Numerama</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-09-18T22:00:05+00:00</t>
+          <t>2026-09-18T22:01:00+00:00</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Actualité : Bon plan – L'enceinte connectée Audio Pro C5 MkII à 149,00 € (-26%)</t>
+          <t>Sophie Adenot a une peluche Pikachu dans l’ISS, et ce n’est pas pour devenir la meilleure dresseuse</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/enceintes-sans-fil/bon-plan-l-enceinte-connectee-audio-pro-c5-mkii-a-149-00-26-n262046.html</t>
+          <t>https://www.numerama.com/sciences/2335725-sophie-adenot-a-une-peluche-pikachu-dans-liss-et-ce-nest-pas-pour-devenir-la-meilleure-dresseuse.html</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>8. Audio</t>
+          <t>18. Sciences</t>
         </is>
       </c>
     </row>
@@ -3252,184 +3252,184 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-09-18T22:00:04+00:00</t>
+          <t>2026-09-18T22:00:05+00:00</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Actualité : Bon plan – Le smartphone Samsung Galaxy A57 5G 128 Go à 329,00 € (-14%)</t>
+          <t>Actualité : Bon plan – L'enceinte connectée Audio Pro C5 MkII à 149,00 € (-26%)</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/telephone-portable/bon-plan-le-smartphone-samsung-galaxy-a57-5g-128-go-a-329-00-14-n262045.html</t>
+          <t>https://www.lesnumeriques.com/enceintes-sans-fil/bon-plan-l-enceinte-connectee-audio-pro-c5-mkii-a-149-00-26-n262046.html</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>8. Audio</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>KultureGeek</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-09-18T20:50:26+00:00</t>
+          <t>2026-09-18T22:00:04+00:00</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Des chercheurs en sécurité ont piraté OpenAI grâce à l’IA Claude</t>
+          <t>Actualité : Bon plan – Le smartphone Samsung Galaxy A57 5G 128 Go à 329,00 € (-14%)</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>https://kulturegeek.fr/news-359758/chercheurs-securite-pirate-openai-grace-lia-claude</t>
+          <t>https://www.lesnumeriques.com/telephone-portable/bon-plan-le-smartphone-samsung-galaxy-a57-5g-128-go-a-329-00-14-n262045.html</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>6. IA</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Frandroid - RSS</t>
+          <t>KultureGeek</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-09-18T19:05:31+00:00</t>
+          <t>2026-09-18T20:50:26+00:00</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>« Un plein à 10 euros » : Lidl casse le prix de sa recharge électrique, c’est le tarif le moins cher de France</t>
+          <t>Des chercheurs en sécurité ont piraté OpenAI grâce à l’IA Claude</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/survoltes/voitures-electriques/3253487_un-plein-a-10-euros-lidl-casse-le-prix-de-sa-recharge-electrique-cest-le-tarif-le-moins-cher-de-france</t>
+          <t>https://kulturegeek.fr/news-359758/chercheurs-securite-pirate-openai-grace-lia-claude</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>10. Voiture</t>
+          <t>6. IA</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>Frandroid - RSS</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-09-18T18:49:08+00:00</t>
+          <t>2026-09-18T19:05:31+00:00</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Garmin Forerunner 265 : -51% ce week-end, une belle affaire pour les vrais sportifs</t>
+          <t>« Un plein à 10 euros » : Lidl casse le prix de sa recharge électrique, c’est le tarif le moins cher de France</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>https://www.01net.com/bons-plans/garmin-forerunner-265-51-ce-week-end-une-belle-affaire-pour-les-vrais-sportifs.html</t>
+          <t>https://www.frandroid.com/survoltes/voitures-electriques/3253487_un-plein-a-10-euros-lidl-casse-le-prix-de-sa-recharge-electrique-cest-le-tarif-le-moins-cher-de-france</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>14. Santé</t>
+          <t>10. Voiture</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>KultureGeek</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-09-18T18:15:44+00:00</t>
+          <t>2026-09-18T18:49:08+00:00</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Elias 2-24 b : les astronomes découvrent la plus jeune planète jamais observée, et sa taille défie les modèles</t>
+          <t>Garmin Forerunner 265 : -51% ce week-end, une belle affaire pour les vrais sportifs</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>https://kulturegeek.fr/news-359753/elias-2-24-b-astronomes-decouvrent-plus-jeune-planete-jamais-observee-taille-defie-modeles</t>
+          <t>https://www.01net.com/bons-plans/garmin-forerunner-265-51-ce-week-end-une-belle-affaire-pour-les-vrais-sportifs.html</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>18. Sciences</t>
+          <t>14. Santé</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>KultureGeek</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-09-18T18:13:58+00:00</t>
+          <t>2026-09-18T18:15:44+00:00</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Xiaomi s’est gouré : il vend le dernier Poco X8 Pro au prix du modèle d’il y a 2 ans 😱</t>
+          <t>Elias 2-24 b : les astronomes découvrent la plus jeune planète jamais observée, et sa taille défie les modèles</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>https://www.01net.com/bons-plans/xiaomi-sest-goure-il-vend-le-dernier-poco-x8-pro-au-prix-du-modele-dil-y-a-2-ans.html</t>
+          <t>https://kulturegeek.fr/news-359753/elias-2-24-b-astronomes-decouvrent-plus-jeune-planete-jamais-observee-taille-defie-modeles</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>18. Sciences</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Phonandroid</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-09-18T17:46:14+00:00</t>
+          <t>2026-09-18T18:13:58+00:00</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Amazon arrête la livraison gratuite de livres via lockers en France</t>
+          <t>Xiaomi s’est gouré : il vend le dernier Poco X8 Pro au prix du modèle d’il y a 2 ans 😱</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>https://www.phonandroid.com/amazon-arrete-la-livraison-gratuite-de-livres-via-lockers-en-france.html</t>
+          <t>https://www.01net.com/bons-plans/xiaomi-sest-goure-il-vend-le-dernier-poco-x8-pro-au-prix-du-modele-dil-y-a-2-ans.html</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>4. Tablette</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
@@ -3441,76 +3441,76 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-09-18T17:46:07+00:00</t>
+          <t>2026-09-18T17:46:14+00:00</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>L’excellent aspirateur balai sans fil Shark PowerDetect Speed Collection Luxe Clean &amp; Empty passe à prix cassé avec ce code</t>
+          <t>Amazon arrête la livraison gratuite de livres via lockers en France</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>https://www.phonandroid.com/lexcellent-aspirateur-balai-sans-fil-shark-powerdetect-speed-collection-luxe-clean-empty-passe-a-prix-casse-avec-ce-code.html</t>
+          <t>https://www.phonandroid.com/amazon-arrete-la-livraison-gratuite-de-livres-via-lockers-en-france.html</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>11. Menage</t>
+          <t>4. Tablette</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>KultureGeek</t>
+          <t>Phonandroid</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-09-18T17:43:50+00:00</t>
+          <t>2026-09-18T17:46:07+00:00</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>La Californie veut imposer un bouton d’arrêt d’urgence aux IA</t>
+          <t>L’excellent aspirateur balai sans fil Shark PowerDetect Speed Collection Luxe Clean &amp; Empty passe à prix cassé avec ce code</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>https://kulturegeek.fr/news-359748/californie-veut-imposer-bouton-darret-durgence-ia</t>
+          <t>https://www.phonandroid.com/lexcellent-aspirateur-balai-sans-fil-shark-powerdetect-speed-collection-luxe-clean-empty-passe-a-prix-casse-avec-ce-code.html</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>6. IA</t>
+          <t>11. Menage</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>KultureGeek</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-09-18T17:30:13+00:00</t>
+          <t>2026-09-18T17:43:50+00:00</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>La bêta de World of Warcraft Forever est ouverte, voici tout ce qu’il faut savoir avant de l’installer !</t>
+          <t>La Californie veut imposer un bouton d’arrêt d’urgence aux IA</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/18/la-beta-de-world-of-warcraft-forever-est-ouverte-voici-tout-ce-quil-faut-savoir-avant-de-linstaller/</t>
+          <t>https://kulturegeek.fr/news-359748/californie-veut-imposer-bouton-darret-durgence-ia</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>NON_CLASSE</t>
+          <t>6. IA</t>
         </is>
       </c>
     </row>
@@ -3522,49 +3522,49 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-09-18T17:03:19+00:00</t>
+          <t>2026-09-18T17:30:13+00:00</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Les États-Unis admettent qu’ils ont déployé des armes en orbite : la militarisation de l’espace s’accélère</t>
+          <t>La bêta de World of Warcraft Forever est ouverte, voici tout ce qu’il faut savoir avant de l’installer !</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/18/etats-unis-admettent-deploye-armes-orbite-militarisation-lespace-saccelere/</t>
+          <t>https://www.journaldugeek.com/2026/09/18/la-beta-de-world-of-warcraft-forever-est-ouverte-voici-tout-ce-quil-faut-savoir-avant-de-linstaller/</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>16. actu jur et pol</t>
+          <t>NON_CLASSE</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Frandroid - RSS</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-09-18T17:00:00+00:00</t>
+          <t>2026-09-18T17:03:19+00:00</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>J’ai testé le Leica SL3-P : 45 Mpx, 40 i/s… le Leica qui veut tout faire</t>
+          <t>Les États-Unis admettent qu’ils ont déployé des armes en orbite : la militarisation de l’espace s’accélère</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/marques/leica/3235591_jai-teste-le-leica-sl3-p-45-mpx-40-i-s-le-leica-qui-veut-tout-faire</t>
+          <t>https://www.journaldugeek.com/2026/09/18/etats-unis-admettent-deploye-armes-orbite-militarisation-lespace-saccelere/</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>6. IA</t>
+          <t>16. actu jur et pol</t>
         </is>
       </c>
     </row>
@@ -3576,292 +3576,292 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-09-18T16:57:51+00:00</t>
+          <t>2026-09-18T17:00:00+00:00</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Pour ses 80 ans, EDF ouvre 70 sites secrets au public, dont ses centrales nucléaires</t>
+          <t>J’ai testé le Leica SL3-P : 45 Mpx, 40 i/s… le Leica qui veut tout faire</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/survoltes/energie/3252663_pour-ses-80-ans-edf-ouvre-70-sites-secrets-au-public-dont-ses-centrales-nucleaires</t>
+          <t>https://www.frandroid.com/marques/leica/3235591_jai-teste-le-leica-sl3-p-45-mpx-40-i-s-le-leica-qui-veut-tout-faire</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>13. Maison</t>
+          <t>6. IA</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>KultureGeek</t>
+          <t>Frandroid - RSS</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-09-18T16:50:20+00:00</t>
+          <t>2026-09-18T16:57:51+00:00</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Anthropic ouvre un laboratoire de biologie : Claude pourrait bientôt piloter des robots scientifiques</t>
+          <t>Pour ses 80 ans, EDF ouvre 70 sites secrets au public, dont ses centrales nucléaires</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>https://kulturegeek.fr/news-359736/anthropic-ouvre-laboratoire-biologie-claude-pourrait-piloter-robots-scientifiques</t>
+          <t>https://www.frandroid.com/survoltes/energie/3252663_pour-ses-80-ans-edf-ouvre-70-sites-secrets-au-public-dont-ses-centrales-nucleaires</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>6. IA</t>
+          <t>13. Maison</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Frandroid - RSS</t>
+          <t>KultureGeek</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-09-18T16:43:50+00:00</t>
+          <t>2026-09-18T16:50:20+00:00</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>1 heure et 4 erreurs : comment l’IA a métamorphosé ma vieille liseuse en écran domotique</t>
+          <t>Anthropic ouvre un laboratoire de biologie : Claude pourrait bientôt piloter des robots scientifiques</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/marques/3251785_1-heure-et-4-erreurs-comment-lia-a-metamorphose-ma-vieille-liseuse-en-ecran-domotique</t>
+          <t>https://kulturegeek.fr/news-359736/anthropic-ouvre-laboratoire-biologie-claude-pourrait-piloter-robots-scientifiques</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>3. Periphérique</t>
+          <t>6. IA</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Phonandroid</t>
+          <t>Frandroid - RSS</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-09-18T16:40:37+00:00</t>
+          <t>2026-09-18T16:43:50+00:00</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>100 € en moins sur les Galaxy Buds 4 Pro chez Samsung : les écouteurs perdent 40% de leur prix</t>
+          <t>1 heure et 4 erreurs : comment l’IA a métamorphosé ma vieille liseuse en écran domotique</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>https://www.phonandroid.com/100-e-moins-galaxy-buds-4-pro-samsung-ecouteurs-perdent-40-prix.html</t>
+          <t>https://www.frandroid.com/marques/3251785_1-heure-et-4-erreurs-comment-lia-a-metamorphose-ma-vieille-liseuse-en-ecran-domotique</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>8. Audio</t>
+          <t>3. Periphérique</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>Phonandroid</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-09-18T16:30:47+00:00</t>
+          <t>2026-09-18T16:40:37+00:00</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>HONOR Magic V5 : bradé à -52 %, il n’a pourtant rien d’un smartphone au rabais, bien au contraire</t>
+          <t>100 € en moins sur les Galaxy Buds 4 Pro chez Samsung : les écouteurs perdent 40% de leur prix</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>https://www.01net.com/bons-plans/honor-magic-v5-brade-a-52-il-na-pourtant-rien-dun-smartphone-au-rabais-bien-au-contraire.html</t>
+          <t>https://www.phonandroid.com/100-e-moins-galaxy-buds-4-pro-samsung-ecouteurs-perdent-40-prix.html</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>8. Audio</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-09-18T16:30:35+00:00</t>
+          <t>2026-09-18T16:30:47+00:00</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Test du Ninja Crispi DualZone : l’airfryer en verre XXL qui remplace notre four</t>
+          <t>HONOR Magic V5 : bradé à -52 %, il n’a pourtant rien d’un smartphone au rabais, bien au contraire</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/test/test-du-ninja-crispi-dualzone-lairfryer-en-verre-xxl-qui-remplace-notre-four/</t>
+          <t>https://www.01net.com/bons-plans/honor-magic-v5-brade-a-52-il-na-pourtant-rien-dun-smartphone-au-rabais-bien-au-contraire.html</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>12. Cuisine</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Frandroid - RSS</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-09-18T16:17:00+00:00</t>
+          <t>2026-09-18T16:30:35+00:00</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Les mythiques courses de pod de Star Wars reviennent bientôt dans Galactic Racer, en précommande à 44,99 € sur PS5</t>
+          <t>Test du Ninja Crispi DualZone : l’airfryer en verre XXL qui remplace notre four</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/bons-plans/3253083_les-mythiques-courses-de-pod-de-star-wars-reviennent-bientot-dans-galactic-racer-en-precommande-a-4499-e-sur-ps5</t>
+          <t>https://www.journaldugeek.com/test/test-du-ninja-crispi-dualzone-lairfryer-en-verre-xxl-qui-remplace-notre-four/</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>14. Santé</t>
+          <t>12. Cuisine</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Frandroid - Actualités</t>
+          <t>Frandroid - RSS</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-09-18T16:15:51+00:00</t>
+          <t>2026-09-18T16:17:00+00:00</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Test du Xiaomi Redmi Note 17 Pro 5G, le smartphone qui mise tout sur l’autonomie</t>
+          <t>Les mythiques courses de pod de Star Wars reviennent bientôt dans Galactic Racer, en précommande à 44,99 € sur PS5</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/marques/xiaomi/3235547_test-du-xiaomi-redmi-note-17-pro-5g-le-smartphone-qui-mise-tout-sur-lautonomie</t>
+          <t>https://www.frandroid.com/bons-plans/3253083_les-mythiques-courses-de-pod-de-star-wars-reviennent-bientot-dans-galactic-racer-en-precommande-a-4499-e-sur-ps5</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>14. Santé</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Phonandroid</t>
+          <t>Frandroid - Actualités</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-09-18T16:03:51+00:00</t>
+          <t>2026-09-18T16:15:51+00:00</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Disney+ va diffuser de la publicité aux abonnés Standard et Premium, les déceptions s’enchaînent avec la plateforme de streaming</t>
+          <t>Test du Xiaomi Redmi Note 17 Pro 5G, le smartphone qui mise tout sur l’autonomie</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>https://www.phonandroid.com/disney-va-diffuser-de-la-publicite-aux-abonnes-standard-et-premium-les-deceptions-senchainent-avec-la-plateforme-de-streaming.html</t>
+          <t>https://www.frandroid.com/marques/xiaomi/3235547_test-du-xiaomi-redmi-note-17-pro-5g-le-smartphone-qui-mise-tout-sur-lautonomie</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>15. ludique</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>Phonandroid</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-09-18T16:00:11+00:00</t>
+          <t>2026-09-18T16:03:51+00:00</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Lunettes connectées : suite à plusieurs plaintes pour harcèlement sexuel, la France lance une enquête</t>
+          <t>Disney+ va diffuser de la publicité aux abonnés Standard et Premium, les déceptions s’enchaînent avec la plateforme de streaming</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>https://www.01net.com/actualites/lunettes-connectees-suite-a-plusieurs-plaintes-pour-harcelement-sexuel-la-france-lance-une-enquete.html</t>
+          <t>https://www.phonandroid.com/disney-va-diffuser-de-la-publicite-aux-abonnes-standard-et-premium-les-deceptions-senchainent-avec-la-plateforme-de-streaming.html</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>15. ludique</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Frandroid - Actualités</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-09-18T15:59:18+00:00</t>
+          <t>2026-09-18T16:00:11+00:00</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Tesla Semi : la formule « une journée complète avec un seul arrêt » arrive en France</t>
+          <t>Lunettes connectées : suite à plusieurs plaintes pour harcèlement sexuel, la France lance une enquête</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/marques/tesla/3252189_tesla-semi-la-formule-une-journee-complete-avec-un-seul-arret-arrive-en-france</t>
+          <t>https://www.01net.com/actualites/lunettes-connectees-suite-a-plusieurs-plaintes-pour-harcelement-sexuel-la-france-lance-une-enquete.html</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>10. Voiture</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
@@ -3873,44 +3873,44 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-09-18T15:57:34+00:00</t>
+          <t>2026-09-18T15:59:18+00:00</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>DAS : qu’est-ce que c’est et quels sont les smartphones qui émettent le moins de rayonnement ?</t>
+          <t>Tesla Semi : la formule « une journée complète avec un seul arrêt » arrive en France</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/produits-android/smartphone/462065_classement-das-quels-sont-les-smartphones-qui-emettent-le-moins-et-le-plus-de-radiations</t>
+          <t>https://www.frandroid.com/marques/tesla/3252189_tesla-semi-la-formule-une-journee-complete-avec-un-seul-arret-arrive-en-france</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>10. Voiture</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>KultureGeek</t>
+          <t>Frandroid - Actualités</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-09-18T15:52:37+00:00</t>
+          <t>2026-09-18T15:57:34+00:00</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Samsung rend disponible One UI 9 (Android 17) sur ses Galaxy</t>
+          <t>DAS : qu’est-ce que c’est et quels sont les smartphones qui émettent le moins de rayonnement ?</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>https://kulturegeek.fr/news-359738/samsung-rend-disponible-one-ui-9-android-17-galaxy</t>
+          <t>https://www.frandroid.com/produits-android/smartphone/462065_classement-das-quels-sont-les-smartphones-qui-emettent-le-moins-et-le-plus-de-radiations</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -3922,22 +3922,22 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Frandroid - Actualités</t>
+          <t>KultureGeek</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-09-18T15:49:14+00:00</t>
+          <t>2026-09-18T15:52:37+00:00</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Honor présente le Tiangong AXB35 Ultra, un mini-PC surpuissant conçu avec Nvidia</t>
+          <t>Samsung rend disponible One UI 9 (Android 17) sur ses Galaxy</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/produits-android/3253331_honor-presente-le-tiangong-axb35-ultra-un-mini-pc-surpuissant-concu-avec-nvidia</t>
+          <t>https://kulturegeek.fr/news-359738/samsung-rend-disponible-one-ui-9-android-17-galaxy</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -3954,22 +3954,22 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-09-18T15:41:43+00:00</t>
+          <t>2026-09-18T15:49:14+00:00</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>À bord du Tesla Semi, son responsable nous explique comment le FSD va débarquer</t>
+          <t>Honor présente le Tiangong AXB35 Ultra, un mini-PC surpuissant conçu avec Nvidia</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/marques/tesla/3252483_a-bord-du-tesla-semi-son-responsable-nous-explique-comment-le-fsd-va-debarquer</t>
+          <t>https://www.frandroid.com/produits-android/3253331_honor-presente-le-tiangong-axb35-ultra-un-mini-pc-surpuissant-concu-avec-nvidia</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>8. Audio</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
@@ -3981,103 +3981,103 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-09-18T15:39:57+00:00</t>
+          <t>2026-09-18T15:41:43+00:00</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Gears of War: E-Day, une configuration exigeante à prévoir sur PC</t>
+          <t>À bord du Tesla Semi, son responsable nous explique comment le FSD va débarquer</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/guide-dachat/3253211_gears-of-war-e-day-une-configuration-exigeante-a-prevoir-sur-pc</t>
+          <t>https://www.frandroid.com/marques/tesla/3252483_a-bord-du-tesla-semi-son-responsable-nous-explique-comment-le-fsd-va-debarquer</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2. PC</t>
+          <t>8. Audio</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Phonandroid</t>
+          <t>Frandroid - Actualités</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-09-18T15:30:48+00:00</t>
+          <t>2026-09-18T15:39:57+00:00</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Test Samsung Galaxy Z Flip8 : j’ai troqué mon iPhone contre ce smartphone pliant, ai-je vraiment envie de revenir en arrière ?</t>
+          <t>Gears of War: E-Day, une configuration exigeante à prévoir sur PC</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>https://www.phonandroid.com/test-samsung-galaxy-z-flip8-jai-troque-mon-iphone-contre-ce-smartphone-pliant-ai-je-vraiment-envie-de-revenir-en-arriere.html</t>
+          <t>https://www.frandroid.com/guide-dachat/3253211_gears-of-war-e-day-une-configuration-exigeante-a-prevoir-sur-pc</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>2. PC</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>Phonandroid</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-09-18T15:30:22+00:00</t>
+          <t>2026-09-18T15:30:48+00:00</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Batman Day 2026 : voici le programme complet, avec une exclu mondiale pour la France</t>
+          <t>Test Samsung Galaxy Z Flip8 : j’ai troqué mon iPhone contre ce smartphone pliant, ai-je vraiment envie de revenir en arrière ?</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/18/batman-day-2026-voici-le-programme-complet-avec-une-exclu-mondiale-pour-la-france/</t>
+          <t>https://www.phonandroid.com/test-samsung-galaxy-z-flip8-jai-troque-mon-iphone-contre-ce-smartphone-pliant-ai-je-vraiment-envie-de-revenir-en-arriere.html</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>16. actu jur et pol</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Phonandroid</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-09-18T15:30:21+00:00</t>
+          <t>2026-09-18T15:30:22+00:00</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Nous avons essayé les Vive Eagle, voici notre avis sur les lunettes connectées de HTC</t>
+          <t>Batman Day 2026 : voici le programme complet, avec une exclu mondiale pour la France</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>https://www.phonandroid.com/essai-htc-vive-eagle.html</t>
+          <t>https://www.journaldugeek.com/2026/09/18/batman-day-2026-voici-le-programme-complet-avec-une-exclu-mondiale-pour-la-france/</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>16. actu jur et pol</t>
         </is>
       </c>
     </row>
@@ -4089,22 +4089,22 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-09-18T15:29:57+00:00</t>
+          <t>2026-09-18T15:30:21+00:00</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Voitures électriques : plus besoin d’extraire du lithium neuf, Porsche vient de le prouver sur ses propres batteries</t>
+          <t>Nous avons essayé les Vive Eagle, voici notre avis sur les lunettes connectées de HTC</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>https://www.phonandroid.com/voitures-electriques-plus-besoin-dextraire-du-lithium-neuf-porsche-vient-de-le-prouver-sur-ses-propres-batteries.html</t>
+          <t>https://www.phonandroid.com/essai-htc-vive-eagle.html</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>10. Voiture</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
@@ -4116,76 +4116,76 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-09-18T15:16:13+00:00</t>
+          <t>2026-09-18T15:29:57+00:00</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>On a joué à Marvel’s Wolverine sur PS5 : trois raisons de ne pas perdre votre temps avec ce jeu</t>
+          <t>Voitures électriques : plus besoin d’extraire du lithium neuf, Porsche vient de le prouver sur ses propres batteries</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>https://www.phonandroid.com/marvel-wolverine-ps5-notre-avis-complet.html</t>
+          <t>https://www.phonandroid.com/voitures-electriques-plus-besoin-dextraire-du-lithium-neuf-porsche-vient-de-le-prouver-sur-ses-propres-batteries.html</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>15. ludique</t>
+          <t>10. Voiture</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>Phonandroid</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-09-18T15:14:44+00:00</t>
+          <t>2026-09-18T15:16:13+00:00</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Le casque à conduction osseuse Shokz à prix cassé : AliExpress le dégomme ce week-end 🥊</t>
+          <t>On a joué à Marvel’s Wolverine sur PS5 : trois raisons de ne pas perdre votre temps avec ce jeu</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>https://www.01net.com/bons-plans/le-casque-a-conduction-osseuse-shokz-a-prix-casse-aliexpress-le-degomme-ce-week-end.html</t>
+          <t>https://www.phonandroid.com/marvel-wolverine-ps5-notre-avis-complet.html</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>8. Audio</t>
+          <t>15. ludique</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Frandroid - Actualités</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-09-18T15:13:27+00:00</t>
+          <t>2026-09-18T15:14:44+00:00</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Asus lance le premier routeur Wi-Fi 8 : 900 euros et aucun appareil n’est compatible</t>
+          <t>Le casque à conduction osseuse Shokz à prix cassé : AliExpress le dégomme ce week-end 🥊</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/marques/asus/3253227_asus-lance-le-premier-routeur-wi-fi-8-900-euros-et-aucun-appareil-nest-compatible</t>
+          <t>https://www.01net.com/bons-plans/le-casque-a-conduction-osseuse-shokz-a-prix-casse-aliexpress-le-degomme-ce-week-end.html</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2. PC</t>
+          <t>8. Audio</t>
         </is>
       </c>
     </row>
@@ -4197,179 +4197,179 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-09-18T15:07:20+00:00</t>
+          <t>2026-09-18T15:13:27+00:00</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>iPhone 18 Pro : comment Spigen réinvente l’usage de votre nouveau smartphone au quotidien</t>
+          <t>Asus lance le premier routeur Wi-Fi 8 : 900 euros et aucun appareil n’est compatible</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/produits-android/smartphone/3250977_iphone-18-pro-comment-spigen-reinvente-lusage-de-votre-nouveau-smartphone-au-quotidien</t>
+          <t>https://www.frandroid.com/marques/asus/3253227_asus-lance-le-premier-routeur-wi-fi-8-900-euros-et-aucun-appareil-nest-compatible</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>2. PC</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>Frandroid - Actualités</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-09-18T15:02:45+00:00</t>
+          <t>2026-09-18T15:07:20+00:00</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>PS6 : la console portable serait un monstre de puissance grâce au PSSR3</t>
+          <t>iPhone 18 Pro : comment Spigen réinvente l’usage de votre nouveau smartphone au quotidien</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/18/ps6-la-console-portable-serait-un-monstre-de-puissance-grace-au-pssr3/</t>
+          <t>https://www.frandroid.com/produits-android/smartphone/3250977_iphone-18-pro-comment-spigen-reinvente-lusage-de-votre-nouveau-smartphone-au-quotidien</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>2. PC</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Frandroid - Actualités</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-09-18T14:57:26+00:00</t>
+          <t>2026-09-18T15:02:45+00:00</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Avec son cadre garantie à vie, ce vélo cargo électrique peut grimper jusqu’à 350 km d’autonomie dans un cas très précis</t>
+          <t>PS6 : la console portable serait un monstre de puissance grâce au PSSR3</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/marques/vello-bike/3252383_avec-son-cadre-garantie-a-vie-ce-velo-cargo-electrique-peut-grimper-jusqua-350-km-dautonomie-dans-un-cas-tres-precis</t>
+          <t>https://www.journaldugeek.com/2026/09/18/ps6-la-console-portable-serait-un-monstre-de-puissance-grace-au-pssr3/</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>8. Audio</t>
+          <t>2. PC</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>KultureGeek</t>
+          <t>Frandroid - Actualités</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-09-18T14:56:56+00:00</t>
+          <t>2026-09-18T14:57:26+00:00</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>[#BonPlan] Les promos High-Tech du 18 septembre</t>
+          <t>Avec son cadre garantie à vie, ce vélo cargo électrique peut grimper jusqu’à 350 km d’autonomie dans un cas très précis</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>https://kulturegeek.fr/news-359633/bonplan-promos-high-tech-18-septembre-2026</t>
+          <t>https://www.frandroid.com/marques/vello-bike/3252383_avec-son-cadre-garantie-a-vie-ce-velo-cargo-electrique-peut-grimper-jusqua-350-km-dautonomie-dans-un-cas-tres-precis</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>19. Sponso</t>
+          <t>8. Audio</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>KultureGeek</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-09-18T14:52:01+00:00</t>
+          <t>2026-09-18T14:56:56+00:00</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Ce billet de 5 euros peut vous rapporter 5 000 € !</t>
+          <t>[#BonPlan] Les promos High-Tech du 18 septembre</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/18/ce-billet-de-5-euros-qui-peut-vous-rapporter-5-000-e/</t>
+          <t>https://kulturegeek.fr/news-359633/bonplan-promos-high-tech-18-septembre-2026</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>NON_CLASSE</t>
+          <t>19. Sponso</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Frandroid - Actualités</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-09-18T14:50:44+00:00</t>
+          <t>2026-09-18T14:52:01+00:00</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Des PC portables « K-Bossés », mais de bonne qualité : la recette des Ateliers du Bocage face aux géants du reconditionné</t>
+          <t>Ce billet de 5 euros peut vous rapporter 5 000 € !</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/produits-android/3250423_des-pc-portables-k-bosses-mais-de-bonne-qualite-la-recette-des-ateliers-du-bocage-face-aux-geants-du-reconditionne</t>
+          <t>https://www.journaldugeek.com/2026/09/18/ce-billet-de-5-euros-qui-peut-vous-rapporter-5-000-e/</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>NON_CLASSE</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Phonandroid</t>
+          <t>Frandroid - Actualités</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-09-18T14:50:03+00:00</t>
+          <t>2026-09-18T14:50:44+00:00</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Voici comment synchroniser Samsung Galerie et Google Photos sur votre smartphone Galaxy</t>
+          <t>Des PC portables « K-Bossés », mais de bonne qualité : la recette des Ateliers du Bocage face aux géants du reconditionné</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>https://www.phonandroid.com/voici-comment-synchroniser-samsung-galerie-et-google-photos-sur-votre-smartphone-galaxy.html</t>
+          <t>https://www.frandroid.com/produits-android/3250423_des-pc-portables-k-bosses-mais-de-bonne-qualite-la-recette-des-ateliers-du-bocage-face-aux-geants-du-reconditionne</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -4381,76 +4381,76 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Numerama</t>
+          <t>Phonandroid</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-09-18T14:49:51+00:00</t>
+          <t>2026-09-18T14:50:03+00:00</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>La Game Boy en Lego perd près d’un tiers de son prix : difficile de ne pas être nostalgique</t>
+          <t>Voici comment synchroniser Samsung Galerie et Google Photos sur votre smartphone Galaxy</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>https://www.numerama.com/pop-culture/2058629-la-game-boy-en-lego-perd-pres-dun-tiers-de-son-prix-difficile-de-ne-pas-etre-nostalgique.html</t>
+          <t>https://www.phonandroid.com/voici-comment-synchroniser-samsung-galerie-et-google-photos-sur-votre-smartphone-galaxy.html</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>8. Audio</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>Numerama</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-09-18T14:48:16+00:00</t>
+          <t>2026-09-18T14:49:51+00:00</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>iPhone 18 Pro : on a passé la nouvelle Dynamic Island sous le microscope et voici ce qu’on a découvert</t>
+          <t>La Game Boy en Lego perd près d’un tiers de son prix : difficile de ne pas être nostalgique</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>https://www.01net.com/actualites/iphone-18-pro-on-a-passe-la-nouvelle-dynamic-island-sous-le-microscope-et-voici-ce-quon-a-decouvert.html</t>
+          <t>https://www.numerama.com/pop-culture/2058629-la-game-boy-en-lego-perd-pres-dun-tiers-de-son-prix-difficile-de-ne-pas-etre-nostalgique.html</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>8. Audio</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>TomsHardware</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-09-18T14:47:00+00:00</t>
+          <t>2026-09-18T14:48:16+00:00</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>iPhone 18 Pro Max : que vaut la chambre à vapeur trois fois plus grande ?</t>
+          <t>iPhone 18 Pro : on a passé la nouvelle Dynamic Island sous le microscope et voici ce qu’on a découvert</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.fr/iphone-18-pro-max-que-vaut-la-chambre-a-vapeur-trois-fois-plus-grande/</t>
+          <t>https://www.01net.com/actualites/iphone-18-pro-on-a-passe-la-nouvelle-dynamic-island-sous-le-microscope-et-voici-ce-quon-a-decouvert.html</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -4462,103 +4462,103 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>TomsHardware</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-09-18T14:40:19+00:00</t>
+          <t>2026-09-18T14:47:00+00:00</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Bon plan : les dernières versions de Microsoft Office 2024 et Windows 11 à partir de 12,25 €</t>
+          <t>iPhone 18 Pro Max : que vaut la chambre à vapeur trois fois plus grande ?</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>https://www.01net.com/bons-plans/bon-plan-les-dernieres-versions-de-microsoft-office-2024-et-windows-11-a-partir-de-1225-e.html</t>
+          <t>https://www.tomshardware.fr/iphone-18-pro-max-que-vaut-la-chambre-a-vapeur-trois-fois-plus-grande/</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>5. Logiciels _ OS</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-09-18T14:34:00+00:00</t>
+          <t>2026-09-18T14:40:19+00:00</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Actualité : Waze vient de changer en profondeur : les 5 réglages à connaître après la mise à jour de juillet</t>
+          <t>Bon plan : les dernières versions de Microsoft Office 2024 et Windows 11 à partir de 12,25 €</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/gps/waze-vient-de-changer-en-profondeur-les-5-reglages-a-connaitre-apres-la-mise-a-jour-de-juillet-n262032.html</t>
+          <t>https://www.01net.com/bons-plans/bon-plan-les-dernieres-versions-de-microsoft-office-2024-et-windows-11-a-partir-de-1225-e.html</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>9. Moiilité douce</t>
+          <t>5. Logiciels _ OS</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-09-18T14:33:30+00:00</t>
+          <t>2026-09-18T14:34:00+00:00</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>La France va-t-elle interdire la revente des cartes Pokémon avec plus de 20 % de marge ? (les scalpers en PLS)</t>
+          <t>Actualité : Waze vient de changer en profondeur : les 5 réglages à connaître après la mise à jour de juillet</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/18/la-france-va-t-elle-interdire-la-revente-des-cartes-pokemon-avec-plus-de-20-de-marge-les-scalpers-en-pls/</t>
+          <t>https://www.lesnumeriques.com/gps/waze-vient-de-changer-en-profondeur-les-5-reglages-a-connaitre-apres-la-mise-a-jour-de-juillet-n262032.html</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>15. ludique</t>
+          <t>9. Moiilité douce</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Frandroid - Actualités</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-09-18T14:33:07+00:00</t>
+          <t>2026-09-18T14:33:30+00:00</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Nouveau service de streaming gratuit : le célèbre guide JustWatch frappe un très grand coup</t>
+          <t>La France va-t-elle interdire la revente des cartes Pokémon avec plus de 20 % de marge ? (les scalpers en PLS)</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/services/svod/3252777_nouveau-service-de-streaming-gratuit-le-celebre-guide-justwatch-frappe-un-tres-grand-coup</t>
+          <t>https://www.journaldugeek.com/2026/09/18/la-france-va-t-elle-interdire-la-revente-des-cartes-pokemon-avec-plus-de-20-de-marge-les-scalpers-en-pls/</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -4570,76 +4570,76 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>Frandroid - Actualités</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-09-18T14:21:07+00:00</t>
+          <t>2026-09-18T14:33:07+00:00</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Vente flash DJI : à prix mini, son drone Neo 2 se vend par camions 🚛</t>
+          <t>Nouveau service de streaming gratuit : le célèbre guide JustWatch frappe un très grand coup</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>https://www.01net.com/bons-plans/vente-flash-en-cours-chez-dji-a-prix-mini-son-drone-neo-2-se-vend-par-camions.html</t>
+          <t>https://www.frandroid.com/services/svod/3252777_nouveau-service-de-streaming-gratuit-le-celebre-guide-justwatch-frappe-un-tres-grand-coup</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>7. Video</t>
+          <t>15. ludique</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Numerama</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-09-18T14:17:02+00:00</t>
+          <t>2026-09-18T14:21:07+00:00</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Quel iPhone acheter en 2026 ? Ceux qui valent leur prix, ceux qu’on vous déconseille</t>
+          <t>Vente flash DJI : à prix mini, son drone Neo 2 se vend par camions 🚛</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>https://www.numerama.com/tech/288962-guide-dachat-meilleur-iphone-a-acheter.html</t>
+          <t>https://www.01net.com/bons-plans/vente-flash-en-cours-chez-dji-a-prix-mini-son-drone-neo-2-se-vend-par-camions.html</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>7. Video</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Frandroid - Actualités</t>
+          <t>Numerama</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-09-18T14:15:06+00:00</t>
+          <t>2026-09-18T14:17:02+00:00</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Muse fait renaître les produits high-tech vintages</t>
+          <t>Quel iPhone acheter en 2026 ? Ceux qui valent leur prix, ceux qu’on vous déconseille</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/produits-android/audio/3253075_muse-fait-renaitre-les-produits-high-tech-vintages</t>
+          <t>https://www.numerama.com/tech/288962-guide-dachat-meilleur-iphone-a-acheter.html</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -4651,22 +4651,22 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>KultureGeek</t>
+          <t>Frandroid - Actualités</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-09-18T14:11:50+00:00</t>
+          <t>2026-09-18T14:15:06+00:00</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Motorola Signature 27 : un nouveau smartphone premium annoncé pour le 22 septembre, en pleine conférence Qualcomm</t>
+          <t>Muse fait renaître les produits high-tech vintages</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>https://kulturegeek.fr/news-359722/motorola-signature-27-nouveau-smartphone-premium-annonce-22-septembre-pleine-conference-qualcomm</t>
+          <t>https://www.frandroid.com/produits-android/audio/3253075_muse-fait-renaitre-les-produits-high-tech-vintages</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -4678,54 +4678,54 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>KultureGeek</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-09-18T14:05:16+00:00</t>
+          <t>2026-09-18T14:11:50+00:00</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Xiaomi se lâche complet : il pulvérise le prix du 17T Pro sans aucune explication 🤯</t>
+          <t>Motorola Signature 27 : un nouveau smartphone premium annoncé pour le 22 septembre, en pleine conférence Qualcomm</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>https://www.01net.com/bons-plans/xiaomi-pete-les-plombs-il-pulverise-le-prix-du-17t-pro-sans-aucune-explication.html</t>
+          <t>https://kulturegeek.fr/news-359722/motorola-signature-27-nouveau-smartphone-premium-annonce-22-septembre-pleine-conference-qualcomm</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>NON_CLASSE</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-09-18T14:02:09+00:00</t>
+          <t>2026-09-18T14:05:16+00:00</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Un sous-marin de la Première Guerre mondiale a été retrouvé : coulé en 1917, du TNT s’échappe de son épave</t>
+          <t>Xiaomi se lâche complet : il pulvérise le prix du 17T Pro sans aucune explication 🤯</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/18/sous-marin-premiere-guerre-mondiale-retrouve-1917-tnt-sechappe-epave/</t>
+          <t>https://www.01net.com/bons-plans/xiaomi-pete-les-plombs-il-pulverise-le-prix-du-17t-pro-sans-aucune-explication.html</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>8. Audio</t>
+          <t>NON_CLASSE</t>
         </is>
       </c>
     </row>
@@ -4737,17 +4737,17 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-09-18T14:02:08+00:00</t>
+          <t>2026-09-18T14:02:09+00:00</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>La série FarCry dévoile son casting, et les premiers noms sont prometteurs</t>
+          <t>Un sous-marin de la Première Guerre mondiale a été retrouvé : coulé en 1917, du TNT s’échappe de son épave</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/18/la-serie-farcry-devoile-son-casting-et-les-premiers-noms-sont-prometteurs/</t>
+          <t>https://www.journaldugeek.com/2026/09/18/sous-marin-premiere-guerre-mondiale-retrouve-1917-tnt-sechappe-epave/</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -4759,81 +4759,81 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>KultureGeek</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-09-18T14:01:37+00:00</t>
+          <t>2026-09-18T14:02:08+00:00</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Netflix devient le premier financeur privé de la production française</t>
+          <t>La série FarCry dévoile son casting, et les premiers noms sont prometteurs</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>https://kulturegeek.fr/news-359723/netflix-devient-premier-financeur-prive-production-francaise</t>
+          <t>https://www.journaldugeek.com/2026/09/18/la-serie-farcry-devoile-son-casting-et-les-premiers-noms-sont-prometteurs/</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>15. ludique</t>
+          <t>8. Audio</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>KultureGeek</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-09-18T14:01:08+00:00</t>
+          <t>2026-09-18T14:01:37+00:00</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>OpenAI a été piraté grâce à l’IA de son grand rival</t>
+          <t>Netflix devient le premier financeur privé de la production française</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>https://www.01net.com/actualites/openai-a-ete-pirate-grace-a-lia-de-son-grand-rival.html</t>
+          <t>https://kulturegeek.fr/news-359723/netflix-devient-premier-financeur-prive-production-francaise</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>6. IA</t>
+          <t>15. ludique</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Numerama</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-09-18T13:59:00+00:00</t>
+          <t>2026-09-18T14:01:08+00:00</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Le reboot Netflix de Narnia par la réalisatrice de Barbie déjà jugé woke par les fans</t>
+          <t>OpenAI a été piraté grâce à l’IA de son grand rival</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>https://www.numerama.com/tech/2335261-le-reboot-netflix-de-narnia-deja-juge-trop-woke-enrage-les-puristes.html</t>
+          <t>https://www.01net.com/actualites/openai-a-ete-pirate-grace-a-lia-de-son-grand-rival.html</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>15. ludique</t>
+          <t>6. IA</t>
         </is>
       </c>
     </row>
@@ -4845,103 +4845,103 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-09-18T13:48:20+00:00</t>
+          <t>2026-09-18T13:59:00+00:00</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Domino’s Pizza se moque de la lave « PS2 » de Marvel’s Wolverine</t>
+          <t>Le reboot Netflix de Narnia par la réalisatrice de Barbie déjà jugé woke par les fans</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>https://www.numerama.com/pop-culture/2335787-dominos-pizza-se-moque-de-la-lave-ps2-de-marvels-wolverine.html</t>
+          <t>https://www.numerama.com/tech/2335261-le-reboot-netflix-de-narnia-deja-juge-trop-woke-enrage-les-puristes.html</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>NON_CLASSE</t>
+          <t>15. ludique</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>Numerama</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-09-18T13:38:00+00:00</t>
+          <t>2026-09-18T13:48:20+00:00</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Actualité : Google simule un cerveau de mouche, un internaute l’utilise pour battre un célèbre jeu vidéo</t>
+          <t>Domino’s Pizza se moque de la lave « PS2 » de Marvel’s Wolverine</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/intelligence-artificielle/google-simule-un-cerveau-de-mouche-un-internaute-l-utilise-pour-battre-un-celebre-jeu-video-n262030.html</t>
+          <t>https://www.numerama.com/pop-culture/2335787-dominos-pizza-se-moque-de-la-lave-ps2-de-marvels-wolverine.html</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>7. Video</t>
+          <t>NON_CLASSE</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Numerama</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-09-18T13:36:27+00:00</t>
+          <t>2026-09-18T13:38:00+00:00</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Boulanger fait tomber le clavier Logitech MX Keys S sous la barre des 50 €</t>
+          <t>Actualité : Google simule un cerveau de mouche, un internaute l’utilise pour battre un célèbre jeu vidéo</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>https://www.numerama.com/tech/2335761-amazon-fait-tomber-le-clavier-logitech-mx-keys-s-sous-la-barre-des-50-e.html</t>
+          <t>https://www.lesnumeriques.com/intelligence-artificielle/google-simule-un-cerveau-de-mouche-un-internaute-l-utilise-pour-battre-un-celebre-jeu-video-n262030.html</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>3. Periphérique</t>
+          <t>7. Video</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Frandroid - Actualités</t>
+          <t>Numerama</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-09-18T13:33:53+00:00</t>
+          <t>2026-09-18T13:36:27+00:00</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Le Honor 700 Pro s’inspirerait de Xiaomi avec un écran au dos</t>
+          <t>Boulanger fait tomber le clavier Logitech MX Keys S sous la barre des 50 €</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/produits-android/3252413_le-futur-honor-700-pro-se-devoile-avec-un-ecran-secondaire-au-dos-et-un-capteur-de-200-megapixels</t>
+          <t>https://www.numerama.com/tech/2335761-amazon-fait-tomber-le-clavier-logitech-mx-keys-s-sous-la-barre-des-50-e.html</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>3. Periphérique</t>
         </is>
       </c>
     </row>
@@ -4953,76 +4953,76 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-09-18T13:22:10+00:00</t>
+          <t>2026-09-18T13:33:53+00:00</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Après Doom, un internaute entraîne le cerveau de mouche de Google à jouer à Balatro</t>
+          <t>Le Honor 700 Pro s’inspirerait de Xiaomi avec un écran au dos</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/culture-tech/3252303_apres-doom-ce-cerveau-de-mouche-modelise-par-google-gagne-maintenant-a-balatro</t>
+          <t>https://www.frandroid.com/produits-android/3252413_le-futur-honor-700-pro-se-devoile-avec-un-ecran-secondaire-au-dos-et-un-capteur-de-200-megapixels</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>NON_CLASSE</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>Frandroid - Actualités</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-09-18T13:20:32+00:00</t>
+          <t>2026-09-18T13:22:10+00:00</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Actualité : Voici le meilleur hub usb-c à prix abordable de notre comparatif</t>
+          <t>Après Doom, un internaute entraîne le cerveau de mouche de Google à jouer à Balatro</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/hub-usb-c/voici-le-meilleur-hub-usb-c-a-prix-abordable-de-notre-comparatif-n262028.html</t>
+          <t>https://www.frandroid.com/culture-tech/3252303_apres-doom-ce-cerveau-de-mouche-modelise-par-google-gagne-maintenant-a-balatro</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>3. Periphérique</t>
+          <t>NON_CLASSE</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Frandroid - Actualités</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-09-18T13:17:39+00:00</t>
+          <t>2026-09-18T13:20:32+00:00</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Vous passez 30 minutes à chercher quoi regarder ? Disney+ a enfin la solution</t>
+          <t>Actualité : Voici le meilleur hub usb-c à prix abordable de notre comparatif</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/services/svod/3252681_vous-passez-30-minutes-a-chercher-quoi-regarder-disney-a-enfin-la-solution</t>
+          <t>https://www.lesnumeriques.com/hub-usb-c/voici-le-meilleur-hub-usb-c-a-prix-abordable-de-notre-comparatif-n262028.html</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>15. ludique</t>
+          <t>3. Periphérique</t>
         </is>
       </c>
     </row>
@@ -5034,125 +5034,125 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-09-18T13:16:37+00:00</t>
+          <t>2026-09-18T13:17:39+00:00</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Huawei sonde ses utilisateurs sur un bracelet connecté sans écran, à la manière de Whoop</t>
+          <t>Vous passez 30 minutes à chercher quoi regarder ? Disney+ a enfin la solution</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/marques/huawei/3252849_huawei-sonde-ses-utilisateurs-sur-un-bracelet-connecte-sans-ecran-a-la-maniere-de-whoop</t>
+          <t>https://www.frandroid.com/services/svod/3252681_vous-passez-30-minutes-a-chercher-quoi-regarder-disney-a-enfin-la-solution</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>3. Periphérique</t>
+          <t>15. ludique</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>Frandroid - Actualités</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-09-18T13:02:48+00:00</t>
+          <t>2026-09-18T13:16:37+00:00</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>GTA 6 : la sortie du Online très attendu se précise pour 2027</t>
+          <t>Huawei sonde ses utilisateurs sur un bracelet connecté sans écran, à la manière de Whoop</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/18/gta-6-la-sortie-du-online-tres-attendu-se-precise-pour-2027/</t>
+          <t>https://www.frandroid.com/marques/huawei/3252849_huawei-sonde-ses-utilisateurs-sur-un-bracelet-connecte-sans-ecran-a-la-maniere-de-whoop</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>15. ludique</t>
+          <t>3. Periphérique</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-09-18T13:02:39+00:00</t>
+          <t>2026-09-18T13:02:48+00:00</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Copier-coller cassé dans Excel : Microsoft partage une bidouille pour contourner le bug</t>
+          <t>GTA 6 : la sortie du Online très attendu se précise pour 2027</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>https://www.01net.com/actualites/copier-coller-casse-dans-excel-microsoft-partage-une-bidouille-pour-contourner-le-bug.html</t>
+          <t>https://www.journaldugeek.com/2026/09/18/gta-6-la-sortie-du-online-tres-attendu-se-precise-pour-2027/</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>5. Logiciels _ OS</t>
+          <t>15. ludique</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Frandroid - Actualités</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-09-18T13:01:53+00:00</t>
+          <t>2026-09-18T13:02:39+00:00</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Monaco-Lens : comment voir le match d’ouverture de la 5e journée de Ligue 1 en direct et en streaming ?</t>
+          <t>Copier-coller cassé dans Excel : Microsoft partage une bidouille pour contourner le bug</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/produits-android/3252865_monaco-lens-comment-voir-le-match-douverture-de-la-5e-journee-de-ligue-1-en-direct-et-en-streaming</t>
+          <t>https://www.01net.com/actualites/copier-coller-casse-dans-excel-microsoft-partage-une-bidouille-pour-contourner-le-bug.html</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>5. Logiciels _ OS</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>Frandroid - Actualités</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-09-18T13:00:00+00:00</t>
+          <t>2026-09-18T13:01:53+00:00</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Test Xiaomi Redmi Note 17 5G : il n'est sauvé que par son autonomie</t>
+          <t>Monaco-Lens : comment voir le match d’ouverture de la 5e journée de Ligue 1 en direct et en streaming ?</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/telephone-portable/xiaomi-redmi-note-17-5g-p78893/test.html</t>
+          <t>https://www.frandroid.com/produits-android/3252865_monaco-lens-comment-voir-le-match-douverture-de-la-5e-journee-de-ligue-1-en-direct-et-en-streaming</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -5164,7 +5164,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Numerama</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -5174,24 +5174,24 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Test de Control Resonant, le nouveau chef-d’œuvre de Remedy</t>
+          <t>Test Xiaomi Redmi Note 17 5G : il n'est sauvé que par son autonomie</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>https://www.numerama.com/pop-culture/2335251-test-de-control-resonant-le-nouveau-chef-doeuvre-de-remedy.html</t>
+          <t>https://www.lesnumeriques.com/telephone-portable/xiaomi-redmi-note-17-5g-p78893/test.html</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>NON_CLASSE</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Korben</t>
+          <t>Numerama</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -5201,44 +5201,44 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Comment mesurer et dégonfler l'index de recherche de Windows</t>
+          <t>Test de Control Resonant, le nouveau chef-d’œuvre de Remedy</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>https://korben.info/windows-search-indexation-etendue-ssd.html</t>
+          <t>https://www.numerama.com/pop-culture/2335251-test-de-control-resonant-le-nouveau-chef-doeuvre-de-remedy.html</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>2. PC</t>
+          <t>NON_CLASSE</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Phonandroid</t>
+          <t>Korben</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-09-18T12:44:03+00:00</t>
+          <t>2026-09-18T13:00:00+00:00</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>AliExpress lance sa French Week et fait chuter les prix : voici les offres à saisir</t>
+          <t>Comment mesurer et dégonfler l'index de recherche de Windows</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>https://www.phonandroid.com/aliexpress-french-week-fait-chuter-prix-voici-offres-saisir.html</t>
+          <t>https://korben.info/windows-search-indexation-etendue-ssd.html</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>19. Sponso</t>
+          <t>2. PC</t>
         </is>
       </c>
     </row>
@@ -5250,265 +5250,265 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-09-18T12:39:25+00:00</t>
+          <t>2026-09-18T12:44:03+00:00</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>iPhone 18 Pro : Apple augmente le prix du remplacement de la batterie</t>
+          <t>AliExpress lance sa French Week et fait chuter les prix : voici les offres à saisir</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>https://www.phonandroid.com/iphone-18-pro-apple-augmente-le-prix-du-remplacement-de-la-batterie.html</t>
+          <t>https://www.phonandroid.com/aliexpress-french-week-fait-chuter-prix-voici-offres-saisir.html</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>19. Sponso</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Numerama</t>
+          <t>Phonandroid</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-09-18T12:37:21+00:00</t>
+          <t>2026-09-18T12:39:25+00:00</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Devinez quel personnage joue Madds mikkelsen dans le prochain Call of Duty</t>
+          <t>iPhone 18 Pro : Apple augmente le prix du remplacement de la batterie</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>https://www.numerama.com/pop-culture/2335755-devinez-quel-personnage-joue-madds-mikkelsen-dans-le-prochain-call-of-duty.html</t>
+          <t>https://www.phonandroid.com/iphone-18-pro-apple-augmente-le-prix-du-remplacement-de-la-batterie.html</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>NON_CLASSE</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Frandroid - Actualités</t>
+          <t>Numerama</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-09-18T12:30:50+00:00</t>
+          <t>2026-09-18T12:37:21+00:00</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>aptX, LDAC, SBC, LC3 : tout comprendre aux codecs Bluetooth audio</t>
+          <t>Devinez quel personnage joue Madds mikkelsen dans le prochain Call of Duty</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/comment-faire/comment-fonctionne-la-technologie/752329_aptx-ldac-sbc-tout-comprendre-aux-codecs-bluetooth-audio</t>
+          <t>https://www.numerama.com/pop-culture/2335755-devinez-quel-personnage-joue-madds-mikkelsen-dans-le-prochain-call-of-duty.html</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>8. Audio</t>
+          <t>NON_CLASSE</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>Frandroid - Actualités</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-09-18T12:30:11+00:00</t>
+          <t>2026-09-18T12:30:50+00:00</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Ce nouveau télescope de la NASA va chercher des milliers de planètes dans l’univers</t>
+          <t>aptX, LDAC, SBC, LC3 : tout comprendre aux codecs Bluetooth audio</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>https://www.01net.com/actualites/ce-nouveau-telescope-de-la-nasa-va-chercher-des-milliers-de-planetes-dans-lunivers.html</t>
+          <t>https://www.frandroid.com/comment-faire/comment-fonctionne-la-technologie/752329_aptx-ldac-sbc-tout-comprendre-aux-codecs-bluetooth-audio</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>18. Sciences</t>
+          <t>8. Audio</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Numerama</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-09-18T12:30:00+00:00</t>
+          <t>2026-09-18T12:30:11+00:00</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Le géant de la batterie CATL perd de son emprise sur les constructeurs chinois</t>
+          <t>Ce nouveau télescope de la NASA va chercher des milliers de planètes dans l’univers</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>https://www.numerama.com/vroom/2335713-le-geant-de-la-batterie-catl-perd-de-son-emprise-sur-les-constructeurs-chinois.html</t>
+          <t>https://www.01net.com/actualites/ce-nouveau-telescope-de-la-nasa-va-chercher-des-milliers-de-planetes-dans-lunivers.html</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>8. Audio</t>
+          <t>18. Sciences</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Frandroid - Actualités</t>
+          <t>Numerama</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-09-18T12:25:55+00:00</t>
+          <t>2026-09-18T12:30:00+00:00</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Moins de 800 kg et 110 km/h : à quoi ressemble la voiture électrique à 15 000 € qui pourrait bientôt déferler sur nos routes ?</t>
+          <t>Le géant de la batterie CATL perd de son emprise sur les constructeurs chinois</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/survoltes/3252389_moins-de-800-kg-et-110-km-h-a-quoi-ressemble-la-voiture-electrique-a-15-000-e-qui-pourrait-bientot-deferler-sur-nos-routes</t>
+          <t>https://www.numerama.com/vroom/2335713-le-geant-de-la-batterie-catl-perd-de-son-emprise-sur-les-constructeurs-chinois.html</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>10. Voiture</t>
+          <t>8. Audio</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>Frandroid - Actualités</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-09-18T12:16:00+00:00</t>
+          <t>2026-09-18T12:25:55+00:00</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Actualité : Le lave-linge Dreame Slim Washer S passe sous les 350 €</t>
+          <t>Moins de 800 kg et 110 km/h : à quoi ressemble la voiture électrique à 15 000 € qui pourrait bientôt déferler sur nos routes ?</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/lave-linge/le-lave-linge-dreame-slim-washer-s-passe-sous-les-350-n262024.html</t>
+          <t>https://www.frandroid.com/survoltes/3252389_moins-de-800-kg-et-110-km-h-a-quoi-ressemble-la-voiture-electrique-a-15-000-e-qui-pourrait-bientot-deferler-sur-nos-routes</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>11. Menage</t>
+          <t>10. Voiture</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Numerama</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-09-18T12:11:12+00:00</t>
+          <t>2026-09-18T12:16:00+00:00</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>25 000 taxis autonomes en Europe : Bolt et Lucid veulent couper l’herbe sous le pied à Waymo</t>
+          <t>Actualité : Le lave-linge Dreame Slim Washer S passe sous les 350 €</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>https://www.numerama.com/vroom/2335711-25-000-taxis-autonomes-en-europe-bolt-et-lucid-veulent-couper-lherbe-sous-le-pied-a-waymo.html</t>
+          <t>https://www.lesnumeriques.com/lave-linge/le-lave-linge-dreame-slim-washer-s-passe-sous-les-350-n262024.html</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>9. Moiilité douce</t>
+          <t>11. Menage</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>KultureGeek</t>
+          <t>Numerama</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-09-18T12:10:53+00:00</t>
+          <t>2026-09-18T12:11:12+00:00</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Mark Zuckerberg rejette l’idée de ralentir le développement de l’IA</t>
+          <t>25 000 taxis autonomes en Europe : Bolt et Lucid veulent couper l’herbe sous le pied à Waymo</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>https://kulturegeek.fr/news-359716/mark-zuckerberg-rejette-lidee-ralentir-developpement-lia</t>
+          <t>https://www.numerama.com/vroom/2335711-25-000-taxis-autonomes-en-europe-bolt-et-lucid-veulent-couper-lherbe-sous-le-pied-a-waymo.html</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>6. IA</t>
+          <t>9. Moiilité douce</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>KultureGeek</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-09-18T12:04:27+00:00</t>
+          <t>2026-09-18T12:10:53+00:00</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>iPhone 18 Pro et Pro Max : les premiers tests sont tombés, faut-il craquer ? Voici ce qu’il faut vraiment retenir</t>
+          <t>Mark Zuckerberg rejette l’idée de ralentir le développement de l’IA</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/18/iphone-18-pro-et-pro-max-les-premiers-tests-sont-tombes-faut-il-craquer-voici-ce-quil-faut-vraiment-retenir/</t>
+          <t>https://kulturegeek.fr/news-359716/mark-zuckerberg-rejette-lidee-ralentir-developpement-lia</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>6. IA</t>
         </is>
       </c>
     </row>
@@ -5520,71 +5520,71 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-09-18T11:35:34+00:00</t>
+          <t>2026-09-18T12:04:27+00:00</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Des chercheurs découvrent une nouvelle structure cruciale cachée dans nos cellules</t>
+          <t>iPhone 18 Pro et Pro Max : les premiers tests sont tombés, faut-il craquer ? Voici ce qu’il faut vraiment retenir</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/18/des-chercheurs-decouvrent-une-nouvelle-structure-cruciale-cachee-dans-nos-cellules/</t>
+          <t>https://www.journaldugeek.com/2026/09/18/iphone-18-pro-et-pro-max-les-premiers-tests-sont-tombes-faut-il-craquer-voici-ce-quil-faut-vraiment-retenir/</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>18. Sciences</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Numerama</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-09-18T11:30:00+00:00</t>
+          <t>2026-09-18T11:35:34+00:00</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Miami Vice 85  : après Michael B. Jordan et Austin Butler, le film pioche dans le casting de L’Odyssée</t>
+          <t>Des chercheurs découvrent une nouvelle structure cruciale cachée dans nos cellules</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>https://www.numerama.com/pop-culture/2335553-miami-vice-85-apres-michael-b-jordan-et-austin-butler-le-film-pioche-dans-le-casting-de-lodyssee.html</t>
+          <t>https://www.journaldugeek.com/2026/09/18/des-chercheurs-decouvrent-une-nouvelle-structure-cruciale-cachee-dans-nos-cellules/</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>15. ludique</t>
+          <t>18. Sciences</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>Numerama</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-09-18T11:20:00+00:00</t>
+          <t>2026-09-18T11:30:00+00:00</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Actualité : Disney+ continue d'empirer : de la publicité obligatoire arrive dans tous les abonnements</t>
+          <t>Miami Vice 85  : après Michael B. Jordan et Austin Butler, le film pioche dans le casting de L’Odyssée</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/cine-svod/disney-continue-d-empirer-de-la-publicite-obligatoire-arrive-dans-tous-les-abonnements-n262015.html</t>
+          <t>https://www.numerama.com/pop-culture/2335553-miami-vice-85-apres-michael-b-jordan-et-austin-butler-le-film-pioche-dans-le-casting-de-lodyssee.html</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -5596,297 +5596,297 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-09-18T11:10:49+00:00</t>
+          <t>2026-09-18T11:20:00+00:00</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Smartphones pliants : l’effet Apple est là, et Samsung en profite… deux fois</t>
+          <t>Actualité : Disney+ continue d'empirer : de la publicité obligatoire arrive dans tous les abonnements</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>https://www.01net.com/actualites/smartphones-pliants-leffet-apple-est-la-et-samsung-en-profite-deux-fois.html</t>
+          <t>https://www.lesnumeriques.com/cine-svod/disney-continue-d-empirer-de-la-publicite-obligatoire-arrive-dans-tous-les-abonnements-n262015.html</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>15. ludique</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Frandroid - Actualités</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-09-18T11:02:51+00:00</t>
+          <t>2026-09-18T11:10:49+00:00</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Galaxy S27 Ultra : après six ans d’attente, Samsung va enfin augmenter la batterie</t>
+          <t>Smartphones pliants : l’effet Apple est là, et Samsung en profite… deux fois</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/marques/samsung/3252641_galaxy-s27-ultra-apres-six-ans-dattente-samsung-va-enfin-augmenter-la-batterie</t>
+          <t>https://www.01net.com/actualites/smartphones-pliants-leffet-apple-est-la-et-samsung-en-profite-deux-fois.html</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>NON_CLASSE</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>Frandroid - Actualités</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-09-18T10:45:32+00:00</t>
+          <t>2026-09-18T11:02:51+00:00</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Mastercard offre des cartes bancaires aux IA pour dépenser votre argent</t>
+          <t>Galaxy S27 Ultra : après six ans d’attente, Samsung va enfin augmenter la batterie</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>https://www.01net.com/actualites/mastercard-offre-des-cartes-bancaires-aux-ia-pour-depenser-votre-argent.html</t>
+          <t>https://www.frandroid.com/marques/samsung/3252641_galaxy-s27-ultra-apres-six-ans-dattente-samsung-va-enfin-augmenter-la-batterie</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>6. IA</t>
+          <t>NON_CLASSE</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-09-18T10:44:00+00:00</t>
+          <t>2026-09-18T10:45:32+00:00</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Actualité : MobLand saison 2 : quand sortent les épisodes de la série sur Paramount+ ?</t>
+          <t>Mastercard offre des cartes bancaires aux IA pour dépenser votre argent</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/cine-svod/mobland-saison-2-quand-sortent-les-episodes-de-la-serie-sur-paramount-n262014.html</t>
+          <t>https://www.01net.com/actualites/mastercard-offre-des-cartes-bancaires-aux-ia-pour-depenser-votre-argent.html</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>15. ludique</t>
+          <t>6. IA</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>KultureGeek</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-09-18T10:41:49+00:00</t>
+          <t>2026-09-18T10:44:00+00:00</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Huawei accélère le lancement de sa puce IA Ascend 960DT pour concurrencer Nvidia dès 2027</t>
+          <t>Actualité : MobLand saison 2 : quand sortent les épisodes de la série sur Paramount+ ?</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>https://kulturegeek.fr/news-359713/huawei-accelere-lancement-puce-ia-ascend-960dt-concurrencer-nvidia-2027</t>
+          <t>https://www.lesnumeriques.com/cine-svod/mobland-saison-2-quand-sortent-les-episodes-de-la-serie-sur-paramount-n262014.html</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>2. PC</t>
+          <t>15. ludique</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>KultureGeek</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-09-18T10:33:23+00:00</t>
+          <t>2026-09-18T10:41:49+00:00</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Free débloque (enfin) cette fonction qui peut doubler le débit Wi-Fi de votre Freebox !</t>
+          <t>Huawei accélère le lancement de sa puce IA Ascend 960DT pour concurrencer Nvidia dès 2027</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/18/free-debloque-enfin-cette-fonction-qui-peut-doubler-le-debit-wi-fi-de-votre-freebox/</t>
+          <t>https://kulturegeek.fr/news-359713/huawei-accelere-lancement-puce-ia-ascend-960dt-concurrencer-nvidia-2027</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>3. Periphérique</t>
+          <t>2. PC</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Frandroid - Actualités</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-09-18T10:32:33+00:00</t>
+          <t>2026-09-18T10:33:23+00:00</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>L’iPhone 18 Pro est mieux refroidi que certains smartphones gaming, comme le démontrent ces tests</t>
+          <t>Free débloque (enfin) cette fonction qui peut doubler le débit Wi-Fi de votre Freebox !</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/produits-android/smartphone/3252289_liphone-18-pro-est-mieux-refroidi-que-les-meilleurs-smartphones-gaming-comme-le-demontrent-ces-tests</t>
+          <t>https://www.journaldugeek.com/2026/09/18/free-debloque-enfin-cette-fonction-qui-peut-doubler-le-debit-wi-fi-de-votre-freebox/</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>3. Periphérique</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Korben</t>
+          <t>Frandroid - Actualités</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-09-18T10:21:37+00:00</t>
+          <t>2026-09-18T10:32:33+00:00</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Calibre lance le livre dont vous êtes le héros, généré par IA</t>
+          <t>L’iPhone 18 Pro est mieux refroidi que certains smartphones gaming, comme le démontrent ces tests</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>https://korben.info/calibre-9-15-jeu-aventure-ia.html</t>
+          <t>https://www.frandroid.com/produits-android/smartphone/3252289_liphone-18-pro-est-mieux-refroidi-que-les-meilleurs-smartphones-gaming-comme-le-demontrent-ces-tests</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>4. Tablette</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>Korben</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-09-18T10:19:00+00:00</t>
+          <t>2026-09-18T10:21:37+00:00</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Actualité : Trois hackers ont utilisé Claude pour pirater OpenAI en 72 heures, et ils n'ont eu besoin que d'un abonnement</t>
+          <t>Calibre lance le livre dont vous êtes le héros, généré par IA</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/intelligence-artificielle/trois-hackers-ont-utilise-claude-pour-pirater-openai-en-72-heures-et-ils-n-ont-eu-besoin-que-d-un-abonnement-n262016.html</t>
+          <t>https://korben.info/calibre-9-15-jeu-aventure-ia.html</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>6. IA</t>
+          <t>4. Tablette</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-09-18T10:15:26+00:00</t>
+          <t>2026-09-18T10:19:00+00:00</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Disney+ fait une très mauvaise blague à ses abonnés en ajoutant de la pub sur toutes ses offres !</t>
+          <t>Actualité : Trois hackers ont utilisé Claude pour pirater OpenAI en 72 heures, et ils n'ont eu besoin que d'un abonnement</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/18/disney-fait-une-tres-mauvaise-blague-a-ses-abonnes-en-ajoutant-de-la-pub-sur-toutes-ses-offres/</t>
+          <t>https://www.lesnumeriques.com/intelligence-artificielle/trois-hackers-ont-utilise-claude-pour-pirater-openai-en-72-heures-et-ils-n-ont-eu-besoin-que-d-un-abonnement-n262016.html</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>15. ludique</t>
+          <t>6. IA</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-09-18T10:15:00+00:00</t>
+          <t>2026-09-18T10:15:26+00:00</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Actualité : Le câble USB-C vers Jack 6.35 (pour un ampli par ex.) est à 8.79 €</t>
+          <t>Disney+ fait une très mauvaise blague à ses abonnés en ajoutant de la pub sur toutes ses offres !</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/accessoire-audio/le-cable-usb-c-vers-jack-6-35-pour-un-ampli-par-ex-est-a-8-79-n262020.html</t>
+          <t>https://www.journaldugeek.com/2026/09/18/disney-fait-une-tres-mauvaise-blague-a-ses-abonnes-en-ajoutant-de-la-pub-sur-toutes-ses-offres/</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>3. Periphérique</t>
+          <t>15. ludique</t>
         </is>
       </c>
     </row>
@@ -5898,103 +5898,103 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-09-18T10:11:33+00:00</t>
+          <t>2026-09-18T10:15:00+00:00</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Actualité : Ces écouteurs sans fil présentent le meilleur rapport qualité / prix de notre comparatif</t>
+          <t>Actualité : Le câble USB-C vers Jack 6.35 (pour un ampli par ex.) est à 8.79 €</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/ecouteurs-sans-fil/ces-ecouteurs-sans-fil-presentent-le-meilleur-rapport-qualite-prix-de-notre-comparatif-n262019.html</t>
+          <t>https://www.lesnumeriques.com/accessoire-audio/le-cable-usb-c-vers-jack-6-35-pour-un-ampli-par-ex-est-a-8-79-n262020.html</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>8. Audio</t>
+          <t>3. Periphérique</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-09-18T10:05:56+00:00</t>
+          <t>2026-09-18T10:11:33+00:00</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Xiaomi 15T Pro : deal de FOLIE à saisir sur ce best-seller en puissance (-44%) ⚡️</t>
+          <t>Actualité : Ces écouteurs sans fil présentent le meilleur rapport qualité / prix de notre comparatif</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>https://www.01net.com/bons-plans/xiaomi-15t-pro-deal-de-folie-a-saisir-rapidement-sur-ce-best-seller-en-puissance.html</t>
+          <t>https://www.lesnumeriques.com/ecouteurs-sans-fil/ces-ecouteurs-sans-fil-presentent-le-meilleur-rapport-qualite-prix-de-notre-comparatif-n262019.html</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>NON_CLASSE</t>
+          <t>8. Audio</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-09-18T10:03:11+00:00</t>
+          <t>2026-09-18T10:05:56+00:00</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>25 000 véhicules vont débarquer dans plusieurs grandes villes européennes !</t>
+          <t>Xiaomi 15T Pro : deal de FOLIE à saisir sur ce best-seller en puissance (-44%) ⚡️</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/18/25-000-vehicules-vont-debarquer-dans-plusieurs-grandes-villes-europeennes/</t>
+          <t>https://www.01net.com/bons-plans/xiaomi-15t-pro-deal-de-folie-a-saisir-rapidement-sur-ce-best-seller-en-puissance.html</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>10. Voiture</t>
+          <t>NON_CLASSE</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Frandroid - Actualités</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-09-18T10:02:00+00:00</t>
+          <t>2026-09-18T10:03:11+00:00</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>En France comme à l’étranger, ce forfait mobile Bouygues Telecom 200 Go ne vous laissera jamais tomber</t>
+          <t>25 000 véhicules vont débarquer dans plusieurs grandes villes européennes !</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/telecom/forfait-mobile/3249431_en-france-comme-a-letranger-ce-forfait-mobile-bouygues-telecom-200-go-ne-vous-laissera-jamais-tomber</t>
+          <t>https://www.journaldugeek.com/2026/09/18/25-000-vehicules-vont-debarquer-dans-plusieurs-grandes-villes-europeennes/</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>10. Voiture</t>
         </is>
       </c>
     </row>
@@ -6006,260 +6006,260 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-09-18T10:00:18+00:00</t>
+          <t>2026-09-18T10:02:00+00:00</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Comment installer un SSD M.2 dans sa PS5 pour agrandir le stockage ? Notre tutoriel</t>
+          <t>En France comme à l’étranger, ce forfait mobile Bouygues Telecom 200 Go ne vous laissera jamais tomber</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/marques/sony/1077003_ps5-comment-installer-un-ssd-m-2-dans-la-console-et-transferer-ses-jeux</t>
+          <t>https://www.frandroid.com/telecom/forfait-mobile/3249431_en-france-comme-a-letranger-ce-forfait-mobile-bouygues-telecom-200-go-ne-vous-laissera-jamais-tomber</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>2. PC</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>Frandroid - Actualités</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-09-18T09:58:29+00:00</t>
+          <t>2026-09-18T10:00:18+00:00</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>L’iPhone 18 Pro est trop cher ? Vous n’êtes pas prêts pour la suite</t>
+          <t>Comment installer un SSD M.2 dans sa PS5 pour agrandir le stockage ? Notre tutoriel</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>https://www.01net.com/actualites/liphone-18-pro-est-trop-cher-vous-netes-pas-prets-pour-la-suite.html</t>
+          <t>https://www.frandroid.com/marques/sony/1077003_ps5-comment-installer-un-ssd-m-2-dans-la-console-et-transferer-ses-jeux</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>2. PC</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Frandroid - Actualités</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-09-18T09:57:26+00:00</t>
+          <t>2026-09-18T09:58:29+00:00</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>AMD s’apprêterait à augmenter de 10 % le prix de ses cartes graphiques et processeurs</t>
+          <t>L’iPhone 18 Pro est trop cher ? Vous n’êtes pas prêts pour la suite</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/marques/amd/3252391_amd-sappreterait-a-augmenter-de-10-le-prix-de-ses-cartes-graphiques-et-processeurs</t>
+          <t>https://www.01net.com/actualites/liphone-18-pro-est-trop-cher-vous-netes-pas-prets-pour-la-suite.html</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>2. PC</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>Frandroid - Actualités</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-09-18T09:53:00+00:00</t>
+          <t>2026-09-18T09:57:26+00:00</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Actualité : Freebox : Free exploite enfin pleinement les capacités Wi-Fi de ses box et répéteurs</t>
+          <t>AMD s’apprêterait à augmenter de 10 % le prix de ses cartes graphiques et processeurs</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/societe-numerique/freebox-free-exploite-enfin-pleinement-les-capacites-wi-fi-de-ses-box-et-repeteurs-n262009.html</t>
+          <t>https://www.frandroid.com/marques/amd/3252391_amd-sappreterait-a-augmenter-de-10-le-prix-de-ses-cartes-graphiques-et-processeurs</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>3. Periphérique</t>
+          <t>2. PC</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Frandroid - Actualités</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-09-18T09:49:45+00:00</t>
+          <t>2026-09-18T09:53:00+00:00</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>iPhone Duo Max : Apple pourrait muscler son jeu face au Samsung Galaxy Z Fold 8 Ultra</t>
+          <t>Actualité : Freebox : Free exploite enfin pleinement les capacités Wi-Fi de ses box et répéteurs</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/marques/apple/3251957_iphone-duo-max-apple-pourrait-muscler-son-jeu-face-au-samsung-galaxy-z-fold-8-ultra</t>
+          <t>https://www.lesnumeriques.com/societe-numerique/freebox-free-exploite-enfin-pleinement-les-capacites-wi-fi-de-ses-box-et-repeteurs-n262009.html</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>3. Periphérique</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>Frandroid - Actualités</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-09-18T09:49:43+00:00</t>
+          <t>2026-09-18T09:49:45+00:00</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Révolutionnez  le ménage chez vous : cet aspirateur robot tout-en-un est à -72%</t>
+          <t>iPhone Duo Max : Apple pourrait muscler son jeu face au Samsung Galaxy Z Fold 8 Ultra</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>https://www.01net.com/bons-plans/revolutionnez-le-menage-chez-vous-cet-aspirateur-robot-tout-en-un-est-a-72.html</t>
+          <t>https://www.frandroid.com/marques/apple/3251957_iphone-duo-max-apple-pourrait-muscler-son-jeu-face-au-samsung-galaxy-z-fold-8-ultra</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>11. Menage</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Frandroid - Actualités</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-09-18T09:45:25+00:00</t>
+          <t>2026-09-18T09:49:43+00:00</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>PS5 Slim ou PS5 Pro : quelle PS5 choisir ?</t>
+          <t>Révolutionnez  le ménage chez vous : cet aspirateur robot tout-en-un est à -72%</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/marques/sony/767530_ps5-ou-ps5-digital-edition-quel-modele-choisir</t>
+          <t>https://www.01net.com/bons-plans/revolutionnez-le-menage-chez-vous-cet-aspirateur-robot-tout-en-un-est-a-72.html</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>7. Video</t>
+          <t>11. Menage</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>Frandroid - Actualités</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-09-18T09:30:51+00:00</t>
+          <t>2026-09-18T09:45:25+00:00</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Le retour de la canicule dès la semaine prochaine ? Une nouvelle vague de chaleur annoncée pour fin septembre et au-delà</t>
+          <t>PS5 Slim ou PS5 Pro : quelle PS5 choisir ?</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/18/le-retour-de-la-canicule-des-la-semaine-prochaine-une-nouvelle-vague-de-chaleur-annoncee-pour-fin-septembre-et-au-dela/</t>
+          <t>https://www.frandroid.com/marques/sony/767530_ps5-ou-ps5-digital-edition-quel-modele-choisir</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>NON_CLASSE</t>
+          <t>7. Video</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-09-18T09:30:13+00:00</t>
+          <t>2026-09-18T09:30:51+00:00</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>iPhone 18 Pro, Apple Watch 12, AirPods 5… :  une mise à jour obligatoire vous attend dès le déballage</t>
+          <t>Le retour de la canicule dès la semaine prochaine ? Une nouvelle vague de chaleur annoncée pour fin septembre et au-delà</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>https://www.01net.com/actualites/iphone-18-pro-apple-watch-12-airpods-5-mise-jour-obligatoire-attend-deballage.html</t>
+          <t>https://www.journaldugeek.com/2026/09/18/le-retour-de-la-canicule-des-la-semaine-prochaine-une-nouvelle-vague-de-chaleur-annoncee-pour-fin-septembre-et-au-dela/</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>NON_CLASSE</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-09-18T09:30:00+00:00</t>
+          <t>2026-09-18T09:30:13+00:00</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Bitdefender Premium Security : comment repérer les deepfakes et éviter les arnaques ?</t>
+          <t>iPhone 18 Pro, Apple Watch 12, AirPods 5… :  une mise à jour obligatoire vous attend dès le déballage</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/appli-logiciel/bitdefender-premium-security-comment-reperer-les-deepfakes-et-eviter-les-arnaques-na262018.html</t>
+          <t>https://www.01net.com/actualites/iphone-18-pro-apple-watch-12-airpods-5-mise-jour-obligatoire-attend-deballage.html</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -6271,54 +6271,54 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-09-18T09:20:28+00:00</t>
+          <t>2026-09-18T09:30:00+00:00</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Mauvaise nouvelle si vous achetez des livres sur Amazon</t>
+          <t>Bitdefender Premium Security : comment repérer les deepfakes et éviter les arnaques ?</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>https://www.01net.com/actualites/amazon-met-fin-livraison-gratuite-livres-dans-lockers.html</t>
+          <t>https://www.lesnumeriques.com/appli-logiciel/bitdefender-premium-security-comment-reperer-les-deepfakes-et-eviter-les-arnaques-na262018.html</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>4. Tablette</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-09-18T09:20:00+00:00</t>
+          <t>2026-09-18T09:20:28+00:00</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Actualité : Narnia : des premières images magiques pour le blockbuster Netflix signé Greta Gerwig</t>
+          <t>Mauvaise nouvelle si vous achetez des livres sur Amazon</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/cine-svod/narnia-des-premieres-images-magiques-pour-le-blockbuster-netflix-signe-greta-gerwig-n262013.html</t>
+          <t>https://www.01net.com/actualites/amazon-met-fin-livraison-gratuite-livres-dans-lockers.html</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>7. Video</t>
+          <t>4. Tablette</t>
         </is>
       </c>
     </row>
@@ -6330,125 +6330,125 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-09-18T09:19:00+00:00</t>
+          <t>2026-09-18T09:20:00+00:00</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Actualité : Un astéroïde grand comme un immeuble de trois à six étages s’est écrasé sur la Lune : voici l’incroyable cratère géant découvert par la NASA</t>
+          <t>Actualité : Narnia : des premières images magiques pour le blockbuster Netflix signé Greta Gerwig</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/vers-la-lune/un-asteroide-grand-comme-un-immeuble-de-trois-a-six-etages-s-est-ecrase-sur-la-lune-voici-l-incroyable-cratere-geant-decouvert-par-la-nasa-n262017.html</t>
+          <t>https://www.lesnumeriques.com/cine-svod/narnia-des-premieres-images-magiques-pour-le-blockbuster-netflix-signe-greta-gerwig-n262013.html</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>18. Sciences</t>
+          <t>7. Video</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>KultureGeek</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-09-18T09:15:00+00:00</t>
+          <t>2026-09-18T09:19:00+00:00</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Intelligence artificielle et emploi : près de la moitié de la population anticipe des suppressions massives de postes selon une étude</t>
+          <t>Actualité : Un astéroïde grand comme un immeuble de trois à six étages s’est écrasé sur la Lune : voici l’incroyable cratère géant découvert par la NASA</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>https://kulturegeek.fr/news-359700/intelligence-artificielle-emploi-pres-moitie-population-anticipe-suppressions-massives-postes-etude</t>
+          <t>https://www.lesnumeriques.com/vers-la-lune/un-asteroide-grand-comme-un-immeuble-de-trois-a-six-etages-s-est-ecrase-sur-la-lune-voici-l-incroyable-cratere-geant-decouvert-par-la-nasa-n262017.html</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>6. IA</t>
+          <t>18. Sciences</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>KultureGeek</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-09-18T09:03:28+00:00</t>
+          <t>2026-09-18T09:15:00+00:00</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Cette prime promise par EDF à l’achat d’une BYD met le feu aux poudres au gouvernement !</t>
+          <t>Intelligence artificielle et emploi : près de la moitié de la population anticipe des suppressions massives de postes selon une étude</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/18/cette-prime-promise-par-edf-a-lachat-dune-byd-met-le-feu-aux-poudres-au-gouvernement/</t>
+          <t>https://kulturegeek.fr/news-359700/intelligence-artificielle-emploi-pres-moitie-population-anticipe-suppressions-massives-postes-etude</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>10. Voiture</t>
+          <t>6. IA</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-09-18T09:03:08+00:00</t>
+          <t>2026-09-18T09:03:28+00:00</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>La Redmi Pad 2 est vendue une misère : Xiaomi vide le stock et la fait à -65%</t>
+          <t>Cette prime promise par EDF à l’achat d’une BYD met le feu aux poudres au gouvernement !</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>https://www.01net.com/bons-plans/la-redmi-pad-2-est-vendue-une-misere-xiaomi-vide-le-stock-et-la-fait-a-65.html</t>
+          <t>https://www.journaldugeek.com/2026/09/18/cette-prime-promise-par-edf-a-lachat-dune-byd-met-le-feu-aux-poudres-au-gouvernement/</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>10. Voiture</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-09-18T08:56:00+00:00</t>
+          <t>2026-09-18T09:03:08+00:00</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Actualité : Adieu Microsoft Office : ce logiciel open source et 100 % européen arrive enfin sur ordinateur pour chasser Word et Excel</t>
+          <t>La Redmi Pad 2 est vendue une misère : Xiaomi vide le stock et la fait à -65%</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/appli-logiciel/adieu-microsoft-office-ce-logiciel-open-source-et-100-europeen-arrive-enfin-sur-ordinateur-pour-chasser-word-et-excel-n262008.html</t>
+          <t>https://www.01net.com/bons-plans/la-redmi-pad-2-est-vendue-une-misere-xiaomi-vide-le-stock-et-la-fait-a-65.html</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -6460,297 +6460,297 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-09-18T08:35:03+00:00</t>
+          <t>2026-09-18T08:56:00+00:00</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Euro Office : l’alternative européenne à Microsoft Office arrive sur Windows, macOS et Linux</t>
+          <t>Actualité : Adieu Microsoft Office : ce logiciel open source et 100 % européen arrive enfin sur ordinateur pour chasser Word et Excel</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>https://www.01net.com/actualites/euro-office-lalternative-europeenne-a-microsoft-office-arrive-sur-windows-macos-et-linux.html</t>
+          <t>https://www.lesnumeriques.com/appli-logiciel/adieu-microsoft-office-ce-logiciel-open-source-et-100-europeen-arrive-enfin-sur-ordinateur-pour-chasser-word-et-excel-n262008.html</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>5. Logiciels _ OS</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-09-18T08:31:00+00:00</t>
+          <t>2026-09-18T08:35:03+00:00</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Actualité : Fusion nucléaire : des chercheurs génèrent des rayons X aussi brillants qu'une étoile et jamais vus sur Terre</t>
+          <t>Euro Office : l’alternative européenne à Microsoft Office arrive sur Windows, macOS et Linux</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/concept/fusion-nucleaire-des-chercheurs-generent-des-rayons-x-aussi-brillants-qu-une-etoile-et-jamais-vus-sur-terre-n262003.html</t>
+          <t>https://www.01net.com/actualites/euro-office-lalternative-europeenne-a-microsoft-office-arrive-sur-windows-macos-et-linux.html</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>17. Actualité éco</t>
+          <t>5. Logiciels _ OS</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-09-18T08:30:23+00:00</t>
+          <t>2026-09-18T08:31:00+00:00</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Extension Pokémon 30 ans : les magasins ont-ils le droit de desceller les cartes pour éviter les scalpers ?</t>
+          <t>Actualité : Fusion nucléaire : des chercheurs génèrent des rayons X aussi brillants qu'une étoile et jamais vus sur Terre</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/18/extension-pokemon-30-ans-les-magasins-ont-ils-le-droit-de-desceller-les-cartes-pour-eviter-les-scalpers/</t>
+          <t>https://www.lesnumeriques.com/concept/fusion-nucleaire-des-chercheurs-generent-des-rayons-x-aussi-brillants-qu-une-etoile-et-jamais-vus-sur-terre-n262003.html</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>15. ludique</t>
+          <t>17. Actualité éco</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Korben</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-09-18T08:27:24+00:00</t>
+          <t>2026-09-18T08:30:23+00:00</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Linux sur PS5 Pro n'arrivera pas tout de suite</t>
+          <t>Extension Pokémon 30 ans : les magasins ont-ils le droit de desceller les cartes pour éviter les scalpers ?</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>https://korben.info/ps5-linux-developpeur-principal-abandonne.html</t>
+          <t>https://www.journaldugeek.com/2026/09/18/extension-pokemon-30-ans-les-magasins-ont-ils-le-droit-de-desceller-les-cartes-pour-eviter-les-scalpers/</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>5. Logiciels _ OS</t>
+          <t>15. ludique</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>Korben</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-09-18T08:16:02+00:00</t>
+          <t>2026-09-18T08:27:24+00:00</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Quelle est la valeur de votre vieille console Nintendo en 2026 ? Le classement des 10 modèles les plus côtés</t>
+          <t>Linux sur PS5 Pro n'arrivera pas tout de suite</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/18/quelle-est-la-valeur-de-votre-vieille-console-nintendo/</t>
+          <t>https://korben.info/ps5-linux-developpeur-principal-abandonne.html</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>15. ludique</t>
+          <t>5. Logiciels _ OS</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-09-18T08:08:19+00:00</t>
+          <t>2026-09-18T08:16:02+00:00</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Google Keep change le design d’un de ses widgets de la meilleure des manières</t>
+          <t>Quelle est la valeur de votre vieille console Nintendo en 2026 ? Le classement des 10 modèles les plus côtés</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>https://www.01net.com/actualites/google-keep-change-design-widgets-meilleures-des-manieres.html</t>
+          <t>https://www.journaldugeek.com/2026/09/18/quelle-est-la-valeur-de-votre-vieille-console-nintendo/</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>5. Logiciels _ OS</t>
+          <t>15. ludique</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Korben</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-09-18T08:07:06+00:00</t>
+          <t>2026-09-18T08:08:19+00:00</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Mes 2 nouveaux interrupteurs Sonoff Zigbee</t>
+          <t>Google Keep change le design d’un de ses widgets de la meilleure des manières</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>https://korben.info/sonoff-volet-lumiere-zigbee-bureau.html</t>
+          <t>https://www.01net.com/actualites/google-keep-change-design-widgets-meilleures-des-manieres.html</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>12. Cuisine</t>
+          <t>5. Logiciels _ OS</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>Korben</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-09-18T08:04:00+00:00</t>
+          <t>2026-09-18T08:07:06+00:00</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Actualité : Bon plan – Le répéteur Wifi Huawei WiFi Mesh 3 Pack de 3 à 119,99 € (-38%)</t>
+          <t>Mes 2 nouveaux interrupteurs Sonoff Zigbee</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/repeteurs-wi-fi/bon-plan-le-repeteur-wifi-huawei-wifi-mesh-3-pack-de-3-a-119-99-38-n262007.html</t>
+          <t>https://korben.info/sonoff-volet-lumiere-zigbee-bureau.html</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>3. Periphérique</t>
+          <t>12. Cuisine</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-09-18T08:02:22+00:00</t>
+          <t>2026-09-18T08:04:00+00:00</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Un roman inédit de Tolkien sort en France, 80 ans après sa création</t>
+          <t>Actualité : Bon plan – Le répéteur Wifi Huawei WiFi Mesh 3 Pack de 3 à 119,99 € (-38%)</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/18/un-roman-inedit-de-tolkien-sort-en-france-80-ans-apres-sa-creation/</t>
+          <t>https://www.lesnumeriques.com/repeteurs-wi-fi/bon-plan-le-repeteur-wifi-huawei-wifi-mesh-3-pack-de-3-a-119-99-38-n262007.html</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>NON_CLASSE</t>
+          <t>3. Periphérique</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-09-18T08:00:00+00:00</t>
+          <t>2026-09-18T08:02:22+00:00</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>SharkNinja Crispi DualZone, un Airfryer avec deux compartiments pour préparer un repas complet en une seule fois</t>
+          <t>Un roman inédit de Tolkien sort en France, 80 ans après sa création</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/electromenager/sharkninja-crispi-dualzone-un-airfryer-avec-deux-compartiments-pour-preparer-un-repas-complet-en-une-seule-fois-na261964.html</t>
+          <t>https://www.journaldugeek.com/2026/09/18/un-roman-inedit-de-tolkien-sort-en-france-80-ans-apres-sa-creation/</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>12. Cuisine</t>
+          <t>NON_CLASSE</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>KultureGeek</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-09-18T07:53:40+00:00</t>
+          <t>2026-09-18T08:00:00+00:00</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Claude dirige déjà 26 % de la recherche d’Anthropic sur ses prochaines IA</t>
+          <t>SharkNinja Crispi DualZone, un Airfryer avec deux compartiments pour préparer un repas complet en une seule fois</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>https://kulturegeek.fr/news-359684/claude-dirige-26-recherche-anthropic-prochaines-ia</t>
+          <t>https://www.lesnumeriques.com/electromenager/sharkninja-crispi-dualzone-un-airfryer-avec-deux-compartiments-pour-preparer-un-repas-complet-en-une-seule-fois-na261964.html</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>6. IA</t>
+          <t>12. Cuisine</t>
         </is>
       </c>
     </row>
@@ -6762,125 +6762,125 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026-09-18T07:38:12+00:00</t>
+          <t>2026-09-18T07:53:40+00:00</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Lunettes connectées : le parquet de Paris ouvre une enquête après des vidéos filmées sans consentement</t>
+          <t>Claude dirige déjà 26 % de la recherche d’Anthropic sur ses prochaines IA</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>https://kulturegeek.fr/news-359682/lunettes-connectees-parquet-paris-enquete-videos-consentement</t>
+          <t>https://kulturegeek.fr/news-359684/claude-dirige-26-recherche-anthropic-prochaines-ia</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>6. IA</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>KultureGeek</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2026-09-18T07:31:55+00:00</t>
+          <t>2026-09-18T07:38:12+00:00</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Les premières images de Narnia : Le Neveu du magicien sont là et elles risquent de ne pas vous plaire !</t>
+          <t>Lunettes connectées : le parquet de Paris ouvre une enquête après des vidéos filmées sans consentement</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/18/premieres-images-narnia-le-neveu-du-magicien-film-netflix/</t>
+          <t>https://kulturegeek.fr/news-359682/lunettes-connectees-parquet-paris-enquete-videos-consentement</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>7. Video</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2026-09-18T07:14:16+00:00</t>
+          <t>2026-09-18T07:31:55+00:00</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Revolut : après la fuite de données, une arnaque redoutable vise les clients</t>
+          <t>Les premières images de Narnia : Le Neveu du magicien sont là et elles risquent de ne pas vous plaire !</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>https://www.01net.com/actualites/revolut-apres-fuite-donnees-arnaque-redoutable-vise-clients.html</t>
+          <t>https://www.journaldugeek.com/2026/09/18/premieres-images-narnia-le-neveu-du-magicien-film-netflix/</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>16. actu jur et pol</t>
+          <t>7. Video</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>01net</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2026-09-18T07:06:18+00:00</t>
+          <t>2026-09-18T07:14:16+00:00</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Bornes de recharges : voici ce qui change pour les voitures électriques dès le 1er janvier 2027</t>
+          <t>Revolut : après la fuite de données, une arnaque redoutable vise les clients</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/18/bornes-de-recharges-voici-ce-qui-change-pour-les-voitures-electriques-des-le-1er-janvier-2027/</t>
+          <t>https://www.01net.com/actualites/revolut-apres-fuite-donnees-arnaque-redoutable-vise-clients.html</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>10. Voiture</t>
+          <t>16. actu jur et pol</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2026-09-18T07:00:00+00:00</t>
+          <t>2026-09-18T07:06:18+00:00</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Repérer la marque automobile au système de navigation le plus fluide : 6 démonstrations en concession</t>
+          <t>Bornes de recharges : voici ce qui change pour les voitures électriques dès le 1er janvier 2027</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/traceurs-gps/reperer-la-marque-automobile-au-systeme-de-navigation-le-plus-fluide-6-demonstrations-en-concession-na262029.html</t>
+          <t>https://www.journaldugeek.com/2026/09/18/bornes-de-recharges-voici-ce-qui-change-pour-les-voitures-electriques-des-le-1er-janvier-2027/</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -6892,54 +6892,54 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>TomsHardware</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2026-09-18T06:55:00+00:00</t>
+          <t>2026-09-18T07:00:00+00:00</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Les premières cartes mères Z990 en vue ? Six modèles en préparation chez ASRock</t>
+          <t>Repérer la marque automobile au système de navigation le plus fluide : 6 démonstrations en concession</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.fr/les-premieres-cartes-meres-z990-en-vue-six-modeles-en-preparation-chez-asrock/</t>
+          <t>https://www.lesnumeriques.com/traceurs-gps/reperer-la-marque-automobile-au-systeme-de-navigation-le-plus-fluide-6-demonstrations-en-concession-na262029.html</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>2. PC</t>
+          <t>10. Voiture</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>TomsHardware</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2026-09-18T06:38:02+00:00</t>
+          <t>2026-09-18T06:55:00+00:00</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Des avions vont changer d’altitude pour tenter d’effacer leurs traînées du ciel</t>
+          <t>Les premières cartes mères Z990 en vue ? Six modèles en préparation chez ASRock</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/18/des-avions-vont-changer-daltitude-pour-tenter-deffacer-leurs-trainees-du-ciel/</t>
+          <t>https://www.tomshardware.fr/les-premieres-cartes-meres-z990-en-vue-six-modeles-en-preparation-chez-asrock/</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>9. Moiilité douce</t>
+          <t>2. PC</t>
         </is>
       </c>
     </row>
@@ -6951,22 +6951,22 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>2026-09-18T06:37:59+00:00</t>
+          <t>2026-09-18T06:38:02+00:00</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Bose s’ouvre encore plus avec deux nouveautés oreilles libres</t>
+          <t>Des avions vont changer d’altitude pour tenter d’effacer leurs traînées du ciel</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/18/bose-souvre-encore-plus-avec-deux-nouveautes-oreilles-libres/</t>
+          <t>https://www.journaldugeek.com/2026/09/18/des-avions-vont-changer-daltitude-pour-tenter-deffacer-leurs-trainees-du-ciel/</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>8. Audio</t>
+          <t>9. Moiilité douce</t>
         </is>
       </c>
     </row>
@@ -6978,184 +6978,184 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>2026-09-18T06:32:17+00:00</t>
+          <t>2026-09-18T06:37:59+00:00</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Claude fait le ménage dans ses onglets en fusionnant le chat et Cowork</t>
+          <t>Bose s’ouvre encore plus avec deux nouveautés oreilles libres</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/18/claude-fait-le-menage-dans-ses-onglets-en-fusionnant-le-chat-et-cowork/</t>
+          <t>https://www.journaldugeek.com/2026/09/18/bose-souvre-encore-plus-avec-deux-nouveautes-oreilles-libres/</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>5. Logiciels _ OS</t>
+          <t>8. Audio</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>TomsHardware</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>2026-09-18T06:30:00+00:00</t>
+          <t>2026-09-18T06:32:17+00:00</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Windows 11, Office, Gemini… équipez votre PC à moindre coût en 2026</t>
+          <t>Claude fait le ménage dans ses onglets en fusionnant le chat et Cowork</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.fr/windows-11-office-gemini-equipez-votre-pc-a-moindre-cout-en-2026/</t>
+          <t>https://www.journaldugeek.com/2026/09/18/claude-fait-le-menage-dans-ses-onglets-en-fusionnant-le-chat-et-cowork/</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>2. PC</t>
+          <t>5. Logiciels _ OS</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>JournalDuGeek</t>
+          <t>TomsHardware</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2026-09-18T06:03:54+00:00</t>
+          <t>2026-09-18T06:30:00+00:00</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Google Home ouvre la porte aux agents IA… avec un sérieux avertissement</t>
+          <t>Windows 11, Office, Gemini… équipez votre PC à moindre coût en 2026</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>https://www.journaldugeek.com/2026/09/18/google-home-ouvre-la-porte-aux-agents-ia-avec-un-serieux-avertissement/</t>
+          <t>https://www.tomshardware.fr/windows-11-office-gemini-equipez-votre-pc-a-moindre-cout-en-2026/</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>6. IA</t>
+          <t>2. PC</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>TomsHardware</t>
+          <t>JournalDuGeek</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>2026-09-18T04:48:00+00:00</t>
+          <t>2026-09-18T06:03:54+00:00</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Pour les 13 ans de GTA 5, un moddeur met à jour le plugin NaturalVision</t>
+          <t>Google Home ouvre la porte aux agents IA… avec un sérieux avertissement</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.fr/pour-les-13-ans-de-gta-5-un-moddeur-met-a-jour-le-plugin-naturalvision/</t>
+          <t>https://www.journaldugeek.com/2026/09/18/google-home-ouvre-la-porte-aux-agents-ia-avec-un-serieux-avertissement/</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>15. ludique</t>
+          <t>6. IA</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Korben</t>
+          <t>TomsHardware</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2026-09-17T15:15:41+00:00</t>
+          <t>2026-09-18T04:48:00+00:00</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Fugleramme - Le cadre qui dessine les oiseaux qu'il entend</t>
+          <t>Pour les 13 ans de GTA 5, un moddeur met à jour le plugin NaturalVision</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>https://korben.info/fugleramme-detection-oiseaux-eink.html</t>
+          <t>https://www.tomshardware.fr/pour-les-13-ans-de-gta-5-un-moddeur-met-a-jour-le-plugin-naturalvision/</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>NON_CLASSE</t>
+          <t>15. ludique</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>TomsHardware</t>
+          <t>Korben</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2026-09-17T15:01:00+00:00</t>
+          <t>2026-09-17T15:15:41+00:00</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>SteamOS : Valve s’attaque à la prise en charge des cartes Nvidia, un chantier de plusieurs années</t>
+          <t>Fugleramme - Le cadre qui dessine les oiseaux qu'il entend</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.fr/steamos-valve-sattaque-a-la-prise-en-charge-des-cartes-nvidia-un-chantier-de-plusieurs-annees/</t>
+          <t>https://korben.info/fugleramme-detection-oiseaux-eink.html</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>2. PC</t>
+          <t>NON_CLASSE</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Korben</t>
+          <t>TomsHardware</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2026-09-17T14:56:31+00:00</t>
+          <t>2026-09-17T15:01:00+00:00</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>MechaCon - La puce qui condamnait les PS2 enfin hackée</t>
+          <t>SteamOS : Valve s’attaque à la prise en charge des cartes Nvidia, un chantier de plusieurs années</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>https://korben.info/mechacon-ps2-craque-retro-ingenierie.html</t>
+          <t>https://www.tomshardware.fr/steamos-valve-sattaque-a-la-prise-en-charge-des-cartes-nvidia-un-chantier-de-plusieurs-annees/</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>NON_CLASSE</t>
+          <t>2. PC</t>
         </is>
       </c>
     </row>
@@ -7167,22 +7167,22 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>2026-09-17T13:40:30+00:00</t>
+          <t>2026-09-17T14:56:31+00:00</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Des agents IA spamment le web pour payer leurs propres serveurs</t>
+          <t>MechaCon - La puce qui condamnait les PS2 enfin hackée</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>https://korben.info/des-agents-ia-spamment-le-web-pour-payer-leurs-propres-serveurs.html</t>
+          <t>https://korben.info/mechacon-ps2-craque-retro-ingenierie.html</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>2. PC</t>
+          <t>NON_CLASSE</t>
         </is>
       </c>
     </row>
@@ -7194,22 +7194,22 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>2026-09-17T13:26:03+00:00</t>
+          <t>2026-09-17T13:40:30+00:00</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Google Home laisse ChatGPT et Claude piloter votre maison</t>
+          <t>Des agents IA spamment le web pour payer leurs propres serveurs</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>https://korben.info/google-home-laisse-chatgpt-et-claude-piloter-votre-maison.html</t>
+          <t>https://korben.info/des-agents-ia-spamment-le-web-pour-payer-leurs-propres-serveurs.html</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>6. IA</t>
+          <t>2. PC</t>
         </is>
       </c>
     </row>
@@ -7221,17 +7221,17 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>2026-09-17T11:20:32+00:00</t>
+          <t>2026-09-17T13:26:03+00:00</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Cloudflare lance son skill d'audit de sécurité par IA</t>
+          <t>Google Home laisse ChatGPT et Claude piloter votre maison</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>https://korben.info/cloudflare-security-audit-skill.html</t>
+          <t>https://korben.info/google-home-laisse-chatgpt-et-claude-piloter-votre-maison.html</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -7243,27 +7243,27 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>TomsHardware</t>
+          <t>Korben</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>2026-09-17T10:11:00+00:00</t>
+          <t>2026-09-17T11:20:32+00:00</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Faire évoluer son installation solaire : comment ajouter une batterie sans tout changer ?</t>
+          <t>Cloudflare lance son skill d'audit de sécurité par IA</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.fr/faire-evoluer-son-installation-solaire-comment-ajouter-une-batterie-sans-tout-changer/</t>
+          <t>https://korben.info/cloudflare-security-audit-skill.html</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>8. Audio</t>
+          <t>6. IA</t>
         </is>
       </c>
     </row>
@@ -7275,22 +7275,22 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>2026-09-17T06:35:00+00:00</t>
+          <t>2026-09-17T10:11:00+00:00</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Smart Window, la fonctionnalité IA de Firefox, arrive en France avec Mistral</t>
+          <t>Faire évoluer son installation solaire : comment ajouter une batterie sans tout changer ?</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.fr/smart-window-la-fonctionnalite-ia-de-firefox-arrive-en-france-avec-mistral/</t>
+          <t>https://www.tomshardware.fr/faire-evoluer-son-installation-solaire-comment-ajouter-une-batterie-sans-tout-changer/</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>5. Logiciels _ OS</t>
+          <t>8. Audio</t>
         </is>
       </c>
     </row>
@@ -7302,22 +7302,22 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>2026-09-17T05:34:00+00:00</t>
+          <t>2026-09-17T06:35:00+00:00</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Microsoft Edge peut planter si vous utilisez certaines applications</t>
+          <t>Smart Window, la fonctionnalité IA de Firefox, arrive en France avec Mistral</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.fr/microsoft-edge-peut-planter-si-vous-utilisez-certaines-applications/</t>
+          <t>https://www.tomshardware.fr/smart-window-la-fonctionnalite-ia-de-firefox-arrive-en-france-avec-mistral/</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>5. Logiciels _ OS</t>
         </is>
       </c>
     </row>
@@ -7329,49 +7329,49 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2026-09-16T15:05:00+00:00</t>
+          <t>2026-09-17T05:34:00+00:00</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Le prix de ce clavier SteelSeries chute sur Amazon, c’est le moment d’en profiter</t>
+          <t>Microsoft Edge peut planter si vous utilisez certaines applications</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.fr/le-prix-de-ce-clavier-steelseries-chute-sur-amazon-cest-le-moment-den-profiter/</t>
+          <t>https://www.tomshardware.fr/microsoft-edge-peut-planter-si-vous-utilisez-certaines-applications/</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>3. Periphérique</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Korben</t>
+          <t>TomsHardware</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2026-09-16T13:33:01+00:00</t>
+          <t>2026-09-16T15:05:00+00:00</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Shuffle Drummer - FL Studio n'a qu'à bien se tenir</t>
+          <t>Le prix de ce clavier SteelSeries chute sur Amazon, c’est le moment d’en profiter</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>https://korben.info/shuffle-drummer-groovebox-navigateur.html</t>
+          <t>https://www.tomshardware.fr/le-prix-de-ce-clavier-steelseries-chute-sur-amazon-cest-le-moment-den-profiter/</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>5. Logiciels _ OS</t>
+          <t>3. Periphérique</t>
         </is>
       </c>
     </row>
@@ -7383,17 +7383,17 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2026-09-16T07:49:19+00:00</t>
+          <t>2026-09-16T13:33:01+00:00</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Fuse-archive - Vos ZIP montés en dossiers ordinaires</t>
+          <t>Shuffle Drummer - FL Studio n'a qu'à bien se tenir</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>https://korben.info/mount-archive-monter-archives-comme-un-dossier.html</t>
+          <t>https://korben.info/shuffle-drummer-groovebox-navigateur.html</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -7410,76 +7410,76 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2026-09-16T07:35:05+00:00</t>
+          <t>2026-09-16T07:49:19+00:00</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>La Forge - Le GitLab public des profs codeurs</t>
+          <t>Fuse-archive - Vos ZIP montés en dossiers ordinaires</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>https://korben.info/forge-apps-education-enseignants-code.html</t>
+          <t>https://korben.info/mount-archive-monter-archives-comme-un-dossier.html</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>NON_CLASSE</t>
+          <t>5. Logiciels _ OS</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>TomsHardware</t>
+          <t>Korben</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>2026-09-16T06:47:00+00:00</t>
+          <t>2026-09-16T07:35:05+00:00</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Pourquoi décaler la sortie de l’iPhone 18 au printemps 2027 est une bonne idée ?</t>
+          <t>La Forge - Le GitLab public des profs codeurs</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.fr/pourquoi-decaler-la-sortie-de-liphone-18-au-printemps-2027-est-une-bonne-idee/</t>
+          <t>https://korben.info/forge-apps-education-enseignants-code.html</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>NON_CLASSE</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Korben</t>
+          <t>TomsHardware</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2026-09-15T15:43:58+00:00</t>
+          <t>2026-09-16T06:47:00+00:00</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Test d'une batterie externe et dock magnétique Antank pour Nintendo Switch 2</t>
+          <t>Pourquoi décaler la sortie de l’iPhone 18 au printemps 2027 est une bonne idée ?</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>https://korben.info/test-dune-batterie-externe-et-dock-magentique-antank-pour-nintendo-switch-2.html</t>
+          <t>https://www.tomshardware.fr/pourquoi-decaler-la-sortie-de-liphone-18-au-printemps-2027-est-une-bonne-idee/</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>3. Periphérique</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
@@ -7491,22 +7491,22 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>2026-09-15T13:53:18+00:00</t>
+          <t>2026-09-15T15:43:58+00:00</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Suyu tire sa révérence sur un mode de recompilation pour jeux Switch</t>
+          <t>Test d'une batterie externe et dock magnétique Antank pour Nintendo Switch 2</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>https://korben.info/suyu-recompilation-statique-emulation-switch.html</t>
+          <t>https://korben.info/test-dune-batterie-externe-et-dock-magentique-antank-pour-nintendo-switch-2.html</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>15. ludique</t>
+          <t>3. Periphérique</t>
         </is>
       </c>
     </row>
@@ -7518,22 +7518,22 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>2026-09-15T13:28:51+00:00</t>
+          <t>2026-09-15T13:53:18+00:00</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>CUDA-for-AMD-Windows - Le .exe NVIDIA pour votre Radeon</t>
+          <t>Suyu tire sa révérence sur un mode de recompilation pour jeux Switch</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>https://korben.info/zluda-hip-cuda-radeon-windows.html</t>
+          <t>https://korben.info/suyu-recompilation-statique-emulation-switch.html</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>2. PC</t>
+          <t>15. ludique</t>
         </is>
       </c>
     </row>
@@ -7545,22 +7545,22 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2026-09-15T13:13:09+00:00</t>
+          <t>2026-09-15T13:28:51+00:00</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>OpenDisplay - Étendre l'affichage Mac avec ce que vous avez sous la main</t>
+          <t>CUDA-for-AMD-Windows - Le .exe NVIDIA pour votre Radeon</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>https://korben.info/opendisplay-ecran-secondaire-iphone-ipad-mac.html</t>
+          <t>https://korben.info/zluda-hip-cuda-radeon-windows.html</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>2. PC</t>
         </is>
       </c>
     </row>
@@ -7572,22 +7572,22 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2026-09-15T11:49:03+00:00</t>
+          <t>2026-09-15T13:13:09+00:00</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Windows 11 - Un clic sur le bon lien et hop, vous avez un compte local</t>
+          <t>OpenDisplay - Étendre l'affichage Mac avec ce que vous avez sous la main</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>https://korben.info/bypass-compte-microsoft-windows-11.html</t>
+          <t>https://korben.info/opendisplay-ecran-secondaire-iphone-ipad-mac.html</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>5. Logiciels _ OS</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
@@ -7599,22 +7599,22 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>2026-09-15T08:16:10+00:00</t>
+          <t>2026-09-15T11:49:03+00:00</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Kits IA Korben - Des tutos pour vos agents IA</t>
+          <t>Windows 11 - Un clic sur le bon lien et hop, vous avez un compte local</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>https://korben.info/kits-ia-korben-tutos-agents-ia.html</t>
+          <t>https://korben.info/bypass-compte-microsoft-windows-11.html</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>6. IA</t>
+          <t>5. Logiciels _ OS</t>
         </is>
       </c>
     </row>
@@ -7626,22 +7626,22 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>2026-09-15T08:00:00+00:00</t>
+          <t>2026-09-15T08:16:10+00:00</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>TP-Link Deco BE25-5G - Le routeur qui garde la maison</t>
+          <t>Kits IA Korben - Des tutos pour vos agents IA</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>https://korben.info/deco-be25-5g-test.html</t>
+          <t>https://korben.info/kits-ia-korben-tutos-agents-ia.html</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>6. IA</t>
         </is>
       </c>
     </row>
@@ -7653,22 +7653,22 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>2026-09-15T07:23:22+00:00</t>
+          <t>2026-09-15T08:00:00+00:00</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>GNOME Boxes - L'outil qui monte les VM à votre place</t>
+          <t>TP-Link Deco BE25-5G - Le routeur qui garde la maison</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>https://korben.info/gnome-boxes-virtualisation-simple-linux.html</t>
+          <t>https://korben.info/deco-be25-5g-test.html</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>5. Logiciels _ OS</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
@@ -7680,22 +7680,22 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>2026-09-15T06:53:24+00:00</t>
+          <t>2026-09-15T07:23:22+00:00</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>SpruceOS - Le guide pour rhabiller votre console rétro</t>
+          <t>GNOME Boxes - L'outil qui monte les VM à votre place</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>https://korben.info/spruceos-guide-installation-console-retro.html</t>
+          <t>https://korben.info/gnome-boxes-virtualisation-simple-linux.html</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>15. ludique</t>
+          <t>5. Logiciels _ OS</t>
         </is>
       </c>
     </row>
@@ -7707,22 +7707,22 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>2026-09-14T15:10:49+00:00</t>
+          <t>2026-09-15T06:53:24+00:00</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Test Thermal Master P3 : voir ce qui chauffe avec son smartphone</t>
+          <t>SpruceOS - Le guide pour rhabiller votre console rétro</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>https://korben.info/test-thermal-master-p3-voir-ce-qui-chauffe-avec-son-smartphone.html</t>
+          <t>https://korben.info/spruceos-guide-installation-console-retro.html</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>15. ludique</t>
         </is>
       </c>
     </row>
@@ -7734,22 +7734,22 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>2026-09-14T13:33:00+00:00</t>
+          <t>2026-09-14T15:10:49+00:00</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Antro pique ?</t>
+          <t>Test Thermal Master P3 : voir ce qui chauffe avec son smartphone</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>https://korben.info/test-antro-avis.html</t>
+          <t>https://korben.info/test-thermal-master-p3-voir-ce-qui-chauffe-avec-son-smartphone.html</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>NON_CLASSE</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
@@ -7761,17 +7761,17 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>2026-09-14T09:14:55+00:00</t>
+          <t>2026-09-14T13:33:00+00:00</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Tomb Raider peut tourner sur un ESP32-P4</t>
+          <t>Antro pique ?</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>https://korben.info/tomb-raider-peut-tourner-sur-un-esp32-p4.html</t>
+          <t>https://korben.info/test-antro-avis.html</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
@@ -7788,22 +7788,22 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>2026-09-14T08:30:00+00:00</t>
+          <t>2026-09-14T09:14:55+00:00</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Apple Configurator - Pour transformer votre iPhone en Dumbphone</t>
+          <t>Tomb Raider peut tourner sur un ESP32-P4</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>https://korben.info/apple-configurator-iphone-dumbphone-temps-ecran.html</t>
+          <t>https://korben.info/tomb-raider-peut-tourner-sur-un-esp32-p4.html</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>NON_CLASSE</t>
         </is>
       </c>
     </row>
@@ -7815,22 +7815,22 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>2026-09-14T07:42:28+00:00</t>
+          <t>2026-09-14T08:30:00+00:00</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>CanoFlash - Du Wi-Fi sur votre GBA (mais pas pour jouer, snif)</t>
+          <t>Apple Configurator - Pour transformer votre iPhone en Dumbphone</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>https://korben.info/gba-link-cable-internet-esp32.html</t>
+          <t>https://korben.info/apple-configurator-iphone-dumbphone-temps-ecran.html</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>3. Periphérique</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
@@ -7842,22 +7842,22 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>2026-09-11T10:00:00+00:00</t>
+          <t>2026-09-14T07:42:28+00:00</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>OmniVoice - Clonez votre propre voix en local et en français</t>
+          <t>CanoFlash - Du Wi-Fi sur votre GBA (mais pas pour jouer, snif)</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>https://korben.info/omnivoice-clonage-voix.html</t>
+          <t>https://korben.info/gba-link-cable-internet-esp32.html</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>8. Audio</t>
+          <t>3. Periphérique</t>
         </is>
       </c>
     </row>
@@ -7869,22 +7869,22 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>2026-09-11T09:52:43+00:00</t>
+          <t>2026-09-11T10:00:00+00:00</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Le Deathray - Le shader WebGPU qui fait redémarrer votre Mac</t>
+          <t>OmniVoice - Clonez votre propre voix en local et en français</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>https://korben.info/webgpu-deathray-freeze-mac.html</t>
+          <t>https://korben.info/omnivoice-clonage-voix.html</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>NON_CLASSE</t>
+          <t>8. Audio</t>
         </is>
       </c>
     </row>
@@ -7896,22 +7896,22 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>2026-09-11T07:19:00+00:00</t>
+          <t>2026-09-11T09:52:43+00:00</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Trynix - Testez des classiques Linux sans rien installer</t>
+          <t>Le Deathray - Le shader WebGPU qui fait redémarrer votre Mac</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>https://korben.info/trynix-tester-paquet-nix-navigateur.html</t>
+          <t>https://korben.info/webgpu-deathray-freeze-mac.html</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>5. Logiciels _ OS</t>
+          <t>NON_CLASSE</t>
         </is>
       </c>
     </row>
@@ -7923,17 +7923,17 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>2026-09-11T07:00:00+00:00</t>
+          <t>2026-09-11T07:19:00+00:00</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Pluton - Le backup chiffré qui se pilote depuis le navigateur</t>
+          <t>Trynix - Testez des classiques Linux sans rien installer</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>https://korben.info/pluton-backup-self-hosted-chiffre-restic-rclone.html</t>
+          <t>https://korben.info/trynix-tester-paquet-nix-navigateur.html</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -7950,22 +7950,22 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>2026-09-11T06:15:54+00:00</t>
+          <t>2026-09-11T07:00:00+00:00</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>ReProgman - L'interface de Windows 3.1 sur PC et Mac</t>
+          <t>Pluton - Le backup chiffré qui se pilote depuis le navigateur</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>https://korben.info/windows-31-shell-vibe-code-claude.html</t>
+          <t>https://korben.info/pluton-backup-self-hosted-chiffre-restic-rclone.html</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>2. PC</t>
+          <t>5. Logiciels _ OS</t>
         </is>
       </c>
     </row>
@@ -7977,17 +7977,17 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>2026-09-11T04:59:04+00:00</t>
+          <t>2026-09-11T06:15:54+00:00</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Super Mario 64 tourne sur un processeur ARM (avec ReactOS)</t>
+          <t>ReProgman - L'interface de Windows 3.1 sur PC et Mac</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>https://korben.info/reactos-arm64-fex-jeux-windows.html</t>
+          <t>https://korben.info/windows-31-shell-vibe-code-claude.html</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -8004,22 +8004,22 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>2026-09-10T13:52:44+00:00</t>
+          <t>2026-09-11T04:59:04+00:00</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Ce que les IA d'OpenAI se sont raconté en se croyant seules</t>
+          <t>Super Mario 64 tourne sur un processeur ARM (avec ReactOS)</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>https://korben.info/agents-ia-organisation-wiki-allemand.html</t>
+          <t>https://korben.info/reactos-arm64-fex-jeux-windows.html</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>6. IA</t>
+          <t>2. PC</t>
         </is>
       </c>
     </row>
@@ -8031,22 +8031,22 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>2026-09-10T11:04:19+00:00</t>
+          <t>2026-09-10T13:52:44+00:00</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>RistOS - L'Android sans applis dont le cerveau reste chez vous</t>
+          <t>Ce que les IA d'OpenAI se sont raconté en se croyant seules</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>https://korben.info/rist-os-handset-android-degoogle.html</t>
+          <t>https://korben.info/agents-ia-organisation-wiki-allemand.html</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>6. IA</t>
         </is>
       </c>
     </row>
@@ -8058,22 +8058,22 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>2026-09-10T08:15:16+00:00</t>
+          <t>2026-09-10T11:04:19+00:00</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Une faille cPanel distribue des accès root</t>
+          <t>RistOS - L'Android sans applis dont le cerveau reste chez vous</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>https://korben.info/cpanel-faille-prise-controle-compte-hebergement.html</t>
+          <t>https://korben.info/rist-os-handset-android-degoogle.html</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>5. Logiciels _ OS</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
@@ -8085,17 +8085,17 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>2026-09-10T04:56:34+00:00</t>
+          <t>2026-09-10T08:15:16+00:00</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Un seul abonnement Surfshark, une infinité d'appareils protégés pour la rentrée</t>
+          <t>Une faille cPanel distribue des accès root</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>https://korben.info/un-seul-abonnement-surfshark.html</t>
+          <t>https://korben.info/cpanel-faille-prise-controle-compte-hebergement.html</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -8112,45 +8112,49 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>2026-09-09T13:07:21+00:00</t>
+          <t>2026-09-10T04:56:34+00:00</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Mettez à jour Plex ! (même sans savoir contre quoi)</t>
+          <t>Un seul abonnement Surfshark, une infinité d'appareils protégés pour la rentrée</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>https://korben.info/plex-serveurs-non-patches-failles.html</t>
+          <t>https://korben.info/un-seul-abonnement-surfshark.html</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>2. PC</t>
+          <t>5. Logiciels _ OS</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Frandroid - Actualités</t>
-        </is>
-      </c>
-      <c r="B286" t="inlineStr"/>
+          <t>Korben</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>2026-09-09T13:07:21+00:00</t>
+        </is>
+      </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Pas de facture mobile avant 2027 : La Poste Mobile offre 4 mois gratuits sur ses forfaits 5G</t>
+          <t>Mettez à jour Plex ! (même sans savoir contre quoi)</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>https://native.humanoid.fr/register-click?s_id=2&amp;sp_id=47&amp;c_id=4224</t>
+          <t>https://korben.info/plex-serveurs-non-patches-failles.html</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>2. PC</t>
         </is>
       </c>
     </row>
@@ -8163,17 +8167,17 @@
       <c r="B287" t="inlineStr"/>
       <c r="C287" t="inlineStr">
         <is>
-          <t>TCL 24G645 : ce moniteur gaming QD-Mini LED en 300 Hz passe sous les 230 euros</t>
+          <t>Pas de facture mobile avant 2027 : La Poste Mobile offre 4 mois gratuits sur ses forfaits 5G</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/bons-plans/3253289_tcl-24g645-ce-moniteur-gaming-qd-mini-led-en-300-hz-passe-sous-les-230-euros</t>
+          <t>https://native.humanoid.fr/register-click?s_id=2&amp;sp_id=47&amp;c_id=4224</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>3. Periphérique</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
@@ -8186,17 +8190,17 @@
       <c r="B288" t="inlineStr"/>
       <c r="C288" t="inlineStr">
         <is>
-          <t>On a trouvé le gadget pas cher qui transforme vos photos de smartphone en autocollants</t>
+          <t>TCL 24G645 : ce moniteur gaming QD-Mini LED en 300 Hz passe sous les 230 euros</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/bons-plans/3253177_on-a-trouve-le-gadget-pas-cher-qui-transforme-vos-photos-de-smartphone-en-autocollants</t>
+          <t>https://www.frandroid.com/bons-plans/3253289_tcl-24g645-ce-moniteur-gaming-qd-mini-led-en-300-hz-passe-sous-les-230-euros</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>3. Periphérique</t>
         </is>
       </c>
     </row>
@@ -8209,17 +8213,17 @@
       <c r="B289" t="inlineStr"/>
       <c r="C289" t="inlineStr">
         <is>
-          <t>C’est le retour des PC portables sous RTX 5060 à moins de 1 000 € grâce à cette offre Boulanger</t>
+          <t>On a trouvé le gadget pas cher qui transforme vos photos de smartphone en autocollants</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/bons-plans/2804177_cest-le-retour-des-pc-portables-sous-rtx-5060-a-moins-de-1-000-euros-grace-a-cette-offre-boulanger</t>
+          <t>https://www.frandroid.com/bons-plans/3253177_on-a-trouve-le-gadget-pas-cher-qui-transforme-vos-photos-de-smartphone-en-autocollants</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>2. PC</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
@@ -8232,17 +8236,17 @@
       <c r="B290" t="inlineStr"/>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Un grand TV QD Mini-LED avec Philips Ambilight à moins de 700 €, ça se regarde de près</t>
+          <t>C’est le retour des PC portables sous RTX 5060 à moins de 1 000 € grâce à cette offre Boulanger</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/bons-plans/3252877_un-grand-tv-qd-mini-led-avec-philips-ambilight-a-moins-de-700-e-ca-se-regarde-de-pres</t>
+          <t>https://www.frandroid.com/bons-plans/2804177_cest-le-retour-des-pc-portables-sous-rtx-5060-a-moins-de-1-000-euros-grace-a-cette-offre-boulanger</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>7. Video</t>
+          <t>2. PC</t>
         </is>
       </c>
     </row>
@@ -8255,17 +8259,17 @@
       <c r="B291" t="inlineStr"/>
       <c r="C291" t="inlineStr">
         <is>
-          <t>JBL Tune 730BT : ce casque sans fil à 76 h d’autonomie tombe à moins de 40 euros</t>
+          <t>Un grand TV QD Mini-LED avec Philips Ambilight à moins de 700 €, ça se regarde de près</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/bons-plans/3252609_jbl-tune-730bt-ce-casque-sans-fil-a-76-h-dautonomie-tombe-a-moins-de-40-euros</t>
+          <t>https://www.frandroid.com/bons-plans/3252877_un-grand-tv-qd-mini-led-avec-philips-ambilight-a-moins-de-700-e-ca-se-regarde-de-pres</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>8. Audio</t>
+          <t>7. Video</t>
         </is>
       </c>
     </row>
@@ -8278,17 +8282,17 @@
       <c r="B292" t="inlineStr"/>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Le Dyson Humidify+Cool PH2 De‑Nox en promo à -200 € : un appareil 3-en-1 pensé pour l’air sec et pollué</t>
+          <t>JBL Tune 730BT : ce casque sans fil à 76 h d’autonomie tombe à moins de 40 euros</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/bons-plans/3252243_le-dyson-humidifycool-ph2-de-nox-en-promo-a-200-e-un-appareil-3-en-1-pense-pour-lair-sec-et-pollue</t>
+          <t>https://www.frandroid.com/bons-plans/3252609_jbl-tune-730bt-ce-casque-sans-fil-a-76-h-dautonomie-tombe-a-moins-de-40-euros</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>11. Menage</t>
+          <t>8. Audio</t>
         </is>
       </c>
     </row>
@@ -8301,17 +8305,17 @@
       <c r="B293" t="inlineStr"/>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Samsung The Frame 65 pouces (2025) à seulement 999 € chez Boulanger : une belle affaire pour ce TV QLED 4K</t>
+          <t>Le Dyson Humidify+Cool PH2 De‑Nox en promo à -200 € : un appareil 3-en-1 pensé pour l’air sec et pollué</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/bons-plans/3252161_samsung-the-frame-65-pouces-2025-a-seulement-999-e-chez-boulanger-une-belle-affaire-pour-ce-tv-qled-4k</t>
+          <t>https://www.frandroid.com/bons-plans/3252243_le-dyson-humidifycool-ph2-de-nox-en-promo-a-200-e-un-appareil-3-en-1-pense-pour-lair-sec-et-pollue</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>7. Video</t>
+          <t>11. Menage</t>
         </is>
       </c>
     </row>
@@ -8324,12 +8328,12 @@
       <c r="B294" t="inlineStr"/>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Vos DONNÉES ont FUITÉ : voici ce qu’il faut faire !</t>
+          <t>Samsung The Frame 65 pouces (2025) à seulement 999 € chez Boulanger : une belle affaire pour ce TV QLED 4K</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/video/3253483_video</t>
+          <t>https://www.frandroid.com/bons-plans/3252161_samsung-the-frame-65-pouces-2025-a-seulement-999-e-chez-boulanger-une-belle-affaire-pour-ce-tv-qled-4k</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -8347,35 +8351,35 @@
       <c r="B295" t="inlineStr"/>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Ce qu’il faut retenir des tests de l’iPhone 18 Pro !</t>
+          <t>Vos DONNÉES ont FUITÉ : voici ce qu’il faut faire !</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/video/3252919_video</t>
+          <t>https://www.frandroid.com/video/3253483_video</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>1. SMARTPHONE</t>
+          <t>7. Video</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Frandroid - Bons plans</t>
+          <t>Frandroid - Actualités</t>
         </is>
       </c>
       <c r="B296" t="inlineStr"/>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Ã peine sorti, le nouveau Xiaomi Redmi Note 17 Pro 5G est dÃ©jÃ  Ã  moitiÃ© prix grÃ¢ce Ã  cette offre</t>
+          <t>Ce qu’il faut retenir des tests de l’iPhone 18 Pro !</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/bons-plans/3252177_a-peine-sorti-le-nouveau-xiaomi-redmi-note-17-pro-5g-est-deja-a-moitie-prix-grace-a-cette-offre</t>
+          <t>https://www.frandroid.com/video/3252919_video</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -8393,17 +8397,17 @@
       <c r="B297" t="inlineStr"/>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Amazon brade le clavier gamer haut de gamme Ã  Rapid Trigger de Razer, le Huntsman V3 Pro TKL</t>
+          <t>Ã peine sorti, le nouveau Xiaomi Redmi Note 17 Pro 5G est dÃ©jÃ  Ã  moitiÃ© prix grÃ¢ce Ã  cette offre</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/bons-plans/3252199_amazon-brade-le-clavier-gamer-haut-de-gamme-a-rapid-trigger-de-razer-le-huntsman-v3-pro-tkl</t>
+          <t>https://www.frandroid.com/bons-plans/3252177_a-peine-sorti-le-nouveau-xiaomi-redmi-note-17-pro-5g-est-deja-a-moitie-prix-grace-a-cette-offre</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>3. Periphérique</t>
+          <t>1. SMARTPHONE</t>
         </is>
       </c>
     </row>
@@ -8416,17 +8420,17 @@
       <c r="B298" t="inlineStr"/>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Ce ventilateur Shark rafraÃ®chit l’air jusqu’Ã  6 Â°C et coÃ»te 110 â¬ de moins avec cette offre</t>
+          <t>Amazon brade le clavier gamer haut de gamme Ã  Rapid Trigger de Razer, le Huntsman V3 Pro TKL</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/bons-plans/3246361_ce-ventilateur-shark-rafraichit-lair-jusqua-6-c-et-coute-110-euros-de-moins-avec-cette-offre</t>
+          <t>https://www.frandroid.com/bons-plans/3252199_amazon-brade-le-clavier-gamer-haut-de-gamme-a-rapid-trigger-de-razer-le-huntsman-v3-pro-tkl</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>11. Menage</t>
+          <t>3. Periphérique</t>
         </is>
       </c>
     </row>
@@ -8439,17 +8443,17 @@
       <c r="B299" t="inlineStr"/>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Ce robot tondeuse 4×4 capable de grimper des pentes Ã  80 % est bradÃ© Ã  un super prix sur Amazon</t>
+          <t>Ce ventilateur Shark rafraÃ®chit l’air jusqu’Ã  6 Â°C et coÃ»te 110 â¬ de moins avec cette offre</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/bons-plans/3251737_ce-robot-tondeuse-4x4-capable-de-grimper-des-pentes-a-80-est-brade-a-un-super-prix-sur-amazon</t>
+          <t>https://www.frandroid.com/bons-plans/3246361_ce-ventilateur-shark-rafraichit-lair-jusqua-6-c-et-coute-110-euros-de-moins-avec-cette-offre</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>13. Maison</t>
+          <t>11. Menage</t>
         </is>
       </c>
     </row>
@@ -8462,17 +8466,17 @@
       <c r="B300" t="inlineStr"/>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Cet ultrabook d’Acer (Intel Core 5, 16 Go de RAM), avec une sacoche et une souris offertes, est dispo pour 200 â¬ de moins</t>
+          <t>Ce robot tondeuse 4×4 capable de grimper des pentes Ã  80 % est bradÃ© Ã  un super prix sur Amazon</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/bons-plans/3251595_cet-ultrabook-dacer-intel-core-5-16-go-de-ram-avec-une-sacoche-et-une-souris-offertes-est-dispo-pour-200-e-de-moins</t>
+          <t>https://www.frandroid.com/bons-plans/3251737_ce-robot-tondeuse-4x4-capable-de-grimper-des-pentes-a-80-est-brade-a-un-super-prix-sur-amazon</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>2. PC</t>
+          <t>13. Maison</t>
         </is>
       </c>
     </row>
@@ -8485,17 +8489,17 @@
       <c r="B301" t="inlineStr"/>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Ecovacs Deebot X12 OmniCyclone : ce robot aspirateur capable de franchir des marches perd plus de 500 â¬ sur Amazon</t>
+          <t>Cet ultrabook d’Acer (Intel Core 5, 16 Go de RAM), avec une sacoche et une souris offertes, est dispo pour 200 â¬ de moins</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/bons-plans/3251753_ecovacs-deebot-x12-omnicyclone-ce-robot-aspirateur-capable-de-franchir-des-marches-perd-plus-de-500-e-sur-amazon</t>
+          <t>https://www.frandroid.com/bons-plans/3251595_cet-ultrabook-dacer-intel-core-5-16-go-de-ram-avec-une-sacoche-et-une-souris-offertes-est-dispo-pour-200-e-de-moins</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>11. Menage</t>
+          <t>2. PC</t>
         </is>
       </c>
     </row>
@@ -8508,17 +8512,17 @@
       <c r="B302" t="inlineStr"/>
       <c r="C302" t="inlineStr">
         <is>
-          <t>La bague connectÃ©e Oura Ring 4 revient Ã  un super prix : une bonne affaire malgrÃ© la sortie du nouveau modÃ¨le ?</t>
+          <t>Ecovacs Deebot X12 OmniCyclone : ce robot aspirateur capable de franchir des marches perd plus de 500 â¬ sur Amazon</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/bons-plans/3190627_la-bague-connectee-oura-ring-4-revient-a-un-super-prix-une-bonne-affaire-malgre-la-sortie-du-nouveau-modele</t>
+          <t>https://www.frandroid.com/bons-plans/3251753_ecovacs-deebot-x12-omnicyclone-ce-robot-aspirateur-capable-de-franchir-des-marches-perd-plus-de-500-e-sur-amazon</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>14. Santé</t>
+          <t>11. Menage</t>
         </is>
       </c>
     </row>
@@ -8531,17 +8535,17 @@
       <c r="B303" t="inlineStr"/>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Bambu Lab lance la H2C, son imprimante 3D anti-gaspillage, dÃ©jÃ  Ã  -150 â¬</t>
+          <t>La bague connectÃ©e Oura Ring 4 revient Ã  un super prix : une bonne affaire malgrÃ© la sortie du nouveau modÃ¨le ?</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/bons-plans/3251523_bambu-lab-lance-la-h2c-son-imprimante-3d-anti-gaspillage-deja-a-150-e</t>
+          <t>https://www.frandroid.com/bons-plans/3190627_la-bague-connectee-oura-ring-4-revient-a-un-super-prix-une-bonne-affaire-malgre-la-sortie-du-nouveau-modele</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>3. Periphérique</t>
+          <t>14. Santé</t>
         </is>
       </c>
     </row>
@@ -8554,40 +8558,40 @@
       <c r="B304" t="inlineStr"/>
       <c r="C304" t="inlineStr">
         <is>
-          <t>On a trouvÃ© une montre Wear OS complÃ¨te pour le prix d’un bracelet connectÃ©</t>
+          <t>Bambu Lab lance la H2C, son imprimante 3D anti-gaspillage, dÃ©jÃ  Ã  -150 â¬</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/bons-plans/3251519_on-a-trouve-une-montre-wear-os-complete-pour-le-prix-dun-bracelet-connecte</t>
+          <t>https://www.frandroid.com/bons-plans/3251523_bambu-lab-lance-la-h2c-son-imprimante-3d-anti-gaspillage-deja-a-150-e</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>5. Logiciels _ OS</t>
+          <t>3. Periphérique</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Frandroid - Actualités</t>
+          <t>Frandroid - Bons plans</t>
         </is>
       </c>
       <c r="B305" t="inlineStr"/>
       <c r="C305" t="inlineStr">
         <is>
-          <t>BNP Paribas propose un prêt étudiant à 0,99 % TAEG pour la rentrée 2026</t>
+          <t>On a trouvÃ© une montre Wear OS complÃ¨te pour le prix d’un bracelet connectÃ©</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>https://native.humanoid.fr/register-click?s_id=2&amp;sp_id=47&amp;c_id=4220</t>
+          <t>https://www.frandroid.com/bons-plans/3251519_on-a-trouve-une-montre-wear-os-complete-pour-le-prix-dun-bracelet-connecte</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>NON_CLASSE</t>
+          <t>5. Logiciels _ OS</t>
         </is>
       </c>
     </row>
@@ -8600,17 +8604,17 @@
       <c r="B306" t="inlineStr"/>
       <c r="C306" t="inlineStr">
         <is>
-          <t>French Days : le nec plus ultra des aspirateurs Roborock s’effondre de 300 €</t>
+          <t>BNP Paribas propose un prêt étudiant à 0,99 % TAEG pour la rentrée 2026</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>https://native.humanoid.fr/register-click?s_id=2&amp;sp_id=47&amp;c_id=4217</t>
+          <t>https://native.humanoid.fr/register-click?s_id=2&amp;sp_id=47&amp;c_id=4220</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>11. Menage</t>
+          <t>NON_CLASSE</t>
         </is>
       </c>
     </row>
@@ -8623,17 +8627,17 @@
       <c r="B307" t="inlineStr"/>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Cette box fibre à moins de 25 € par mois mise sur le Wi-Fi 7 et un prix qui ne bouge pas</t>
+          <t>French Days : le nec plus ultra des aspirateurs Roborock s’effondre de 300 €</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>https://native.humanoid.fr/register-click?s_id=2&amp;sp_id=47&amp;c_id=4225</t>
+          <t>https://native.humanoid.fr/register-click?s_id=2&amp;sp_id=47&amp;c_id=4217</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>3. Periphérique</t>
+          <t>11. Menage</t>
         </is>
       </c>
     </row>
@@ -8646,15 +8650,38 @@
       <c r="B308" t="inlineStr"/>
       <c r="C308" t="inlineStr">
         <is>
+          <t>Cette box fibre à moins de 25 € par mois mise sur le Wi-Fi 7 et un prix qui ne bouge pas</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>https://native.humanoid.fr/register-click?s_id=2&amp;sp_id=47&amp;c_id=4225</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>3. Periphérique</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Frandroid - Actualités</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr"/>
+      <c r="C309" t="inlineStr">
+        <is>
           <t>ASUS baisse le prix de ses Zenbook et PC gaming pour la rentrée 2026 : jusqu’à 600 € de réduction</t>
         </is>
       </c>
-      <c r="D308" t="inlineStr">
+      <c r="D309" t="inlineStr">
         <is>
           <t>https://native.humanoid.fr/register-click?s_id=2&amp;sp_id=47&amp;c_id=4223</t>
         </is>
       </c>
-      <c r="E308" t="inlineStr">
+      <c r="E309" t="inlineStr">
         <is>
           <t>2. PC</t>
         </is>
@@ -9131,7 +9158,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9169,17 +9196,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-19T16:13:32+00:00</t>
+          <t>2026-09-20T01:25:02+00:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Actualité : Cette centrale vapeur présente le meilleur rapport qualité / prix de notre comparatif</t>
+          <t>Actualité : Bon plan – L'aspirateur robot Eureka J15 Pro Ultra à 299,98 € (-14%)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/centrale-vapeur/cette-centrale-vapeur-presente-le-meilleur-rapport-qualite-prix-de-notre-comparatif-n262065.html</t>
+          <t>https://www.lesnumeriques.com/aspirateur-robot/bon-plan-l-aspirateur-robot-eureka-j15-pro-ultra-a-299-98-14-n262070.html</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -9191,22 +9218,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Phonandroid</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-18T17:46:07+00:00</t>
+          <t>2026-09-19T16:13:32+00:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>L’excellent aspirateur balai sans fil Shark PowerDetect Speed Collection Luxe Clean &amp; Empty passe à prix cassé avec ce code</t>
+          <t>Actualité : Cette centrale vapeur présente le meilleur rapport qualité / prix de notre comparatif</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.phonandroid.com/lexcellent-aspirateur-balai-sans-fil-shark-powerdetect-speed-collection-luxe-clean-empty-passe-a-prix-casse-avec-ce-code.html</t>
+          <t>https://www.lesnumeriques.com/centrale-vapeur/cette-centrale-vapeur-presente-le-meilleur-rapport-qualite-prix-de-notre-comparatif-n262065.html</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -9218,22 +9245,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LesNumeriques</t>
+          <t>Phonandroid</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-18T12:16:00+00:00</t>
+          <t>2026-09-18T17:46:07+00:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Actualité : Le lave-linge Dreame Slim Washer S passe sous les 350 €</t>
+          <t>L’excellent aspirateur balai sans fil Shark PowerDetect Speed Collection Luxe Clean &amp; Empty passe à prix cassé avec ce code</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.lesnumeriques.com/lave-linge/le-lave-linge-dreame-slim-washer-s-passe-sous-les-350-n262024.html</t>
+          <t>https://www.phonandroid.com/lexcellent-aspirateur-balai-sans-fil-shark-powerdetect-speed-collection-luxe-clean-empty-passe-a-prix-casse-avec-ce-code.html</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -9245,22 +9272,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>01net</t>
+          <t>LesNumeriques</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-18T09:49:43+00:00</t>
+          <t>2026-09-18T12:16:00+00:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Révolutionnez  le ménage chez vous : cet aspirateur robot tout-en-un est à -72%</t>
+          <t>Actualité : Le lave-linge Dreame Slim Washer S passe sous les 350 €</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.01net.com/bons-plans/revolutionnez-le-menage-chez-vous-cet-aspirateur-robot-tout-en-un-est-a-72.html</t>
+          <t>https://www.lesnumeriques.com/lave-linge/le-lave-linge-dreame-slim-washer-s-passe-sous-les-350-n262024.html</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -9272,18 +9299,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Frandroid - Actualités</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
+          <t>01net</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-09-18T09:49:43+00:00</t>
+        </is>
+      </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Le Dyson Humidify+Cool PH2 De‑Nox en promo à -200 € : un appareil 3-en-1 pensé pour l’air sec et pollué</t>
+          <t>Révolutionnez  le ménage chez vous : cet aspirateur robot tout-en-un est à -72%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/bons-plans/3252243_le-dyson-humidifycool-ph2-de-nox-en-promo-a-200-e-un-appareil-3-en-1-pense-pour-lair-sec-et-pollue</t>
+          <t>https://www.01net.com/bons-plans/revolutionnez-le-menage-chez-vous-cet-aspirateur-robot-tout-en-un-est-a-72.html</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -9295,18 +9326,18 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Frandroid - Bons plans</t>
+          <t>Frandroid - Actualités</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ce ventilateur Shark rafraÃ®chit l’air jusqu’Ã  6 Â°C et coÃ»te 110 â¬ de moins avec cette offre</t>
+          <t>Le Dyson Humidify+Cool PH2 De‑Nox en promo à -200 € : un appareil 3-en-1 pensé pour l’air sec et pollué</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/bons-plans/3246361_ce-ventilateur-shark-rafraichit-lair-jusqua-6-c-et-coute-110-euros-de-moins-avec-cette-offre</t>
+          <t>https://www.frandroid.com/bons-plans/3252243_le-dyson-humidifycool-ph2-de-nox-en-promo-a-200-e-un-appareil-3-en-1-pense-pour-lair-sec-et-pollue</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -9324,12 +9355,12 @@
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ecovacs Deebot X12 OmniCyclone : ce robot aspirateur capable de franchir des marches perd plus de 500 â¬ sur Amazon</t>
+          <t>Ce ventilateur Shark rafraÃ®chit l’air jusqu’Ã  6 Â°C et coÃ»te 110 â¬ de moins avec cette offre</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.frandroid.com/bons-plans/3251753_ecovacs-deebot-x12-omnicyclone-ce-robot-aspirateur-capable-de-franchir-des-marches-perd-plus-de-500-e-sur-amazon</t>
+          <t>https://www.frandroid.com/bons-plans/3246361_ce-ventilateur-shark-rafraichit-lair-jusqua-6-c-et-coute-110-euros-de-moins-avec-cette-offre</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -9341,21 +9372,44 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Frandroid - Actualités</t>
+          <t>Frandroid - Bons plans</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
+          <t>Ecovacs Deebot X12 OmniCyclone : ce robot aspirateur capable de franchir des marches perd plus de 500 â¬ sur Amazon</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://www.frandroid.com/bons-plans/3251753_ecovacs-deebot-x12-omnicyclone-ce-robot-aspirateur-capable-de-franchir-des-marches-perd-plus-de-500-e-sur-amazon</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>11. Menage</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Frandroid - Actualités</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
           <t>French Days : le nec plus ultra des aspirateurs Roborock s’effondre de 300 €</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>https://native.humanoid.fr/register-click?s_id=2&amp;sp_id=47&amp;c_id=4217</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>11. Menage</t>
         </is>

--- a/output/rss_history.xlsx
+++ b/output/rss_history.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E402"/>
+  <dimension ref="A1:E403"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11183,6 +11183,29 @@
       <c r="E402" t="inlineStr">
         <is>
           <t>5. Logiciels _ OS</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>Frandroid - Actualités</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr"/>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>Comment bien choisir son clavier ?</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>https://native.humanoid.fr/register-click?s_id=2&amp;sp_id=47&amp;c_id=4226</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>3. Periphérique</t>
         </is>
       </c>
     </row>
@@ -20257,7 +20280,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20606,6 +20629,29 @@
         </is>
       </c>
       <c r="E13" t="inlineStr">
+        <is>
+          <t>3. Periphérique</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Frandroid - Actualités</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Comment bien choisir son clavier ?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://native.humanoid.fr/register-click?s_id=2&amp;sp_id=47&amp;c_id=4226</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
         <is>
           <t>3. Periphérique</t>
         </is>
